--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D777"/>
+  <dimension ref="A1:D778"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11267,6 +11267,20 @@
       </c>
       <c r="D777">
         <v>77.2736</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4">
+      <c r="A778" s="1">
+        <v>776</v>
+      </c>
+      <c r="B778" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C778">
+        <v>1</v>
+      </c>
+      <c r="D778">
+        <v>77.1734</v>
       </c>
     </row>
   </sheetData>
@@ -11276,7 +11290,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D777"/>
+  <dimension ref="A1:D778"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22152,6 +22166,20 @@
       </c>
       <c r="D777">
         <v>91.29649999999999</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4">
+      <c r="A778" s="1">
+        <v>776</v>
+      </c>
+      <c r="B778" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C778">
+        <v>1</v>
+      </c>
+      <c r="D778">
+        <v>90.7307</v>
       </c>
     </row>
   </sheetData>
@@ -22161,7 +22189,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D777"/>
+  <dimension ref="A1:D778"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33037,6 +33065,20 @@
       </c>
       <c r="D777">
         <v>55.0652</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4">
+      <c r="A778" s="1">
+        <v>776</v>
+      </c>
+      <c r="B778" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C778">
+        <v>1</v>
+      </c>
+      <c r="D778">
+        <v>54.7468</v>
       </c>
     </row>
   </sheetData>
@@ -33046,7 +33088,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D777"/>
+  <dimension ref="A1:D778"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -43922,6 +43964,20 @@
       </c>
       <c r="D777">
         <v>11.2394</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4">
+      <c r="A778" s="1">
+        <v>776</v>
+      </c>
+      <c r="B778" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C778">
+        <v>1</v>
+      </c>
+      <c r="D778">
+        <v>11.196</v>
       </c>
     </row>
   </sheetData>
@@ -43931,7 +43987,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D777"/>
+  <dimension ref="A1:D778"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -54807,6 +54863,20 @@
       </c>
       <c r="D777">
         <v>104.4353</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4">
+      <c r="A778" s="1">
+        <v>776</v>
+      </c>
+      <c r="B778" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C778">
+        <v>1</v>
+      </c>
+      <c r="D778">
+        <v>103.7442</v>
       </c>
     </row>
   </sheetData>
@@ -54816,7 +54886,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D777"/>
+  <dimension ref="A1:D778"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -65692,6 +65762,20 @@
       </c>
       <c r="D777">
         <v>15.4008</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4">
+      <c r="A778" s="1">
+        <v>776</v>
+      </c>
+      <c r="B778" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C778">
+        <v>100</v>
+      </c>
+      <c r="D778">
+        <v>15.5104</v>
       </c>
     </row>
   </sheetData>
@@ -65701,7 +65785,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D777"/>
+  <dimension ref="A1:D778"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -76577,6 +76661,20 @@
       </c>
       <c r="D777">
         <v>49.6107</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4">
+      <c r="A778" s="1">
+        <v>776</v>
+      </c>
+      <c r="B778" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C778">
+        <v>100</v>
+      </c>
+      <c r="D778">
+        <v>49.3436</v>
       </c>
     </row>
   </sheetData>
@@ -76586,7 +76684,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D777"/>
+  <dimension ref="A1:D778"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -87464,6 +87562,20 @@
         <v>99.97880000000001</v>
       </c>
     </row>
+    <row r="778" spans="1:4">
+      <c r="A778" s="1">
+        <v>776</v>
+      </c>
+      <c r="B778" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C778">
+        <v>1</v>
+      </c>
+      <c r="D778">
+        <v>99.96550000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D778"/>
+  <dimension ref="A1:D779"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11281,6 +11281,20 @@
       </c>
       <c r="D778">
         <v>77.1734</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4">
+      <c r="A779" s="1">
+        <v>777</v>
+      </c>
+      <c r="B779" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C779">
+        <v>1</v>
+      </c>
+      <c r="D779">
+        <v>77.6093</v>
       </c>
     </row>
   </sheetData>
@@ -11290,7 +11304,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D778"/>
+  <dimension ref="A1:D779"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22180,6 +22194,20 @@
       </c>
       <c r="D778">
         <v>90.7307</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4">
+      <c r="A779" s="1">
+        <v>777</v>
+      </c>
+      <c r="B779" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C779">
+        <v>1</v>
+      </c>
+      <c r="D779">
+        <v>90.3098</v>
       </c>
     </row>
   </sheetData>
@@ -22189,7 +22217,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D778"/>
+  <dimension ref="A1:D779"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33079,6 +33107,20 @@
       </c>
       <c r="D778">
         <v>54.7468</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4">
+      <c r="A779" s="1">
+        <v>777</v>
+      </c>
+      <c r="B779" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C779">
+        <v>1</v>
+      </c>
+      <c r="D779">
+        <v>55.1336</v>
       </c>
     </row>
   </sheetData>
@@ -33088,7 +33130,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D778"/>
+  <dimension ref="A1:D779"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -43978,6 +44020,20 @@
       </c>
       <c r="D778">
         <v>11.196</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4">
+      <c r="A779" s="1">
+        <v>777</v>
+      </c>
+      <c r="B779" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C779">
+        <v>1</v>
+      </c>
+      <c r="D779">
+        <v>11.221</v>
       </c>
     </row>
   </sheetData>
@@ -43987,7 +44043,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D778"/>
+  <dimension ref="A1:D779"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -54877,6 +54933,20 @@
       </c>
       <c r="D778">
         <v>103.7442</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4">
+      <c r="A779" s="1">
+        <v>777</v>
+      </c>
+      <c r="B779" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C779">
+        <v>1</v>
+      </c>
+      <c r="D779">
+        <v>103.7714</v>
       </c>
     </row>
   </sheetData>
@@ -54886,7 +54956,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D778"/>
+  <dimension ref="A1:D779"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -65776,6 +65846,20 @@
       </c>
       <c r="D778">
         <v>15.5104</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4">
+      <c r="A779" s="1">
+        <v>777</v>
+      </c>
+      <c r="B779" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C779">
+        <v>100</v>
+      </c>
+      <c r="D779">
+        <v>15.4416</v>
       </c>
     </row>
   </sheetData>
@@ -65785,7 +65869,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D778"/>
+  <dimension ref="A1:D779"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -76675,6 +76759,20 @@
       </c>
       <c r="D778">
         <v>49.3436</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4">
+      <c r="A779" s="1">
+        <v>777</v>
+      </c>
+      <c r="B779" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C779">
+        <v>100</v>
+      </c>
+      <c r="D779">
+        <v>49.3039</v>
       </c>
     </row>
   </sheetData>
@@ -76684,7 +76782,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D778"/>
+  <dimension ref="A1:D779"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -87576,6 +87674,20 @@
         <v>99.96550000000001</v>
       </c>
     </row>
+    <row r="779" spans="1:4">
+      <c r="A779" s="1">
+        <v>777</v>
+      </c>
+      <c r="B779" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C779">
+        <v>1</v>
+      </c>
+      <c r="D779">
+        <v>98.7521</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D779"/>
+  <dimension ref="A1:D780"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11295,6 +11295,20 @@
       </c>
       <c r="D779">
         <v>77.6093</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4">
+      <c r="A780" s="1">
+        <v>778</v>
+      </c>
+      <c r="B780" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C780">
+        <v>1</v>
+      </c>
+      <c r="D780">
+        <v>77.8009</v>
       </c>
     </row>
   </sheetData>
@@ -11304,7 +11318,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D779"/>
+  <dimension ref="A1:D780"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22208,6 +22222,20 @@
       </c>
       <c r="D779">
         <v>90.3098</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4">
+      <c r="A780" s="1">
+        <v>778</v>
+      </c>
+      <c r="B780" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C780">
+        <v>1</v>
+      </c>
+      <c r="D780">
+        <v>90.7458</v>
       </c>
     </row>
   </sheetData>
@@ -22217,7 +22245,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D779"/>
+  <dimension ref="A1:D780"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33121,6 +33149,20 @@
       </c>
       <c r="D779">
         <v>55.1336</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4">
+      <c r="A780" s="1">
+        <v>778</v>
+      </c>
+      <c r="B780" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C780">
+        <v>1</v>
+      </c>
+      <c r="D780">
+        <v>54.4295</v>
       </c>
     </row>
   </sheetData>
@@ -33130,7 +33172,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D779"/>
+  <dimension ref="A1:D780"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44034,6 +44076,20 @@
       </c>
       <c r="D779">
         <v>11.221</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4">
+      <c r="A780" s="1">
+        <v>778</v>
+      </c>
+      <c r="B780" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C780">
+        <v>1</v>
+      </c>
+      <c r="D780">
+        <v>11.2488</v>
       </c>
     </row>
   </sheetData>
@@ -44043,7 +44099,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D779"/>
+  <dimension ref="A1:D780"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -54947,6 +55003,20 @@
       </c>
       <c r="D779">
         <v>103.7714</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4">
+      <c r="A780" s="1">
+        <v>778</v>
+      </c>
+      <c r="B780" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C780">
+        <v>1</v>
+      </c>
+      <c r="D780">
+        <v>103.4908</v>
       </c>
     </row>
   </sheetData>
@@ -54956,7 +55026,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D779"/>
+  <dimension ref="A1:D780"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -65860,6 +65930,20 @@
       </c>
       <c r="D779">
         <v>15.4416</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4">
+      <c r="A780" s="1">
+        <v>778</v>
+      </c>
+      <c r="B780" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C780">
+        <v>100</v>
+      </c>
+      <c r="D780">
+        <v>15.6198</v>
       </c>
     </row>
   </sheetData>
@@ -65869,7 +65953,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D779"/>
+  <dimension ref="A1:D780"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -76773,6 +76857,20 @@
       </c>
       <c r="D779">
         <v>49.3039</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4">
+      <c r="A780" s="1">
+        <v>778</v>
+      </c>
+      <c r="B780" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C780">
+        <v>100</v>
+      </c>
+      <c r="D780">
+        <v>49.3473</v>
       </c>
     </row>
   </sheetData>
@@ -76782,7 +76880,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D779"/>
+  <dimension ref="A1:D780"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -87688,6 +87786,20 @@
         <v>98.7521</v>
       </c>
     </row>
+    <row r="780" spans="1:4">
+      <c r="A780" s="1">
+        <v>778</v>
+      </c>
+      <c r="B780" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C780">
+        <v>1</v>
+      </c>
+      <c r="D780">
+        <v>99.31180000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D780"/>
+  <dimension ref="A1:D781"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11309,6 +11309,20 @@
       </c>
       <c r="D780">
         <v>77.8009</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4">
+      <c r="A781" s="1">
+        <v>779</v>
+      </c>
+      <c r="B781" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C781">
+        <v>1</v>
+      </c>
+      <c r="D781">
+        <v>78.19</v>
       </c>
     </row>
   </sheetData>
@@ -11318,7 +11332,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D780"/>
+  <dimension ref="A1:D781"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22236,6 +22250,20 @@
       </c>
       <c r="D780">
         <v>90.7458</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4">
+      <c r="A781" s="1">
+        <v>779</v>
+      </c>
+      <c r="B781" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C781">
+        <v>1</v>
+      </c>
+      <c r="D781">
+        <v>90.79259999999999</v>
       </c>
     </row>
   </sheetData>
@@ -22245,7 +22273,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D780"/>
+  <dimension ref="A1:D781"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33163,6 +33191,20 @@
       </c>
       <c r="D780">
         <v>54.4295</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4">
+      <c r="A781" s="1">
+        <v>779</v>
+      </c>
+      <c r="B781" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C781">
+        <v>1</v>
+      </c>
+      <c r="D781">
+        <v>55.1474</v>
       </c>
     </row>
   </sheetData>
@@ -33172,7 +33214,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D780"/>
+  <dimension ref="A1:D781"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44090,6 +44132,20 @@
       </c>
       <c r="D780">
         <v>11.2488</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4">
+      <c r="A781" s="1">
+        <v>779</v>
+      </c>
+      <c r="B781" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C781">
+        <v>1</v>
+      </c>
+      <c r="D781">
+        <v>11.3486</v>
       </c>
     </row>
   </sheetData>
@@ -44099,7 +44155,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D780"/>
+  <dimension ref="A1:D781"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55017,6 +55073,20 @@
       </c>
       <c r="D780">
         <v>103.4908</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4">
+      <c r="A781" s="1">
+        <v>779</v>
+      </c>
+      <c r="B781" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C781">
+        <v>1</v>
+      </c>
+      <c r="D781">
+        <v>104.5009</v>
       </c>
     </row>
   </sheetData>
@@ -55026,7 +55096,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D780"/>
+  <dimension ref="A1:D781"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -65944,6 +66014,20 @@
       </c>
       <c r="D780">
         <v>15.6198</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4">
+      <c r="A781" s="1">
+        <v>779</v>
+      </c>
+      <c r="B781" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C781">
+        <v>100</v>
+      </c>
+      <c r="D781">
+        <v>15.6433</v>
       </c>
     </row>
   </sheetData>
@@ -65953,7 +66037,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D780"/>
+  <dimension ref="A1:D781"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -76871,6 +76955,20 @@
       </c>
       <c r="D780">
         <v>49.3473</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4">
+      <c r="A781" s="1">
+        <v>779</v>
+      </c>
+      <c r="B781" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C781">
+        <v>100</v>
+      </c>
+      <c r="D781">
+        <v>49.9361</v>
       </c>
     </row>
   </sheetData>
@@ -76880,7 +76978,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D780"/>
+  <dimension ref="A1:D781"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -87800,6 +87898,20 @@
         <v>99.31180000000001</v>
       </c>
     </row>
+    <row r="781" spans="1:4">
+      <c r="A781" s="1">
+        <v>779</v>
+      </c>
+      <c r="B781" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C781">
+        <v>1</v>
+      </c>
+      <c r="D781">
+        <v>100.3465</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D781"/>
+  <dimension ref="A1:D782"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11323,6 +11323,20 @@
       </c>
       <c r="D781">
         <v>78.19</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4">
+      <c r="A782" s="1">
+        <v>780</v>
+      </c>
+      <c r="B782" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C782">
+        <v>1</v>
+      </c>
+      <c r="D782">
+        <v>79.15000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11332,7 +11346,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D781"/>
+  <dimension ref="A1:D782"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22264,6 +22278,20 @@
       </c>
       <c r="D781">
         <v>90.79259999999999</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4">
+      <c r="A782" s="1">
+        <v>780</v>
+      </c>
+      <c r="B782" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C782">
+        <v>1</v>
+      </c>
+      <c r="D782">
+        <v>91.8391</v>
       </c>
     </row>
   </sheetData>
@@ -22273,7 +22301,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D781"/>
+  <dimension ref="A1:D782"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33205,6 +33233,20 @@
       </c>
       <c r="D781">
         <v>55.1474</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4">
+      <c r="A782" s="1">
+        <v>780</v>
+      </c>
+      <c r="B782" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C782">
+        <v>1</v>
+      </c>
+      <c r="D782">
+        <v>55.6345</v>
       </c>
     </row>
   </sheetData>
@@ -33214,7 +33256,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D781"/>
+  <dimension ref="A1:D782"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44146,6 +44188,20 @@
       </c>
       <c r="D781">
         <v>11.3486</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4">
+      <c r="A782" s="1">
+        <v>780</v>
+      </c>
+      <c r="B782" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C782">
+        <v>1</v>
+      </c>
+      <c r="D782">
+        <v>11.4368</v>
       </c>
     </row>
   </sheetData>
@@ -44155,7 +44211,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D781"/>
+  <dimension ref="A1:D782"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55087,6 +55143,20 @@
       </c>
       <c r="D781">
         <v>104.5009</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4">
+      <c r="A782" s="1">
+        <v>780</v>
+      </c>
+      <c r="B782" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C782">
+        <v>1</v>
+      </c>
+      <c r="D782">
+        <v>105.4515</v>
       </c>
     </row>
   </sheetData>
@@ -55096,7 +55166,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D781"/>
+  <dimension ref="A1:D782"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -66028,6 +66098,20 @@
       </c>
       <c r="D781">
         <v>15.6433</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4">
+      <c r="A782" s="1">
+        <v>780</v>
+      </c>
+      <c r="B782" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C782">
+        <v>100</v>
+      </c>
+      <c r="D782">
+        <v>16.0431</v>
       </c>
     </row>
   </sheetData>
@@ -66037,7 +66121,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D781"/>
+  <dimension ref="A1:D782"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -76969,6 +77053,20 @@
       </c>
       <c r="D781">
         <v>49.9361</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4">
+      <c r="A782" s="1">
+        <v>780</v>
+      </c>
+      <c r="B782" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C782">
+        <v>100</v>
+      </c>
+      <c r="D782">
+        <v>50.2859</v>
       </c>
     </row>
   </sheetData>
@@ -76978,7 +77076,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D781"/>
+  <dimension ref="A1:D782"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -87912,6 +88010,20 @@
         <v>100.3465</v>
       </c>
     </row>
+    <row r="782" spans="1:4">
+      <c r="A782" s="1">
+        <v>780</v>
+      </c>
+      <c r="B782" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C782">
+        <v>1</v>
+      </c>
+      <c r="D782">
+        <v>101.2278</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D782"/>
+  <dimension ref="A1:D783"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11337,6 +11337,20 @@
       </c>
       <c r="D782">
         <v>79.15000000000001</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4">
+      <c r="A783" s="1">
+        <v>781</v>
+      </c>
+      <c r="B783" s="2">
+        <v>46092</v>
+      </c>
+      <c r="C783">
+        <v>1</v>
+      </c>
+      <c r="D783">
+        <v>78.7396</v>
       </c>
     </row>
   </sheetData>
@@ -11346,7 +11360,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D782"/>
+  <dimension ref="A1:D783"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22292,6 +22306,20 @@
       </c>
       <c r="D782">
         <v>91.8391</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4">
+      <c r="A783" s="1">
+        <v>781</v>
+      </c>
+      <c r="B783" s="2">
+        <v>46092</v>
+      </c>
+      <c r="C783">
+        <v>1</v>
+      </c>
+      <c r="D783">
+        <v>91.89790000000001</v>
       </c>
     </row>
   </sheetData>
@@ -22301,7 +22329,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D782"/>
+  <dimension ref="A1:D783"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33247,6 +33275,20 @@
       </c>
       <c r="D782">
         <v>55.6345</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4">
+      <c r="A783" s="1">
+        <v>781</v>
+      </c>
+      <c r="B783" s="2">
+        <v>46092</v>
+      </c>
+      <c r="C783">
+        <v>1</v>
+      </c>
+      <c r="D783">
+        <v>55.6138</v>
       </c>
     </row>
   </sheetData>
@@ -33256,7 +33298,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D782"/>
+  <dimension ref="A1:D783"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44202,6 +44244,20 @@
       </c>
       <c r="D782">
         <v>11.4368</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4">
+      <c r="A783" s="1">
+        <v>781</v>
+      </c>
+      <c r="B783" s="2">
+        <v>46092</v>
+      </c>
+      <c r="C783">
+        <v>1</v>
+      </c>
+      <c r="D783">
+        <v>11.4413</v>
       </c>
     </row>
   </sheetData>
@@ -44211,7 +44267,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D782"/>
+  <dimension ref="A1:D783"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55157,6 +55213,20 @@
       </c>
       <c r="D782">
         <v>105.4515</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4">
+      <c r="A783" s="1">
+        <v>781</v>
+      </c>
+      <c r="B783" s="2">
+        <v>46092</v>
+      </c>
+      <c r="C783">
+        <v>1</v>
+      </c>
+      <c r="D783">
+        <v>105.4559</v>
       </c>
     </row>
   </sheetData>
@@ -55166,7 +55236,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D782"/>
+  <dimension ref="A1:D783"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -66112,6 +66182,20 @@
       </c>
       <c r="D782">
         <v>16.0431</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4">
+      <c r="A783" s="1">
+        <v>781</v>
+      </c>
+      <c r="B783" s="2">
+        <v>46092</v>
+      </c>
+      <c r="C783">
+        <v>100</v>
+      </c>
+      <c r="D783">
+        <v>15.944</v>
       </c>
     </row>
   </sheetData>
@@ -66121,7 +66205,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D782"/>
+  <dimension ref="A1:D783"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -77067,6 +77151,20 @@
       </c>
       <c r="D782">
         <v>50.2859</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4">
+      <c r="A783" s="1">
+        <v>781</v>
+      </c>
+      <c r="B783" s="2">
+        <v>46092</v>
+      </c>
+      <c r="C783">
+        <v>100</v>
+      </c>
+      <c r="D783">
+        <v>49.9332</v>
       </c>
     </row>
   </sheetData>
@@ -77076,7 +77174,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D782"/>
+  <dimension ref="A1:D783"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88024,6 +88122,20 @@
         <v>101.2278</v>
       </c>
     </row>
+    <row r="783" spans="1:4">
+      <c r="A783" s="1">
+        <v>781</v>
+      </c>
+      <c r="B783" s="2">
+        <v>46092</v>
+      </c>
+      <c r="C783">
+        <v>1</v>
+      </c>
+      <c r="D783">
+        <v>101.5471</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D783"/>
+  <dimension ref="A1:D784"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11351,6 +11351,20 @@
       </c>
       <c r="D783">
         <v>78.7396</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4">
+      <c r="A784" s="1">
+        <v>782</v>
+      </c>
+      <c r="B784" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C784">
+        <v>1</v>
+      </c>
+      <c r="D784">
+        <v>79.068</v>
       </c>
     </row>
   </sheetData>
@@ -11360,7 +11374,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D783"/>
+  <dimension ref="A1:D784"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22320,6 +22334,20 @@
       </c>
       <c r="D783">
         <v>91.89790000000001</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4">
+      <c r="A784" s="1">
+        <v>782</v>
+      </c>
+      <c r="B784" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C784">
+        <v>1</v>
+      </c>
+      <c r="D784">
+        <v>91.9378</v>
       </c>
     </row>
   </sheetData>
@@ -22329,7 +22357,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D783"/>
+  <dimension ref="A1:D784"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33289,6 +33317,20 @@
       </c>
       <c r="D783">
         <v>55.6138</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4">
+      <c r="A784" s="1">
+        <v>782</v>
+      </c>
+      <c r="B784" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C784">
+        <v>1</v>
+      </c>
+      <c r="D784">
+        <v>56.7945</v>
       </c>
     </row>
   </sheetData>
@@ -33298,7 +33340,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D783"/>
+  <dimension ref="A1:D784"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44258,6 +44300,20 @@
       </c>
       <c r="D783">
         <v>11.4413</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4">
+      <c r="A784" s="1">
+        <v>782</v>
+      </c>
+      <c r="B784" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C784">
+        <v>1</v>
+      </c>
+      <c r="D784">
+        <v>11.5051</v>
       </c>
     </row>
   </sheetData>
@@ -44267,7 +44323,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D783"/>
+  <dimension ref="A1:D784"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55227,6 +55283,20 @@
       </c>
       <c r="D783">
         <v>105.4559</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4">
+      <c r="A784" s="1">
+        <v>782</v>
+      </c>
+      <c r="B784" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C784">
+        <v>1</v>
+      </c>
+      <c r="D784">
+        <v>106.4097</v>
       </c>
     </row>
   </sheetData>
@@ -55236,7 +55306,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D783"/>
+  <dimension ref="A1:D784"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -66196,6 +66266,20 @@
       </c>
       <c r="D783">
         <v>15.944</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4">
+      <c r="A784" s="1">
+        <v>782</v>
+      </c>
+      <c r="B784" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C784">
+        <v>100</v>
+      </c>
+      <c r="D784">
+        <v>16.0841</v>
       </c>
     </row>
   </sheetData>
@@ -66205,7 +66289,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D783"/>
+  <dimension ref="A1:D784"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -77165,6 +77249,20 @@
       </c>
       <c r="D783">
         <v>49.9332</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4">
+      <c r="A784" s="1">
+        <v>782</v>
+      </c>
+      <c r="B784" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C784">
+        <v>100</v>
+      </c>
+      <c r="D784">
+        <v>49.9798</v>
       </c>
     </row>
   </sheetData>
@@ -77174,7 +77272,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D783"/>
+  <dimension ref="A1:D784"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88136,6 +88234,20 @@
         <v>101.5471</v>
       </c>
     </row>
+    <row r="784" spans="1:4">
+      <c r="A784" s="1">
+        <v>782</v>
+      </c>
+      <c r="B784" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C784">
+        <v>1</v>
+      </c>
+      <c r="D784">
+        <v>101.5515</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D784"/>
+  <dimension ref="A1:D785"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11365,6 +11365,20 @@
       </c>
       <c r="D784">
         <v>79.068</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4">
+      <c r="A785" s="1">
+        <v>783</v>
+      </c>
+      <c r="B785" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C785">
+        <v>1</v>
+      </c>
+      <c r="D785">
+        <v>79.0671</v>
       </c>
     </row>
   </sheetData>
@@ -11374,7 +11388,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D784"/>
+  <dimension ref="A1:D785"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22348,6 +22362,20 @@
       </c>
       <c r="D784">
         <v>91.9378</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4">
+      <c r="A785" s="1">
+        <v>783</v>
+      </c>
+      <c r="B785" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C785">
+        <v>1</v>
+      </c>
+      <c r="D785">
+        <v>91.38930000000001</v>
       </c>
     </row>
   </sheetData>
@@ -22357,7 +22385,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D784"/>
+  <dimension ref="A1:D785"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33331,6 +33359,20 @@
       </c>
       <c r="D784">
         <v>56.7945</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4">
+      <c r="A785" s="1">
+        <v>783</v>
+      </c>
+      <c r="B785" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C785">
+        <v>1</v>
+      </c>
+      <c r="D785">
+        <v>56.3353</v>
       </c>
     </row>
   </sheetData>
@@ -33340,7 +33382,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D784"/>
+  <dimension ref="A1:D785"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44314,6 +44356,20 @@
       </c>
       <c r="D784">
         <v>11.5051</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4">
+      <c r="A785" s="1">
+        <v>783</v>
+      </c>
+      <c r="B785" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C785">
+        <v>1</v>
+      </c>
+      <c r="D785">
+        <v>11.5027</v>
       </c>
     </row>
   </sheetData>
@@ -44323,7 +44379,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D784"/>
+  <dimension ref="A1:D785"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55297,6 +55353,20 @@
       </c>
       <c r="D784">
         <v>106.4097</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4">
+      <c r="A785" s="1">
+        <v>783</v>
+      </c>
+      <c r="B785" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C785">
+        <v>1</v>
+      </c>
+      <c r="D785">
+        <v>105.9341</v>
       </c>
     </row>
   </sheetData>
@@ -55306,7 +55376,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D784"/>
+  <dimension ref="A1:D785"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -66280,6 +66350,20 @@
       </c>
       <c r="D784">
         <v>16.0841</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4">
+      <c r="A785" s="1">
+        <v>783</v>
+      </c>
+      <c r="B785" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C785">
+        <v>100</v>
+      </c>
+      <c r="D785">
+        <v>16.1563</v>
       </c>
     </row>
   </sheetData>
@@ -66289,7 +66373,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D784"/>
+  <dimension ref="A1:D785"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -77263,6 +77347,20 @@
       </c>
       <c r="D784">
         <v>49.9798</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4">
+      <c r="A785" s="1">
+        <v>783</v>
+      </c>
+      <c r="B785" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C785">
+        <v>100</v>
+      </c>
+      <c r="D785">
+        <v>49.7277</v>
       </c>
     </row>
   </sheetData>
@@ -77272,7 +77370,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D784"/>
+  <dimension ref="A1:D785"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88248,6 +88346,20 @@
         <v>101.5515</v>
       </c>
     </row>
+    <row r="785" spans="1:4">
+      <c r="A785" s="1">
+        <v>783</v>
+      </c>
+      <c r="B785" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C785">
+        <v>1</v>
+      </c>
+      <c r="D785">
+        <v>101.3031</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D785"/>
+  <dimension ref="A1:D786"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11379,6 +11379,20 @@
       </c>
       <c r="D785">
         <v>79.0671</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4">
+      <c r="A786" s="1">
+        <v>784</v>
+      </c>
+      <c r="B786" s="2">
+        <v>46095</v>
+      </c>
+      <c r="C786">
+        <v>1</v>
+      </c>
+      <c r="D786">
+        <v>80.22539999999999</v>
       </c>
     </row>
   </sheetData>
@@ -11388,7 +11402,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D785"/>
+  <dimension ref="A1:D786"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22376,6 +22390,20 @@
       </c>
       <c r="D785">
         <v>91.38930000000001</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4">
+      <c r="A786" s="1">
+        <v>784</v>
+      </c>
+      <c r="B786" s="2">
+        <v>46095</v>
+      </c>
+      <c r="C786">
+        <v>1</v>
+      </c>
+      <c r="D786">
+        <v>91.9847</v>
       </c>
     </row>
   </sheetData>
@@ -22385,7 +22413,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D785"/>
+  <dimension ref="A1:D786"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33373,6 +33401,20 @@
       </c>
       <c r="D785">
         <v>56.3353</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4">
+      <c r="A786" s="1">
+        <v>784</v>
+      </c>
+      <c r="B786" s="2">
+        <v>46095</v>
+      </c>
+      <c r="C786">
+        <v>1</v>
+      </c>
+      <c r="D786">
+        <v>56.6632</v>
       </c>
     </row>
   </sheetData>
@@ -33382,7 +33424,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D785"/>
+  <dimension ref="A1:D786"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44370,6 +44412,20 @@
       </c>
       <c r="D785">
         <v>11.5027</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4">
+      <c r="A786" s="1">
+        <v>784</v>
+      </c>
+      <c r="B786" s="2">
+        <v>46095</v>
+      </c>
+      <c r="C786">
+        <v>1</v>
+      </c>
+      <c r="D786">
+        <v>11.6504</v>
       </c>
     </row>
   </sheetData>
@@ -44379,7 +44435,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D785"/>
+  <dimension ref="A1:D786"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55367,6 +55423,20 @@
       </c>
       <c r="D785">
         <v>105.9341</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4">
+      <c r="A786" s="1">
+        <v>784</v>
+      </c>
+      <c r="B786" s="2">
+        <v>46095</v>
+      </c>
+      <c r="C786">
+        <v>1</v>
+      </c>
+      <c r="D786">
+        <v>107.0929</v>
       </c>
     </row>
   </sheetData>
@@ -55376,7 +55446,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D785"/>
+  <dimension ref="A1:D786"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -66364,6 +66434,20 @@
       </c>
       <c r="D785">
         <v>16.1563</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4">
+      <c r="A786" s="1">
+        <v>784</v>
+      </c>
+      <c r="B786" s="2">
+        <v>46095</v>
+      </c>
+      <c r="C786">
+        <v>100</v>
+      </c>
+      <c r="D786">
+        <v>16.3166</v>
       </c>
     </row>
   </sheetData>
@@ -66373,7 +66457,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D785"/>
+  <dimension ref="A1:D786"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -77361,6 +77445,20 @@
       </c>
       <c r="D785">
         <v>49.7277</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4">
+      <c r="A786" s="1">
+        <v>784</v>
+      </c>
+      <c r="B786" s="2">
+        <v>46095</v>
+      </c>
+      <c r="C786">
+        <v>100</v>
+      </c>
+      <c r="D786">
+        <v>50.3928</v>
       </c>
     </row>
   </sheetData>
@@ -77370,7 +77468,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D785"/>
+  <dimension ref="A1:D786"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88360,6 +88458,20 @@
         <v>101.3031</v>
       </c>
     </row>
+    <row r="786" spans="1:4">
+      <c r="A786" s="1">
+        <v>784</v>
+      </c>
+      <c r="B786" s="2">
+        <v>46095</v>
+      </c>
+      <c r="C786">
+        <v>1</v>
+      </c>
+      <c r="D786">
+        <v>101.7701</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D786"/>
+  <dimension ref="A1:D787"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11393,6 +11393,20 @@
       </c>
       <c r="D786">
         <v>80.22539999999999</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4">
+      <c r="A787" s="1">
+        <v>785</v>
+      </c>
+      <c r="B787" s="2">
+        <v>46098</v>
+      </c>
+      <c r="C787">
+        <v>1</v>
+      </c>
+      <c r="D787">
+        <v>81.0517</v>
       </c>
     </row>
   </sheetData>
@@ -11402,7 +11416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D786"/>
+  <dimension ref="A1:D787"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22404,6 +22418,20 @@
       </c>
       <c r="D786">
         <v>91.9847</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4">
+      <c r="A787" s="1">
+        <v>785</v>
+      </c>
+      <c r="B787" s="2">
+        <v>46098</v>
+      </c>
+      <c r="C787">
+        <v>1</v>
+      </c>
+      <c r="D787">
+        <v>92.6555</v>
       </c>
     </row>
   </sheetData>
@@ -22413,7 +22441,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D786"/>
+  <dimension ref="A1:D787"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33415,6 +33443,20 @@
       </c>
       <c r="D786">
         <v>56.6632</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4">
+      <c r="A787" s="1">
+        <v>785</v>
+      </c>
+      <c r="B787" s="2">
+        <v>46098</v>
+      </c>
+      <c r="C787">
+        <v>1</v>
+      </c>
+      <c r="D787">
+        <v>56.7929</v>
       </c>
     </row>
   </sheetData>
@@ -33424,7 +33466,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D786"/>
+  <dimension ref="A1:D787"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44426,6 +44468,20 @@
       </c>
       <c r="D786">
         <v>11.6504</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4">
+      <c r="A787" s="1">
+        <v>785</v>
+      </c>
+      <c r="B787" s="2">
+        <v>46098</v>
+      </c>
+      <c r="C787">
+        <v>1</v>
+      </c>
+      <c r="D787">
+        <v>11.7441</v>
       </c>
     </row>
   </sheetData>
@@ -44435,7 +44491,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D786"/>
+  <dimension ref="A1:D787"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55437,6 +55493,20 @@
       </c>
       <c r="D786">
         <v>107.0929</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4">
+      <c r="A787" s="1">
+        <v>785</v>
+      </c>
+      <c r="B787" s="2">
+        <v>46098</v>
+      </c>
+      <c r="C787">
+        <v>1</v>
+      </c>
+      <c r="D787">
+        <v>107.3043</v>
       </c>
     </row>
   </sheetData>
@@ -55446,7 +55516,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D786"/>
+  <dimension ref="A1:D787"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -66448,6 +66518,20 @@
       </c>
       <c r="D786">
         <v>16.3166</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4">
+      <c r="A787" s="1">
+        <v>785</v>
+      </c>
+      <c r="B787" s="2">
+        <v>46098</v>
+      </c>
+      <c r="C787">
+        <v>100</v>
+      </c>
+      <c r="D787">
+        <v>16.4977</v>
       </c>
     </row>
   </sheetData>
@@ -66457,7 +66541,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D786"/>
+  <dimension ref="A1:D787"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -77459,6 +77543,20 @@
       </c>
       <c r="D786">
         <v>50.3928</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4">
+      <c r="A787" s="1">
+        <v>785</v>
+      </c>
+      <c r="B787" s="2">
+        <v>46098</v>
+      </c>
+      <c r="C787">
+        <v>100</v>
+      </c>
+      <c r="D787">
+        <v>50.8448</v>
       </c>
     </row>
   </sheetData>
@@ -77468,7 +77566,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D786"/>
+  <dimension ref="A1:D787"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88472,6 +88570,20 @@
         <v>101.7701</v>
       </c>
     </row>
+    <row r="787" spans="1:4">
+      <c r="A787" s="1">
+        <v>785</v>
+      </c>
+      <c r="B787" s="2">
+        <v>46098</v>
+      </c>
+      <c r="C787">
+        <v>1</v>
+      </c>
+      <c r="D787">
+        <v>102.7011</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D787"/>
+  <dimension ref="A1:D788"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11407,6 +11407,20 @@
       </c>
       <c r="D787">
         <v>81.0517</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4">
+      <c r="A788" s="1">
+        <v>786</v>
+      </c>
+      <c r="B788" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C788">
+        <v>1</v>
+      </c>
+      <c r="D788">
+        <v>81.91030000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11416,7 +11430,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D787"/>
+  <dimension ref="A1:D788"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22432,6 +22446,20 @@
       </c>
       <c r="D787">
         <v>92.6555</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4">
+      <c r="A788" s="1">
+        <v>786</v>
+      </c>
+      <c r="B788" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C788">
+        <v>1</v>
+      </c>
+      <c r="D788">
+        <v>93.1557</v>
       </c>
     </row>
   </sheetData>
@@ -22441,7 +22469,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D787"/>
+  <dimension ref="A1:D788"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33457,6 +33485,20 @@
       </c>
       <c r="D787">
         <v>56.7929</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4">
+      <c r="A788" s="1">
+        <v>786</v>
+      </c>
+      <c r="B788" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C788">
+        <v>1</v>
+      </c>
+      <c r="D788">
+        <v>57.9433</v>
       </c>
     </row>
   </sheetData>
@@ -33466,7 +33508,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D787"/>
+  <dimension ref="A1:D788"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44482,6 +44524,20 @@
       </c>
       <c r="D787">
         <v>11.7441</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4">
+      <c r="A788" s="1">
+        <v>786</v>
+      </c>
+      <c r="B788" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C788">
+        <v>1</v>
+      </c>
+      <c r="D788">
+        <v>11.8865</v>
       </c>
     </row>
   </sheetData>
@@ -44491,7 +44547,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D787"/>
+  <dimension ref="A1:D788"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55507,6 +55563,20 @@
       </c>
       <c r="D787">
         <v>107.3043</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4">
+      <c r="A788" s="1">
+        <v>786</v>
+      </c>
+      <c r="B788" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C788">
+        <v>1</v>
+      </c>
+      <c r="D788">
+        <v>108.9571</v>
       </c>
     </row>
   </sheetData>
@@ -55516,7 +55586,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D787"/>
+  <dimension ref="A1:D788"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -66532,6 +66602,20 @@
       </c>
       <c r="D787">
         <v>16.4977</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4">
+      <c r="A788" s="1">
+        <v>786</v>
+      </c>
+      <c r="B788" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C788">
+        <v>100</v>
+      </c>
+      <c r="D788">
+        <v>16.847</v>
       </c>
     </row>
   </sheetData>
@@ -66541,7 +66625,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D787"/>
+  <dimension ref="A1:D788"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -77557,6 +77641,20 @@
       </c>
       <c r="D787">
         <v>50.8448</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4">
+      <c r="A788" s="1">
+        <v>786</v>
+      </c>
+      <c r="B788" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C788">
+        <v>100</v>
+      </c>
+      <c r="D788">
+        <v>51.4092</v>
       </c>
     </row>
   </sheetData>
@@ -77566,7 +77664,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D787"/>
+  <dimension ref="A1:D788"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88584,6 +88682,20 @@
         <v>102.7011</v>
       </c>
     </row>
+    <row r="788" spans="1:4">
+      <c r="A788" s="1">
+        <v>786</v>
+      </c>
+      <c r="B788" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C788">
+        <v>1</v>
+      </c>
+      <c r="D788">
+        <v>104.0792</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D788"/>
+  <dimension ref="A1:D789"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11421,6 +11421,20 @@
       </c>
       <c r="D788">
         <v>81.91030000000001</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4">
+      <c r="A789" s="1">
+        <v>787</v>
+      </c>
+      <c r="B789" s="2">
+        <v>46100</v>
+      </c>
+      <c r="C789">
+        <v>1</v>
+      </c>
+      <c r="D789">
+        <v>83.1259</v>
       </c>
     </row>
   </sheetData>
@@ -11430,7 +11444,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D788"/>
+  <dimension ref="A1:D789"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22460,6 +22474,20 @@
       </c>
       <c r="D788">
         <v>93.1557</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4">
+      <c r="A789" s="1">
+        <v>787</v>
+      </c>
+      <c r="B789" s="2">
+        <v>46100</v>
+      </c>
+      <c r="C789">
+        <v>1</v>
+      </c>
+      <c r="D789">
+        <v>94.66630000000001</v>
       </c>
     </row>
   </sheetData>
@@ -22469,7 +22497,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D788"/>
+  <dimension ref="A1:D789"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33499,6 +33527,20 @@
       </c>
       <c r="D788">
         <v>57.9433</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4">
+      <c r="A789" s="1">
+        <v>787</v>
+      </c>
+      <c r="B789" s="2">
+        <v>46100</v>
+      </c>
+      <c r="C789">
+        <v>1</v>
+      </c>
+      <c r="D789">
+        <v>59.1441</v>
       </c>
     </row>
   </sheetData>
@@ -33508,7 +33550,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D788"/>
+  <dimension ref="A1:D789"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44538,6 +44580,20 @@
       </c>
       <c r="D788">
         <v>11.8865</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4">
+      <c r="A789" s="1">
+        <v>787</v>
+      </c>
+      <c r="B789" s="2">
+        <v>46100</v>
+      </c>
+      <c r="C789">
+        <v>1</v>
+      </c>
+      <c r="D789">
+        <v>12.1155</v>
       </c>
     </row>
   </sheetData>
@@ -44547,7 +44603,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D788"/>
+  <dimension ref="A1:D789"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55577,6 +55633,20 @@
       </c>
       <c r="D788">
         <v>108.9571</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4">
+      <c r="A789" s="1">
+        <v>787</v>
+      </c>
+      <c r="B789" s="2">
+        <v>46100</v>
+      </c>
+      <c r="C789">
+        <v>1</v>
+      </c>
+      <c r="D789">
+        <v>110.9149</v>
       </c>
     </row>
   </sheetData>
@@ -55586,7 +55656,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D788"/>
+  <dimension ref="A1:D789"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -66616,6 +66686,20 @@
       </c>
       <c r="D788">
         <v>16.847</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4">
+      <c r="A789" s="1">
+        <v>787</v>
+      </c>
+      <c r="B789" s="2">
+        <v>46100</v>
+      </c>
+      <c r="C789">
+        <v>100</v>
+      </c>
+      <c r="D789">
+        <v>17.3533</v>
       </c>
     </row>
   </sheetData>
@@ -66625,7 +66709,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D788"/>
+  <dimension ref="A1:D789"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -77655,6 +77739,20 @@
       </c>
       <c r="D788">
         <v>51.4092</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4">
+      <c r="A789" s="1">
+        <v>787</v>
+      </c>
+      <c r="B789" s="2">
+        <v>46100</v>
+      </c>
+      <c r="C789">
+        <v>100</v>
+      </c>
+      <c r="D789">
+        <v>52.241</v>
       </c>
     </row>
   </sheetData>
@@ -77664,7 +77762,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D788"/>
+  <dimension ref="A1:D789"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88696,6 +88794,20 @@
         <v>104.0792</v>
       </c>
     </row>
+    <row r="789" spans="1:4">
+      <c r="A789" s="1">
+        <v>787</v>
+      </c>
+      <c r="B789" s="2">
+        <v>46100</v>
+      </c>
+      <c r="C789">
+        <v>1</v>
+      </c>
+      <c r="D789">
+        <v>105.7312</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D789"/>
+  <dimension ref="A1:D790"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11435,6 +11435,20 @@
       </c>
       <c r="D789">
         <v>83.1259</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4">
+      <c r="A790" s="1">
+        <v>788</v>
+      </c>
+      <c r="B790" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C790">
+        <v>1</v>
+      </c>
+      <c r="D790">
+        <v>84.8379</v>
       </c>
     </row>
   </sheetData>
@@ -11444,7 +11458,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D789"/>
+  <dimension ref="A1:D790"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22488,6 +22502,20 @@
       </c>
       <c r="D789">
         <v>94.66630000000001</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4">
+      <c r="A790" s="1">
+        <v>788</v>
+      </c>
+      <c r="B790" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C790">
+        <v>1</v>
+      </c>
+      <c r="D790">
+        <v>96.91549999999999</v>
       </c>
     </row>
   </sheetData>
@@ -22497,7 +22525,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D789"/>
+  <dimension ref="A1:D790"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33541,6 +33569,20 @@
       </c>
       <c r="D789">
         <v>59.1441</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4">
+      <c r="A790" s="1">
+        <v>788</v>
+      </c>
+      <c r="B790" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C790">
+        <v>1</v>
+      </c>
+      <c r="D790">
+        <v>59.7089</v>
       </c>
     </row>
   </sheetData>
@@ -33550,7 +33592,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D789"/>
+  <dimension ref="A1:D790"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44594,6 +44636,20 @@
       </c>
       <c r="D789">
         <v>12.1155</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4">
+      <c r="A790" s="1">
+        <v>788</v>
+      </c>
+      <c r="B790" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C790">
+        <v>1</v>
+      </c>
+      <c r="D790">
+        <v>12.3824</v>
       </c>
     </row>
   </sheetData>
@@ -44603,7 +44659,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D789"/>
+  <dimension ref="A1:D790"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55647,6 +55703,20 @@
       </c>
       <c r="D789">
         <v>110.9149</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4">
+      <c r="A790" s="1">
+        <v>788</v>
+      </c>
+      <c r="B790" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C790">
+        <v>1</v>
+      </c>
+      <c r="D790">
+        <v>113.0295</v>
       </c>
     </row>
   </sheetData>
@@ -55656,7 +55726,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D789"/>
+  <dimension ref="A1:D790"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -66700,6 +66770,20 @@
       </c>
       <c r="D789">
         <v>17.3533</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4">
+      <c r="A790" s="1">
+        <v>788</v>
+      </c>
+      <c r="B790" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C790">
+        <v>100</v>
+      </c>
+      <c r="D790">
+        <v>17.5833</v>
       </c>
     </row>
   </sheetData>
@@ -66709,7 +66793,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D789"/>
+  <dimension ref="A1:D790"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -77753,6 +77837,20 @@
       </c>
       <c r="D789">
         <v>52.241</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4">
+      <c r="A790" s="1">
+        <v>788</v>
+      </c>
+      <c r="B790" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C790">
+        <v>100</v>
+      </c>
+      <c r="D790">
+        <v>53.0901</v>
       </c>
     </row>
   </sheetData>
@@ -77762,7 +77860,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D789"/>
+  <dimension ref="A1:D790"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88808,6 +88906,20 @@
         <v>105.7312</v>
       </c>
     </row>
+    <row r="790" spans="1:4">
+      <c r="A790" s="1">
+        <v>788</v>
+      </c>
+      <c r="B790" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C790">
+        <v>1</v>
+      </c>
+      <c r="D790">
+        <v>106.7949</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D790"/>
+  <dimension ref="A1:D791"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11449,6 +11449,20 @@
       </c>
       <c r="D790">
         <v>84.8379</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4">
+      <c r="A791" s="1">
+        <v>789</v>
+      </c>
+      <c r="B791" s="2">
+        <v>46102</v>
+      </c>
+      <c r="C791">
+        <v>1</v>
+      </c>
+      <c r="D791">
+        <v>83.9982</v>
       </c>
     </row>
   </sheetData>
@@ -11458,7 +11472,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D790"/>
+  <dimension ref="A1:D791"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22516,6 +22530,20 @@
       </c>
       <c r="D790">
         <v>96.91549999999999</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4">
+      <c r="A791" s="1">
+        <v>789</v>
+      </c>
+      <c r="B791" s="2">
+        <v>46102</v>
+      </c>
+      <c r="C791">
+        <v>1</v>
+      </c>
+      <c r="D791">
+        <v>97.2886</v>
       </c>
     </row>
   </sheetData>
@@ -22525,7 +22553,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D790"/>
+  <dimension ref="A1:D791"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33583,6 +33611,20 @@
       </c>
       <c r="D790">
         <v>59.7089</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4">
+      <c r="A791" s="1">
+        <v>789</v>
+      </c>
+      <c r="B791" s="2">
+        <v>46102</v>
+      </c>
+      <c r="C791">
+        <v>1</v>
+      </c>
+      <c r="D791">
+        <v>59.5379</v>
       </c>
     </row>
   </sheetData>
@@ -33592,7 +33634,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D790"/>
+  <dimension ref="A1:D791"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44650,6 +44692,20 @@
       </c>
       <c r="D790">
         <v>12.3824</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4">
+      <c r="A791" s="1">
+        <v>789</v>
+      </c>
+      <c r="B791" s="2">
+        <v>46102</v>
+      </c>
+      <c r="C791">
+        <v>1</v>
+      </c>
+      <c r="D791">
+        <v>12.2171</v>
       </c>
     </row>
   </sheetData>
@@ -44659,7 +44715,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D790"/>
+  <dimension ref="A1:D791"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55717,6 +55773,20 @@
       </c>
       <c r="D790">
         <v>113.0295</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4">
+      <c r="A791" s="1">
+        <v>789</v>
+      </c>
+      <c r="B791" s="2">
+        <v>46102</v>
+      </c>
+      <c r="C791">
+        <v>1</v>
+      </c>
+      <c r="D791">
+        <v>112.2132</v>
       </c>
     </row>
   </sheetData>
@@ -55726,7 +55796,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D790"/>
+  <dimension ref="A1:D791"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -66784,6 +66854,20 @@
       </c>
       <c r="D790">
         <v>17.5833</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4">
+      <c r="A791" s="1">
+        <v>789</v>
+      </c>
+      <c r="B791" s="2">
+        <v>46102</v>
+      </c>
+      <c r="C791">
+        <v>100</v>
+      </c>
+      <c r="D791">
+        <v>17.4155</v>
       </c>
     </row>
   </sheetData>
@@ -66793,7 +66877,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D790"/>
+  <dimension ref="A1:D791"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -77851,6 +77935,20 @@
       </c>
       <c r="D790">
         <v>53.0901</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4">
+      <c r="A791" s="1">
+        <v>789</v>
+      </c>
+      <c r="B791" s="2">
+        <v>46102</v>
+      </c>
+      <c r="C791">
+        <v>100</v>
+      </c>
+      <c r="D791">
+        <v>52.5646</v>
       </c>
     </row>
   </sheetData>
@@ -77860,7 +77958,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D790"/>
+  <dimension ref="A1:D791"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88920,6 +89018,20 @@
         <v>106.7949</v>
       </c>
     </row>
+    <row r="791" spans="1:4">
+      <c r="A791" s="1">
+        <v>789</v>
+      </c>
+      <c r="B791" s="2">
+        <v>46102</v>
+      </c>
+      <c r="C791">
+        <v>1</v>
+      </c>
+      <c r="D791">
+        <v>106.5561</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D791"/>
+  <dimension ref="A1:D792"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11463,6 +11463,20 @@
       </c>
       <c r="D791">
         <v>83.9982</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4">
+      <c r="A792" s="1">
+        <v>790</v>
+      </c>
+      <c r="B792" s="2">
+        <v>46105</v>
+      </c>
+      <c r="C792">
+        <v>1</v>
+      </c>
+      <c r="D792">
+        <v>81.8763</v>
       </c>
     </row>
   </sheetData>
@@ -11472,7 +11486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D791"/>
+  <dimension ref="A1:D792"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22544,6 +22558,20 @@
       </c>
       <c r="D791">
         <v>97.2886</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4">
+      <c r="A792" s="1">
+        <v>790</v>
+      </c>
+      <c r="B792" s="2">
+        <v>46105</v>
+      </c>
+      <c r="C792">
+        <v>1</v>
+      </c>
+      <c r="D792">
+        <v>94.7264</v>
       </c>
     </row>
   </sheetData>
@@ -22553,7 +22581,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D791"/>
+  <dimension ref="A1:D792"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33625,6 +33653,20 @@
       </c>
       <c r="D791">
         <v>59.5379</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4">
+      <c r="A792" s="1">
+        <v>790</v>
+      </c>
+      <c r="B792" s="2">
+        <v>46105</v>
+      </c>
+      <c r="C792">
+        <v>1</v>
+      </c>
+      <c r="D792">
+        <v>57.1497</v>
       </c>
     </row>
   </sheetData>
@@ -33634,7 +33676,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D791"/>
+  <dimension ref="A1:D792"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44706,6 +44748,20 @@
       </c>
       <c r="D791">
         <v>12.2171</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4">
+      <c r="A792" s="1">
+        <v>790</v>
+      </c>
+      <c r="B792" s="2">
+        <v>46105</v>
+      </c>
+      <c r="C792">
+        <v>1</v>
+      </c>
+      <c r="D792">
+        <v>11.8709</v>
       </c>
     </row>
   </sheetData>
@@ -44715,7 +44771,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D791"/>
+  <dimension ref="A1:D792"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55787,6 +55843,20 @@
       </c>
       <c r="D791">
         <v>112.2132</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4">
+      <c r="A792" s="1">
+        <v>790</v>
+      </c>
+      <c r="B792" s="2">
+        <v>46105</v>
+      </c>
+      <c r="C792">
+        <v>1</v>
+      </c>
+      <c r="D792">
+        <v>108.9119</v>
       </c>
     </row>
   </sheetData>
@@ -55796,7 +55866,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D791"/>
+  <dimension ref="A1:D792"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -66868,6 +66938,20 @@
       </c>
       <c r="D791">
         <v>17.4155</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4">
+      <c r="A792" s="1">
+        <v>790</v>
+      </c>
+      <c r="B792" s="2">
+        <v>46105</v>
+      </c>
+      <c r="C792">
+        <v>100</v>
+      </c>
+      <c r="D792">
+        <v>16.9752</v>
       </c>
     </row>
   </sheetData>
@@ -66877,7 +66961,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D791"/>
+  <dimension ref="A1:D792"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -77949,6 +78033,20 @@
       </c>
       <c r="D791">
         <v>52.5646</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4">
+      <c r="A792" s="1">
+        <v>790</v>
+      </c>
+      <c r="B792" s="2">
+        <v>46105</v>
+      </c>
+      <c r="C792">
+        <v>100</v>
+      </c>
+      <c r="D792">
+        <v>51.3428</v>
       </c>
     </row>
   </sheetData>
@@ -77958,7 +78056,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D791"/>
+  <dimension ref="A1:D792"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -89032,6 +89130,20 @@
         <v>106.5561</v>
       </c>
     </row>
+    <row r="792" spans="1:4">
+      <c r="A792" s="1">
+        <v>790</v>
+      </c>
+      <c r="B792" s="2">
+        <v>46105</v>
+      </c>
+      <c r="C792">
+        <v>1</v>
+      </c>
+      <c r="D792">
+        <v>103.2358</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D792"/>
+  <dimension ref="A1:D793"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11477,6 +11477,20 @@
       </c>
       <c r="D792">
         <v>81.8763</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4">
+      <c r="A793" s="1">
+        <v>791</v>
+      </c>
+      <c r="B793" s="2">
+        <v>46106</v>
+      </c>
+      <c r="C793">
+        <v>1</v>
+      </c>
+      <c r="D793">
+        <v>80.96040000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11486,7 +11500,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D792"/>
+  <dimension ref="A1:D793"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22572,6 +22586,20 @@
       </c>
       <c r="D792">
         <v>94.7264</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4">
+      <c r="A793" s="1">
+        <v>791</v>
+      </c>
+      <c r="B793" s="2">
+        <v>46106</v>
+      </c>
+      <c r="C793">
+        <v>1</v>
+      </c>
+      <c r="D793">
+        <v>93.9247</v>
       </c>
     </row>
   </sheetData>
@@ -22581,7 +22609,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D792"/>
+  <dimension ref="A1:D793"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33667,6 +33695,20 @@
       </c>
       <c r="D792">
         <v>57.1497</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4">
+      <c r="A793" s="1">
+        <v>791</v>
+      </c>
+      <c r="B793" s="2">
+        <v>46106</v>
+      </c>
+      <c r="C793">
+        <v>1</v>
+      </c>
+      <c r="D793">
+        <v>56.397</v>
       </c>
     </row>
   </sheetData>
@@ -33676,7 +33718,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D792"/>
+  <dimension ref="A1:D793"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44762,6 +44804,20 @@
       </c>
       <c r="D792">
         <v>11.8709</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4">
+      <c r="A793" s="1">
+        <v>791</v>
+      </c>
+      <c r="B793" s="2">
+        <v>46106</v>
+      </c>
+      <c r="C793">
+        <v>1</v>
+      </c>
+      <c r="D793">
+        <v>11.7271</v>
       </c>
     </row>
   </sheetData>
@@ -44771,7 +44827,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D792"/>
+  <dimension ref="A1:D793"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55857,6 +55913,20 @@
       </c>
       <c r="D792">
         <v>108.9119</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4">
+      <c r="A793" s="1">
+        <v>791</v>
+      </c>
+      <c r="B793" s="2">
+        <v>46106</v>
+      </c>
+      <c r="C793">
+        <v>1</v>
+      </c>
+      <c r="D793">
+        <v>108.3655</v>
       </c>
     </row>
   </sheetData>
@@ -55866,7 +55936,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D792"/>
+  <dimension ref="A1:D793"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -66952,6 +67022,20 @@
       </c>
       <c r="D792">
         <v>16.9752</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4">
+      <c r="A793" s="1">
+        <v>791</v>
+      </c>
+      <c r="B793" s="2">
+        <v>46106</v>
+      </c>
+      <c r="C793">
+        <v>100</v>
+      </c>
+      <c r="D793">
+        <v>16.7853</v>
       </c>
     </row>
   </sheetData>
@@ -66961,7 +67045,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D792"/>
+  <dimension ref="A1:D793"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -78047,6 +78131,20 @@
       </c>
       <c r="D792">
         <v>51.3428</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4">
+      <c r="A793" s="1">
+        <v>791</v>
+      </c>
+      <c r="B793" s="2">
+        <v>46106</v>
+      </c>
+      <c r="C793">
+        <v>100</v>
+      </c>
+      <c r="D793">
+        <v>51.0533</v>
       </c>
     </row>
   </sheetData>
@@ -78056,7 +78154,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D792"/>
+  <dimension ref="A1:D793"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -89144,6 +89242,20 @@
         <v>103.2358</v>
       </c>
     </row>
+    <row r="793" spans="1:4">
+      <c r="A793" s="1">
+        <v>791</v>
+      </c>
+      <c r="B793" s="2">
+        <v>46106</v>
+      </c>
+      <c r="C793">
+        <v>1</v>
+      </c>
+      <c r="D793">
+        <v>102.9245</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D793"/>
+  <dimension ref="A1:D794"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11491,6 +11491,20 @@
       </c>
       <c r="D793">
         <v>80.96040000000001</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4">
+      <c r="A794" s="1">
+        <v>792</v>
+      </c>
+      <c r="B794" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C794">
+        <v>1</v>
+      </c>
+      <c r="D794">
+        <v>80.7192</v>
       </c>
     </row>
   </sheetData>
@@ -11500,7 +11514,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D793"/>
+  <dimension ref="A1:D794"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22600,6 +22614,20 @@
       </c>
       <c r="D793">
         <v>93.9247</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4">
+      <c r="A794" s="1">
+        <v>792</v>
+      </c>
+      <c r="B794" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C794">
+        <v>1</v>
+      </c>
+      <c r="D794">
+        <v>93.80970000000001</v>
       </c>
     </row>
   </sheetData>
@@ -22609,7 +22637,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D793"/>
+  <dimension ref="A1:D794"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33709,6 +33737,20 @@
       </c>
       <c r="D793">
         <v>56.397</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4">
+      <c r="A794" s="1">
+        <v>792</v>
+      </c>
+      <c r="B794" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C794">
+        <v>1</v>
+      </c>
+      <c r="D794">
+        <v>56.2936</v>
       </c>
     </row>
   </sheetData>
@@ -33718,7 +33760,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D793"/>
+  <dimension ref="A1:D794"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44818,6 +44860,20 @@
       </c>
       <c r="D793">
         <v>11.7271</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4">
+      <c r="A794" s="1">
+        <v>792</v>
+      </c>
+      <c r="B794" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C794">
+        <v>1</v>
+      </c>
+      <c r="D794">
+        <v>11.6947</v>
       </c>
     </row>
   </sheetData>
@@ -44827,7 +44883,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D793"/>
+  <dimension ref="A1:D794"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55927,6 +55983,20 @@
       </c>
       <c r="D793">
         <v>108.3655</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4">
+      <c r="A794" s="1">
+        <v>792</v>
+      </c>
+      <c r="B794" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C794">
+        <v>1</v>
+      </c>
+      <c r="D794">
+        <v>108.0184</v>
       </c>
     </row>
   </sheetData>
@@ -55936,7 +56006,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D793"/>
+  <dimension ref="A1:D794"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -67036,6 +67106,20 @@
       </c>
       <c r="D793">
         <v>16.7853</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4">
+      <c r="A794" s="1">
+        <v>792</v>
+      </c>
+      <c r="B794" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C794">
+        <v>100</v>
+      </c>
+      <c r="D794">
+        <v>16.7353</v>
       </c>
     </row>
   </sheetData>
@@ -67045,7 +67129,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D793"/>
+  <dimension ref="A1:D794"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -78145,6 +78229,20 @@
       </c>
       <c r="D793">
         <v>51.0533</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4">
+      <c r="A794" s="1">
+        <v>792</v>
+      </c>
+      <c r="B794" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C794">
+        <v>100</v>
+      </c>
+      <c r="D794">
+        <v>50.8852</v>
       </c>
     </row>
   </sheetData>
@@ -78154,7 +78252,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D793"/>
+  <dimension ref="A1:D794"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -89256,6 +89354,20 @@
         <v>102.9245</v>
       </c>
     </row>
+    <row r="794" spans="1:4">
+      <c r="A794" s="1">
+        <v>792</v>
+      </c>
+      <c r="B794" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C794">
+        <v>1</v>
+      </c>
+      <c r="D794">
+        <v>102.1633</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D794"/>
+  <dimension ref="A1:D795"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11505,6 +11505,20 @@
       </c>
       <c r="D794">
         <v>80.7192</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4">
+      <c r="A795" s="1">
+        <v>793</v>
+      </c>
+      <c r="B795" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C795">
+        <v>1</v>
+      </c>
+      <c r="D795">
+        <v>82.1314</v>
       </c>
     </row>
   </sheetData>
@@ -11514,7 +11528,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D794"/>
+  <dimension ref="A1:D795"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22628,6 +22642,20 @@
       </c>
       <c r="D794">
         <v>93.80970000000001</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4">
+      <c r="A795" s="1">
+        <v>793</v>
+      </c>
+      <c r="B795" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C795">
+        <v>1</v>
+      </c>
+      <c r="D795">
+        <v>95.0038</v>
       </c>
     </row>
   </sheetData>
@@ -22637,7 +22665,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D794"/>
+  <dimension ref="A1:D795"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33751,6 +33779,20 @@
       </c>
       <c r="D794">
         <v>56.2936</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4">
+      <c r="A795" s="1">
+        <v>793</v>
+      </c>
+      <c r="B795" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C795">
+        <v>1</v>
+      </c>
+      <c r="D795">
+        <v>57.1224</v>
       </c>
     </row>
   </sheetData>
@@ -33760,7 +33802,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D794"/>
+  <dimension ref="A1:D795"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44874,6 +44916,20 @@
       </c>
       <c r="D794">
         <v>11.6947</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4">
+      <c r="A795" s="1">
+        <v>793</v>
+      </c>
+      <c r="B795" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C795">
+        <v>1</v>
+      </c>
+      <c r="D795">
+        <v>11.9001</v>
       </c>
     </row>
   </sheetData>
@@ -44883,7 +44939,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D794"/>
+  <dimension ref="A1:D795"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -55997,6 +56053,20 @@
       </c>
       <c r="D794">
         <v>108.0184</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4">
+      <c r="A795" s="1">
+        <v>793</v>
+      </c>
+      <c r="B795" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C795">
+        <v>1</v>
+      </c>
+      <c r="D795">
+        <v>109.8261</v>
       </c>
     </row>
   </sheetData>
@@ -56006,7 +56076,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D794"/>
+  <dimension ref="A1:D795"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -67120,6 +67190,20 @@
       </c>
       <c r="D794">
         <v>16.7353</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4">
+      <c r="A795" s="1">
+        <v>793</v>
+      </c>
+      <c r="B795" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C795">
+        <v>100</v>
+      </c>
+      <c r="D795">
+        <v>17.0281</v>
       </c>
     </row>
   </sheetData>
@@ -67129,7 +67213,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D794"/>
+  <dimension ref="A1:D795"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -78243,6 +78327,20 @@
       </c>
       <c r="D794">
         <v>50.8852</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4">
+      <c r="A795" s="1">
+        <v>793</v>
+      </c>
+      <c r="B795" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C795">
+        <v>100</v>
+      </c>
+      <c r="D795">
+        <v>51.5156</v>
       </c>
     </row>
   </sheetData>
@@ -78252,7 +78350,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D794"/>
+  <dimension ref="A1:D795"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -89368,6 +89466,20 @@
         <v>102.1633</v>
       </c>
     </row>
+    <row r="795" spans="1:4">
+      <c r="A795" s="1">
+        <v>793</v>
+      </c>
+      <c r="B795" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C795">
+        <v>1</v>
+      </c>
+      <c r="D795">
+        <v>103.6882</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D795"/>
+  <dimension ref="A1:D796"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11519,6 +11519,20 @@
       </c>
       <c r="D795">
         <v>82.1314</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4">
+      <c r="A796" s="1">
+        <v>794</v>
+      </c>
+      <c r="B796" s="2">
+        <v>46109</v>
+      </c>
+      <c r="C796">
+        <v>1</v>
+      </c>
+      <c r="D796">
+        <v>81.1443</v>
       </c>
     </row>
   </sheetData>
@@ -11528,7 +11542,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D795"/>
+  <dimension ref="A1:D796"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22656,6 +22670,20 @@
       </c>
       <c r="D795">
         <v>95.0038</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4">
+      <c r="A796" s="1">
+        <v>794</v>
+      </c>
+      <c r="B796" s="2">
+        <v>46109</v>
+      </c>
+      <c r="C796">
+        <v>1</v>
+      </c>
+      <c r="D796">
+        <v>93.4247</v>
       </c>
     </row>
   </sheetData>
@@ -22665,7 +22693,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D795"/>
+  <dimension ref="A1:D796"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33793,6 +33821,20 @@
       </c>
       <c r="D795">
         <v>57.1224</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4">
+      <c r="A796" s="1">
+        <v>794</v>
+      </c>
+      <c r="B796" s="2">
+        <v>46109</v>
+      </c>
+      <c r="C796">
+        <v>1</v>
+      </c>
+      <c r="D796">
+        <v>56.0788</v>
       </c>
     </row>
   </sheetData>
@@ -33802,7 +33844,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D795"/>
+  <dimension ref="A1:D796"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44930,6 +44972,20 @@
       </c>
       <c r="D795">
         <v>11.9001</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4">
+      <c r="A796" s="1">
+        <v>794</v>
+      </c>
+      <c r="B796" s="2">
+        <v>46109</v>
+      </c>
+      <c r="C796">
+        <v>1</v>
+      </c>
+      <c r="D796">
+        <v>11.7301</v>
       </c>
     </row>
   </sheetData>
@@ -44939,7 +44995,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D795"/>
+  <dimension ref="A1:D796"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56067,6 +56123,20 @@
       </c>
       <c r="D795">
         <v>109.8261</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4">
+      <c r="A796" s="1">
+        <v>794</v>
+      </c>
+      <c r="B796" s="2">
+        <v>46109</v>
+      </c>
+      <c r="C796">
+        <v>1</v>
+      </c>
+      <c r="D796">
+        <v>108.3358</v>
       </c>
     </row>
   </sheetData>
@@ -56076,7 +56146,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D795"/>
+  <dimension ref="A1:D796"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -67204,6 +67274,20 @@
       </c>
       <c r="D795">
         <v>17.0281</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4">
+      <c r="A796" s="1">
+        <v>794</v>
+      </c>
+      <c r="B796" s="2">
+        <v>46109</v>
+      </c>
+      <c r="C796">
+        <v>100</v>
+      </c>
+      <c r="D796">
+        <v>16.8409</v>
       </c>
     </row>
   </sheetData>
@@ -67213,7 +67297,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D795"/>
+  <dimension ref="A1:D796"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -78341,6 +78425,20 @@
       </c>
       <c r="D795">
         <v>51.5156</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4">
+      <c r="A796" s="1">
+        <v>794</v>
+      </c>
+      <c r="B796" s="2">
+        <v>46109</v>
+      </c>
+      <c r="C796">
+        <v>100</v>
+      </c>
+      <c r="D796">
+        <v>50.8646</v>
       </c>
     </row>
   </sheetData>
@@ -78350,7 +78448,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D795"/>
+  <dimension ref="A1:D796"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -89480,6 +89578,20 @@
         <v>103.6882</v>
       </c>
     </row>
+    <row r="796" spans="1:4">
+      <c r="A796" s="1">
+        <v>794</v>
+      </c>
+      <c r="B796" s="2">
+        <v>46109</v>
+      </c>
+      <c r="C796">
+        <v>1</v>
+      </c>
+      <c r="D796">
+        <v>101.7611</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D796"/>
+  <dimension ref="A1:D797"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11533,6 +11533,20 @@
       </c>
       <c r="D796">
         <v>81.1443</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4">
+      <c r="A797" s="1">
+        <v>795</v>
+      </c>
+      <c r="B797" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C797">
+        <v>1</v>
+      </c>
+      <c r="D797">
+        <v>81.2955</v>
       </c>
     </row>
   </sheetData>
@@ -11542,7 +11556,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D796"/>
+  <dimension ref="A1:D797"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22684,6 +22698,20 @@
       </c>
       <c r="D796">
         <v>93.4247</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4">
+      <c r="A797" s="1">
+        <v>795</v>
+      </c>
+      <c r="B797" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C797">
+        <v>1</v>
+      </c>
+      <c r="D797">
+        <v>93.43689999999999</v>
       </c>
     </row>
   </sheetData>
@@ -22693,7 +22721,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D796"/>
+  <dimension ref="A1:D797"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33835,6 +33863,20 @@
       </c>
       <c r="D796">
         <v>56.0788</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4">
+      <c r="A797" s="1">
+        <v>795</v>
+      </c>
+      <c r="B797" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C797">
+        <v>1</v>
+      </c>
+      <c r="D797">
+        <v>55.8419</v>
       </c>
     </row>
   </sheetData>
@@ -33844,7 +33886,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D796"/>
+  <dimension ref="A1:D797"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -44986,6 +45028,20 @@
       </c>
       <c r="D796">
         <v>11.7301</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4">
+      <c r="A797" s="1">
+        <v>795</v>
+      </c>
+      <c r="B797" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C797">
+        <v>1</v>
+      </c>
+      <c r="D797">
+        <v>11.7439</v>
       </c>
     </row>
   </sheetData>
@@ -44995,7 +45051,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D796"/>
+  <dimension ref="A1:D797"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56137,6 +56193,20 @@
       </c>
       <c r="D796">
         <v>108.3358</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4">
+      <c r="A797" s="1">
+        <v>795</v>
+      </c>
+      <c r="B797" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C797">
+        <v>1</v>
+      </c>
+      <c r="D797">
+        <v>108.0498</v>
       </c>
     </row>
   </sheetData>
@@ -56146,7 +56216,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D796"/>
+  <dimension ref="A1:D797"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -67288,6 +67358,20 @@
       </c>
       <c r="D796">
         <v>16.8409</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4">
+      <c r="A797" s="1">
+        <v>795</v>
+      </c>
+      <c r="B797" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C797">
+        <v>100</v>
+      </c>
+      <c r="D797">
+        <v>16.8478</v>
       </c>
     </row>
   </sheetData>
@@ -67297,7 +67381,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D796"/>
+  <dimension ref="A1:D797"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -78439,6 +78523,20 @@
       </c>
       <c r="D796">
         <v>50.8646</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4">
+      <c r="A797" s="1">
+        <v>795</v>
+      </c>
+      <c r="B797" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C797">
+        <v>100</v>
+      </c>
+      <c r="D797">
+        <v>50.8129</v>
       </c>
     </row>
   </sheetData>
@@ -78448,7 +78546,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D796"/>
+  <dimension ref="A1:D797"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -89592,6 +89690,20 @@
         <v>101.7611</v>
       </c>
     </row>
+    <row r="797" spans="1:4">
+      <c r="A797" s="1">
+        <v>795</v>
+      </c>
+      <c r="B797" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C797">
+        <v>1</v>
+      </c>
+      <c r="D797">
+        <v>101.6067</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D797"/>
+  <dimension ref="A1:D798"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11547,6 +11547,20 @@
       </c>
       <c r="D797">
         <v>81.2955</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4">
+      <c r="A798" s="1">
+        <v>796</v>
+      </c>
+      <c r="B798" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C798">
+        <v>1</v>
+      </c>
+      <c r="D798">
+        <v>81.2504</v>
       </c>
     </row>
   </sheetData>
@@ -11556,7 +11570,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D797"/>
+  <dimension ref="A1:D798"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22712,6 +22726,20 @@
       </c>
       <c r="D797">
         <v>93.43689999999999</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4">
+      <c r="A798" s="1">
+        <v>796</v>
+      </c>
+      <c r="B798" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C798">
+        <v>1</v>
+      </c>
+      <c r="D798">
+        <v>93.2739</v>
       </c>
     </row>
   </sheetData>
@@ -22721,7 +22749,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D797"/>
+  <dimension ref="A1:D798"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33877,6 +33905,20 @@
       </c>
       <c r="D797">
         <v>55.8419</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4">
+      <c r="A798" s="1">
+        <v>796</v>
+      </c>
+      <c r="B798" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C798">
+        <v>1</v>
+      </c>
+      <c r="D798">
+        <v>55.6159</v>
       </c>
     </row>
   </sheetData>
@@ -33886,7 +33928,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D797"/>
+  <dimension ref="A1:D798"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45042,6 +45084,20 @@
       </c>
       <c r="D797">
         <v>11.7439</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4">
+      <c r="A798" s="1">
+        <v>796</v>
+      </c>
+      <c r="B798" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C798">
+        <v>1</v>
+      </c>
+      <c r="D798">
+        <v>11.7804</v>
       </c>
     </row>
   </sheetData>
@@ -45051,7 +45107,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D797"/>
+  <dimension ref="A1:D798"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56207,6 +56263,20 @@
       </c>
       <c r="D797">
         <v>108.0498</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4">
+      <c r="A798" s="1">
+        <v>796</v>
+      </c>
+      <c r="B798" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C798">
+        <v>1</v>
+      </c>
+      <c r="D798">
+        <v>107.2343</v>
       </c>
     </row>
   </sheetData>
@@ -56216,7 +56286,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D797"/>
+  <dimension ref="A1:D798"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -67372,6 +67442,20 @@
       </c>
       <c r="D797">
         <v>16.8478</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4">
+      <c r="A798" s="1">
+        <v>796</v>
+      </c>
+      <c r="B798" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C798">
+        <v>100</v>
+      </c>
+      <c r="D798">
+        <v>16.873</v>
       </c>
     </row>
   </sheetData>
@@ -67381,7 +67465,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D797"/>
+  <dimension ref="A1:D798"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -78537,6 +78621,20 @@
       </c>
       <c r="D797">
         <v>50.8129</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4">
+      <c r="A798" s="1">
+        <v>796</v>
+      </c>
+      <c r="B798" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C798">
+        <v>100</v>
+      </c>
+      <c r="D798">
+        <v>50.8451</v>
       </c>
     </row>
   </sheetData>
@@ -78546,7 +78644,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D797"/>
+  <dimension ref="A1:D798"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -89704,6 +89802,20 @@
         <v>101.6067</v>
       </c>
     </row>
+    <row r="798" spans="1:4">
+      <c r="A798" s="1">
+        <v>796</v>
+      </c>
+      <c r="B798" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C798">
+        <v>1</v>
+      </c>
+      <c r="D798">
+        <v>101.563</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D798"/>
+  <dimension ref="A1:D799"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11561,6 +11561,20 @@
       </c>
       <c r="D798">
         <v>81.2504</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4">
+      <c r="A799" s="1">
+        <v>797</v>
+      </c>
+      <c r="B799" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C799">
+        <v>1</v>
+      </c>
+      <c r="D799">
+        <v>80.6234</v>
       </c>
     </row>
   </sheetData>
@@ -11570,7 +11584,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D798"/>
+  <dimension ref="A1:D799"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22740,6 +22754,20 @@
       </c>
       <c r="D798">
         <v>93.2739</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4">
+      <c r="A799" s="1">
+        <v>797</v>
+      </c>
+      <c r="B799" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C799">
+        <v>1</v>
+      </c>
+      <c r="D799">
+        <v>93.4443</v>
       </c>
     </row>
   </sheetData>
@@ -22749,7 +22777,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D798"/>
+  <dimension ref="A1:D799"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33919,6 +33947,20 @@
       </c>
       <c r="D798">
         <v>55.6159</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4">
+      <c r="A799" s="1">
+        <v>797</v>
+      </c>
+      <c r="B799" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C799">
+        <v>1</v>
+      </c>
+      <c r="D799">
+        <v>55.6624</v>
       </c>
     </row>
   </sheetData>
@@ -33928,7 +33970,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D798"/>
+  <dimension ref="A1:D799"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45098,6 +45140,20 @@
       </c>
       <c r="D798">
         <v>11.7804</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4">
+      <c r="A799" s="1">
+        <v>797</v>
+      </c>
+      <c r="B799" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C799">
+        <v>1</v>
+      </c>
+      <c r="D799">
+        <v>11.707</v>
       </c>
     </row>
   </sheetData>
@@ -45107,7 +45163,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D798"/>
+  <dimension ref="A1:D799"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56277,6 +56333,20 @@
       </c>
       <c r="D798">
         <v>107.2343</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4">
+      <c r="A799" s="1">
+        <v>797</v>
+      </c>
+      <c r="B799" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C799">
+        <v>1</v>
+      </c>
+      <c r="D799">
+        <v>106.3261</v>
       </c>
     </row>
   </sheetData>
@@ -56286,7 +56356,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D798"/>
+  <dimension ref="A1:D799"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -67456,6 +67526,20 @@
       </c>
       <c r="D798">
         <v>16.873</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4">
+      <c r="A799" s="1">
+        <v>797</v>
+      </c>
+      <c r="B799" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C799">
+        <v>100</v>
+      </c>
+      <c r="D799">
+        <v>16.8397</v>
       </c>
     </row>
   </sheetData>
@@ -67465,7 +67549,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D798"/>
+  <dimension ref="A1:D799"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -78635,6 +78719,20 @@
       </c>
       <c r="D798">
         <v>50.8451</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4">
+      <c r="A799" s="1">
+        <v>797</v>
+      </c>
+      <c r="B799" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C799">
+        <v>100</v>
+      </c>
+      <c r="D799">
+        <v>50.7576</v>
       </c>
     </row>
   </sheetData>
@@ -78644,7 +78742,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D798"/>
+  <dimension ref="A1:D799"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -89816,6 +89914,20 @@
         <v>101.563</v>
       </c>
     </row>
+    <row r="799" spans="1:4">
+      <c r="A799" s="1">
+        <v>797</v>
+      </c>
+      <c r="B799" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C799">
+        <v>1</v>
+      </c>
+      <c r="D799">
+        <v>101.592</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D799"/>
+  <dimension ref="A1:D800"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11575,6 +11575,20 @@
       </c>
       <c r="D799">
         <v>80.6234</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4">
+      <c r="A800" s="1">
+        <v>798</v>
+      </c>
+      <c r="B800" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C800">
+        <v>1</v>
+      </c>
+      <c r="D800">
+        <v>80.33320000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11584,7 +11598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D799"/>
+  <dimension ref="A1:D800"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22768,6 +22782,20 @@
       </c>
       <c r="D799">
         <v>93.4443</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4">
+      <c r="A800" s="1">
+        <v>798</v>
+      </c>
+      <c r="B800" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C800">
+        <v>1</v>
+      </c>
+      <c r="D800">
+        <v>92.73260000000001</v>
       </c>
     </row>
   </sheetData>
@@ -22777,7 +22805,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D799"/>
+  <dimension ref="A1:D800"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33961,6 +33989,20 @@
       </c>
       <c r="D799">
         <v>55.6624</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4">
+      <c r="A800" s="1">
+        <v>798</v>
+      </c>
+      <c r="B800" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C800">
+        <v>1</v>
+      </c>
+      <c r="D800">
+        <v>55.2612</v>
       </c>
     </row>
   </sheetData>
@@ -33970,7 +34012,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D799"/>
+  <dimension ref="A1:D800"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45154,6 +45196,20 @@
       </c>
       <c r="D799">
         <v>11.707</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4">
+      <c r="A800" s="1">
+        <v>798</v>
+      </c>
+      <c r="B800" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C800">
+        <v>1</v>
+      </c>
+      <c r="D800">
+        <v>11.6278</v>
       </c>
     </row>
   </sheetData>
@@ -45163,7 +45219,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D799"/>
+  <dimension ref="A1:D800"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56347,6 +56403,20 @@
       </c>
       <c r="D799">
         <v>106.3261</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4">
+      <c r="A800" s="1">
+        <v>798</v>
+      </c>
+      <c r="B800" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C800">
+        <v>1</v>
+      </c>
+      <c r="D800">
+        <v>107.1163</v>
       </c>
     </row>
   </sheetData>
@@ -56356,7 +56426,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D799"/>
+  <dimension ref="A1:D800"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -67540,6 +67610,20 @@
       </c>
       <c r="D799">
         <v>16.8397</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4">
+      <c r="A800" s="1">
+        <v>798</v>
+      </c>
+      <c r="B800" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C800">
+        <v>100</v>
+      </c>
+      <c r="D800">
+        <v>16.909</v>
       </c>
     </row>
   </sheetData>
@@ -67549,7 +67633,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D799"/>
+  <dimension ref="A1:D800"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -78733,6 +78817,20 @@
       </c>
       <c r="D799">
         <v>50.7576</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4">
+      <c r="A800" s="1">
+        <v>798</v>
+      </c>
+      <c r="B800" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C800">
+        <v>100</v>
+      </c>
+      <c r="D800">
+        <v>50.6323</v>
       </c>
     </row>
   </sheetData>
@@ -78742,7 +78840,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D799"/>
+  <dimension ref="A1:D800"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -89928,6 +90026,20 @@
         <v>101.592</v>
       </c>
     </row>
+    <row r="800" spans="1:4">
+      <c r="A800" s="1">
+        <v>798</v>
+      </c>
+      <c r="B800" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C800">
+        <v>1</v>
+      </c>
+      <c r="D800">
+        <v>101.2263</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D800"/>
+  <dimension ref="A1:D801"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11589,6 +11589,20 @@
       </c>
       <c r="D800">
         <v>80.33320000000001</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4">
+      <c r="A801" s="1">
+        <v>799</v>
+      </c>
+      <c r="B801" s="2">
+        <v>46116</v>
+      </c>
+      <c r="C801">
+        <v>1</v>
+      </c>
+      <c r="D801">
+        <v>79.72929999999999</v>
       </c>
     </row>
   </sheetData>
@@ -11598,7 +11612,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D800"/>
+  <dimension ref="A1:D801"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22796,6 +22810,20 @@
       </c>
       <c r="D800">
         <v>92.73260000000001</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4">
+      <c r="A801" s="1">
+        <v>799</v>
+      </c>
+      <c r="B801" s="2">
+        <v>46116</v>
+      </c>
+      <c r="C801">
+        <v>1</v>
+      </c>
+      <c r="D801">
+        <v>92.1915</v>
       </c>
     </row>
   </sheetData>
@@ -22805,7 +22833,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D800"/>
+  <dimension ref="A1:D801"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34003,6 +34031,20 @@
       </c>
       <c r="D800">
         <v>55.2612</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4">
+      <c r="A801" s="1">
+        <v>799</v>
+      </c>
+      <c r="B801" s="2">
+        <v>46116</v>
+      </c>
+      <c r="C801">
+        <v>1</v>
+      </c>
+      <c r="D801">
+        <v>54.8458</v>
       </c>
     </row>
   </sheetData>
@@ -34012,7 +34054,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D800"/>
+  <dimension ref="A1:D801"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45210,6 +45252,20 @@
       </c>
       <c r="D800">
         <v>11.6278</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4">
+      <c r="A801" s="1">
+        <v>799</v>
+      </c>
+      <c r="B801" s="2">
+        <v>46116</v>
+      </c>
+      <c r="C801">
+        <v>1</v>
+      </c>
+      <c r="D801">
+        <v>11.5743</v>
       </c>
     </row>
   </sheetData>
@@ -45219,7 +45275,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D800"/>
+  <dimension ref="A1:D801"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56417,6 +56473,20 @@
       </c>
       <c r="D800">
         <v>107.1163</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4">
+      <c r="A801" s="1">
+        <v>799</v>
+      </c>
+      <c r="B801" s="2">
+        <v>46116</v>
+      </c>
+      <c r="C801">
+        <v>1</v>
+      </c>
+      <c r="D801">
+        <v>106.311</v>
       </c>
     </row>
   </sheetData>
@@ -56426,7 +56496,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D800"/>
+  <dimension ref="A1:D801"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -67624,6 +67694,20 @@
       </c>
       <c r="D800">
         <v>16.909</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4">
+      <c r="A801" s="1">
+        <v>799</v>
+      </c>
+      <c r="B801" s="2">
+        <v>46116</v>
+      </c>
+      <c r="C801">
+        <v>100</v>
+      </c>
+      <c r="D801">
+        <v>16.8807</v>
       </c>
     </row>
   </sheetData>
@@ -67633,7 +67717,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D800"/>
+  <dimension ref="A1:D801"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -78831,6 +78915,20 @@
       </c>
       <c r="D800">
         <v>50.6323</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4">
+      <c r="A801" s="1">
+        <v>799</v>
+      </c>
+      <c r="B801" s="2">
+        <v>46116</v>
+      </c>
+      <c r="C801">
+        <v>100</v>
+      </c>
+      <c r="D801">
+        <v>49.9463</v>
       </c>
     </row>
   </sheetData>
@@ -78840,7 +78938,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D800"/>
+  <dimension ref="A1:D801"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -90040,6 +90138,20 @@
         <v>101.2263</v>
       </c>
     </row>
+    <row r="801" spans="1:4">
+      <c r="A801" s="1">
+        <v>799</v>
+      </c>
+      <c r="B801" s="2">
+        <v>46116</v>
+      </c>
+      <c r="C801">
+        <v>1</v>
+      </c>
+      <c r="D801">
+        <v>99.7115</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D801"/>
+  <dimension ref="A1:D802"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11603,6 +11603,20 @@
       </c>
       <c r="D801">
         <v>79.72929999999999</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4">
+      <c r="A802" s="1">
+        <v>800</v>
+      </c>
+      <c r="B802" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C802">
+        <v>1</v>
+      </c>
+      <c r="D802">
+        <v>78.7277</v>
       </c>
     </row>
   </sheetData>
@@ -11612,7 +11626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D801"/>
+  <dimension ref="A1:D802"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22824,6 +22838,20 @@
       </c>
       <c r="D801">
         <v>92.1915</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4">
+      <c r="A802" s="1">
+        <v>800</v>
+      </c>
+      <c r="B802" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C802">
+        <v>1</v>
+      </c>
+      <c r="D802">
+        <v>91.0034</v>
       </c>
     </row>
   </sheetData>
@@ -22833,7 +22861,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D801"/>
+  <dimension ref="A1:D802"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34045,6 +34073,20 @@
       </c>
       <c r="D801">
         <v>54.8458</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4">
+      <c r="A802" s="1">
+        <v>800</v>
+      </c>
+      <c r="B802" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C802">
+        <v>1</v>
+      </c>
+      <c r="D802">
+        <v>54.1568</v>
       </c>
     </row>
   </sheetData>
@@ -34054,7 +34096,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D801"/>
+  <dimension ref="A1:D802"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45266,6 +45308,20 @@
       </c>
       <c r="D801">
         <v>11.5743</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4">
+      <c r="A802" s="1">
+        <v>800</v>
+      </c>
+      <c r="B802" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C802">
+        <v>1</v>
+      </c>
+      <c r="D802">
+        <v>11.4481</v>
       </c>
     </row>
   </sheetData>
@@ -45275,7 +45331,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D801"/>
+  <dimension ref="A1:D802"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56487,6 +56543,20 @@
       </c>
       <c r="D801">
         <v>106.311</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4">
+      <c r="A802" s="1">
+        <v>800</v>
+      </c>
+      <c r="B802" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C802">
+        <v>1</v>
+      </c>
+      <c r="D802">
+        <v>104.9755</v>
       </c>
     </row>
   </sheetData>
@@ -56496,7 +56566,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D801"/>
+  <dimension ref="A1:D802"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -67708,6 +67778,20 @@
       </c>
       <c r="D801">
         <v>16.8807</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4">
+      <c r="A802" s="1">
+        <v>800</v>
+      </c>
+      <c r="B802" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C802">
+        <v>100</v>
+      </c>
+      <c r="D802">
+        <v>16.7342</v>
       </c>
     </row>
   </sheetData>
@@ -67717,7 +67801,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D801"/>
+  <dimension ref="A1:D802"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -78929,6 +79013,20 @@
       </c>
       <c r="D801">
         <v>49.9463</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4">
+      <c r="A802" s="1">
+        <v>800</v>
+      </c>
+      <c r="B802" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C802">
+        <v>100</v>
+      </c>
+      <c r="D802">
+        <v>49.3405</v>
       </c>
     </row>
   </sheetData>
@@ -78938,7 +79036,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D801"/>
+  <dimension ref="A1:D802"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -90152,6 +90250,20 @@
         <v>99.7115</v>
       </c>
     </row>
+    <row r="802" spans="1:4">
+      <c r="A802" s="1">
+        <v>800</v>
+      </c>
+      <c r="B802" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C802">
+        <v>1</v>
+      </c>
+      <c r="D802">
+        <v>98.4589</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D802"/>
+  <dimension ref="A1:D803"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11617,6 +11617,20 @@
       </c>
       <c r="D802">
         <v>78.7277</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4">
+      <c r="A803" s="1">
+        <v>801</v>
+      </c>
+      <c r="B803" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C803">
+        <v>1</v>
+      </c>
+      <c r="D803">
+        <v>78.7496</v>
       </c>
     </row>
   </sheetData>
@@ -11626,7 +11640,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D802"/>
+  <dimension ref="A1:D803"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22852,6 +22866,20 @@
       </c>
       <c r="D802">
         <v>91.0034</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4">
+      <c r="A803" s="1">
+        <v>801</v>
+      </c>
+      <c r="B803" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C803">
+        <v>1</v>
+      </c>
+      <c r="D803">
+        <v>91.0279</v>
       </c>
     </row>
   </sheetData>
@@ -22861,7 +22889,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D802"/>
+  <dimension ref="A1:D803"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34087,6 +34115,20 @@
       </c>
       <c r="D802">
         <v>54.1568</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4">
+      <c r="A803" s="1">
+        <v>801</v>
+      </c>
+      <c r="B803" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C803">
+        <v>1</v>
+      </c>
+      <c r="D803">
+        <v>54.4632</v>
       </c>
     </row>
   </sheetData>
@@ -34096,7 +34138,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D802"/>
+  <dimension ref="A1:D803"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45322,6 +45364,20 @@
       </c>
       <c r="D802">
         <v>11.4481</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4">
+      <c r="A803" s="1">
+        <v>801</v>
+      </c>
+      <c r="B803" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C803">
+        <v>1</v>
+      </c>
+      <c r="D803">
+        <v>11.4713</v>
       </c>
     </row>
   </sheetData>
@@ -45331,7 +45387,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D802"/>
+  <dimension ref="A1:D803"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56557,6 +56613,20 @@
       </c>
       <c r="D802">
         <v>104.9755</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4">
+      <c r="A803" s="1">
+        <v>801</v>
+      </c>
+      <c r="B803" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C803">
+        <v>1</v>
+      </c>
+      <c r="D803">
+        <v>104.296</v>
       </c>
     </row>
   </sheetData>
@@ -56566,7 +56636,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D802"/>
+  <dimension ref="A1:D803"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -67792,6 +67862,20 @@
       </c>
       <c r="D802">
         <v>16.7342</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4">
+      <c r="A803" s="1">
+        <v>801</v>
+      </c>
+      <c r="B803" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C803">
+        <v>100</v>
+      </c>
+      <c r="D803">
+        <v>16.8871</v>
       </c>
     </row>
   </sheetData>
@@ -67801,7 +67885,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D802"/>
+  <dimension ref="A1:D803"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -79027,6 +79111,20 @@
       </c>
       <c r="D802">
         <v>49.3405</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4">
+      <c r="A803" s="1">
+        <v>801</v>
+      </c>
+      <c r="B803" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C803">
+        <v>100</v>
+      </c>
+      <c r="D803">
+        <v>49.2801</v>
       </c>
     </row>
   </sheetData>
@@ -79036,7 +79134,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D802"/>
+  <dimension ref="A1:D803"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -90264,6 +90362,20 @@
         <v>98.4589</v>
       </c>
     </row>
+    <row r="803" spans="1:4">
+      <c r="A803" s="1">
+        <v>801</v>
+      </c>
+      <c r="B803" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C803">
+        <v>1</v>
+      </c>
+      <c r="D803">
+        <v>98.65900000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D803"/>
+  <dimension ref="A1:D804"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11631,6 +11631,20 @@
       </c>
       <c r="D803">
         <v>78.7496</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4">
+      <c r="A804" s="1">
+        <v>802</v>
+      </c>
+      <c r="B804" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C804">
+        <v>1</v>
+      </c>
+      <c r="D804">
+        <v>78.3043</v>
       </c>
     </row>
   </sheetData>
@@ -11640,7 +11654,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D803"/>
+  <dimension ref="A1:D804"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22880,6 +22894,20 @@
       </c>
       <c r="D803">
         <v>91.0279</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4">
+      <c r="A804" s="1">
+        <v>802</v>
+      </c>
+      <c r="B804" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C804">
+        <v>1</v>
+      </c>
+      <c r="D804">
+        <v>91.5641</v>
       </c>
     </row>
   </sheetData>
@@ -22889,7 +22917,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D803"/>
+  <dimension ref="A1:D804"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34129,6 +34157,20 @@
       </c>
       <c r="D803">
         <v>54.4632</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4">
+      <c r="A804" s="1">
+        <v>802</v>
+      </c>
+      <c r="B804" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C804">
+        <v>1</v>
+      </c>
+      <c r="D804">
+        <v>55.3768</v>
       </c>
     </row>
   </sheetData>
@@ -34138,7 +34180,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D803"/>
+  <dimension ref="A1:D804"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45378,6 +45420,20 @@
       </c>
       <c r="D803">
         <v>11.4713</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4">
+      <c r="A804" s="1">
+        <v>802</v>
+      </c>
+      <c r="B804" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C804">
+        <v>1</v>
+      </c>
+      <c r="D804">
+        <v>11.4581</v>
       </c>
     </row>
   </sheetData>
@@ -45387,7 +45443,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D803"/>
+  <dimension ref="A1:D804"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56627,6 +56683,20 @@
       </c>
       <c r="D803">
         <v>104.296</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4">
+      <c r="A804" s="1">
+        <v>802</v>
+      </c>
+      <c r="B804" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C804">
+        <v>1</v>
+      </c>
+      <c r="D804">
+        <v>103.7297</v>
       </c>
     </row>
   </sheetData>
@@ -56636,7 +56706,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D803"/>
+  <dimension ref="A1:D804"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -67876,6 +67946,20 @@
       </c>
       <c r="D803">
         <v>16.8871</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4">
+      <c r="A804" s="1">
+        <v>802</v>
+      </c>
+      <c r="B804" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C804">
+        <v>100</v>
+      </c>
+      <c r="D804">
+        <v>17.009</v>
       </c>
     </row>
   </sheetData>
@@ -67885,7 +67969,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D803"/>
+  <dimension ref="A1:D804"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -79125,6 +79209,20 @@
       </c>
       <c r="D803">
         <v>49.2801</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4">
+      <c r="A804" s="1">
+        <v>802</v>
+      </c>
+      <c r="B804" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C804">
+        <v>100</v>
+      </c>
+      <c r="D804">
+        <v>49.3566</v>
       </c>
     </row>
   </sheetData>
@@ -79134,7 +79232,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D803"/>
+  <dimension ref="A1:D804"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -90376,6 +90474,20 @@
         <v>98.65900000000001</v>
       </c>
     </row>
+    <row r="804" spans="1:4">
+      <c r="A804" s="1">
+        <v>802</v>
+      </c>
+      <c r="B804" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C804">
+        <v>1</v>
+      </c>
+      <c r="D804">
+        <v>99.28270000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D804"/>
+  <dimension ref="A1:D805"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11645,6 +11645,20 @@
       </c>
       <c r="D804">
         <v>78.3043</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4">
+      <c r="A805" s="1">
+        <v>803</v>
+      </c>
+      <c r="B805" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C805">
+        <v>1</v>
+      </c>
+      <c r="D805">
+        <v>77.8366</v>
       </c>
     </row>
   </sheetData>
@@ -11654,7 +11668,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D804"/>
+  <dimension ref="A1:D805"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22908,6 +22922,20 @@
       </c>
       <c r="D804">
         <v>91.5641</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4">
+      <c r="A805" s="1">
+        <v>803</v>
+      </c>
+      <c r="B805" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C805">
+        <v>1</v>
+      </c>
+      <c r="D805">
+        <v>90.8813</v>
       </c>
     </row>
   </sheetData>
@@ -22917,7 +22945,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D804"/>
+  <dimension ref="A1:D805"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34171,6 +34199,20 @@
       </c>
       <c r="D804">
         <v>55.3768</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4">
+      <c r="A805" s="1">
+        <v>803</v>
+      </c>
+      <c r="B805" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C805">
+        <v>1</v>
+      </c>
+      <c r="D805">
+        <v>54.7658</v>
       </c>
     </row>
   </sheetData>
@@ -34180,7 +34222,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D804"/>
+  <dimension ref="A1:D805"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45434,6 +45476,20 @@
       </c>
       <c r="D804">
         <v>11.4581</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4">
+      <c r="A805" s="1">
+        <v>803</v>
+      </c>
+      <c r="B805" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C805">
+        <v>1</v>
+      </c>
+      <c r="D805">
+        <v>11.3685</v>
       </c>
     </row>
   </sheetData>
@@ -45443,7 +45499,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D804"/>
+  <dimension ref="A1:D805"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56697,6 +56753,20 @@
       </c>
       <c r="D804">
         <v>103.7297</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4">
+      <c r="A805" s="1">
+        <v>803</v>
+      </c>
+      <c r="B805" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C805">
+        <v>1</v>
+      </c>
+      <c r="D805">
+        <v>104.6824</v>
       </c>
     </row>
   </sheetData>
@@ -56706,7 +56776,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D804"/>
+  <dimension ref="A1:D805"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -67960,6 +68030,20 @@
       </c>
       <c r="D804">
         <v>17.009</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4">
+      <c r="A805" s="1">
+        <v>803</v>
+      </c>
+      <c r="B805" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C805">
+        <v>100</v>
+      </c>
+      <c r="D805">
+        <v>16.376</v>
       </c>
     </row>
   </sheetData>
@@ -67969,7 +68053,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D804"/>
+  <dimension ref="A1:D805"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -79223,6 +79307,20 @@
       </c>
       <c r="D804">
         <v>49.3566</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4">
+      <c r="A805" s="1">
+        <v>803</v>
+      </c>
+      <c r="B805" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C805">
+        <v>100</v>
+      </c>
+      <c r="D805">
+        <v>48.997</v>
       </c>
     </row>
   </sheetData>
@@ -79232,7 +79330,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D804"/>
+  <dimension ref="A1:D805"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -90488,6 +90586,20 @@
         <v>99.28270000000001</v>
       </c>
     </row>
+    <row r="805" spans="1:4">
+      <c r="A805" s="1">
+        <v>803</v>
+      </c>
+      <c r="B805" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C805">
+        <v>1</v>
+      </c>
+      <c r="D805">
+        <v>98.4152</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D805"/>
+  <dimension ref="A1:D806"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11659,6 +11659,20 @@
       </c>
       <c r="D805">
         <v>77.8366</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4">
+      <c r="A806" s="1">
+        <v>804</v>
+      </c>
+      <c r="B806" s="2">
+        <v>46123</v>
+      </c>
+      <c r="C806">
+        <v>1</v>
+      </c>
+      <c r="D806">
+        <v>76.97239999999999</v>
       </c>
     </row>
   </sheetData>
@@ -11668,7 +11682,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D805"/>
+  <dimension ref="A1:D806"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22936,6 +22950,20 @@
       </c>
       <c r="D805">
         <v>90.8813</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4">
+      <c r="A806" s="1">
+        <v>804</v>
+      </c>
+      <c r="B806" s="2">
+        <v>46123</v>
+      </c>
+      <c r="C806">
+        <v>1</v>
+      </c>
+      <c r="D806">
+        <v>90.012</v>
       </c>
     </row>
   </sheetData>
@@ -22945,7 +22973,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D805"/>
+  <dimension ref="A1:D806"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34213,6 +34241,20 @@
       </c>
       <c r="D805">
         <v>54.7658</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4">
+      <c r="A806" s="1">
+        <v>804</v>
+      </c>
+      <c r="B806" s="2">
+        <v>46123</v>
+      </c>
+      <c r="C806">
+        <v>1</v>
+      </c>
+      <c r="D806">
+        <v>54.4272</v>
       </c>
     </row>
   </sheetData>
@@ -34222,7 +34264,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D805"/>
+  <dimension ref="A1:D806"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45490,6 +45532,20 @@
       </c>
       <c r="D805">
         <v>11.3685</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4">
+      <c r="A806" s="1">
+        <v>804</v>
+      </c>
+      <c r="B806" s="2">
+        <v>46123</v>
+      </c>
+      <c r="C806">
+        <v>1</v>
+      </c>
+      <c r="D806">
+        <v>11.2521</v>
       </c>
     </row>
   </sheetData>
@@ -45499,7 +45555,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D805"/>
+  <dimension ref="A1:D806"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56767,6 +56823,20 @@
       </c>
       <c r="D805">
         <v>104.6824</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4">
+      <c r="A806" s="1">
+        <v>804</v>
+      </c>
+      <c r="B806" s="2">
+        <v>46123</v>
+      </c>
+      <c r="C806">
+        <v>1</v>
+      </c>
+      <c r="D806">
+        <v>103.2585</v>
       </c>
     </row>
   </sheetData>
@@ -56776,7 +56846,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D805"/>
+  <dimension ref="A1:D806"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -68044,6 +68114,20 @@
       </c>
       <c r="D805">
         <v>16.376</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4">
+      <c r="A806" s="1">
+        <v>804</v>
+      </c>
+      <c r="B806" s="2">
+        <v>46123</v>
+      </c>
+      <c r="C806">
+        <v>100</v>
+      </c>
+      <c r="D806">
+        <v>16.0419</v>
       </c>
     </row>
   </sheetData>
@@ -68053,7 +68137,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D805"/>
+  <dimension ref="A1:D806"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -79321,6 +79405,20 @@
       </c>
       <c r="D805">
         <v>48.997</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4">
+      <c r="A806" s="1">
+        <v>804</v>
+      </c>
+      <c r="B806" s="2">
+        <v>46123</v>
+      </c>
+      <c r="C806">
+        <v>100</v>
+      </c>
+      <c r="D806">
+        <v>48.3404</v>
       </c>
     </row>
   </sheetData>
@@ -79330,7 +79428,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D805"/>
+  <dimension ref="A1:D806"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -90600,6 +90698,20 @@
         <v>98.4152</v>
       </c>
     </row>
+    <row r="806" spans="1:4">
+      <c r="A806" s="1">
+        <v>804</v>
+      </c>
+      <c r="B806" s="2">
+        <v>46123</v>
+      </c>
+      <c r="C806">
+        <v>1</v>
+      </c>
+      <c r="D806">
+        <v>97.4088</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D806"/>
+  <dimension ref="A1:D807"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11673,6 +11673,20 @@
       </c>
       <c r="D806">
         <v>76.97239999999999</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4">
+      <c r="A807" s="1">
+        <v>805</v>
+      </c>
+      <c r="B807" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C807">
+        <v>1</v>
+      </c>
+      <c r="D807">
+        <v>76.24890000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11682,7 +11696,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D806"/>
+  <dimension ref="A1:D807"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22964,6 +22978,20 @@
       </c>
       <c r="D806">
         <v>90.012</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4">
+      <c r="A807" s="1">
+        <v>805</v>
+      </c>
+      <c r="B807" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C807">
+        <v>1</v>
+      </c>
+      <c r="D807">
+        <v>89.1373</v>
       </c>
     </row>
   </sheetData>
@@ -22973,7 +23001,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D806"/>
+  <dimension ref="A1:D807"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34255,6 +34283,20 @@
       </c>
       <c r="D806">
         <v>54.4272</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4">
+      <c r="A807" s="1">
+        <v>805</v>
+      </c>
+      <c r="B807" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C807">
+        <v>1</v>
+      </c>
+      <c r="D807">
+        <v>53.6792</v>
       </c>
     </row>
   </sheetData>
@@ -34264,7 +34306,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D806"/>
+  <dimension ref="A1:D807"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45546,6 +45588,20 @@
       </c>
       <c r="D806">
         <v>11.2521</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4">
+      <c r="A807" s="1">
+        <v>805</v>
+      </c>
+      <c r="B807" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C807">
+        <v>1</v>
+      </c>
+      <c r="D807">
+        <v>11.1338</v>
       </c>
     </row>
   </sheetData>
@@ -45555,7 +45611,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D806"/>
+  <dimension ref="A1:D807"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56837,6 +56893,20 @@
       </c>
       <c r="D806">
         <v>103.2585</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4">
+      <c r="A807" s="1">
+        <v>805</v>
+      </c>
+      <c r="B807" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C807">
+        <v>1</v>
+      </c>
+      <c r="D807">
+        <v>102.6386</v>
       </c>
     </row>
   </sheetData>
@@ -56846,7 +56916,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D806"/>
+  <dimension ref="A1:D807"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -68128,6 +68198,20 @@
       </c>
       <c r="D806">
         <v>16.0419</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4">
+      <c r="A807" s="1">
+        <v>805</v>
+      </c>
+      <c r="B807" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C807">
+        <v>100</v>
+      </c>
+      <c r="D807">
+        <v>16.1158</v>
       </c>
     </row>
   </sheetData>
@@ -68137,7 +68221,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D806"/>
+  <dimension ref="A1:D807"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -79419,6 +79503,20 @@
       </c>
       <c r="D806">
         <v>48.3404</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4">
+      <c r="A807" s="1">
+        <v>805</v>
+      </c>
+      <c r="B807" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C807">
+        <v>100</v>
+      </c>
+      <c r="D807">
+        <v>47.7003</v>
       </c>
     </row>
   </sheetData>
@@ -79428,7 +79526,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D806"/>
+  <dimension ref="A1:D807"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -90712,6 +90810,20 @@
         <v>97.4088</v>
       </c>
     </row>
+    <row r="807" spans="1:4">
+      <c r="A807" s="1">
+        <v>805</v>
+      </c>
+      <c r="B807" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C807">
+        <v>1</v>
+      </c>
+      <c r="D807">
+        <v>96.45650000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D807"/>
+  <dimension ref="A1:D808"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11687,6 +11687,20 @@
       </c>
       <c r="D807">
         <v>76.24890000000001</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4">
+      <c r="A808" s="1">
+        <v>806</v>
+      </c>
+      <c r="B808" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C808">
+        <v>1</v>
+      </c>
+      <c r="D808">
+        <v>75.8532</v>
       </c>
     </row>
   </sheetData>
@@ -11696,7 +11710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D807"/>
+  <dimension ref="A1:D808"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22992,6 +23006,20 @@
       </c>
       <c r="D807">
         <v>89.1373</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4">
+      <c r="A808" s="1">
+        <v>806</v>
+      </c>
+      <c r="B808" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C808">
+        <v>1</v>
+      </c>
+      <c r="D808">
+        <v>89.2556</v>
       </c>
     </row>
   </sheetData>
@@ -23001,7 +23029,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D807"/>
+  <dimension ref="A1:D808"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34297,6 +34325,20 @@
       </c>
       <c r="D807">
         <v>53.6792</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4">
+      <c r="A808" s="1">
+        <v>806</v>
+      </c>
+      <c r="B808" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C808">
+        <v>1</v>
+      </c>
+      <c r="D808">
+        <v>53.7268</v>
       </c>
     </row>
   </sheetData>
@@ -34306,7 +34348,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D807"/>
+  <dimension ref="A1:D808"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45602,6 +45644,20 @@
       </c>
       <c r="D807">
         <v>11.1338</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4">
+      <c r="A808" s="1">
+        <v>806</v>
+      </c>
+      <c r="B808" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C808">
+        <v>1</v>
+      </c>
+      <c r="D808">
+        <v>11.091</v>
       </c>
     </row>
   </sheetData>
@@ -45611,7 +45667,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D807"/>
+  <dimension ref="A1:D808"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56907,6 +56963,20 @@
       </c>
       <c r="D807">
         <v>102.6386</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4">
+      <c r="A808" s="1">
+        <v>806</v>
+      </c>
+      <c r="B808" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C808">
+        <v>1</v>
+      </c>
+      <c r="D808">
+        <v>102.106</v>
       </c>
     </row>
   </sheetData>
@@ -56916,7 +56986,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D807"/>
+  <dimension ref="A1:D808"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -68212,6 +68282,20 @@
       </c>
       <c r="D807">
         <v>16.1158</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4">
+      <c r="A808" s="1">
+        <v>806</v>
+      </c>
+      <c r="B808" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C808">
+        <v>100</v>
+      </c>
+      <c r="D808">
+        <v>15.9725</v>
       </c>
     </row>
   </sheetData>
@@ -68221,7 +68305,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D807"/>
+  <dimension ref="A1:D808"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -79517,6 +79601,20 @@
       </c>
       <c r="D807">
         <v>47.7003</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4">
+      <c r="A808" s="1">
+        <v>806</v>
+      </c>
+      <c r="B808" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C808">
+        <v>100</v>
+      </c>
+      <c r="D808">
+        <v>47.6435</v>
       </c>
     </row>
   </sheetData>
@@ -79526,7 +79624,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D807"/>
+  <dimension ref="A1:D808"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -90824,6 +90922,20 @@
         <v>96.45650000000001</v>
       </c>
     </row>
+    <row r="808" spans="1:4">
+      <c r="A808" s="1">
+        <v>806</v>
+      </c>
+      <c r="B808" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C808">
+        <v>1</v>
+      </c>
+      <c r="D808">
+        <v>97.1729</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D808"/>
+  <dimension ref="A1:D809"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11701,6 +11701,20 @@
       </c>
       <c r="D808">
         <v>75.8532</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4">
+      <c r="A809" s="1">
+        <v>807</v>
+      </c>
+      <c r="B809" s="2">
+        <v>46128</v>
+      </c>
+      <c r="C809">
+        <v>1</v>
+      </c>
+      <c r="D809">
+        <v>75.2346</v>
       </c>
     </row>
   </sheetData>
@@ -11710,7 +11724,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D808"/>
+  <dimension ref="A1:D809"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23020,6 +23034,20 @@
       </c>
       <c r="D808">
         <v>89.2556</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4">
+      <c r="A809" s="1">
+        <v>807</v>
+      </c>
+      <c r="B809" s="2">
+        <v>46128</v>
+      </c>
+      <c r="C809">
+        <v>1</v>
+      </c>
+      <c r="D809">
+        <v>88.7303</v>
       </c>
     </row>
   </sheetData>
@@ -23029,7 +23057,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D808"/>
+  <dimension ref="A1:D809"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34339,6 +34367,20 @@
       </c>
       <c r="D808">
         <v>53.7268</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4">
+      <c r="A809" s="1">
+        <v>807</v>
+      </c>
+      <c r="B809" s="2">
+        <v>46128</v>
+      </c>
+      <c r="C809">
+        <v>1</v>
+      </c>
+      <c r="D809">
+        <v>53.7025</v>
       </c>
     </row>
   </sheetData>
@@ -34348,7 +34390,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D808"/>
+  <dimension ref="A1:D809"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45658,6 +45700,20 @@
       </c>
       <c r="D808">
         <v>11.091</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4">
+      <c r="A809" s="1">
+        <v>807</v>
+      </c>
+      <c r="B809" s="2">
+        <v>46128</v>
+      </c>
+      <c r="C809">
+        <v>1</v>
+      </c>
+      <c r="D809">
+        <v>11.0334</v>
       </c>
     </row>
   </sheetData>
@@ -45667,7 +45723,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D808"/>
+  <dimension ref="A1:D809"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -56977,6 +57033,20 @@
       </c>
       <c r="D808">
         <v>102.106</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4">
+      <c r="A809" s="1">
+        <v>807</v>
+      </c>
+      <c r="B809" s="2">
+        <v>46128</v>
+      </c>
+      <c r="C809">
+        <v>1</v>
+      </c>
+      <c r="D809">
+        <v>102.2288</v>
       </c>
     </row>
   </sheetData>
@@ -56986,7 +57056,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D808"/>
+  <dimension ref="A1:D809"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -68296,6 +68366,20 @@
       </c>
       <c r="D808">
         <v>15.9725</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4">
+      <c r="A809" s="1">
+        <v>807</v>
+      </c>
+      <c r="B809" s="2">
+        <v>46128</v>
+      </c>
+      <c r="C809">
+        <v>100</v>
+      </c>
+      <c r="D809">
+        <v>15.7734</v>
       </c>
     </row>
   </sheetData>
@@ -68305,7 +68389,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D808"/>
+  <dimension ref="A1:D809"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -79615,6 +79699,20 @@
       </c>
       <c r="D808">
         <v>47.6435</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4">
+      <c r="A809" s="1">
+        <v>807</v>
+      </c>
+      <c r="B809" s="2">
+        <v>46128</v>
+      </c>
+      <c r="C809">
+        <v>100</v>
+      </c>
+      <c r="D809">
+        <v>47.3561</v>
       </c>
     </row>
   </sheetData>
@@ -79624,7 +79722,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D808"/>
+  <dimension ref="A1:D809"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -90936,6 +91034,20 @@
         <v>97.1729</v>
       </c>
     </row>
+    <row r="809" spans="1:4">
+      <c r="A809" s="1">
+        <v>807</v>
+      </c>
+      <c r="B809" s="2">
+        <v>46128</v>
+      </c>
+      <c r="C809">
+        <v>1</v>
+      </c>
+      <c r="D809">
+        <v>96.3434</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D809"/>
+  <dimension ref="A1:D810"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11715,6 +11715,20 @@
       </c>
       <c r="D809">
         <v>75.2346</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4">
+      <c r="A810" s="1">
+        <v>808</v>
+      </c>
+      <c r="B810" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C810">
+        <v>1</v>
+      </c>
+      <c r="D810">
+        <v>76.0861</v>
       </c>
     </row>
   </sheetData>
@@ -11724,7 +11738,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D809"/>
+  <dimension ref="A1:D810"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23048,6 +23062,20 @@
       </c>
       <c r="D809">
         <v>88.7303</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4">
+      <c r="A810" s="1">
+        <v>808</v>
+      </c>
+      <c r="B810" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C810">
+        <v>1</v>
+      </c>
+      <c r="D810">
+        <v>89.4113</v>
       </c>
     </row>
   </sheetData>
@@ -23057,7 +23085,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D809"/>
+  <dimension ref="A1:D810"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34381,6 +34409,20 @@
       </c>
       <c r="D809">
         <v>53.7025</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4">
+      <c r="A810" s="1">
+        <v>808</v>
+      </c>
+      <c r="B810" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C810">
+        <v>1</v>
+      </c>
+      <c r="D810">
+        <v>54.6983</v>
       </c>
     </row>
   </sheetData>
@@ -34390,7 +34432,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D809"/>
+  <dimension ref="A1:D810"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45714,6 +45756,20 @@
       </c>
       <c r="D809">
         <v>11.0334</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4">
+      <c r="A810" s="1">
+        <v>808</v>
+      </c>
+      <c r="B810" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C810">
+        <v>1</v>
+      </c>
+      <c r="D810">
+        <v>11.17</v>
       </c>
     </row>
   </sheetData>
@@ -45723,7 +45779,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D809"/>
+  <dimension ref="A1:D810"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57047,6 +57103,20 @@
       </c>
       <c r="D809">
         <v>102.2288</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4">
+      <c r="A810" s="1">
+        <v>808</v>
+      </c>
+      <c r="B810" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C810">
+        <v>1</v>
+      </c>
+      <c r="D810">
+        <v>103.2412</v>
       </c>
     </row>
   </sheetData>
@@ -57056,7 +57126,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D809"/>
+  <dimension ref="A1:D810"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -68380,6 +68450,20 @@
       </c>
       <c r="D809">
         <v>15.7734</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4">
+      <c r="A810" s="1">
+        <v>808</v>
+      </c>
+      <c r="B810" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C810">
+        <v>100</v>
+      </c>
+      <c r="D810">
+        <v>16.0492</v>
       </c>
     </row>
   </sheetData>
@@ -68389,7 +68473,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D809"/>
+  <dimension ref="A1:D810"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -79713,6 +79797,20 @@
       </c>
       <c r="D809">
         <v>47.3561</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4">
+      <c r="A810" s="1">
+        <v>808</v>
+      </c>
+      <c r="B810" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C810">
+        <v>100</v>
+      </c>
+      <c r="D810">
+        <v>47.9252</v>
       </c>
     </row>
   </sheetData>
@@ -79722,7 +79820,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D809"/>
+  <dimension ref="A1:D810"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -91048,6 +91146,20 @@
         <v>96.3434</v>
       </c>
     </row>
+    <row r="810" spans="1:4">
+      <c r="A810" s="1">
+        <v>808</v>
+      </c>
+      <c r="B810" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C810">
+        <v>1</v>
+      </c>
+      <c r="D810">
+        <v>97.2595</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D810"/>
+  <dimension ref="A1:D811"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11729,6 +11729,20 @@
       </c>
       <c r="D810">
         <v>76.0861</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4">
+      <c r="A811" s="1">
+        <v>809</v>
+      </c>
+      <c r="B811" s="2">
+        <v>46130</v>
+      </c>
+      <c r="C811">
+        <v>1</v>
+      </c>
+      <c r="D811">
+        <v>76.0535</v>
       </c>
     </row>
   </sheetData>
@@ -11738,7 +11752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D810"/>
+  <dimension ref="A1:D811"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23076,6 +23090,20 @@
       </c>
       <c r="D810">
         <v>89.4113</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4">
+      <c r="A811" s="1">
+        <v>809</v>
+      </c>
+      <c r="B811" s="2">
+        <v>46130</v>
+      </c>
+      <c r="C811">
+        <v>1</v>
+      </c>
+      <c r="D811">
+        <v>89.62560000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23085,7 +23113,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D810"/>
+  <dimension ref="A1:D811"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34423,6 +34451,20 @@
       </c>
       <c r="D810">
         <v>54.6983</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4">
+      <c r="A811" s="1">
+        <v>809</v>
+      </c>
+      <c r="B811" s="2">
+        <v>46130</v>
+      </c>
+      <c r="C811">
+        <v>1</v>
+      </c>
+      <c r="D811">
+        <v>54.5304</v>
       </c>
     </row>
   </sheetData>
@@ -34432,7 +34474,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D810"/>
+  <dimension ref="A1:D811"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45770,6 +45812,20 @@
       </c>
       <c r="D810">
         <v>11.17</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4">
+      <c r="A811" s="1">
+        <v>809</v>
+      </c>
+      <c r="B811" s="2">
+        <v>46130</v>
+      </c>
+      <c r="C811">
+        <v>1</v>
+      </c>
+      <c r="D811">
+        <v>11.1457</v>
       </c>
     </row>
   </sheetData>
@@ -45779,7 +45835,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D810"/>
+  <dimension ref="A1:D811"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57117,6 +57173,20 @@
       </c>
       <c r="D810">
         <v>103.2412</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4">
+      <c r="A811" s="1">
+        <v>809</v>
+      </c>
+      <c r="B811" s="2">
+        <v>46130</v>
+      </c>
+      <c r="C811">
+        <v>1</v>
+      </c>
+      <c r="D811">
+        <v>102.8395</v>
       </c>
     </row>
   </sheetData>
@@ -57126,7 +57196,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D810"/>
+  <dimension ref="A1:D811"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -68464,6 +68534,20 @@
       </c>
       <c r="D810">
         <v>16.0492</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4">
+      <c r="A811" s="1">
+        <v>809</v>
+      </c>
+      <c r="B811" s="2">
+        <v>46130</v>
+      </c>
+      <c r="C811">
+        <v>100</v>
+      </c>
+      <c r="D811">
+        <v>16.1315</v>
       </c>
     </row>
   </sheetData>
@@ -68473,7 +68557,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D810"/>
+  <dimension ref="A1:D811"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -79811,6 +79895,20 @@
       </c>
       <c r="D810">
         <v>47.9252</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4">
+      <c r="A811" s="1">
+        <v>809</v>
+      </c>
+      <c r="B811" s="2">
+        <v>46130</v>
+      </c>
+      <c r="C811">
+        <v>100</v>
+      </c>
+      <c r="D811">
+        <v>47.6824</v>
       </c>
     </row>
   </sheetData>
@@ -79820,7 +79918,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D810"/>
+  <dimension ref="A1:D811"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -91160,6 +91258,20 @@
         <v>97.2595</v>
       </c>
     </row>
+    <row r="811" spans="1:4">
+      <c r="A811" s="1">
+        <v>809</v>
+      </c>
+      <c r="B811" s="2">
+        <v>46130</v>
+      </c>
+      <c r="C811">
+        <v>1</v>
+      </c>
+      <c r="D811">
+        <v>97.2178</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D811"/>
+  <dimension ref="A1:D812"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11743,6 +11743,20 @@
       </c>
       <c r="D811">
         <v>76.0535</v>
+      </c>
+    </row>
+    <row r="812" spans="1:4">
+      <c r="A812" s="1">
+        <v>810</v>
+      </c>
+      <c r="B812" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C812">
+        <v>1</v>
+      </c>
+      <c r="D812">
+        <v>75.23699999999999</v>
       </c>
     </row>
   </sheetData>
@@ -11752,7 +11766,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D811"/>
+  <dimension ref="A1:D812"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23104,6 +23118,20 @@
       </c>
       <c r="D811">
         <v>89.62560000000001</v>
+      </c>
+    </row>
+    <row r="812" spans="1:4">
+      <c r="A812" s="1">
+        <v>810</v>
+      </c>
+      <c r="B812" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C812">
+        <v>1</v>
+      </c>
+      <c r="D812">
+        <v>88.37690000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23113,7 +23141,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D811"/>
+  <dimension ref="A1:D812"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34465,6 +34493,20 @@
       </c>
       <c r="D811">
         <v>54.5304</v>
+      </c>
+    </row>
+    <row r="812" spans="1:4">
+      <c r="A812" s="1">
+        <v>810</v>
+      </c>
+      <c r="B812" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C812">
+        <v>1</v>
+      </c>
+      <c r="D812">
+        <v>53.7869</v>
       </c>
     </row>
   </sheetData>
@@ -34474,7 +34516,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D811"/>
+  <dimension ref="A1:D812"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45826,6 +45868,20 @@
       </c>
       <c r="D811">
         <v>11.1457</v>
+      </c>
+    </row>
+    <row r="812" spans="1:4">
+      <c r="A812" s="1">
+        <v>810</v>
+      </c>
+      <c r="B812" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C812">
+        <v>1</v>
+      </c>
+      <c r="D812">
+        <v>11.0418</v>
       </c>
     </row>
   </sheetData>
@@ -45835,7 +45891,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D811"/>
+  <dimension ref="A1:D812"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57187,6 +57243,20 @@
       </c>
       <c r="D811">
         <v>102.8395</v>
+      </c>
+    </row>
+    <row r="812" spans="1:4">
+      <c r="A812" s="1">
+        <v>810</v>
+      </c>
+      <c r="B812" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C812">
+        <v>1</v>
+      </c>
+      <c r="D812">
+        <v>102.0966</v>
       </c>
     </row>
   </sheetData>
@@ -57196,7 +57266,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D811"/>
+  <dimension ref="A1:D812"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -68548,6 +68618,20 @@
       </c>
       <c r="D811">
         <v>16.1315</v>
+      </c>
+    </row>
+    <row r="812" spans="1:4">
+      <c r="A812" s="1">
+        <v>810</v>
+      </c>
+      <c r="B812" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C812">
+        <v>100</v>
+      </c>
+      <c r="D812">
+        <v>16.0242</v>
       </c>
     </row>
   </sheetData>
@@ -68557,7 +68641,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D811"/>
+  <dimension ref="A1:D812"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -79909,6 +79993,20 @@
       </c>
       <c r="D811">
         <v>47.6824</v>
+      </c>
+    </row>
+    <row r="812" spans="1:4">
+      <c r="A812" s="1">
+        <v>810</v>
+      </c>
+      <c r="B812" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C812">
+        <v>100</v>
+      </c>
+      <c r="D812">
+        <v>47.3248</v>
       </c>
     </row>
   </sheetData>
@@ -79918,7 +80016,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D811"/>
+  <dimension ref="A1:D812"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -91272,6 +91370,20 @@
         <v>97.2178</v>
       </c>
     </row>
+    <row r="812" spans="1:4">
+      <c r="A812" s="1">
+        <v>810</v>
+      </c>
+      <c r="B812" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C812">
+        <v>1</v>
+      </c>
+      <c r="D812">
+        <v>96.211</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D812"/>
+  <dimension ref="A1:D813"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11757,6 +11757,20 @@
       </c>
       <c r="D812">
         <v>75.23699999999999</v>
+      </c>
+    </row>
+    <row r="813" spans="1:4">
+      <c r="A813" s="1">
+        <v>811</v>
+      </c>
+      <c r="B813" s="2">
+        <v>46134</v>
+      </c>
+      <c r="C813">
+        <v>1</v>
+      </c>
+      <c r="D813">
+        <v>74.58969999999999</v>
       </c>
     </row>
   </sheetData>
@@ -11766,7 +11780,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D812"/>
+  <dimension ref="A1:D813"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23132,6 +23146,20 @@
       </c>
       <c r="D812">
         <v>88.37690000000001</v>
+      </c>
+    </row>
+    <row r="813" spans="1:4">
+      <c r="A813" s="1">
+        <v>811</v>
+      </c>
+      <c r="B813" s="2">
+        <v>46134</v>
+      </c>
+      <c r="C813">
+        <v>1</v>
+      </c>
+      <c r="D813">
+        <v>87.7659</v>
       </c>
     </row>
   </sheetData>
@@ -23141,7 +23169,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D812"/>
+  <dimension ref="A1:D813"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34507,6 +34535,20 @@
       </c>
       <c r="D812">
         <v>53.7869</v>
+      </c>
+    </row>
+    <row r="813" spans="1:4">
+      <c r="A813" s="1">
+        <v>811</v>
+      </c>
+      <c r="B813" s="2">
+        <v>46134</v>
+      </c>
+      <c r="C813">
+        <v>1</v>
+      </c>
+      <c r="D813">
+        <v>53.451</v>
       </c>
     </row>
   </sheetData>
@@ -34516,7 +34558,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D812"/>
+  <dimension ref="A1:D813"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45882,6 +45924,20 @@
       </c>
       <c r="D812">
         <v>11.0418</v>
+      </c>
+    </row>
+    <row r="813" spans="1:4">
+      <c r="A813" s="1">
+        <v>811</v>
+      </c>
+      <c r="B813" s="2">
+        <v>46134</v>
+      </c>
+      <c r="C813">
+        <v>1</v>
+      </c>
+      <c r="D813">
+        <v>10.9451</v>
       </c>
     </row>
   </sheetData>
@@ -45891,7 +45947,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D812"/>
+  <dimension ref="A1:D813"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57257,6 +57313,20 @@
       </c>
       <c r="D812">
         <v>102.0966</v>
+      </c>
+    </row>
+    <row r="813" spans="1:4">
+      <c r="A813" s="1">
+        <v>811</v>
+      </c>
+      <c r="B813" s="2">
+        <v>46134</v>
+      </c>
+      <c r="C813">
+        <v>1</v>
+      </c>
+      <c r="D813">
+        <v>100.8751</v>
       </c>
     </row>
   </sheetData>
@@ -57266,7 +57336,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D812"/>
+  <dimension ref="A1:D813"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -68632,6 +68702,20 @@
       </c>
       <c r="D812">
         <v>16.0242</v>
+      </c>
+    </row>
+    <row r="813" spans="1:4">
+      <c r="A813" s="1">
+        <v>811</v>
+      </c>
+      <c r="B813" s="2">
+        <v>46134</v>
+      </c>
+      <c r="C813">
+        <v>100</v>
+      </c>
+      <c r="D813">
+        <v>15.8874</v>
       </c>
     </row>
   </sheetData>
@@ -68641,7 +68725,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D812"/>
+  <dimension ref="A1:D813"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -80007,6 +80091,20 @@
       </c>
       <c r="D812">
         <v>47.3248</v>
+      </c>
+    </row>
+    <row r="813" spans="1:4">
+      <c r="A813" s="1">
+        <v>811</v>
+      </c>
+      <c r="B813" s="2">
+        <v>46134</v>
+      </c>
+      <c r="C813">
+        <v>100</v>
+      </c>
+      <c r="D813">
+        <v>46.9177</v>
       </c>
     </row>
   </sheetData>
@@ -80016,7 +80114,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D812"/>
+  <dimension ref="A1:D813"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -91384,6 +91482,20 @@
         <v>96.211</v>
       </c>
     </row>
+    <row r="813" spans="1:4">
+      <c r="A813" s="1">
+        <v>811</v>
+      </c>
+      <c r="B813" s="2">
+        <v>46134</v>
+      </c>
+      <c r="C813">
+        <v>1</v>
+      </c>
+      <c r="D813">
+        <v>95.5788</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D813"/>
+  <dimension ref="A1:D814"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11771,6 +11771,20 @@
       </c>
       <c r="D813">
         <v>74.58969999999999</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4">
+      <c r="A814" s="1">
+        <v>812</v>
+      </c>
+      <c r="B814" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C814">
+        <v>1</v>
+      </c>
+      <c r="D814">
+        <v>74.9995</v>
       </c>
     </row>
   </sheetData>
@@ -11780,7 +11794,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D813"/>
+  <dimension ref="A1:D814"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23160,6 +23174,20 @@
       </c>
       <c r="D813">
         <v>87.7659</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4">
+      <c r="A814" s="1">
+        <v>812</v>
+      </c>
+      <c r="B814" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C814">
+        <v>1</v>
+      </c>
+      <c r="D814">
+        <v>87.97329999999999</v>
       </c>
     </row>
   </sheetData>
@@ -23169,7 +23197,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D813"/>
+  <dimension ref="A1:D814"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34549,6 +34577,20 @@
       </c>
       <c r="D813">
         <v>53.451</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4">
+      <c r="A814" s="1">
+        <v>812</v>
+      </c>
+      <c r="B814" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C814">
+        <v>1</v>
+      </c>
+      <c r="D814">
+        <v>53.7746</v>
       </c>
     </row>
   </sheetData>
@@ -34558,7 +34600,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D813"/>
+  <dimension ref="A1:D814"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45938,6 +45980,20 @@
       </c>
       <c r="D813">
         <v>10.9451</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4">
+      <c r="A814" s="1">
+        <v>812</v>
+      </c>
+      <c r="B814" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C814">
+        <v>1</v>
+      </c>
+      <c r="D814">
+        <v>10.9931</v>
       </c>
     </row>
   </sheetData>
@@ -45947,7 +46003,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D813"/>
+  <dimension ref="A1:D814"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57327,6 +57383,20 @@
       </c>
       <c r="D813">
         <v>100.8751</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4">
+      <c r="A814" s="1">
+        <v>812</v>
+      </c>
+      <c r="B814" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C814">
+        <v>1</v>
+      </c>
+      <c r="D814">
+        <v>101.3168</v>
       </c>
     </row>
   </sheetData>
@@ -57336,7 +57406,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D813"/>
+  <dimension ref="A1:D814"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -68716,6 +68786,20 @@
       </c>
       <c r="D813">
         <v>15.8874</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4">
+      <c r="A814" s="1">
+        <v>812</v>
+      </c>
+      <c r="B814" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C814">
+        <v>100</v>
+      </c>
+      <c r="D814">
+        <v>16.1383</v>
       </c>
     </row>
   </sheetData>
@@ -68725,7 +68809,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D813"/>
+  <dimension ref="A1:D814"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -80105,6 +80189,20 @@
       </c>
       <c r="D813">
         <v>46.9177</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4">
+      <c r="A814" s="1">
+        <v>812</v>
+      </c>
+      <c r="B814" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C814">
+        <v>100</v>
+      </c>
+      <c r="D814">
+        <v>47.1102</v>
       </c>
     </row>
   </sheetData>
@@ -80114,7 +80212,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D813"/>
+  <dimension ref="A1:D814"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -91496,6 +91594,20 @@
         <v>95.5788</v>
       </c>
     </row>
+    <row r="814" spans="1:4">
+      <c r="A814" s="1">
+        <v>812</v>
+      </c>
+      <c r="B814" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C814">
+        <v>1</v>
+      </c>
+      <c r="D814">
+        <v>96.1532</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D814"/>
+  <dimension ref="A1:D815"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11785,6 +11785,20 @@
       </c>
       <c r="D814">
         <v>74.9995</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4">
+      <c r="A815" s="1">
+        <v>813</v>
+      </c>
+      <c r="B815" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C815">
+        <v>1</v>
+      </c>
+      <c r="D815">
+        <v>74.8349</v>
       </c>
     </row>
   </sheetData>
@@ -11794,7 +11808,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D814"/>
+  <dimension ref="A1:D815"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23188,6 +23202,20 @@
       </c>
       <c r="D814">
         <v>87.97329999999999</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4">
+      <c r="A815" s="1">
+        <v>813</v>
+      </c>
+      <c r="B815" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C815">
+        <v>1</v>
+      </c>
+      <c r="D815">
+        <v>87.5261</v>
       </c>
     </row>
   </sheetData>
@@ -23197,7 +23225,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D814"/>
+  <dimension ref="A1:D815"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34591,6 +34619,20 @@
       </c>
       <c r="D814">
         <v>53.7746</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4">
+      <c r="A815" s="1">
+        <v>813</v>
+      </c>
+      <c r="B815" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C815">
+        <v>1</v>
+      </c>
+      <c r="D815">
+        <v>53.5444</v>
       </c>
     </row>
   </sheetData>
@@ -34600,7 +34642,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D814"/>
+  <dimension ref="A1:D815"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -45994,6 +46036,20 @@
       </c>
       <c r="D814">
         <v>10.9931</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4">
+      <c r="A815" s="1">
+        <v>813</v>
+      </c>
+      <c r="B815" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C815">
+        <v>1</v>
+      </c>
+      <c r="D815">
+        <v>10.9441</v>
       </c>
     </row>
   </sheetData>
@@ -46003,7 +46059,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D814"/>
+  <dimension ref="A1:D815"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57397,6 +57453,20 @@
       </c>
       <c r="D814">
         <v>101.3168</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4">
+      <c r="A815" s="1">
+        <v>813</v>
+      </c>
+      <c r="B815" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C815">
+        <v>1</v>
+      </c>
+      <c r="D815">
+        <v>101.0196</v>
       </c>
     </row>
   </sheetData>
@@ -57406,7 +57476,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D814"/>
+  <dimension ref="A1:D815"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -68800,6 +68870,20 @@
       </c>
       <c r="D814">
         <v>16.1383</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4">
+      <c r="A815" s="1">
+        <v>813</v>
+      </c>
+      <c r="B815" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C815">
+        <v>100</v>
+      </c>
+      <c r="D815">
+        <v>16.2201</v>
       </c>
     </row>
   </sheetData>
@@ -68809,7 +68893,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D814"/>
+  <dimension ref="A1:D815"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -80203,6 +80287,20 @@
       </c>
       <c r="D814">
         <v>47.1102</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4">
+      <c r="A815" s="1">
+        <v>813</v>
+      </c>
+      <c r="B815" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C815">
+        <v>100</v>
+      </c>
+      <c r="D815">
+        <v>46.9744</v>
       </c>
     </row>
   </sheetData>
@@ -80212,7 +80310,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D814"/>
+  <dimension ref="A1:D815"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -91608,6 +91706,20 @@
         <v>96.1532</v>
       </c>
     </row>
+    <row r="815" spans="1:4">
+      <c r="A815" s="1">
+        <v>813</v>
+      </c>
+      <c r="B815" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C815">
+        <v>1</v>
+      </c>
+      <c r="D815">
+        <v>95.42829999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D815"/>
+  <dimension ref="A1:D816"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11799,6 +11799,20 @@
       </c>
       <c r="D815">
         <v>74.8349</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4">
+      <c r="A816" s="1">
+        <v>814</v>
+      </c>
+      <c r="B816" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C816">
+        <v>1</v>
+      </c>
+      <c r="D816">
+        <v>75.5273</v>
       </c>
     </row>
   </sheetData>
@@ -11808,7 +11822,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D815"/>
+  <dimension ref="A1:D816"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23216,6 +23230,20 @@
       </c>
       <c r="D815">
         <v>87.5261</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4">
+      <c r="A816" s="1">
+        <v>814</v>
+      </c>
+      <c r="B816" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C816">
+        <v>1</v>
+      </c>
+      <c r="D816">
+        <v>88.2826</v>
       </c>
     </row>
   </sheetData>
@@ -23225,7 +23253,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D815"/>
+  <dimension ref="A1:D816"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34633,6 +34661,20 @@
       </c>
       <c r="D815">
         <v>53.5444</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4">
+      <c r="A816" s="1">
+        <v>814</v>
+      </c>
+      <c r="B816" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C816">
+        <v>1</v>
+      </c>
+      <c r="D816">
+        <v>53.8359</v>
       </c>
     </row>
   </sheetData>
@@ -34642,7 +34684,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D815"/>
+  <dimension ref="A1:D816"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46050,6 +46092,20 @@
       </c>
       <c r="D815">
         <v>10.9441</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4">
+      <c r="A816" s="1">
+        <v>814</v>
+      </c>
+      <c r="B816" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C816">
+        <v>1</v>
+      </c>
+      <c r="D816">
+        <v>11.027</v>
       </c>
     </row>
   </sheetData>
@@ -46059,7 +46115,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D815"/>
+  <dimension ref="A1:D816"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57467,6 +57523,20 @@
       </c>
       <c r="D815">
         <v>101.0196</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4">
+      <c r="A816" s="1">
+        <v>814</v>
+      </c>
+      <c r="B816" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C816">
+        <v>1</v>
+      </c>
+      <c r="D816">
+        <v>102.0374</v>
       </c>
     </row>
   </sheetData>
@@ -57476,7 +57546,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D815"/>
+  <dimension ref="A1:D816"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -68884,6 +68954,20 @@
       </c>
       <c r="D815">
         <v>16.2201</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4">
+      <c r="A816" s="1">
+        <v>814</v>
+      </c>
+      <c r="B816" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C816">
+        <v>100</v>
+      </c>
+      <c r="D816">
+        <v>16.3172</v>
       </c>
     </row>
   </sheetData>
@@ -68893,7 +68977,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D815"/>
+  <dimension ref="A1:D816"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -80301,6 +80385,20 @@
       </c>
       <c r="D815">
         <v>46.9744</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4">
+      <c r="A816" s="1">
+        <v>814</v>
+      </c>
+      <c r="B816" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C816">
+        <v>100</v>
+      </c>
+      <c r="D816">
+        <v>47.2636</v>
       </c>
     </row>
   </sheetData>
@@ -80310,7 +80408,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D815"/>
+  <dimension ref="A1:D816"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -91720,6 +91818,20 @@
         <v>95.42829999999999</v>
       </c>
     </row>
+    <row r="816" spans="1:4">
+      <c r="A816" s="1">
+        <v>814</v>
+      </c>
+      <c r="B816" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C816">
+        <v>1</v>
+      </c>
+      <c r="D816">
+        <v>96.05410000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D816"/>
+  <dimension ref="A1:D817"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11813,6 +11813,20 @@
       </c>
       <c r="D816">
         <v>75.5273</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4">
+      <c r="A817" s="1">
+        <v>815</v>
+      </c>
+      <c r="B817" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C817">
+        <v>1</v>
+      </c>
+      <c r="D817">
+        <v>74.8081</v>
       </c>
     </row>
   </sheetData>
@@ -11822,7 +11836,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D816"/>
+  <dimension ref="A1:D817"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23244,6 +23258,20 @@
       </c>
       <c r="D816">
         <v>88.2826</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4">
+      <c r="A817" s="1">
+        <v>815</v>
+      </c>
+      <c r="B817" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C817">
+        <v>1</v>
+      </c>
+      <c r="D817">
+        <v>87.8826</v>
       </c>
     </row>
   </sheetData>
@@ -23253,7 +23281,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D816"/>
+  <dimension ref="A1:D817"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34675,6 +34703,20 @@
       </c>
       <c r="D816">
         <v>53.8359</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4">
+      <c r="A817" s="1">
+        <v>815</v>
+      </c>
+      <c r="B817" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C817">
+        <v>1</v>
+      </c>
+      <c r="D817">
+        <v>53.3232</v>
       </c>
     </row>
   </sheetData>
@@ -34684,7 +34726,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D816"/>
+  <dimension ref="A1:D817"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46106,6 +46148,20 @@
       </c>
       <c r="D816">
         <v>11.027</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4">
+      <c r="A817" s="1">
+        <v>815</v>
+      </c>
+      <c r="B817" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C817">
+        <v>1</v>
+      </c>
+      <c r="D817">
+        <v>10.9513</v>
       </c>
     </row>
   </sheetData>
@@ -46115,7 +46171,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D816"/>
+  <dimension ref="A1:D817"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57537,6 +57593,20 @@
       </c>
       <c r="D816">
         <v>102.0374</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4">
+      <c r="A817" s="1">
+        <v>815</v>
+      </c>
+      <c r="B817" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C817">
+        <v>1</v>
+      </c>
+      <c r="D817">
+        <v>100.9909</v>
       </c>
     </row>
   </sheetData>
@@ -57546,7 +57616,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D816"/>
+  <dimension ref="A1:D817"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -68968,6 +69038,20 @@
       </c>
       <c r="D816">
         <v>16.3172</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4">
+      <c r="A817" s="1">
+        <v>815</v>
+      </c>
+      <c r="B817" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C817">
+        <v>100</v>
+      </c>
+      <c r="D817">
+        <v>16.0926</v>
       </c>
     </row>
   </sheetData>
@@ -68977,7 +69061,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D816"/>
+  <dimension ref="A1:D817"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -80399,6 +80483,20 @@
       </c>
       <c r="D816">
         <v>47.2636</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4">
+      <c r="A817" s="1">
+        <v>815</v>
+      </c>
+      <c r="B817" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C817">
+        <v>100</v>
+      </c>
+      <c r="D817">
+        <v>46.8928</v>
       </c>
     </row>
   </sheetData>
@@ -80408,7 +80506,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D816"/>
+  <dimension ref="A1:D817"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -91832,6 +91930,20 @@
         <v>96.05410000000001</v>
       </c>
     </row>
+    <row r="817" spans="1:4">
+      <c r="A817" s="1">
+        <v>815</v>
+      </c>
+      <c r="B817" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C817">
+        <v>1</v>
+      </c>
+      <c r="D817">
+        <v>95.4794</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D817"/>
+  <dimension ref="A1:D818"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11827,6 +11827,20 @@
       </c>
       <c r="D817">
         <v>74.8081</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4">
+      <c r="A818" s="1">
+        <v>816</v>
+      </c>
+      <c r="B818" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C818">
+        <v>1</v>
+      </c>
+      <c r="D818">
+        <v>74.6947</v>
       </c>
     </row>
   </sheetData>
@@ -11836,7 +11850,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D817"/>
+  <dimension ref="A1:D818"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23272,6 +23286,20 @@
       </c>
       <c r="D817">
         <v>87.8826</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4">
+      <c r="A818" s="1">
+        <v>816</v>
+      </c>
+      <c r="B818" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C818">
+        <v>1</v>
+      </c>
+      <c r="D818">
+        <v>87.5928</v>
       </c>
     </row>
   </sheetData>
@@ -23281,7 +23309,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D817"/>
+  <dimension ref="A1:D818"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34717,6 +34745,20 @@
       </c>
       <c r="D817">
         <v>53.3232</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4">
+      <c r="A818" s="1">
+        <v>816</v>
+      </c>
+      <c r="B818" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C818">
+        <v>1</v>
+      </c>
+      <c r="D818">
+        <v>53.571</v>
       </c>
     </row>
   </sheetData>
@@ -34726,7 +34768,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D817"/>
+  <dimension ref="A1:D818"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46162,6 +46204,20 @@
       </c>
       <c r="D817">
         <v>10.9513</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4">
+      <c r="A818" s="1">
+        <v>816</v>
+      </c>
+      <c r="B818" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C818">
+        <v>1</v>
+      </c>
+      <c r="D818">
+        <v>10.942</v>
       </c>
     </row>
   </sheetData>
@@ -46171,7 +46227,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D817"/>
+  <dimension ref="A1:D818"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57607,6 +57663,20 @@
       </c>
       <c r="D817">
         <v>100.9909</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4">
+      <c r="A818" s="1">
+        <v>816</v>
+      </c>
+      <c r="B818" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C818">
+        <v>1</v>
+      </c>
+      <c r="D818">
+        <v>101.2561</v>
       </c>
     </row>
   </sheetData>
@@ -57616,7 +57686,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D817"/>
+  <dimension ref="A1:D818"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -69052,6 +69122,20 @@
       </c>
       <c r="D817">
         <v>16.0926</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4">
+      <c r="A818" s="1">
+        <v>816</v>
+      </c>
+      <c r="B818" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C818">
+        <v>100</v>
+      </c>
+      <c r="D818">
+        <v>16.2098</v>
       </c>
     </row>
   </sheetData>
@@ -69061,7 +69145,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D817"/>
+  <dimension ref="A1:D818"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -80497,6 +80581,20 @@
       </c>
       <c r="D817">
         <v>46.8928</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4">
+      <c r="A818" s="1">
+        <v>816</v>
+      </c>
+      <c r="B818" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C818">
+        <v>100</v>
+      </c>
+      <c r="D818">
+        <v>46.8335</v>
       </c>
     </row>
   </sheetData>
@@ -80506,7 +80604,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D817"/>
+  <dimension ref="A1:D818"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -91944,6 +92042,20 @@
         <v>95.4794</v>
       </c>
     </row>
+    <row r="818" spans="1:4">
+      <c r="A818" s="1">
+        <v>816</v>
+      </c>
+      <c r="B818" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C818">
+        <v>1</v>
+      </c>
+      <c r="D818">
+        <v>94.67010000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D818"/>
+  <dimension ref="A1:D819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11841,6 +11841,20 @@
       </c>
       <c r="D818">
         <v>74.6947</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4">
+      <c r="A819" s="1">
+        <v>817</v>
+      </c>
+      <c r="B819" s="2">
+        <v>46142</v>
+      </c>
+      <c r="C819">
+        <v>1</v>
+      </c>
+      <c r="D819">
+        <v>74.8806</v>
       </c>
     </row>
   </sheetData>
@@ -11850,7 +11864,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D818"/>
+  <dimension ref="A1:D819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23300,6 +23314,20 @@
       </c>
       <c r="D818">
         <v>87.5928</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4">
+      <c r="A819" s="1">
+        <v>817</v>
+      </c>
+      <c r="B819" s="2">
+        <v>46142</v>
+      </c>
+      <c r="C819">
+        <v>1</v>
+      </c>
+      <c r="D819">
+        <v>87.7771</v>
       </c>
     </row>
   </sheetData>
@@ -23309,7 +23337,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D818"/>
+  <dimension ref="A1:D819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34759,6 +34787,20 @@
       </c>
       <c r="D818">
         <v>53.571</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4">
+      <c r="A819" s="1">
+        <v>817</v>
+      </c>
+      <c r="B819" s="2">
+        <v>46142</v>
+      </c>
+      <c r="C819">
+        <v>1</v>
+      </c>
+      <c r="D819">
+        <v>53.6295</v>
       </c>
     </row>
   </sheetData>
@@ -34768,7 +34810,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D818"/>
+  <dimension ref="A1:D819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46218,6 +46260,20 @@
       </c>
       <c r="D818">
         <v>10.942</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4">
+      <c r="A819" s="1">
+        <v>817</v>
+      </c>
+      <c r="B819" s="2">
+        <v>46142</v>
+      </c>
+      <c r="C819">
+        <v>1</v>
+      </c>
+      <c r="D819">
+        <v>10.9535</v>
       </c>
     </row>
   </sheetData>
@@ -46227,7 +46283,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D818"/>
+  <dimension ref="A1:D819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57677,6 +57733,20 @@
       </c>
       <c r="D818">
         <v>101.2561</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4">
+      <c r="A819" s="1">
+        <v>817</v>
+      </c>
+      <c r="B819" s="2">
+        <v>46142</v>
+      </c>
+      <c r="C819">
+        <v>1</v>
+      </c>
+      <c r="D819">
+        <v>101.0738</v>
       </c>
     </row>
   </sheetData>
@@ -57686,7 +57756,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D818"/>
+  <dimension ref="A1:D819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -69136,6 +69206,20 @@
       </c>
       <c r="D818">
         <v>16.2098</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4">
+      <c r="A819" s="1">
+        <v>817</v>
+      </c>
+      <c r="B819" s="2">
+        <v>46142</v>
+      </c>
+      <c r="C819">
+        <v>100</v>
+      </c>
+      <c r="D819">
+        <v>16.3777</v>
       </c>
     </row>
   </sheetData>
@@ -69145,7 +69229,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D818"/>
+  <dimension ref="A1:D819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -80595,6 +80679,20 @@
       </c>
       <c r="D818">
         <v>46.8335</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4">
+      <c r="A819" s="1">
+        <v>817</v>
+      </c>
+      <c r="B819" s="2">
+        <v>46142</v>
+      </c>
+      <c r="C819">
+        <v>100</v>
+      </c>
+      <c r="D819">
+        <v>46.95</v>
       </c>
     </row>
   </sheetData>
@@ -80604,7 +80702,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D818"/>
+  <dimension ref="A1:D819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -92056,6 +92154,20 @@
         <v>94.67010000000001</v>
       </c>
     </row>
+    <row r="819" spans="1:4">
+      <c r="A819" s="1">
+        <v>817</v>
+      </c>
+      <c r="B819" s="2">
+        <v>46142</v>
+      </c>
+      <c r="C819">
+        <v>1</v>
+      </c>
+      <c r="D819">
+        <v>94.8456</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D819"/>
+  <dimension ref="A1:D820"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11855,6 +11855,20 @@
       </c>
       <c r="D819">
         <v>74.8806</v>
+      </c>
+    </row>
+    <row r="820" spans="1:4">
+      <c r="A820" s="1">
+        <v>818</v>
+      </c>
+      <c r="B820" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C820">
+        <v>1</v>
+      </c>
+      <c r="D820">
+        <v>74.8014</v>
       </c>
     </row>
   </sheetData>
@@ -11864,7 +11878,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D819"/>
+  <dimension ref="A1:D820"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23328,6 +23342,20 @@
       </c>
       <c r="D819">
         <v>87.7771</v>
+      </c>
+    </row>
+    <row r="820" spans="1:4">
+      <c r="A820" s="1">
+        <v>818</v>
+      </c>
+      <c r="B820" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C820">
+        <v>1</v>
+      </c>
+      <c r="D820">
+        <v>88.6429</v>
       </c>
     </row>
   </sheetData>
@@ -23337,7 +23365,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D819"/>
+  <dimension ref="A1:D820"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34801,6 +34829,20 @@
       </c>
       <c r="D819">
         <v>53.6295</v>
+      </c>
+    </row>
+    <row r="820" spans="1:4">
+      <c r="A820" s="1">
+        <v>818</v>
+      </c>
+      <c r="B820" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C820">
+        <v>1</v>
+      </c>
+      <c r="D820">
+        <v>53.2062</v>
       </c>
     </row>
   </sheetData>
@@ -34810,7 +34852,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D819"/>
+  <dimension ref="A1:D820"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46274,6 +46316,20 @@
       </c>
       <c r="D819">
         <v>10.9535</v>
+      </c>
+    </row>
+    <row r="820" spans="1:4">
+      <c r="A820" s="1">
+        <v>818</v>
+      </c>
+      <c r="B820" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C820">
+        <v>1</v>
+      </c>
+      <c r="D820">
+        <v>10.9593</v>
       </c>
     </row>
   </sheetData>
@@ -46283,7 +46339,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D819"/>
+  <dimension ref="A1:D820"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57747,6 +57803,20 @@
       </c>
       <c r="D819">
         <v>101.0738</v>
+      </c>
+    </row>
+    <row r="820" spans="1:4">
+      <c r="A820" s="1">
+        <v>818</v>
+      </c>
+      <c r="B820" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C820">
+        <v>1</v>
+      </c>
+      <c r="D820">
+        <v>100.9894</v>
       </c>
     </row>
   </sheetData>
@@ -57756,7 +57826,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D819"/>
+  <dimension ref="A1:D820"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -69220,6 +69290,20 @@
       </c>
       <c r="D819">
         <v>16.3777</v>
+      </c>
+    </row>
+    <row r="820" spans="1:4">
+      <c r="A820" s="1">
+        <v>818</v>
+      </c>
+      <c r="B820" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C820">
+        <v>100</v>
+      </c>
+      <c r="D820">
+        <v>16.2066</v>
       </c>
     </row>
   </sheetData>
@@ -69229,7 +69313,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D819"/>
+  <dimension ref="A1:D820"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -80693,6 +80777,20 @@
       </c>
       <c r="D819">
         <v>46.95</v>
+      </c>
+    </row>
+    <row r="820" spans="1:4">
+      <c r="A820" s="1">
+        <v>818</v>
+      </c>
+      <c r="B820" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C820">
+        <v>100</v>
+      </c>
+      <c r="D820">
+        <v>46.6721</v>
       </c>
     </row>
   </sheetData>
@@ -80702,7 +80800,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D819"/>
+  <dimension ref="A1:D820"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -92168,6 +92266,20 @@
         <v>94.8456</v>
       </c>
     </row>
+    <row r="820" spans="1:4">
+      <c r="A820" s="1">
+        <v>818</v>
+      </c>
+      <c r="B820" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C820">
+        <v>1</v>
+      </c>
+      <c r="D820">
+        <v>94.7093</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D820"/>
+  <dimension ref="A1:D821"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11869,6 +11869,20 @@
       </c>
       <c r="D820">
         <v>74.8014</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4">
+      <c r="A821" s="1">
+        <v>819</v>
+      </c>
+      <c r="B821" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C821">
+        <v>1</v>
+      </c>
+      <c r="D821">
+        <v>75.4388</v>
       </c>
     </row>
   </sheetData>
@@ -11878,7 +11892,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D820"/>
+  <dimension ref="A1:D821"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23356,6 +23370,20 @@
       </c>
       <c r="D820">
         <v>88.6429</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4">
+      <c r="A821" s="1">
+        <v>819</v>
+      </c>
+      <c r="B821" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C821">
+        <v>1</v>
+      </c>
+      <c r="D821">
+        <v>88.2651</v>
       </c>
     </row>
   </sheetData>
@@ -23365,7 +23393,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D820"/>
+  <dimension ref="A1:D821"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34843,6 +34871,20 @@
       </c>
       <c r="D820">
         <v>53.2062</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4">
+      <c r="A821" s="1">
+        <v>819</v>
+      </c>
+      <c r="B821" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C821">
+        <v>1</v>
+      </c>
+      <c r="D821">
+        <v>54.3763</v>
       </c>
     </row>
   </sheetData>
@@ -34852,7 +34894,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D820"/>
+  <dimension ref="A1:D821"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46330,6 +46372,20 @@
       </c>
       <c r="D820">
         <v>10.9593</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4">
+      <c r="A821" s="1">
+        <v>819</v>
+      </c>
+      <c r="B821" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C821">
+        <v>1</v>
+      </c>
+      <c r="D821">
+        <v>11.0343</v>
       </c>
     </row>
   </sheetData>
@@ -46339,7 +46395,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D820"/>
+  <dimension ref="A1:D821"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57817,6 +57873,20 @@
       </c>
       <c r="D820">
         <v>100.9894</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4">
+      <c r="A821" s="1">
+        <v>819</v>
+      </c>
+      <c r="B821" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C821">
+        <v>1</v>
+      </c>
+      <c r="D821">
+        <v>102.461</v>
       </c>
     </row>
   </sheetData>
@@ -57826,7 +57896,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D820"/>
+  <dimension ref="A1:D821"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -69304,6 +69374,20 @@
       </c>
       <c r="D820">
         <v>16.2066</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4">
+      <c r="A821" s="1">
+        <v>819</v>
+      </c>
+      <c r="B821" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C821">
+        <v>100</v>
+      </c>
+      <c r="D821">
+        <v>16.2966</v>
       </c>
     </row>
   </sheetData>
@@ -69313,7 +69397,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D820"/>
+  <dimension ref="A1:D821"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -80791,6 +80875,20 @@
       </c>
       <c r="D820">
         <v>46.6721</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4">
+      <c r="A821" s="1">
+        <v>819</v>
+      </c>
+      <c r="B821" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C821">
+        <v>100</v>
+      </c>
+      <c r="D821">
+        <v>47.9982</v>
       </c>
     </row>
   </sheetData>
@@ -80800,7 +80898,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D820"/>
+  <dimension ref="A1:D821"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -92280,6 +92378,20 @@
         <v>94.7093</v>
       </c>
     </row>
+    <row r="821" spans="1:4">
+      <c r="A821" s="1">
+        <v>819</v>
+      </c>
+      <c r="B821" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C821">
+        <v>1</v>
+      </c>
+      <c r="D821">
+        <v>96.41970000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D821"/>
+  <dimension ref="A1:D822"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11883,6 +11883,20 @@
       </c>
       <c r="D821">
         <v>75.4388</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4">
+      <c r="A822" s="1">
+        <v>820</v>
+      </c>
+      <c r="B822" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C822">
+        <v>1</v>
+      </c>
+      <c r="D822">
+        <v>75.34480000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11892,7 +11906,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D821"/>
+  <dimension ref="A1:D822"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23384,6 +23398,20 @@
       </c>
       <c r="D821">
         <v>88.2651</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4">
+      <c r="A822" s="1">
+        <v>820</v>
+      </c>
+      <c r="B822" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C822">
+        <v>1</v>
+      </c>
+      <c r="D822">
+        <v>88.3463</v>
       </c>
     </row>
   </sheetData>
@@ -23393,7 +23421,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D821"/>
+  <dimension ref="A1:D822"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34885,6 +34913,20 @@
       </c>
       <c r="D821">
         <v>54.3763</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4">
+      <c r="A822" s="1">
+        <v>820</v>
+      </c>
+      <c r="B822" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C822">
+        <v>1</v>
+      </c>
+      <c r="D822">
+        <v>53.8037</v>
       </c>
     </row>
   </sheetData>
@@ -34894,7 +34936,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D821"/>
+  <dimension ref="A1:D822"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46386,6 +46428,20 @@
       </c>
       <c r="D821">
         <v>11.0343</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4">
+      <c r="A822" s="1">
+        <v>820</v>
+      </c>
+      <c r="B822" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C822">
+        <v>1</v>
+      </c>
+      <c r="D822">
+        <v>11.0247</v>
       </c>
     </row>
   </sheetData>
@@ -46395,7 +46451,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D821"/>
+  <dimension ref="A1:D822"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57887,6 +57943,20 @@
       </c>
       <c r="D821">
         <v>102.461</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4">
+      <c r="A822" s="1">
+        <v>820</v>
+      </c>
+      <c r="B822" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C822">
+        <v>1</v>
+      </c>
+      <c r="D822">
+        <v>102.6498</v>
       </c>
     </row>
   </sheetData>
@@ -57896,7 +57966,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D821"/>
+  <dimension ref="A1:D822"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -69388,6 +69458,20 @@
       </c>
       <c r="D821">
         <v>16.2966</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4">
+      <c r="A822" s="1">
+        <v>820</v>
+      </c>
+      <c r="B822" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C822">
+        <v>100</v>
+      </c>
+      <c r="D822">
+        <v>16.2196</v>
       </c>
     </row>
   </sheetData>
@@ -69397,7 +69481,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D821"/>
+  <dimension ref="A1:D822"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -80889,6 +80973,20 @@
       </c>
       <c r="D821">
         <v>47.9982</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4">
+      <c r="A822" s="1">
+        <v>820</v>
+      </c>
+      <c r="B822" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C822">
+        <v>100</v>
+      </c>
+      <c r="D822">
+        <v>47.9384</v>
       </c>
     </row>
   </sheetData>
@@ -80898,7 +80996,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D821"/>
+  <dimension ref="A1:D822"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -92392,6 +92490,20 @@
         <v>96.41970000000001</v>
       </c>
     </row>
+    <row r="822" spans="1:4">
+      <c r="A822" s="1">
+        <v>820</v>
+      </c>
+      <c r="B822" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C822">
+        <v>1</v>
+      </c>
+      <c r="D822">
+        <v>96.1767</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D822"/>
+  <dimension ref="A1:D823"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11897,6 +11897,20 @@
       </c>
       <c r="D822">
         <v>75.34480000000001</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4">
+      <c r="A823" s="1">
+        <v>821</v>
+      </c>
+      <c r="B823" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C823">
+        <v>1</v>
+      </c>
+      <c r="D823">
+        <v>75.2246</v>
       </c>
     </row>
   </sheetData>
@@ -11906,7 +11920,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D822"/>
+  <dimension ref="A1:D823"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23412,6 +23426,20 @@
       </c>
       <c r="D822">
         <v>88.3463</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4">
+      <c r="A823" s="1">
+        <v>821</v>
+      </c>
+      <c r="B823" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C823">
+        <v>1</v>
+      </c>
+      <c r="D823">
+        <v>88.06</v>
       </c>
     </row>
   </sheetData>
@@ -23421,7 +23449,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D822"/>
+  <dimension ref="A1:D823"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34927,6 +34955,20 @@
       </c>
       <c r="D822">
         <v>53.8037</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4">
+      <c r="A823" s="1">
+        <v>821</v>
+      </c>
+      <c r="B823" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C823">
+        <v>1</v>
+      </c>
+      <c r="D823">
+        <v>54.5228</v>
       </c>
     </row>
   </sheetData>
@@ -34936,7 +34978,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D822"/>
+  <dimension ref="A1:D823"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46442,6 +46484,20 @@
       </c>
       <c r="D822">
         <v>11.0247</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4">
+      <c r="A823" s="1">
+        <v>821</v>
+      </c>
+      <c r="B823" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C823">
+        <v>1</v>
+      </c>
+      <c r="D823">
+        <v>10.9949</v>
       </c>
     </row>
   </sheetData>
@@ -46451,7 +46507,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D822"/>
+  <dimension ref="A1:D823"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -57957,6 +58013,20 @@
       </c>
       <c r="D822">
         <v>102.6498</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4">
+      <c r="A823" s="1">
+        <v>821</v>
+      </c>
+      <c r="B823" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C823">
+        <v>1</v>
+      </c>
+      <c r="D823">
+        <v>102.0422</v>
       </c>
     </row>
   </sheetData>
@@ -57966,7 +58036,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D822"/>
+  <dimension ref="A1:D823"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -69472,6 +69542,20 @@
       </c>
       <c r="D822">
         <v>16.2196</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4">
+      <c r="A823" s="1">
+        <v>821</v>
+      </c>
+      <c r="B823" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C823">
+        <v>100</v>
+      </c>
+      <c r="D823">
+        <v>16.177</v>
       </c>
     </row>
   </sheetData>
@@ -69481,7 +69565,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D822"/>
+  <dimension ref="A1:D823"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -80987,6 +81071,20 @@
       </c>
       <c r="D822">
         <v>47.9384</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4">
+      <c r="A823" s="1">
+        <v>821</v>
+      </c>
+      <c r="B823" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C823">
+        <v>100</v>
+      </c>
+      <c r="D823">
+        <v>47.8619</v>
       </c>
     </row>
   </sheetData>
@@ -80996,7 +81094,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D822"/>
+  <dimension ref="A1:D823"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -92504,6 +92602,20 @@
         <v>96.1767</v>
       </c>
     </row>
+    <row r="823" spans="1:4">
+      <c r="A823" s="1">
+        <v>821</v>
+      </c>
+      <c r="B823" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C823">
+        <v>1</v>
+      </c>
+      <c r="D823">
+        <v>96.6152</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D823"/>
+  <dimension ref="A1:D824"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11911,6 +11911,20 @@
       </c>
       <c r="D823">
         <v>75.2246</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4">
+      <c r="A824" s="1">
+        <v>822</v>
+      </c>
+      <c r="B824" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C824">
+        <v>1</v>
+      </c>
+      <c r="D824">
+        <v>74.62090000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11920,7 +11934,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D823"/>
+  <dimension ref="A1:D824"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23440,6 +23454,20 @@
       </c>
       <c r="D823">
         <v>88.06</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4">
+      <c r="A824" s="1">
+        <v>822</v>
+      </c>
+      <c r="B824" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C824">
+        <v>1</v>
+      </c>
+      <c r="D824">
+        <v>87.8897</v>
       </c>
     </row>
   </sheetData>
@@ -23449,7 +23477,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D823"/>
+  <dimension ref="A1:D824"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34969,6 +34997,20 @@
       </c>
       <c r="D823">
         <v>54.5228</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4">
+      <c r="A824" s="1">
+        <v>822</v>
+      </c>
+      <c r="B824" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C824">
+        <v>1</v>
+      </c>
+      <c r="D824">
+        <v>54.0778</v>
       </c>
     </row>
   </sheetData>
@@ -34978,7 +35020,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D823"/>
+  <dimension ref="A1:D824"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46498,6 +46540,20 @@
       </c>
       <c r="D823">
         <v>10.9949</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4">
+      <c r="A824" s="1">
+        <v>822</v>
+      </c>
+      <c r="B824" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C824">
+        <v>1</v>
+      </c>
+      <c r="D824">
+        <v>10.9709</v>
       </c>
     </row>
   </sheetData>
@@ -46507,7 +46563,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D823"/>
+  <dimension ref="A1:D824"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58027,6 +58083,20 @@
       </c>
       <c r="D823">
         <v>102.0422</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4">
+      <c r="A824" s="1">
+        <v>822</v>
+      </c>
+      <c r="B824" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C824">
+        <v>1</v>
+      </c>
+      <c r="D824">
+        <v>101.5068</v>
       </c>
     </row>
   </sheetData>
@@ -58036,7 +58106,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D823"/>
+  <dimension ref="A1:D824"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -69556,6 +69626,20 @@
       </c>
       <c r="D823">
         <v>16.177</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4">
+      <c r="A824" s="1">
+        <v>822</v>
+      </c>
+      <c r="B824" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C824">
+        <v>100</v>
+      </c>
+      <c r="D824">
+        <v>16.1026</v>
       </c>
     </row>
   </sheetData>
@@ -69565,7 +69649,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D823"/>
+  <dimension ref="A1:D824"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -81085,6 +81169,20 @@
       </c>
       <c r="D823">
         <v>47.8619</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4">
+      <c r="A824" s="1">
+        <v>822</v>
+      </c>
+      <c r="B824" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C824">
+        <v>100</v>
+      </c>
+      <c r="D824">
+        <v>47.7268</v>
       </c>
     </row>
   </sheetData>
@@ -81094,7 +81192,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D823"/>
+  <dimension ref="A1:D824"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -92616,6 +92714,20 @@
         <v>96.6152</v>
       </c>
     </row>
+    <row r="824" spans="1:4">
+      <c r="A824" s="1">
+        <v>822</v>
+      </c>
+      <c r="B824" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C824">
+        <v>1</v>
+      </c>
+      <c r="D824">
+        <v>95.9508</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D824"/>
+  <dimension ref="A1:D825"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11925,6 +11925,20 @@
       </c>
       <c r="D824">
         <v>74.62090000000001</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4">
+      <c r="A825" s="1">
+        <v>823</v>
+      </c>
+      <c r="B825" s="2">
+        <v>46151</v>
+      </c>
+      <c r="C825">
+        <v>1</v>
+      </c>
+      <c r="D825">
+        <v>74.2963</v>
       </c>
     </row>
   </sheetData>
@@ -11934,7 +11948,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D824"/>
+  <dimension ref="A1:D825"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23468,6 +23482,20 @@
       </c>
       <c r="D824">
         <v>87.8897</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4">
+      <c r="A825" s="1">
+        <v>823</v>
+      </c>
+      <c r="B825" s="2">
+        <v>46151</v>
+      </c>
+      <c r="C825">
+        <v>1</v>
+      </c>
+      <c r="D825">
+        <v>88.54900000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23477,7 +23505,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D824"/>
+  <dimension ref="A1:D825"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35011,6 +35039,20 @@
       </c>
       <c r="D824">
         <v>54.0778</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4">
+      <c r="A825" s="1">
+        <v>823</v>
+      </c>
+      <c r="B825" s="2">
+        <v>46151</v>
+      </c>
+      <c r="C825">
+        <v>1</v>
+      </c>
+      <c r="D825">
+        <v>53.6791</v>
       </c>
     </row>
   </sheetData>
@@ -35020,7 +35062,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D824"/>
+  <dimension ref="A1:D825"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46554,6 +46596,20 @@
       </c>
       <c r="D824">
         <v>10.9709</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4">
+      <c r="A825" s="1">
+        <v>823</v>
+      </c>
+      <c r="B825" s="2">
+        <v>46151</v>
+      </c>
+      <c r="C825">
+        <v>1</v>
+      </c>
+      <c r="D825">
+        <v>10.9306</v>
       </c>
     </row>
   </sheetData>
@@ -46563,7 +46619,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D824"/>
+  <dimension ref="A1:D825"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58097,6 +58153,20 @@
       </c>
       <c r="D824">
         <v>101.5068</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4">
+      <c r="A825" s="1">
+        <v>823</v>
+      </c>
+      <c r="B825" s="2">
+        <v>46151</v>
+      </c>
+      <c r="C825">
+        <v>1</v>
+      </c>
+      <c r="D825">
+        <v>101.2733</v>
       </c>
     </row>
   </sheetData>
@@ -58106,7 +58176,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D824"/>
+  <dimension ref="A1:D825"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -69640,6 +69710,20 @@
       </c>
       <c r="D824">
         <v>16.1026</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4">
+      <c r="A825" s="1">
+        <v>823</v>
+      </c>
+      <c r="B825" s="2">
+        <v>46151</v>
+      </c>
+      <c r="C825">
+        <v>100</v>
+      </c>
+      <c r="D825">
+        <v>16.0325</v>
       </c>
     </row>
   </sheetData>
@@ -69649,7 +69733,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D824"/>
+  <dimension ref="A1:D825"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -81183,6 +81267,20 @@
       </c>
       <c r="D824">
         <v>47.7268</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4">
+      <c r="A825" s="1">
+        <v>823</v>
+      </c>
+      <c r="B825" s="2">
+        <v>46151</v>
+      </c>
+      <c r="C825">
+        <v>100</v>
+      </c>
+      <c r="D825">
+        <v>47.3255</v>
       </c>
     </row>
   </sheetData>
@@ -81192,7 +81290,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D824"/>
+  <dimension ref="A1:D825"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -92728,6 +92826,20 @@
         <v>95.9508</v>
       </c>
     </row>
+    <row r="825" spans="1:4">
+      <c r="A825" s="1">
+        <v>823</v>
+      </c>
+      <c r="B825" s="2">
+        <v>46151</v>
+      </c>
+      <c r="C825">
+        <v>1</v>
+      </c>
+      <c r="D825">
+        <v>95.4597</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D825"/>
+  <dimension ref="A1:D826"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11939,6 +11939,20 @@
       </c>
       <c r="D825">
         <v>74.2963</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4">
+      <c r="A826" s="1">
+        <v>824</v>
+      </c>
+      <c r="B826" s="2">
+        <v>46155</v>
+      </c>
+      <c r="C826">
+        <v>1</v>
+      </c>
+      <c r="D826">
+        <v>73.7878</v>
       </c>
     </row>
   </sheetData>
@@ -11948,7 +11962,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D825"/>
+  <dimension ref="A1:D826"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23496,6 +23510,20 @@
       </c>
       <c r="D825">
         <v>88.54900000000001</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4">
+      <c r="A826" s="1">
+        <v>824</v>
+      </c>
+      <c r="B826" s="2">
+        <v>46155</v>
+      </c>
+      <c r="C826">
+        <v>1</v>
+      </c>
+      <c r="D826">
+        <v>87.37909999999999</v>
       </c>
     </row>
   </sheetData>
@@ -23505,7 +23533,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D825"/>
+  <dimension ref="A1:D826"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35053,6 +35081,20 @@
       </c>
       <c r="D825">
         <v>53.6791</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4">
+      <c r="A826" s="1">
+        <v>824</v>
+      </c>
+      <c r="B826" s="2">
+        <v>46155</v>
+      </c>
+      <c r="C826">
+        <v>1</v>
+      </c>
+      <c r="D826">
+        <v>53.356</v>
       </c>
     </row>
   </sheetData>
@@ -35062,7 +35104,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D825"/>
+  <dimension ref="A1:D826"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46610,6 +46652,20 @@
       </c>
       <c r="D825">
         <v>10.9306</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4">
+      <c r="A826" s="1">
+        <v>824</v>
+      </c>
+      <c r="B826" s="2">
+        <v>46155</v>
+      </c>
+      <c r="C826">
+        <v>1</v>
+      </c>
+      <c r="D826">
+        <v>10.8522</v>
       </c>
     </row>
   </sheetData>
@@ -46619,7 +46675,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D825"/>
+  <dimension ref="A1:D826"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58167,6 +58223,20 @@
       </c>
       <c r="D825">
         <v>101.2733</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4">
+      <c r="A826" s="1">
+        <v>824</v>
+      </c>
+      <c r="B826" s="2">
+        <v>46155</v>
+      </c>
+      <c r="C826">
+        <v>1</v>
+      </c>
+      <c r="D826">
+        <v>100.6392</v>
       </c>
     </row>
   </sheetData>
@@ -58176,7 +58246,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D825"/>
+  <dimension ref="A1:D826"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -69724,6 +69794,20 @@
       </c>
       <c r="D825">
         <v>16.0325</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4">
+      <c r="A826" s="1">
+        <v>824</v>
+      </c>
+      <c r="B826" s="2">
+        <v>46155</v>
+      </c>
+      <c r="C826">
+        <v>100</v>
+      </c>
+      <c r="D826">
+        <v>15.997</v>
       </c>
     </row>
   </sheetData>
@@ -69733,7 +69817,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D825"/>
+  <dimension ref="A1:D826"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -81281,6 +81365,20 @@
       </c>
       <c r="D825">
         <v>47.3255</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4">
+      <c r="A826" s="1">
+        <v>824</v>
+      </c>
+      <c r="B826" s="2">
+        <v>46155</v>
+      </c>
+      <c r="C826">
+        <v>100</v>
+      </c>
+      <c r="D826">
+        <v>46.7929</v>
       </c>
     </row>
   </sheetData>
@@ -81290,7 +81388,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D825"/>
+  <dimension ref="A1:D826"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -92840,6 +92938,20 @@
         <v>95.4597</v>
       </c>
     </row>
+    <row r="826" spans="1:4">
+      <c r="A826" s="1">
+        <v>824</v>
+      </c>
+      <c r="B826" s="2">
+        <v>46155</v>
+      </c>
+      <c r="C826">
+        <v>1</v>
+      </c>
+      <c r="D826">
+        <v>94.527</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D826"/>
+  <dimension ref="A1:D827"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11953,6 +11953,20 @@
       </c>
       <c r="D826">
         <v>73.7878</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4">
+      <c r="A827" s="1">
+        <v>825</v>
+      </c>
+      <c r="B827" s="2">
+        <v>46156</v>
+      </c>
+      <c r="C827">
+        <v>1</v>
+      </c>
+      <c r="D827">
+        <v>73.342</v>
       </c>
     </row>
   </sheetData>
@@ -11962,7 +11976,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D826"/>
+  <dimension ref="A1:D827"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23524,6 +23538,20 @@
       </c>
       <c r="D826">
         <v>87.37909999999999</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4">
+      <c r="A827" s="1">
+        <v>825</v>
+      </c>
+      <c r="B827" s="2">
+        <v>46156</v>
+      </c>
+      <c r="C827">
+        <v>1</v>
+      </c>
+      <c r="D827">
+        <v>85.90170000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23533,7 +23561,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D826"/>
+  <dimension ref="A1:D827"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35095,6 +35123,20 @@
       </c>
       <c r="D826">
         <v>53.356</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4">
+      <c r="A827" s="1">
+        <v>825</v>
+      </c>
+      <c r="B827" s="2">
+        <v>46156</v>
+      </c>
+      <c r="C827">
+        <v>1</v>
+      </c>
+      <c r="D827">
+        <v>53.0996</v>
       </c>
     </row>
   </sheetData>
@@ -35104,7 +35146,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D826"/>
+  <dimension ref="A1:D827"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46666,6 +46708,20 @@
       </c>
       <c r="D826">
         <v>10.8522</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4">
+      <c r="A827" s="1">
+        <v>825</v>
+      </c>
+      <c r="B827" s="2">
+        <v>46156</v>
+      </c>
+      <c r="C827">
+        <v>1</v>
+      </c>
+      <c r="D827">
+        <v>10.7933</v>
       </c>
     </row>
   </sheetData>
@@ -46675,7 +46731,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D826"/>
+  <dimension ref="A1:D827"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58237,6 +58293,20 @@
       </c>
       <c r="D826">
         <v>100.6392</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4">
+      <c r="A827" s="1">
+        <v>825</v>
+      </c>
+      <c r="B827" s="2">
+        <v>46156</v>
+      </c>
+      <c r="C827">
+        <v>1</v>
+      </c>
+      <c r="D827">
+        <v>99.1951</v>
       </c>
     </row>
   </sheetData>
@@ -58246,7 +58316,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D826"/>
+  <dimension ref="A1:D827"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -69808,6 +69878,20 @@
       </c>
       <c r="D826">
         <v>15.997</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4">
+      <c r="A827" s="1">
+        <v>825</v>
+      </c>
+      <c r="B827" s="2">
+        <v>46156</v>
+      </c>
+      <c r="C827">
+        <v>100</v>
+      </c>
+      <c r="D827">
+        <v>15.8095</v>
       </c>
     </row>
   </sheetData>
@@ -69817,7 +69901,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D826"/>
+  <dimension ref="A1:D827"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -81379,6 +81463,20 @@
       </c>
       <c r="D826">
         <v>46.7929</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4">
+      <c r="A827" s="1">
+        <v>825</v>
+      </c>
+      <c r="B827" s="2">
+        <v>46156</v>
+      </c>
+      <c r="C827">
+        <v>100</v>
+      </c>
+      <c r="D827">
+        <v>46.4867</v>
       </c>
     </row>
   </sheetData>
@@ -81388,7 +81486,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D826"/>
+  <dimension ref="A1:D827"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -92952,6 +93050,20 @@
         <v>94.527</v>
       </c>
     </row>
+    <row r="827" spans="1:4">
+      <c r="A827" s="1">
+        <v>825</v>
+      </c>
+      <c r="B827" s="2">
+        <v>46156</v>
+      </c>
+      <c r="C827">
+        <v>1</v>
+      </c>
+      <c r="D827">
+        <v>93.7637</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D827"/>
+  <dimension ref="A1:D828"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11967,6 +11967,20 @@
       </c>
       <c r="D827">
         <v>73.342</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4">
+      <c r="A828" s="1">
+        <v>826</v>
+      </c>
+      <c r="B828" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C828">
+        <v>1</v>
+      </c>
+      <c r="D828">
+        <v>73.13849999999999</v>
       </c>
     </row>
   </sheetData>
@@ -11976,7 +11990,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D827"/>
+  <dimension ref="A1:D828"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23552,6 +23566,20 @@
       </c>
       <c r="D827">
         <v>85.90170000000001</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4">
+      <c r="A828" s="1">
+        <v>826</v>
+      </c>
+      <c r="B828" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C828">
+        <v>1</v>
+      </c>
+      <c r="D828">
+        <v>86.2899</v>
       </c>
     </row>
   </sheetData>
@@ -23561,7 +23589,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D827"/>
+  <dimension ref="A1:D828"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35137,6 +35165,20 @@
       </c>
       <c r="D827">
         <v>53.0996</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4">
+      <c r="A828" s="1">
+        <v>826</v>
+      </c>
+      <c r="B828" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C828">
+        <v>1</v>
+      </c>
+      <c r="D828">
+        <v>53.0839</v>
       </c>
     </row>
   </sheetData>
@@ -35146,7 +35188,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D827"/>
+  <dimension ref="A1:D828"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46722,6 +46764,20 @@
       </c>
       <c r="D827">
         <v>10.7933</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4">
+      <c r="A828" s="1">
+        <v>826</v>
+      </c>
+      <c r="B828" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C828">
+        <v>1</v>
+      </c>
+      <c r="D828">
+        <v>10.7855</v>
       </c>
     </row>
   </sheetData>
@@ -46731,7 +46787,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D827"/>
+  <dimension ref="A1:D828"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58307,6 +58363,20 @@
       </c>
       <c r="D827">
         <v>99.1951</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4">
+      <c r="A828" s="1">
+        <v>826</v>
+      </c>
+      <c r="B828" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C828">
+        <v>1</v>
+      </c>
+      <c r="D828">
+        <v>98.8394</v>
       </c>
     </row>
   </sheetData>
@@ -58316,7 +58386,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D827"/>
+  <dimension ref="A1:D828"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -69892,6 +69962,20 @@
       </c>
       <c r="D827">
         <v>15.8095</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4">
+      <c r="A828" s="1">
+        <v>826</v>
+      </c>
+      <c r="B828" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C828">
+        <v>100</v>
+      </c>
+      <c r="D828">
+        <v>15.6402</v>
       </c>
     </row>
   </sheetData>
@@ -69901,7 +69985,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D827"/>
+  <dimension ref="A1:D828"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -81477,6 +81561,20 @@
       </c>
       <c r="D827">
         <v>46.4867</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4">
+      <c r="A828" s="1">
+        <v>826</v>
+      </c>
+      <c r="B828" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C828">
+        <v>100</v>
+      </c>
+      <c r="D828">
+        <v>46.3342</v>
       </c>
     </row>
   </sheetData>
@@ -81486,7 +81584,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D827"/>
+  <dimension ref="A1:D828"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -93064,6 +93162,20 @@
         <v>93.7637</v>
       </c>
     </row>
+    <row r="828" spans="1:4">
+      <c r="A828" s="1">
+        <v>826</v>
+      </c>
+      <c r="B828" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C828">
+        <v>1</v>
+      </c>
+      <c r="D828">
+        <v>93.50360000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D828"/>
+  <dimension ref="A1:D829"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11981,6 +11981,20 @@
       </c>
       <c r="D828">
         <v>73.13849999999999</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4">
+      <c r="A829" s="1">
+        <v>827</v>
+      </c>
+      <c r="B829" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C829">
+        <v>1</v>
+      </c>
+      <c r="D829">
+        <v>73.1275</v>
       </c>
     </row>
   </sheetData>
@@ -11990,7 +12004,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D828"/>
+  <dimension ref="A1:D829"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23580,6 +23594,20 @@
       </c>
       <c r="D828">
         <v>86.2899</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4">
+      <c r="A829" s="1">
+        <v>827</v>
+      </c>
+      <c r="B829" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C829">
+        <v>1</v>
+      </c>
+      <c r="D829">
+        <v>85.18300000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23589,7 +23617,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D828"/>
+  <dimension ref="A1:D829"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35179,6 +35207,20 @@
       </c>
       <c r="D828">
         <v>53.0839</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4">
+      <c r="A829" s="1">
+        <v>827</v>
+      </c>
+      <c r="B829" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C829">
+        <v>1</v>
+      </c>
+      <c r="D829">
+        <v>52.3593</v>
       </c>
     </row>
   </sheetData>
@@ -35188,7 +35230,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D828"/>
+  <dimension ref="A1:D829"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46778,6 +46820,20 @@
       </c>
       <c r="D828">
         <v>10.7855</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4">
+      <c r="A829" s="1">
+        <v>827</v>
+      </c>
+      <c r="B829" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C829">
+        <v>1</v>
+      </c>
+      <c r="D829">
+        <v>10.7318</v>
       </c>
     </row>
   </sheetData>
@@ -46787,7 +46843,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D828"/>
+  <dimension ref="A1:D829"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58377,6 +58433,20 @@
       </c>
       <c r="D828">
         <v>98.8394</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4">
+      <c r="A829" s="1">
+        <v>827</v>
+      </c>
+      <c r="B829" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C829">
+        <v>1</v>
+      </c>
+      <c r="D829">
+        <v>98.61239999999999</v>
       </c>
     </row>
   </sheetData>
@@ -58386,7 +58456,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D828"/>
+  <dimension ref="A1:D829"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -69976,6 +70046,20 @@
       </c>
       <c r="D828">
         <v>15.6402</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4">
+      <c r="A829" s="1">
+        <v>827</v>
+      </c>
+      <c r="B829" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C829">
+        <v>100</v>
+      </c>
+      <c r="D829">
+        <v>15.4264</v>
       </c>
     </row>
   </sheetData>
@@ -69985,7 +70069,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D828"/>
+  <dimension ref="A1:D829"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -81575,6 +81659,20 @@
       </c>
       <c r="D828">
         <v>46.3342</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4">
+      <c r="A829" s="1">
+        <v>827</v>
+      </c>
+      <c r="B829" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C829">
+        <v>100</v>
+      </c>
+      <c r="D829">
+        <v>46.1372</v>
       </c>
     </row>
   </sheetData>
@@ -81584,7 +81682,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D828"/>
+  <dimension ref="A1:D829"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -93176,6 +93274,20 @@
         <v>93.50360000000001</v>
       </c>
     </row>
+    <row r="829" spans="1:4">
+      <c r="A829" s="1">
+        <v>827</v>
+      </c>
+      <c r="B829" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C829">
+        <v>1</v>
+      </c>
+      <c r="D829">
+        <v>93.0612</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D829"/>
+  <dimension ref="A1:D830"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11995,6 +11995,20 @@
       </c>
       <c r="D829">
         <v>73.1275</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4">
+      <c r="A830" s="1">
+        <v>828</v>
+      </c>
+      <c r="B830" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C830">
+        <v>1</v>
+      </c>
+      <c r="D830">
+        <v>72.3497</v>
       </c>
     </row>
   </sheetData>
@@ -12004,7 +12018,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D829"/>
+  <dimension ref="A1:D830"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23608,6 +23622,20 @@
       </c>
       <c r="D829">
         <v>85.18300000000001</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4">
+      <c r="A830" s="1">
+        <v>828</v>
+      </c>
+      <c r="B830" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C830">
+        <v>1</v>
+      </c>
+      <c r="D830">
+        <v>84.0742</v>
       </c>
     </row>
   </sheetData>
@@ -23617,7 +23645,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D829"/>
+  <dimension ref="A1:D830"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35221,6 +35249,20 @@
       </c>
       <c r="D829">
         <v>52.3593</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4">
+      <c r="A830" s="1">
+        <v>828</v>
+      </c>
+      <c r="B830" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C830">
+        <v>1</v>
+      </c>
+      <c r="D830">
+        <v>51.5998</v>
       </c>
     </row>
   </sheetData>
@@ -35230,7 +35272,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D829"/>
+  <dimension ref="A1:D830"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46834,6 +46876,20 @@
       </c>
       <c r="D829">
         <v>10.7318</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4">
+      <c r="A830" s="1">
+        <v>828</v>
+      </c>
+      <c r="B830" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C830">
+        <v>1</v>
+      </c>
+      <c r="D830">
+        <v>10.6279</v>
       </c>
     </row>
   </sheetData>
@@ -46843,7 +46899,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D829"/>
+  <dimension ref="A1:D830"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58447,6 +58503,20 @@
       </c>
       <c r="D829">
         <v>98.61239999999999</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4">
+      <c r="A830" s="1">
+        <v>828</v>
+      </c>
+      <c r="B830" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C830">
+        <v>1</v>
+      </c>
+      <c r="D830">
+        <v>96.55070000000001</v>
       </c>
     </row>
   </sheetData>
@@ -58456,7 +58526,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D829"/>
+  <dimension ref="A1:D830"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -70060,6 +70130,20 @@
       </c>
       <c r="D829">
         <v>15.4264</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4">
+      <c r="A830" s="1">
+        <v>828</v>
+      </c>
+      <c r="B830" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C830">
+        <v>100</v>
+      </c>
+      <c r="D830">
+        <v>15.388</v>
       </c>
     </row>
   </sheetData>
@@ -70069,7 +70153,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D829"/>
+  <dimension ref="A1:D830"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -81673,6 +81757,20 @@
       </c>
       <c r="D829">
         <v>46.1372</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4">
+      <c r="A830" s="1">
+        <v>828</v>
+      </c>
+      <c r="B830" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C830">
+        <v>100</v>
+      </c>
+      <c r="D830">
+        <v>45.5173</v>
       </c>
     </row>
   </sheetData>
@@ -81682,7 +81780,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D829"/>
+  <dimension ref="A1:D830"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -93288,6 +93386,20 @@
         <v>93.0612</v>
       </c>
     </row>
+    <row r="830" spans="1:4">
+      <c r="A830" s="1">
+        <v>828</v>
+      </c>
+      <c r="B830" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C830">
+        <v>1</v>
+      </c>
+      <c r="D830">
+        <v>92.1887</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D830"/>
+  <dimension ref="A1:D831"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12009,6 +12009,20 @@
       </c>
       <c r="D830">
         <v>72.3497</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4">
+      <c r="A831" s="1">
+        <v>829</v>
+      </c>
+      <c r="B831" s="2">
+        <v>46162</v>
+      </c>
+      <c r="C831">
+        <v>1</v>
+      </c>
+      <c r="D831">
+        <v>71.29259999999999</v>
       </c>
     </row>
   </sheetData>
@@ -12018,7 +12032,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D830"/>
+  <dimension ref="A1:D831"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23636,6 +23650,20 @@
       </c>
       <c r="D830">
         <v>84.0742</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4">
+      <c r="A831" s="1">
+        <v>829</v>
+      </c>
+      <c r="B831" s="2">
+        <v>46162</v>
+      </c>
+      <c r="C831">
+        <v>1</v>
+      </c>
+      <c r="D831">
+        <v>82.7871</v>
       </c>
     </row>
   </sheetData>
@@ -23645,7 +23673,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D830"/>
+  <dimension ref="A1:D831"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35263,6 +35291,20 @@
       </c>
       <c r="D830">
         <v>51.5998</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4">
+      <c r="A831" s="1">
+        <v>829</v>
+      </c>
+      <c r="B831" s="2">
+        <v>46162</v>
+      </c>
+      <c r="C831">
+        <v>1</v>
+      </c>
+      <c r="D831">
+        <v>50.8459</v>
       </c>
     </row>
   </sheetData>
@@ -35272,7 +35314,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D830"/>
+  <dimension ref="A1:D831"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46890,6 +46932,20 @@
       </c>
       <c r="D830">
         <v>10.6279</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4">
+      <c r="A831" s="1">
+        <v>829</v>
+      </c>
+      <c r="B831" s="2">
+        <v>46162</v>
+      </c>
+      <c r="C831">
+        <v>1</v>
+      </c>
+      <c r="D831">
+        <v>10.4545</v>
       </c>
     </row>
   </sheetData>
@@ -46899,7 +46955,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D830"/>
+  <dimension ref="A1:D831"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58517,6 +58573,20 @@
       </c>
       <c r="D830">
         <v>96.55070000000001</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4">
+      <c r="A831" s="1">
+        <v>829</v>
+      </c>
+      <c r="B831" s="2">
+        <v>46162</v>
+      </c>
+      <c r="C831">
+        <v>1</v>
+      </c>
+      <c r="D831">
+        <v>95.4893</v>
       </c>
     </row>
   </sheetData>
@@ -58526,7 +58596,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D830"/>
+  <dimension ref="A1:D831"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -70144,6 +70214,20 @@
       </c>
       <c r="D830">
         <v>15.388</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4">
+      <c r="A831" s="1">
+        <v>829</v>
+      </c>
+      <c r="B831" s="2">
+        <v>46162</v>
+      </c>
+      <c r="C831">
+        <v>100</v>
+      </c>
+      <c r="D831">
+        <v>15.2471</v>
       </c>
     </row>
   </sheetData>
@@ -70153,7 +70237,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D830"/>
+  <dimension ref="A1:D831"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -81771,6 +81855,20 @@
       </c>
       <c r="D830">
         <v>45.5173</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4">
+      <c r="A831" s="1">
+        <v>829</v>
+      </c>
+      <c r="B831" s="2">
+        <v>46162</v>
+      </c>
+      <c r="C831">
+        <v>100</v>
+      </c>
+      <c r="D831">
+        <v>44.8409</v>
       </c>
     </row>
   </sheetData>
@@ -81780,7 +81878,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D830"/>
+  <dimension ref="A1:D831"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -93400,6 +93498,20 @@
         <v>92.1887</v>
       </c>
     </row>
+    <row r="831" spans="1:4">
+      <c r="A831" s="1">
+        <v>829</v>
+      </c>
+      <c r="B831" s="2">
+        <v>46162</v>
+      </c>
+      <c r="C831">
+        <v>1</v>
+      </c>
+      <c r="D831">
+        <v>90.5993</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D831"/>
+  <dimension ref="A1:D832"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12023,6 +12023,20 @@
       </c>
       <c r="D831">
         <v>71.29259999999999</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4">
+      <c r="A832" s="1">
+        <v>830</v>
+      </c>
+      <c r="B832" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C832">
+        <v>1</v>
+      </c>
+      <c r="D832">
+        <v>70.9509</v>
       </c>
     </row>
   </sheetData>
@@ -12032,7 +12046,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D831"/>
+  <dimension ref="A1:D832"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23664,6 +23678,20 @@
       </c>
       <c r="D831">
         <v>82.7871</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4">
+      <c r="A832" s="1">
+        <v>830</v>
+      </c>
+      <c r="B832" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C832">
+        <v>1</v>
+      </c>
+      <c r="D832">
+        <v>81.9823</v>
       </c>
     </row>
   </sheetData>
@@ -23673,7 +23701,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D831"/>
+  <dimension ref="A1:D832"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35305,6 +35333,20 @@
       </c>
       <c r="D831">
         <v>50.8459</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4">
+      <c r="A832" s="1">
+        <v>830</v>
+      </c>
+      <c r="B832" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C832">
+        <v>1</v>
+      </c>
+      <c r="D832">
+        <v>50.3964</v>
       </c>
     </row>
   </sheetData>
@@ -35314,7 +35356,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D831"/>
+  <dimension ref="A1:D832"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -46946,6 +46988,20 @@
       </c>
       <c r="D831">
         <v>10.4545</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4">
+      <c r="A832" s="1">
+        <v>830</v>
+      </c>
+      <c r="B832" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C832">
+        <v>1</v>
+      </c>
+      <c r="D832">
+        <v>10.4161</v>
       </c>
     </row>
   </sheetData>
@@ -46955,7 +47011,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D831"/>
+  <dimension ref="A1:D832"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58587,6 +58643,20 @@
       </c>
       <c r="D831">
         <v>95.4893</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4">
+      <c r="A832" s="1">
+        <v>830</v>
+      </c>
+      <c r="B832" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C832">
+        <v>1</v>
+      </c>
+      <c r="D832">
+        <v>95.0245</v>
       </c>
     </row>
   </sheetData>
@@ -58596,7 +58666,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D831"/>
+  <dimension ref="A1:D832"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -70228,6 +70298,20 @@
       </c>
       <c r="D831">
         <v>15.2471</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4">
+      <c r="A832" s="1">
+        <v>830</v>
+      </c>
+      <c r="B832" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C832">
+        <v>100</v>
+      </c>
+      <c r="D832">
+        <v>15.0342</v>
       </c>
     </row>
   </sheetData>
@@ -70237,7 +70321,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D831"/>
+  <dimension ref="A1:D832"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -81869,6 +81953,20 @@
       </c>
       <c r="D831">
         <v>44.8409</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4">
+      <c r="A832" s="1">
+        <v>830</v>
+      </c>
+      <c r="B832" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C832">
+        <v>100</v>
+      </c>
+      <c r="D832">
+        <v>44.6232</v>
       </c>
     </row>
   </sheetData>
@@ -81878,7 +81976,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D831"/>
+  <dimension ref="A1:D832"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -93512,6 +93610,20 @@
         <v>90.5993</v>
       </c>
     </row>
+    <row r="832" spans="1:4">
+      <c r="A832" s="1">
+        <v>830</v>
+      </c>
+      <c r="B832" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C832">
+        <v>1</v>
+      </c>
+      <c r="D832">
+        <v>89.7885</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D832"/>
+  <dimension ref="A1:D833"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12037,6 +12037,20 @@
       </c>
       <c r="D832">
         <v>70.9509</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4">
+      <c r="A833" s="1">
+        <v>831</v>
+      </c>
+      <c r="B833" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C833">
+        <v>1</v>
+      </c>
+      <c r="D833">
+        <v>70.7902</v>
       </c>
     </row>
   </sheetData>
@@ -12046,7 +12060,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D832"/>
+  <dimension ref="A1:D833"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23692,6 +23706,20 @@
       </c>
       <c r="D832">
         <v>81.9823</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4">
+      <c r="A833" s="1">
+        <v>831</v>
+      </c>
+      <c r="B833" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C833">
+        <v>1</v>
+      </c>
+      <c r="D833">
+        <v>83.27460000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23701,7 +23729,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D832"/>
+  <dimension ref="A1:D833"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35347,6 +35375,20 @@
       </c>
       <c r="D832">
         <v>50.3964</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4">
+      <c r="A833" s="1">
+        <v>831</v>
+      </c>
+      <c r="B833" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C833">
+        <v>1</v>
+      </c>
+      <c r="D833">
+        <v>50.438</v>
       </c>
     </row>
   </sheetData>
@@ -35356,7 +35398,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D832"/>
+  <dimension ref="A1:D833"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47002,6 +47044,20 @@
       </c>
       <c r="D832">
         <v>10.4161</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4">
+      <c r="A833" s="1">
+        <v>831</v>
+      </c>
+      <c r="B833" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C833">
+        <v>1</v>
+      </c>
+      <c r="D833">
+        <v>10.398</v>
       </c>
     </row>
   </sheetData>
@@ -47011,7 +47067,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D832"/>
+  <dimension ref="A1:D833"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58657,6 +58713,20 @@
       </c>
       <c r="D832">
         <v>95.0245</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4">
+      <c r="A833" s="1">
+        <v>831</v>
+      </c>
+      <c r="B833" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C833">
+        <v>1</v>
+      </c>
+      <c r="D833">
+        <v>95.0925</v>
       </c>
     </row>
   </sheetData>
@@ -58666,7 +58736,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D832"/>
+  <dimension ref="A1:D833"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -70312,6 +70382,20 @@
       </c>
       <c r="D832">
         <v>15.0342</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4">
+      <c r="A833" s="1">
+        <v>831</v>
+      </c>
+      <c r="B833" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C833">
+        <v>100</v>
+      </c>
+      <c r="D833">
+        <v>15.0052</v>
       </c>
     </row>
   </sheetData>
@@ -70321,7 +70405,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D832"/>
+  <dimension ref="A1:D833"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -81967,6 +82051,20 @@
       </c>
       <c r="D832">
         <v>44.6232</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4">
+      <c r="A833" s="1">
+        <v>831</v>
+      </c>
+      <c r="B833" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C833">
+        <v>100</v>
+      </c>
+      <c r="D833">
+        <v>44.5586</v>
       </c>
     </row>
   </sheetData>
@@ -81976,7 +82074,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D832"/>
+  <dimension ref="A1:D833"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -93624,6 +93722,20 @@
         <v>89.7885</v>
       </c>
     </row>
+    <row r="833" spans="1:4">
+      <c r="A833" s="1">
+        <v>831</v>
+      </c>
+      <c r="B833" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C833">
+        <v>1</v>
+      </c>
+      <c r="D833">
+        <v>89.9609</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D833"/>
+  <dimension ref="A1:D834"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12051,6 +12051,20 @@
       </c>
       <c r="D833">
         <v>70.7902</v>
+      </c>
+    </row>
+    <row r="834" spans="1:4">
+      <c r="A834" s="1">
+        <v>832</v>
+      </c>
+      <c r="B834" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C834">
+        <v>1</v>
+      </c>
+      <c r="D834">
+        <v>71.209</v>
       </c>
     </row>
   </sheetData>
@@ -12060,7 +12074,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D833"/>
+  <dimension ref="A1:D834"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23720,6 +23734,20 @@
       </c>
       <c r="D833">
         <v>83.27460000000001</v>
+      </c>
+    </row>
+    <row r="834" spans="1:4">
+      <c r="A834" s="1">
+        <v>832</v>
+      </c>
+      <c r="B834" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C834">
+        <v>1</v>
+      </c>
+      <c r="D834">
+        <v>82.5445</v>
       </c>
     </row>
   </sheetData>
@@ -23729,7 +23757,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D833"/>
+  <dimension ref="A1:D834"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35389,6 +35417,20 @@
       </c>
       <c r="D833">
         <v>50.438</v>
+      </c>
+    </row>
+    <row r="834" spans="1:4">
+      <c r="A834" s="1">
+        <v>832</v>
+      </c>
+      <c r="B834" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C834">
+        <v>1</v>
+      </c>
+      <c r="D834">
+        <v>50.8361</v>
       </c>
     </row>
   </sheetData>
@@ -35398,7 +35440,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D833"/>
+  <dimension ref="A1:D834"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47058,6 +47100,20 @@
       </c>
       <c r="D833">
         <v>10.398</v>
+      </c>
+    </row>
+    <row r="834" spans="1:4">
+      <c r="A834" s="1">
+        <v>832</v>
+      </c>
+      <c r="B834" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C834">
+        <v>1</v>
+      </c>
+      <c r="D834">
+        <v>10.4823</v>
       </c>
     </row>
   </sheetData>
@@ -47067,7 +47123,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D833"/>
+  <dimension ref="A1:D834"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58727,6 +58783,20 @@
       </c>
       <c r="D833">
         <v>95.0925</v>
+      </c>
+    </row>
+    <row r="834" spans="1:4">
+      <c r="A834" s="1">
+        <v>832</v>
+      </c>
+      <c r="B834" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C834">
+        <v>1</v>
+      </c>
+      <c r="D834">
+        <v>95.5055</v>
       </c>
     </row>
   </sheetData>
@@ -58736,7 +58806,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D833"/>
+  <dimension ref="A1:D834"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -70396,6 +70466,20 @@
       </c>
       <c r="D833">
         <v>15.0052</v>
+      </c>
+    </row>
+    <row r="834" spans="1:4">
+      <c r="A834" s="1">
+        <v>832</v>
+      </c>
+      <c r="B834" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C834">
+        <v>100</v>
+      </c>
+      <c r="D834">
+        <v>15.1043</v>
       </c>
     </row>
   </sheetData>
@@ -70405,7 +70489,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D833"/>
+  <dimension ref="A1:D834"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -82065,6 +82149,20 @@
       </c>
       <c r="D833">
         <v>44.5586</v>
+      </c>
+    </row>
+    <row r="834" spans="1:4">
+      <c r="A834" s="1">
+        <v>832</v>
+      </c>
+      <c r="B834" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C834">
+        <v>100</v>
+      </c>
+      <c r="D834">
+        <v>44.7715</v>
       </c>
     </row>
   </sheetData>
@@ -82074,7 +82172,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D833"/>
+  <dimension ref="A1:D834"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -93736,6 +93834,20 @@
         <v>89.9609</v>
       </c>
     </row>
+    <row r="834" spans="1:4">
+      <c r="A834" s="1">
+        <v>832</v>
+      </c>
+      <c r="B834" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C834">
+        <v>1</v>
+      </c>
+      <c r="D834">
+        <v>90.5852</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D834"/>
+  <dimension ref="A1:D835"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12065,6 +12065,20 @@
       </c>
       <c r="D834">
         <v>71.209</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4">
+      <c r="A835" s="1">
+        <v>833</v>
+      </c>
+      <c r="B835" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C835">
+        <v>1</v>
+      </c>
+      <c r="D835">
+        <v>71.54600000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12074,7 +12088,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D834"/>
+  <dimension ref="A1:D835"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23748,6 +23762,20 @@
       </c>
       <c r="D834">
         <v>82.5445</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4">
+      <c r="A835" s="1">
+        <v>833</v>
+      </c>
+      <c r="B835" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C835">
+        <v>1</v>
+      </c>
+      <c r="D835">
+        <v>85.44929999999999</v>
       </c>
     </row>
   </sheetData>
@@ -23757,7 +23785,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D834"/>
+  <dimension ref="A1:D835"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35431,6 +35459,20 @@
       </c>
       <c r="D834">
         <v>50.8361</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4">
+      <c r="A835" s="1">
+        <v>833</v>
+      </c>
+      <c r="B835" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C835">
+        <v>1</v>
+      </c>
+      <c r="D835">
+        <v>51.2699</v>
       </c>
     </row>
   </sheetData>
@@ -35440,7 +35482,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D834"/>
+  <dimension ref="A1:D835"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47114,6 +47156,20 @@
       </c>
       <c r="D834">
         <v>10.4823</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4">
+      <c r="A835" s="1">
+        <v>833</v>
+      </c>
+      <c r="B835" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C835">
+        <v>1</v>
+      </c>
+      <c r="D835">
+        <v>10.5317</v>
       </c>
     </row>
   </sheetData>
@@ -47123,7 +47179,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D834"/>
+  <dimension ref="A1:D835"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58797,6 +58853,20 @@
       </c>
       <c r="D834">
         <v>95.5055</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4">
+      <c r="A835" s="1">
+        <v>833</v>
+      </c>
+      <c r="B835" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C835">
+        <v>1</v>
+      </c>
+      <c r="D835">
+        <v>95.9575</v>
       </c>
     </row>
   </sheetData>
@@ -58806,7 +58876,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D834"/>
+  <dimension ref="A1:D835"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -70480,6 +70550,20 @@
       </c>
       <c r="D834">
         <v>15.1043</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4">
+      <c r="A835" s="1">
+        <v>833</v>
+      </c>
+      <c r="B835" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C835">
+        <v>100</v>
+      </c>
+      <c r="D835">
+        <v>15.1967</v>
       </c>
     </row>
   </sheetData>
@@ -70489,7 +70573,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D834"/>
+  <dimension ref="A1:D835"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -82163,6 +82247,20 @@
       </c>
       <c r="D834">
         <v>44.7715</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4">
+      <c r="A835" s="1">
+        <v>833</v>
+      </c>
+      <c r="B835" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C835">
+        <v>100</v>
+      </c>
+      <c r="D835">
+        <v>45.04</v>
       </c>
     </row>
   </sheetData>
@@ -82172,7 +82270,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D834"/>
+  <dimension ref="A1:D835"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -93848,6 +93946,20 @@
         <v>90.5852</v>
       </c>
     </row>
+    <row r="835" spans="1:4">
+      <c r="A835" s="1">
+        <v>833</v>
+      </c>
+      <c r="B835" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C835">
+        <v>1</v>
+      </c>
+      <c r="D835">
+        <v>91.01390000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D835"/>
+  <dimension ref="A1:D836"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12079,6 +12079,20 @@
       </c>
       <c r="D835">
         <v>71.54600000000001</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4">
+      <c r="A836" s="1">
+        <v>834</v>
+      </c>
+      <c r="B836" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C836">
+        <v>1</v>
+      </c>
+      <c r="D836">
+        <v>71.66800000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12088,7 +12102,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D835"/>
+  <dimension ref="A1:D836"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23776,6 +23790,20 @@
       </c>
       <c r="D835">
         <v>85.44929999999999</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4">
+      <c r="A836" s="1">
+        <v>834</v>
+      </c>
+      <c r="B836" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C836">
+        <v>1</v>
+      </c>
+      <c r="D836">
+        <v>83.2975</v>
       </c>
     </row>
   </sheetData>
@@ -23785,7 +23813,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D835"/>
+  <dimension ref="A1:D836"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35473,6 +35501,20 @@
       </c>
       <c r="D835">
         <v>51.2699</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4">
+      <c r="A836" s="1">
+        <v>834</v>
+      </c>
+      <c r="B836" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C836">
+        <v>1</v>
+      </c>
+      <c r="D836">
+        <v>51.3143</v>
       </c>
     </row>
   </sheetData>
@@ -35482,7 +35524,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D835"/>
+  <dimension ref="A1:D836"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47170,6 +47212,20 @@
       </c>
       <c r="D835">
         <v>10.5317</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4">
+      <c r="A836" s="1">
+        <v>834</v>
+      </c>
+      <c r="B836" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C836">
+        <v>1</v>
+      </c>
+      <c r="D836">
+        <v>10.5505</v>
       </c>
     </row>
   </sheetData>
@@ -47179,7 +47235,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D835"/>
+  <dimension ref="A1:D836"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58867,6 +58923,20 @@
       </c>
       <c r="D835">
         <v>95.9575</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4">
+      <c r="A836" s="1">
+        <v>834</v>
+      </c>
+      <c r="B836" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C836">
+        <v>1</v>
+      </c>
+      <c r="D836">
+        <v>96.286</v>
       </c>
     </row>
   </sheetData>
@@ -58876,7 +58946,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D835"/>
+  <dimension ref="A1:D836"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -70564,6 +70634,20 @@
       </c>
       <c r="D835">
         <v>15.1967</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4">
+      <c r="A836" s="1">
+        <v>834</v>
+      </c>
+      <c r="B836" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C836">
+        <v>100</v>
+      </c>
+      <c r="D836">
+        <v>15.1685</v>
       </c>
     </row>
   </sheetData>
@@ -70573,7 +70657,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D835"/>
+  <dimension ref="A1:D836"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -82261,6 +82345,20 @@
       </c>
       <c r="D835">
         <v>45.04</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4">
+      <c r="A836" s="1">
+        <v>834</v>
+      </c>
+      <c r="B836" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C836">
+        <v>100</v>
+      </c>
+      <c r="D836">
+        <v>45.077</v>
       </c>
     </row>
   </sheetData>
@@ -82270,7 +82368,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D835"/>
+  <dimension ref="A1:D836"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -93960,6 +94058,20 @@
         <v>91.01390000000001</v>
       </c>
     </row>
+    <row r="836" spans="1:4">
+      <c r="A836" s="1">
+        <v>834</v>
+      </c>
+      <c r="B836" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C836">
+        <v>1</v>
+      </c>
+      <c r="D836">
+        <v>91.3434</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D836"/>
+  <dimension ref="A1:D837"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12093,6 +12093,20 @@
       </c>
       <c r="D836">
         <v>71.66800000000001</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4">
+      <c r="A837" s="1">
+        <v>835</v>
+      </c>
+      <c r="B837" s="2">
+        <v>46170</v>
+      </c>
+      <c r="C837">
+        <v>1</v>
+      </c>
+      <c r="D837">
+        <v>70.9012</v>
       </c>
     </row>
   </sheetData>
@@ -12102,7 +12116,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D836"/>
+  <dimension ref="A1:D837"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23804,6 +23818,20 @@
       </c>
       <c r="D836">
         <v>83.2975</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4">
+      <c r="A837" s="1">
+        <v>835</v>
+      </c>
+      <c r="B837" s="2">
+        <v>46170</v>
+      </c>
+      <c r="C837">
+        <v>1</v>
+      </c>
+      <c r="D837">
+        <v>82.72239999999999</v>
       </c>
     </row>
   </sheetData>
@@ -23813,7 +23841,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D836"/>
+  <dimension ref="A1:D837"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35515,6 +35543,20 @@
       </c>
       <c r="D836">
         <v>51.3143</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4">
+      <c r="A837" s="1">
+        <v>835</v>
+      </c>
+      <c r="B837" s="2">
+        <v>46170</v>
+      </c>
+      <c r="C837">
+        <v>1</v>
+      </c>
+      <c r="D837">
+        <v>50.7369</v>
       </c>
     </row>
   </sheetData>
@@ -35524,7 +35566,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D836"/>
+  <dimension ref="A1:D837"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47226,6 +47268,20 @@
       </c>
       <c r="D836">
         <v>10.5505</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4">
+      <c r="A837" s="1">
+        <v>835</v>
+      </c>
+      <c r="B837" s="2">
+        <v>46170</v>
+      </c>
+      <c r="C837">
+        <v>1</v>
+      </c>
+      <c r="D837">
+        <v>10.4557</v>
       </c>
     </row>
   </sheetData>
@@ -47235,7 +47291,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D836"/>
+  <dimension ref="A1:D837"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -58937,6 +58993,20 @@
       </c>
       <c r="D836">
         <v>96.286</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4">
+      <c r="A837" s="1">
+        <v>835</v>
+      </c>
+      <c r="B837" s="2">
+        <v>46170</v>
+      </c>
+      <c r="C837">
+        <v>1</v>
+      </c>
+      <c r="D837">
+        <v>95.3621</v>
       </c>
     </row>
   </sheetData>
@@ -58946,7 +59016,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D836"/>
+  <dimension ref="A1:D837"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -70648,6 +70718,20 @@
       </c>
       <c r="D836">
         <v>15.1685</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4">
+      <c r="A837" s="1">
+        <v>835</v>
+      </c>
+      <c r="B837" s="2">
+        <v>46170</v>
+      </c>
+      <c r="C837">
+        <v>100</v>
+      </c>
+      <c r="D837">
+        <v>14.849</v>
       </c>
     </row>
   </sheetData>
@@ -70657,7 +70741,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D836"/>
+  <dimension ref="A1:D837"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -82359,6 +82443,20 @@
       </c>
       <c r="D836">
         <v>45.077</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4">
+      <c r="A837" s="1">
+        <v>835</v>
+      </c>
+      <c r="B837" s="2">
+        <v>46170</v>
+      </c>
+      <c r="C837">
+        <v>100</v>
+      </c>
+      <c r="D837">
+        <v>44.508</v>
       </c>
     </row>
   </sheetData>
@@ -82368,7 +82466,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D836"/>
+  <dimension ref="A1:D837"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -94072,6 +94170,20 @@
         <v>91.3434</v>
       </c>
     </row>
+    <row r="837" spans="1:4">
+      <c r="A837" s="1">
+        <v>835</v>
+      </c>
+      <c r="B837" s="2">
+        <v>46170</v>
+      </c>
+      <c r="C837">
+        <v>1</v>
+      </c>
+      <c r="D837">
+        <v>90.1936</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D837"/>
+  <dimension ref="A1:D838"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12107,6 +12107,20 @@
       </c>
       <c r="D837">
         <v>70.9012</v>
+      </c>
+    </row>
+    <row r="838" spans="1:4">
+      <c r="A838" s="1">
+        <v>836</v>
+      </c>
+      <c r="B838" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C838">
+        <v>1</v>
+      </c>
+      <c r="D838">
+        <v>71.3715</v>
       </c>
     </row>
   </sheetData>
@@ -12116,7 +12130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D837"/>
+  <dimension ref="A1:D838"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23832,6 +23846,20 @@
       </c>
       <c r="D837">
         <v>82.72239999999999</v>
+      </c>
+    </row>
+    <row r="838" spans="1:4">
+      <c r="A838" s="1">
+        <v>836</v>
+      </c>
+      <c r="B838" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C838">
+        <v>1</v>
+      </c>
+      <c r="D838">
+        <v>83.6892</v>
       </c>
     </row>
   </sheetData>
@@ -23841,7 +23869,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D837"/>
+  <dimension ref="A1:D838"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35557,6 +35585,20 @@
       </c>
       <c r="D837">
         <v>50.7369</v>
+      </c>
+    </row>
+    <row r="838" spans="1:4">
+      <c r="A838" s="1">
+        <v>836</v>
+      </c>
+      <c r="B838" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C838">
+        <v>1</v>
+      </c>
+      <c r="D838">
+        <v>50.7951</v>
       </c>
     </row>
   </sheetData>
@@ -35566,7 +35608,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D837"/>
+  <dimension ref="A1:D838"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47282,6 +47324,20 @@
       </c>
       <c r="D837">
         <v>10.4557</v>
+      </c>
+    </row>
+    <row r="838" spans="1:4">
+      <c r="A838" s="1">
+        <v>836</v>
+      </c>
+      <c r="B838" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C838">
+        <v>1</v>
+      </c>
+      <c r="D838">
+        <v>10.4487</v>
       </c>
     </row>
   </sheetData>
@@ -47291,7 +47347,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D837"/>
+  <dimension ref="A1:D838"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59007,6 +59063,20 @@
       </c>
       <c r="D837">
         <v>95.3621</v>
+      </c>
+    </row>
+    <row r="838" spans="1:4">
+      <c r="A838" s="1">
+        <v>836</v>
+      </c>
+      <c r="B838" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C838">
+        <v>1</v>
+      </c>
+      <c r="D838">
+        <v>95.7734</v>
       </c>
     </row>
   </sheetData>
@@ -59016,7 +59086,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D837"/>
+  <dimension ref="A1:D838"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -70732,6 +70802,20 @@
       </c>
       <c r="D837">
         <v>14.849</v>
+      </c>
+    </row>
+    <row r="838" spans="1:4">
+      <c r="A838" s="1">
+        <v>836</v>
+      </c>
+      <c r="B838" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C838">
+        <v>100</v>
+      </c>
+      <c r="D838">
+        <v>14.9475</v>
       </c>
     </row>
   </sheetData>
@@ -70741,7 +70825,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D837"/>
+  <dimension ref="A1:D838"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -82457,6 +82541,20 @@
       </c>
       <c r="D837">
         <v>44.508</v>
+      </c>
+    </row>
+    <row r="838" spans="1:4">
+      <c r="A838" s="1">
+        <v>836</v>
+      </c>
+      <c r="B838" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C838">
+        <v>100</v>
+      </c>
+      <c r="D838">
+        <v>44.7246</v>
       </c>
     </row>
   </sheetData>
@@ -82466,7 +82564,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D837"/>
+  <dimension ref="A1:D838"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -94184,6 +94282,20 @@
         <v>90.1936</v>
       </c>
     </row>
+    <row r="838" spans="1:4">
+      <c r="A838" s="1">
+        <v>836</v>
+      </c>
+      <c r="B838" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C838">
+        <v>1</v>
+      </c>
+      <c r="D838">
+        <v>90.45820000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D838"/>
+  <dimension ref="A1:D839"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12121,6 +12121,20 @@
       </c>
       <c r="D838">
         <v>71.3715</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4">
+      <c r="A839" s="1">
+        <v>837</v>
+      </c>
+      <c r="B839" s="2">
+        <v>46172</v>
+      </c>
+      <c r="C839">
+        <v>1</v>
+      </c>
+      <c r="D839">
+        <v>71.0224</v>
       </c>
     </row>
   </sheetData>
@@ -12130,7 +12144,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D838"/>
+  <dimension ref="A1:D839"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23860,6 +23874,20 @@
       </c>
       <c r="D838">
         <v>83.6892</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4">
+      <c r="A839" s="1">
+        <v>837</v>
+      </c>
+      <c r="B839" s="2">
+        <v>46172</v>
+      </c>
+      <c r="C839">
+        <v>1</v>
+      </c>
+      <c r="D839">
+        <v>82.6369</v>
       </c>
     </row>
   </sheetData>
@@ -23869,7 +23897,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D838"/>
+  <dimension ref="A1:D839"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35599,6 +35627,20 @@
       </c>
       <c r="D838">
         <v>50.7951</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4">
+      <c r="A839" s="1">
+        <v>837</v>
+      </c>
+      <c r="B839" s="2">
+        <v>46172</v>
+      </c>
+      <c r="C839">
+        <v>1</v>
+      </c>
+      <c r="D839">
+        <v>50.8804</v>
       </c>
     </row>
   </sheetData>
@@ -35608,7 +35650,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D838"/>
+  <dimension ref="A1:D839"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47338,6 +47380,20 @@
       </c>
       <c r="D838">
         <v>10.4487</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4">
+      <c r="A839" s="1">
+        <v>837</v>
+      </c>
+      <c r="B839" s="2">
+        <v>46172</v>
+      </c>
+      <c r="C839">
+        <v>1</v>
+      </c>
+      <c r="D839">
+        <v>10.4865</v>
       </c>
     </row>
   </sheetData>
@@ -47347,7 +47403,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D838"/>
+  <dimension ref="A1:D839"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59077,6 +59133,20 @@
       </c>
       <c r="D838">
         <v>95.7734</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4">
+      <c r="A839" s="1">
+        <v>837</v>
+      </c>
+      <c r="B839" s="2">
+        <v>46172</v>
+      </c>
+      <c r="C839">
+        <v>1</v>
+      </c>
+      <c r="D839">
+        <v>95.3973</v>
       </c>
     </row>
   </sheetData>
@@ -59086,7 +59156,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D838"/>
+  <dimension ref="A1:D839"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -70816,6 +70886,20 @@
       </c>
       <c r="D838">
         <v>14.9475</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4">
+      <c r="A839" s="1">
+        <v>837</v>
+      </c>
+      <c r="B839" s="2">
+        <v>46172</v>
+      </c>
+      <c r="C839">
+        <v>100</v>
+      </c>
+      <c r="D839">
+        <v>14.6272</v>
       </c>
     </row>
   </sheetData>
@@ -70825,7 +70909,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D838"/>
+  <dimension ref="A1:D839"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -82555,6 +82639,20 @@
       </c>
       <c r="D838">
         <v>44.7246</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4">
+      <c r="A839" s="1">
+        <v>837</v>
+      </c>
+      <c r="B839" s="2">
+        <v>46172</v>
+      </c>
+      <c r="C839">
+        <v>100</v>
+      </c>
+      <c r="D839">
+        <v>44.5841</v>
       </c>
     </row>
   </sheetData>
@@ -82564,7 +82662,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D838"/>
+  <dimension ref="A1:D839"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -94296,6 +94394,20 @@
         <v>90.45820000000001</v>
       </c>
     </row>
+    <row r="839" spans="1:4">
+      <c r="A839" s="1">
+        <v>837</v>
+      </c>
+      <c r="B839" s="2">
+        <v>46172</v>
+      </c>
+      <c r="C839">
+        <v>1</v>
+      </c>
+      <c r="D839">
+        <v>90.5321</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D839"/>
+  <dimension ref="A1:D840"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12135,6 +12135,20 @@
       </c>
       <c r="D839">
         <v>71.0224</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4">
+      <c r="A840" s="1">
+        <v>838</v>
+      </c>
+      <c r="B840" s="2">
+        <v>46175</v>
+      </c>
+      <c r="C840">
+        <v>1</v>
+      </c>
+      <c r="D840">
+        <v>71.5532</v>
       </c>
     </row>
   </sheetData>
@@ -12144,7 +12158,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D839"/>
+  <dimension ref="A1:D840"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23888,6 +23902,20 @@
       </c>
       <c r="D839">
         <v>82.6369</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4">
+      <c r="A840" s="1">
+        <v>838</v>
+      </c>
+      <c r="B840" s="2">
+        <v>46175</v>
+      </c>
+      <c r="C840">
+        <v>1</v>
+      </c>
+      <c r="D840">
+        <v>86.2499</v>
       </c>
     </row>
   </sheetData>
@@ -23897,7 +23925,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D839"/>
+  <dimension ref="A1:D840"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35641,6 +35669,20 @@
       </c>
       <c r="D839">
         <v>50.8804</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4">
+      <c r="A840" s="1">
+        <v>838</v>
+      </c>
+      <c r="B840" s="2">
+        <v>46175</v>
+      </c>
+      <c r="C840">
+        <v>1</v>
+      </c>
+      <c r="D840">
+        <v>51.4324</v>
       </c>
     </row>
   </sheetData>
@@ -35650,7 +35692,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D839"/>
+  <dimension ref="A1:D840"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47394,6 +47436,20 @@
       </c>
       <c r="D839">
         <v>10.4865</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4">
+      <c r="A840" s="1">
+        <v>838</v>
+      </c>
+      <c r="B840" s="2">
+        <v>46175</v>
+      </c>
+      <c r="C840">
+        <v>1</v>
+      </c>
+      <c r="D840">
+        <v>10.5762</v>
       </c>
     </row>
   </sheetData>
@@ -47403,7 +47459,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D839"/>
+  <dimension ref="A1:D840"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59147,6 +59203,20 @@
       </c>
       <c r="D839">
         <v>95.3973</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4">
+      <c r="A840" s="1">
+        <v>838</v>
+      </c>
+      <c r="B840" s="2">
+        <v>46175</v>
+      </c>
+      <c r="C840">
+        <v>1</v>
+      </c>
+      <c r="D840">
+        <v>96.43940000000001</v>
       </c>
     </row>
   </sheetData>
@@ -59156,7 +59226,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D839"/>
+  <dimension ref="A1:D840"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -70900,6 +70970,20 @@
       </c>
       <c r="D839">
         <v>14.6272</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4">
+      <c r="A840" s="1">
+        <v>838</v>
+      </c>
+      <c r="B840" s="2">
+        <v>46175</v>
+      </c>
+      <c r="C840">
+        <v>100</v>
+      </c>
+      <c r="D840">
+        <v>14.7244</v>
       </c>
     </row>
   </sheetData>
@@ -70909,7 +70993,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D839"/>
+  <dimension ref="A1:D840"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -82653,6 +82737,20 @@
       </c>
       <c r="D839">
         <v>44.5841</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4">
+      <c r="A840" s="1">
+        <v>838</v>
+      </c>
+      <c r="B840" s="2">
+        <v>46175</v>
+      </c>
+      <c r="C840">
+        <v>100</v>
+      </c>
+      <c r="D840">
+        <v>44.875</v>
       </c>
     </row>
   </sheetData>
@@ -82662,7 +82760,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D839"/>
+  <dimension ref="A1:D840"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -94408,6 +94506,20 @@
         <v>90.5321</v>
       </c>
     </row>
+    <row r="840" spans="1:4">
+      <c r="A840" s="1">
+        <v>838</v>
+      </c>
+      <c r="B840" s="2">
+        <v>46175</v>
+      </c>
+      <c r="C840">
+        <v>1</v>
+      </c>
+      <c r="D840">
+        <v>91.3601</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D840"/>
+  <dimension ref="A1:D841"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12149,6 +12149,20 @@
       </c>
       <c r="D840">
         <v>71.5532</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4">
+      <c r="A841" s="1">
+        <v>839</v>
+      </c>
+      <c r="B841" s="2">
+        <v>46176</v>
+      </c>
+      <c r="C841">
+        <v>1</v>
+      </c>
+      <c r="D841">
+        <v>72.55970000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12158,7 +12172,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D840"/>
+  <dimension ref="A1:D841"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23916,6 +23930,20 @@
       </c>
       <c r="D840">
         <v>86.2499</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4">
+      <c r="A841" s="1">
+        <v>839</v>
+      </c>
+      <c r="B841" s="2">
+        <v>46176</v>
+      </c>
+      <c r="C841">
+        <v>1</v>
+      </c>
+      <c r="D841">
+        <v>84.6096</v>
       </c>
     </row>
   </sheetData>
@@ -23925,7 +23953,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D840"/>
+  <dimension ref="A1:D841"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35683,6 +35711,20 @@
       </c>
       <c r="D840">
         <v>51.4324</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4">
+      <c r="A841" s="1">
+        <v>839</v>
+      </c>
+      <c r="B841" s="2">
+        <v>46176</v>
+      </c>
+      <c r="C841">
+        <v>1</v>
+      </c>
+      <c r="D841">
+        <v>51.9745</v>
       </c>
     </row>
   </sheetData>
@@ -35692,7 +35734,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D840"/>
+  <dimension ref="A1:D841"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47450,6 +47492,20 @@
       </c>
       <c r="D840">
         <v>10.5762</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4">
+      <c r="A841" s="1">
+        <v>839</v>
+      </c>
+      <c r="B841" s="2">
+        <v>46176</v>
+      </c>
+      <c r="C841">
+        <v>1</v>
+      </c>
+      <c r="D841">
+        <v>10.7312</v>
       </c>
     </row>
   </sheetData>
@@ -47459,7 +47515,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D840"/>
+  <dimension ref="A1:D841"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59217,6 +59273,20 @@
       </c>
       <c r="D840">
         <v>96.43940000000001</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4">
+      <c r="A841" s="1">
+        <v>839</v>
+      </c>
+      <c r="B841" s="2">
+        <v>46176</v>
+      </c>
+      <c r="C841">
+        <v>1</v>
+      </c>
+      <c r="D841">
+        <v>97.49850000000001</v>
       </c>
     </row>
   </sheetData>
@@ -59226,7 +59296,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D840"/>
+  <dimension ref="A1:D841"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -70984,6 +71054,20 @@
       </c>
       <c r="D840">
         <v>14.7244</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4">
+      <c r="A841" s="1">
+        <v>839</v>
+      </c>
+      <c r="B841" s="2">
+        <v>46176</v>
+      </c>
+      <c r="C841">
+        <v>100</v>
+      </c>
+      <c r="D841">
+        <v>14.8396</v>
       </c>
     </row>
   </sheetData>
@@ -70993,7 +71077,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D840"/>
+  <dimension ref="A1:D841"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -82751,6 +82835,20 @@
       </c>
       <c r="D840">
         <v>44.875</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4">
+      <c r="A841" s="1">
+        <v>839</v>
+      </c>
+      <c r="B841" s="2">
+        <v>46176</v>
+      </c>
+      <c r="C841">
+        <v>100</v>
+      </c>
+      <c r="D841">
+        <v>45.4293</v>
       </c>
     </row>
   </sheetData>
@@ -82760,7 +82858,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D840"/>
+  <dimension ref="A1:D841"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -94520,6 +94618,20 @@
         <v>91.3601</v>
       </c>
     </row>
+    <row r="841" spans="1:4">
+      <c r="A841" s="1">
+        <v>839</v>
+      </c>
+      <c r="B841" s="2">
+        <v>46176</v>
+      </c>
+      <c r="C841">
+        <v>1</v>
+      </c>
+      <c r="D841">
+        <v>92.3151</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D841"/>
+  <dimension ref="A1:D842"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12163,6 +12163,20 @@
       </c>
       <c r="D841">
         <v>72.55970000000001</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4">
+      <c r="A842" s="1">
+        <v>840</v>
+      </c>
+      <c r="B842" s="2">
+        <v>46177</v>
+      </c>
+      <c r="C842">
+        <v>1</v>
+      </c>
+      <c r="D842">
+        <v>73.3436</v>
       </c>
     </row>
   </sheetData>
@@ -12172,7 +12186,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D841"/>
+  <dimension ref="A1:D842"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23944,6 +23958,20 @@
       </c>
       <c r="D841">
         <v>84.6096</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4">
+      <c r="A842" s="1">
+        <v>840</v>
+      </c>
+      <c r="B842" s="2">
+        <v>46177</v>
+      </c>
+      <c r="C842">
+        <v>1</v>
+      </c>
+      <c r="D842">
+        <v>85.12430000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23953,7 +23981,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D841"/>
+  <dimension ref="A1:D842"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35725,6 +35753,20 @@
       </c>
       <c r="D841">
         <v>51.9745</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4">
+      <c r="A842" s="1">
+        <v>840</v>
+      </c>
+      <c r="B842" s="2">
+        <v>46177</v>
+      </c>
+      <c r="C842">
+        <v>1</v>
+      </c>
+      <c r="D842">
+        <v>52.5434</v>
       </c>
     </row>
   </sheetData>
@@ -35734,7 +35776,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D841"/>
+  <dimension ref="A1:D842"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47506,6 +47548,20 @@
       </c>
       <c r="D841">
         <v>10.7312</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4">
+      <c r="A842" s="1">
+        <v>840</v>
+      </c>
+      <c r="B842" s="2">
+        <v>46177</v>
+      </c>
+      <c r="C842">
+        <v>1</v>
+      </c>
+      <c r="D842">
+        <v>10.8262</v>
       </c>
     </row>
   </sheetData>
@@ -47515,7 +47571,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D841"/>
+  <dimension ref="A1:D842"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59287,6 +59343,20 @@
       </c>
       <c r="D841">
         <v>97.49850000000001</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4">
+      <c r="A842" s="1">
+        <v>840</v>
+      </c>
+      <c r="B842" s="2">
+        <v>46177</v>
+      </c>
+      <c r="C842">
+        <v>1</v>
+      </c>
+      <c r="D842">
+        <v>98.8085</v>
       </c>
     </row>
   </sheetData>
@@ -59296,7 +59366,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D841"/>
+  <dimension ref="A1:D842"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -71068,6 +71138,20 @@
       </c>
       <c r="D841">
         <v>14.8396</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4">
+      <c r="A842" s="1">
+        <v>840</v>
+      </c>
+      <c r="B842" s="2">
+        <v>46177</v>
+      </c>
+      <c r="C842">
+        <v>100</v>
+      </c>
+      <c r="D842">
+        <v>14.8725</v>
       </c>
     </row>
   </sheetData>
@@ -71077,7 +71161,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D841"/>
+  <dimension ref="A1:D842"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -82849,6 +82933,20 @@
       </c>
       <c r="D841">
         <v>45.4293</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4">
+      <c r="A842" s="1">
+        <v>840</v>
+      </c>
+      <c r="B842" s="2">
+        <v>46177</v>
+      </c>
+      <c r="C842">
+        <v>100</v>
+      </c>
+      <c r="D842">
+        <v>45.8512</v>
       </c>
     </row>
   </sheetData>
@@ -82858,7 +82956,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D841"/>
+  <dimension ref="A1:D842"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -94632,6 +94730,20 @@
         <v>92.3151</v>
       </c>
     </row>
+    <row r="842" spans="1:4">
+      <c r="A842" s="1">
+        <v>840</v>
+      </c>
+      <c r="B842" s="2">
+        <v>46177</v>
+      </c>
+      <c r="C842">
+        <v>1</v>
+      </c>
+      <c r="D842">
+        <v>92.89879999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D842"/>
+  <dimension ref="A1:D843"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12177,6 +12177,20 @@
       </c>
       <c r="D842">
         <v>73.3436</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4">
+      <c r="A843" s="1">
+        <v>841</v>
+      </c>
+      <c r="B843" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C843">
+        <v>1</v>
+      </c>
+      <c r="D843">
+        <v>74.29559999999999</v>
       </c>
     </row>
   </sheetData>
@@ -12186,7 +12200,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D842"/>
+  <dimension ref="A1:D843"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -23972,6 +23986,20 @@
       </c>
       <c r="D842">
         <v>85.12430000000001</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4">
+      <c r="A843" s="1">
+        <v>841</v>
+      </c>
+      <c r="B843" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C843">
+        <v>1</v>
+      </c>
+      <c r="D843">
+        <v>86.27119999999999</v>
       </c>
     </row>
   </sheetData>
@@ -23981,7 +24009,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D842"/>
+  <dimension ref="A1:D843"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35767,6 +35795,20 @@
       </c>
       <c r="D842">
         <v>52.5434</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4">
+      <c r="A843" s="1">
+        <v>841</v>
+      </c>
+      <c r="B843" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C843">
+        <v>1</v>
+      </c>
+      <c r="D843">
+        <v>52.9802</v>
       </c>
     </row>
   </sheetData>
@@ -35776,7 +35818,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D842"/>
+  <dimension ref="A1:D843"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47562,6 +47604,20 @@
       </c>
       <c r="D842">
         <v>10.8262</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4">
+      <c r="A843" s="1">
+        <v>841</v>
+      </c>
+      <c r="B843" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C843">
+        <v>1</v>
+      </c>
+      <c r="D843">
+        <v>10.9536</v>
       </c>
     </row>
   </sheetData>
@@ -47571,7 +47627,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D842"/>
+  <dimension ref="A1:D843"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59357,6 +59413,20 @@
       </c>
       <c r="D842">
         <v>98.8085</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4">
+      <c r="A843" s="1">
+        <v>841</v>
+      </c>
+      <c r="B843" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C843">
+        <v>1</v>
+      </c>
+      <c r="D843">
+        <v>99.831</v>
       </c>
     </row>
   </sheetData>
@@ -59366,7 +59436,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D842"/>
+  <dimension ref="A1:D843"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -71152,6 +71222,20 @@
       </c>
       <c r="D842">
         <v>14.8725</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4">
+      <c r="A843" s="1">
+        <v>841</v>
+      </c>
+      <c r="B843" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C843">
+        <v>100</v>
+      </c>
+      <c r="D843">
+        <v>15.1837</v>
       </c>
     </row>
   </sheetData>
@@ -71161,7 +71245,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D842"/>
+  <dimension ref="A1:D843"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -82947,6 +83031,20 @@
       </c>
       <c r="D842">
         <v>45.8512</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4">
+      <c r="A843" s="1">
+        <v>841</v>
+      </c>
+      <c r="B843" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C843">
+        <v>100</v>
+      </c>
+      <c r="D843">
+        <v>46.4638</v>
       </c>
     </row>
   </sheetData>
@@ -82956,7 +83054,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D842"/>
+  <dimension ref="A1:D843"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -94744,6 +94842,20 @@
         <v>92.89879999999999</v>
       </c>
     </row>
+    <row r="843" spans="1:4">
+      <c r="A843" s="1">
+        <v>841</v>
+      </c>
+      <c r="B843" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C843">
+        <v>1</v>
+      </c>
+      <c r="D843">
+        <v>93.9618</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D843"/>
+  <dimension ref="A1:D844"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12191,6 +12191,20 @@
       </c>
       <c r="D843">
         <v>74.29559999999999</v>
+      </c>
+    </row>
+    <row r="844" spans="1:4">
+      <c r="A844" s="1">
+        <v>842</v>
+      </c>
+      <c r="B844" s="2">
+        <v>46179</v>
+      </c>
+      <c r="C844">
+        <v>1</v>
+      </c>
+      <c r="D844">
+        <v>73.4689</v>
       </c>
     </row>
   </sheetData>
@@ -12200,7 +12214,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D843"/>
+  <dimension ref="A1:D844"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24000,6 +24014,20 @@
       </c>
       <c r="D843">
         <v>86.27119999999999</v>
+      </c>
+    </row>
+    <row r="844" spans="1:4">
+      <c r="A844" s="1">
+        <v>842</v>
+      </c>
+      <c r="B844" s="2">
+        <v>46179</v>
+      </c>
+      <c r="C844">
+        <v>1</v>
+      </c>
+      <c r="D844">
+        <v>85.5582</v>
       </c>
     </row>
   </sheetData>
@@ -24009,7 +24037,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D843"/>
+  <dimension ref="A1:D844"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35809,6 +35837,20 @@
       </c>
       <c r="D843">
         <v>52.9802</v>
+      </c>
+    </row>
+    <row r="844" spans="1:4">
+      <c r="A844" s="1">
+        <v>842</v>
+      </c>
+      <c r="B844" s="2">
+        <v>46179</v>
+      </c>
+      <c r="C844">
+        <v>1</v>
+      </c>
+      <c r="D844">
+        <v>52.3172</v>
       </c>
     </row>
   </sheetData>
@@ -35818,7 +35860,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D843"/>
+  <dimension ref="A1:D844"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47618,6 +47660,20 @@
       </c>
       <c r="D843">
         <v>10.9536</v>
+      </c>
+    </row>
+    <row r="844" spans="1:4">
+      <c r="A844" s="1">
+        <v>842</v>
+      </c>
+      <c r="B844" s="2">
+        <v>46179</v>
+      </c>
+      <c r="C844">
+        <v>1</v>
+      </c>
+      <c r="D844">
+        <v>10.853</v>
       </c>
     </row>
   </sheetData>
@@ -47627,7 +47683,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D843"/>
+  <dimension ref="A1:D844"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59427,6 +59483,20 @@
       </c>
       <c r="D843">
         <v>99.831</v>
+      </c>
+    </row>
+    <row r="844" spans="1:4">
+      <c r="A844" s="1">
+        <v>842</v>
+      </c>
+      <c r="B844" s="2">
+        <v>46179</v>
+      </c>
+      <c r="C844">
+        <v>1</v>
+      </c>
+      <c r="D844">
+        <v>98.77889999999999</v>
       </c>
     </row>
   </sheetData>
@@ -59436,7 +59506,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D843"/>
+  <dimension ref="A1:D844"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -71236,6 +71306,20 @@
       </c>
       <c r="D843">
         <v>15.1837</v>
+      </c>
+    </row>
+    <row r="844" spans="1:4">
+      <c r="A844" s="1">
+        <v>842</v>
+      </c>
+      <c r="B844" s="2">
+        <v>46179</v>
+      </c>
+      <c r="C844">
+        <v>100</v>
+      </c>
+      <c r="D844">
+        <v>15.1376</v>
       </c>
     </row>
   </sheetData>
@@ -71245,7 +71329,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D843"/>
+  <dimension ref="A1:D844"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -83045,6 +83129,20 @@
       </c>
       <c r="D843">
         <v>46.4638</v>
+      </c>
+    </row>
+    <row r="844" spans="1:4">
+      <c r="A844" s="1">
+        <v>842</v>
+      </c>
+      <c r="B844" s="2">
+        <v>46179</v>
+      </c>
+      <c r="C844">
+        <v>100</v>
+      </c>
+      <c r="D844">
+        <v>45.9295</v>
       </c>
     </row>
   </sheetData>
@@ -83054,7 +83152,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D843"/>
+  <dimension ref="A1:D844"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -94856,6 +94954,20 @@
         <v>93.9618</v>
       </c>
     </row>
+    <row r="844" spans="1:4">
+      <c r="A844" s="1">
+        <v>842</v>
+      </c>
+      <c r="B844" s="2">
+        <v>46179</v>
+      </c>
+      <c r="C844">
+        <v>1</v>
+      </c>
+      <c r="D844">
+        <v>93.22280000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D844"/>
+  <dimension ref="A1:D846"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12205,6 +12205,34 @@
       </c>
       <c r="D844">
         <v>73.4689</v>
+      </c>
+    </row>
+    <row r="845" spans="1:4">
+      <c r="A845" s="1">
+        <v>843</v>
+      </c>
+      <c r="B845" s="2">
+        <v>46182</v>
+      </c>
+      <c r="C845">
+        <v>1</v>
+      </c>
+      <c r="D845">
+        <v>73.26439999999999</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4">
+      <c r="A846" s="1">
+        <v>844</v>
+      </c>
+      <c r="B846" s="2">
+        <v>46183</v>
+      </c>
+      <c r="C846">
+        <v>1</v>
+      </c>
+      <c r="D846">
+        <v>71.73180000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12214,7 +12242,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D844"/>
+  <dimension ref="A1:D846"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24028,6 +24056,34 @@
       </c>
       <c r="D844">
         <v>85.5582</v>
+      </c>
+    </row>
+    <row r="845" spans="1:4">
+      <c r="A845" s="1">
+        <v>843</v>
+      </c>
+      <c r="B845" s="2">
+        <v>46182</v>
+      </c>
+      <c r="C845">
+        <v>1</v>
+      </c>
+      <c r="D845">
+        <v>85.27979999999999</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4">
+      <c r="A846" s="1">
+        <v>844</v>
+      </c>
+      <c r="B846" s="2">
+        <v>46183</v>
+      </c>
+      <c r="C846">
+        <v>1</v>
+      </c>
+      <c r="D846">
+        <v>82.77849999999999</v>
       </c>
     </row>
   </sheetData>
@@ -24037,7 +24093,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D844"/>
+  <dimension ref="A1:D846"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35851,6 +35907,34 @@
       </c>
       <c r="D844">
         <v>52.3172</v>
+      </c>
+    </row>
+    <row r="845" spans="1:4">
+      <c r="A845" s="1">
+        <v>843</v>
+      </c>
+      <c r="B845" s="2">
+        <v>46182</v>
+      </c>
+      <c r="C845">
+        <v>1</v>
+      </c>
+      <c r="D845">
+        <v>52.1716</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4">
+      <c r="A846" s="1">
+        <v>844</v>
+      </c>
+      <c r="B846" s="2">
+        <v>46183</v>
+      </c>
+      <c r="C846">
+        <v>1</v>
+      </c>
+      <c r="D846">
+        <v>50.6283</v>
       </c>
     </row>
   </sheetData>
@@ -35860,7 +35944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D844"/>
+  <dimension ref="A1:D846"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47674,6 +47758,34 @@
       </c>
       <c r="D844">
         <v>10.853</v>
+      </c>
+    </row>
+    <row r="845" spans="1:4">
+      <c r="A845" s="1">
+        <v>843</v>
+      </c>
+      <c r="B845" s="2">
+        <v>46182</v>
+      </c>
+      <c r="C845">
+        <v>1</v>
+      </c>
+      <c r="D845">
+        <v>10.7826</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4">
+      <c r="A846" s="1">
+        <v>844</v>
+      </c>
+      <c r="B846" s="2">
+        <v>46183</v>
+      </c>
+      <c r="C846">
+        <v>1</v>
+      </c>
+      <c r="D846">
+        <v>10.5831</v>
       </c>
     </row>
   </sheetData>
@@ -47683,7 +47795,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D844"/>
+  <dimension ref="A1:D846"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59497,6 +59609,34 @@
       </c>
       <c r="D844">
         <v>98.77889999999999</v>
+      </c>
+    </row>
+    <row r="845" spans="1:4">
+      <c r="A845" s="1">
+        <v>843</v>
+      </c>
+      <c r="B845" s="2">
+        <v>46182</v>
+      </c>
+      <c r="C845">
+        <v>1</v>
+      </c>
+      <c r="D845">
+        <v>98.0791</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4">
+      <c r="A846" s="1">
+        <v>844</v>
+      </c>
+      <c r="B846" s="2">
+        <v>46183</v>
+      </c>
+      <c r="C846">
+        <v>1</v>
+      </c>
+      <c r="D846">
+        <v>95.7189</v>
       </c>
     </row>
   </sheetData>
@@ -59506,7 +59646,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D844"/>
+  <dimension ref="A1:D846"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -71320,6 +71460,34 @@
       </c>
       <c r="D844">
         <v>15.1376</v>
+      </c>
+    </row>
+    <row r="845" spans="1:4">
+      <c r="A845" s="1">
+        <v>843</v>
+      </c>
+      <c r="B845" s="2">
+        <v>46182</v>
+      </c>
+      <c r="C845">
+        <v>100</v>
+      </c>
+      <c r="D845">
+        <v>15.0304</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4">
+      <c r="A846" s="1">
+        <v>844</v>
+      </c>
+      <c r="B846" s="2">
+        <v>46183</v>
+      </c>
+      <c r="C846">
+        <v>100</v>
+      </c>
+      <c r="D846">
+        <v>14.7968</v>
       </c>
     </row>
   </sheetData>
@@ -71329,7 +71497,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D844"/>
+  <dimension ref="A1:D846"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -83143,6 +83311,34 @@
       </c>
       <c r="D844">
         <v>45.9295</v>
+      </c>
+    </row>
+    <row r="845" spans="1:4">
+      <c r="A845" s="1">
+        <v>843</v>
+      </c>
+      <c r="B845" s="2">
+        <v>46182</v>
+      </c>
+      <c r="C845">
+        <v>100</v>
+      </c>
+      <c r="D845">
+        <v>45.6903</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4">
+      <c r="A846" s="1">
+        <v>844</v>
+      </c>
+      <c r="B846" s="2">
+        <v>46183</v>
+      </c>
+      <c r="C846">
+        <v>100</v>
+      </c>
+      <c r="D846">
+        <v>44.7568</v>
       </c>
     </row>
   </sheetData>
@@ -83152,7 +83348,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D844"/>
+  <dimension ref="A1:D846"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -94968,6 +95164,34 @@
         <v>93.22280000000001</v>
       </c>
     </row>
+    <row r="845" spans="1:4">
+      <c r="A845" s="1">
+        <v>843</v>
+      </c>
+      <c r="B845" s="2">
+        <v>46182</v>
+      </c>
+      <c r="C845">
+        <v>1</v>
+      </c>
+      <c r="D845">
+        <v>91.81</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4">
+      <c r="A846" s="1">
+        <v>844</v>
+      </c>
+      <c r="B846" s="2">
+        <v>46183</v>
+      </c>
+      <c r="C846">
+        <v>1</v>
+      </c>
+      <c r="D846">
+        <v>90.0701</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D846"/>
+  <dimension ref="A1:D847"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12233,6 +12233,20 @@
       </c>
       <c r="D846">
         <v>71.73180000000001</v>
+      </c>
+    </row>
+    <row r="847" spans="1:4">
+      <c r="A847" s="1">
+        <v>845</v>
+      </c>
+      <c r="B847" s="2">
+        <v>46184</v>
+      </c>
+      <c r="C847">
+        <v>1</v>
+      </c>
+      <c r="D847">
+        <v>71.78919999999999</v>
       </c>
     </row>
   </sheetData>
@@ -12242,7 +12256,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D846"/>
+  <dimension ref="A1:D847"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24084,6 +24098,20 @@
       </c>
       <c r="D846">
         <v>82.77849999999999</v>
+      </c>
+    </row>
+    <row r="847" spans="1:4">
+      <c r="A847" s="1">
+        <v>845</v>
+      </c>
+      <c r="B847" s="2">
+        <v>46184</v>
+      </c>
+      <c r="C847">
+        <v>1</v>
+      </c>
+      <c r="D847">
+        <v>83.08159999999999</v>
       </c>
     </row>
   </sheetData>
@@ -24093,7 +24121,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D846"/>
+  <dimension ref="A1:D847"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35935,6 +35963,20 @@
       </c>
       <c r="D846">
         <v>50.6283</v>
+      </c>
+    </row>
+    <row r="847" spans="1:4">
+      <c r="A847" s="1">
+        <v>845</v>
+      </c>
+      <c r="B847" s="2">
+        <v>46184</v>
+      </c>
+      <c r="C847">
+        <v>1</v>
+      </c>
+      <c r="D847">
+        <v>50.396</v>
       </c>
     </row>
   </sheetData>
@@ -35944,7 +35986,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D846"/>
+  <dimension ref="A1:D847"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47786,6 +47828,20 @@
       </c>
       <c r="D846">
         <v>10.5831</v>
+      </c>
+    </row>
+    <row r="847" spans="1:4">
+      <c r="A847" s="1">
+        <v>845</v>
+      </c>
+      <c r="B847" s="2">
+        <v>46184</v>
+      </c>
+      <c r="C847">
+        <v>1</v>
+      </c>
+      <c r="D847">
+        <v>10.5825</v>
       </c>
     </row>
   </sheetData>
@@ -47795,7 +47851,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D846"/>
+  <dimension ref="A1:D847"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59637,6 +59693,20 @@
       </c>
       <c r="D846">
         <v>95.7189</v>
+      </c>
+    </row>
+    <row r="847" spans="1:4">
+      <c r="A847" s="1">
+        <v>845</v>
+      </c>
+      <c r="B847" s="2">
+        <v>46184</v>
+      </c>
+      <c r="C847">
+        <v>1</v>
+      </c>
+      <c r="D847">
+        <v>96.1832</v>
       </c>
     </row>
   </sheetData>
@@ -59646,7 +59716,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D846"/>
+  <dimension ref="A1:D847"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -71488,6 +71558,20 @@
       </c>
       <c r="D846">
         <v>14.7968</v>
+      </c>
+    </row>
+    <row r="847" spans="1:4">
+      <c r="A847" s="1">
+        <v>845</v>
+      </c>
+      <c r="B847" s="2">
+        <v>46184</v>
+      </c>
+      <c r="C847">
+        <v>100</v>
+      </c>
+      <c r="D847">
+        <v>14.6446</v>
       </c>
     </row>
   </sheetData>
@@ -71497,7 +71581,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D846"/>
+  <dimension ref="A1:D847"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -83339,6 +83423,20 @@
       </c>
       <c r="D846">
         <v>44.7568</v>
+      </c>
+    </row>
+    <row r="847" spans="1:4">
+      <c r="A847" s="1">
+        <v>845</v>
+      </c>
+      <c r="B847" s="2">
+        <v>46184</v>
+      </c>
+      <c r="C847">
+        <v>100</v>
+      </c>
+      <c r="D847">
+        <v>44.7508</v>
       </c>
     </row>
   </sheetData>
@@ -83348,7 +83446,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D846"/>
+  <dimension ref="A1:D847"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -95192,6 +95290,20 @@
         <v>90.0701</v>
       </c>
     </row>
+    <row r="847" spans="1:4">
+      <c r="A847" s="1">
+        <v>845</v>
+      </c>
+      <c r="B847" s="2">
+        <v>46184</v>
+      </c>
+      <c r="C847">
+        <v>1</v>
+      </c>
+      <c r="D847">
+        <v>89.8488</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D847"/>
+  <dimension ref="A1:D848"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12247,6 +12247,20 @@
       </c>
       <c r="D847">
         <v>71.78919999999999</v>
+      </c>
+    </row>
+    <row r="848" spans="1:4">
+      <c r="A848" s="1">
+        <v>846</v>
+      </c>
+      <c r="B848" s="2">
+        <v>46185</v>
+      </c>
+      <c r="C848">
+        <v>1</v>
+      </c>
+      <c r="D848">
+        <v>71.90770000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12256,7 +12270,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D847"/>
+  <dimension ref="A1:D848"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24112,6 +24126,20 @@
       </c>
       <c r="D847">
         <v>83.08159999999999</v>
+      </c>
+    </row>
+    <row r="848" spans="1:4">
+      <c r="A848" s="1">
+        <v>846</v>
+      </c>
+      <c r="B848" s="2">
+        <v>46185</v>
+      </c>
+      <c r="C848">
+        <v>1</v>
+      </c>
+      <c r="D848">
+        <v>82.9743</v>
       </c>
     </row>
   </sheetData>
@@ -24121,7 +24149,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D847"/>
+  <dimension ref="A1:D848"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -35977,6 +36005,20 @@
       </c>
       <c r="D847">
         <v>50.396</v>
+      </c>
+    </row>
+    <row r="848" spans="1:4">
+      <c r="A848" s="1">
+        <v>846</v>
+      </c>
+      <c r="B848" s="2">
+        <v>46185</v>
+      </c>
+      <c r="C848">
+        <v>1</v>
+      </c>
+      <c r="D848">
+        <v>50.3929</v>
       </c>
     </row>
   </sheetData>
@@ -35986,7 +36028,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D847"/>
+  <dimension ref="A1:D848"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47842,6 +47884,20 @@
       </c>
       <c r="D847">
         <v>10.5825</v>
+      </c>
+    </row>
+    <row r="848" spans="1:4">
+      <c r="A848" s="1">
+        <v>846</v>
+      </c>
+      <c r="B848" s="2">
+        <v>46185</v>
+      </c>
+      <c r="C848">
+        <v>1</v>
+      </c>
+      <c r="D848">
+        <v>10.6064</v>
       </c>
     </row>
   </sheetData>
@@ -47851,7 +47907,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D847"/>
+  <dimension ref="A1:D848"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59707,6 +59763,20 @@
       </c>
       <c r="D847">
         <v>96.1832</v>
+      </c>
+    </row>
+    <row r="848" spans="1:4">
+      <c r="A848" s="1">
+        <v>846</v>
+      </c>
+      <c r="B848" s="2">
+        <v>46185</v>
+      </c>
+      <c r="C848">
+        <v>1</v>
+      </c>
+      <c r="D848">
+        <v>96.3707</v>
       </c>
     </row>
   </sheetData>
@@ -59716,7 +59786,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D847"/>
+  <dimension ref="A1:D848"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -71572,6 +71642,20 @@
       </c>
       <c r="D847">
         <v>14.6446</v>
+      </c>
+    </row>
+    <row r="848" spans="1:4">
+      <c r="A848" s="1">
+        <v>846</v>
+      </c>
+      <c r="B848" s="2">
+        <v>46185</v>
+      </c>
+      <c r="C848">
+        <v>100</v>
+      </c>
+      <c r="D848">
+        <v>14.7174</v>
       </c>
     </row>
   </sheetData>
@@ -71581,7 +71665,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D847"/>
+  <dimension ref="A1:D848"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -83437,6 +83521,20 @@
       </c>
       <c r="D847">
         <v>44.7508</v>
+      </c>
+    </row>
+    <row r="848" spans="1:4">
+      <c r="A848" s="1">
+        <v>846</v>
+      </c>
+      <c r="B848" s="2">
+        <v>46185</v>
+      </c>
+      <c r="C848">
+        <v>100</v>
+      </c>
+      <c r="D848">
+        <v>44.7911</v>
       </c>
     </row>
   </sheetData>
@@ -83446,7 +83544,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D847"/>
+  <dimension ref="A1:D848"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -95304,6 +95402,20 @@
         <v>89.8488</v>
       </c>
     </row>
+    <row r="848" spans="1:4">
+      <c r="A848" s="1">
+        <v>846</v>
+      </c>
+      <c r="B848" s="2">
+        <v>46185</v>
+      </c>
+      <c r="C848">
+        <v>1</v>
+      </c>
+      <c r="D848">
+        <v>89.88460000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D848"/>
+  <dimension ref="A1:D849"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12261,6 +12261,20 @@
       </c>
       <c r="D848">
         <v>71.90770000000001</v>
+      </c>
+    </row>
+    <row r="849" spans="1:4">
+      <c r="A849" s="1">
+        <v>847</v>
+      </c>
+      <c r="B849" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C849">
+        <v>1</v>
+      </c>
+      <c r="D849">
+        <v>72.4513</v>
       </c>
     </row>
   </sheetData>
@@ -12270,7 +12284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D848"/>
+  <dimension ref="A1:D849"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24140,6 +24154,20 @@
       </c>
       <c r="D848">
         <v>82.9743</v>
+      </c>
+    </row>
+    <row r="849" spans="1:4">
+      <c r="A849" s="1">
+        <v>847</v>
+      </c>
+      <c r="B849" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C849">
+        <v>1</v>
+      </c>
+      <c r="D849">
+        <v>83.8044</v>
       </c>
     </row>
   </sheetData>
@@ -24149,7 +24177,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D848"/>
+  <dimension ref="A1:D849"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36019,6 +36047,20 @@
       </c>
       <c r="D848">
         <v>50.3929</v>
+      </c>
+    </row>
+    <row r="849" spans="1:4">
+      <c r="A849" s="1">
+        <v>847</v>
+      </c>
+      <c r="B849" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C849">
+        <v>1</v>
+      </c>
+      <c r="D849">
+        <v>51.3028</v>
       </c>
     </row>
   </sheetData>
@@ -36028,7 +36070,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D848"/>
+  <dimension ref="A1:D849"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47898,6 +47940,20 @@
       </c>
       <c r="D848">
         <v>10.6064</v>
+      </c>
+    </row>
+    <row r="849" spans="1:4">
+      <c r="A849" s="1">
+        <v>847</v>
+      </c>
+      <c r="B849" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C849">
+        <v>1</v>
+      </c>
+      <c r="D849">
+        <v>10.7047</v>
       </c>
     </row>
   </sheetData>
@@ -47907,7 +47963,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D848"/>
+  <dimension ref="A1:D849"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59777,6 +59833,20 @@
       </c>
       <c r="D848">
         <v>96.3707</v>
+      </c>
+    </row>
+    <row r="849" spans="1:4">
+      <c r="A849" s="1">
+        <v>847</v>
+      </c>
+      <c r="B849" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C849">
+        <v>1</v>
+      </c>
+      <c r="D849">
+        <v>97.1789</v>
       </c>
     </row>
   </sheetData>
@@ -59786,7 +59856,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D848"/>
+  <dimension ref="A1:D849"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -71656,6 +71726,20 @@
       </c>
       <c r="D848">
         <v>14.7174</v>
+      </c>
+    </row>
+    <row r="849" spans="1:4">
+      <c r="A849" s="1">
+        <v>847</v>
+      </c>
+      <c r="B849" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C849">
+        <v>100</v>
+      </c>
+      <c r="D849">
+        <v>14.8062</v>
       </c>
     </row>
   </sheetData>
@@ -71665,7 +71749,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D848"/>
+  <dimension ref="A1:D849"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -83535,6 +83619,20 @@
       </c>
       <c r="D848">
         <v>44.7911</v>
+      </c>
+    </row>
+    <row r="849" spans="1:4">
+      <c r="A849" s="1">
+        <v>847</v>
+      </c>
+      <c r="B849" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C849">
+        <v>100</v>
+      </c>
+      <c r="D849">
+        <v>45.2481</v>
       </c>
     </row>
   </sheetData>
@@ -83544,7 +83642,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D848"/>
+  <dimension ref="A1:D849"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -95416,6 +95514,20 @@
         <v>89.88460000000001</v>
       </c>
     </row>
+    <row r="849" spans="1:4">
+      <c r="A849" s="1">
+        <v>847</v>
+      </c>
+      <c r="B849" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C849">
+        <v>1</v>
+      </c>
+      <c r="D849">
+        <v>91.3175</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D849"/>
+  <dimension ref="A1:D850"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12275,6 +12275,20 @@
       </c>
       <c r="D849">
         <v>72.4513</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4">
+      <c r="A850" s="1">
+        <v>848</v>
+      </c>
+      <c r="B850" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C850">
+        <v>1</v>
+      </c>
+      <c r="D850">
+        <v>72.1388</v>
       </c>
     </row>
   </sheetData>
@@ -12284,7 +12298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D849"/>
+  <dimension ref="A1:D850"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24168,6 +24182,20 @@
       </c>
       <c r="D849">
         <v>83.8044</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4">
+      <c r="A850" s="1">
+        <v>848</v>
+      </c>
+      <c r="B850" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C850">
+        <v>1</v>
+      </c>
+      <c r="D850">
+        <v>83.7315</v>
       </c>
     </row>
   </sheetData>
@@ -24177,7 +24205,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D849"/>
+  <dimension ref="A1:D850"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36061,6 +36089,20 @@
       </c>
       <c r="D849">
         <v>51.3028</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4">
+      <c r="A850" s="1">
+        <v>848</v>
+      </c>
+      <c r="B850" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C850">
+        <v>1</v>
+      </c>
+      <c r="D850">
+        <v>50.8434</v>
       </c>
     </row>
   </sheetData>
@@ -36070,7 +36112,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D849"/>
+  <dimension ref="A1:D850"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -47954,6 +47996,20 @@
       </c>
       <c r="D849">
         <v>10.7047</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4">
+      <c r="A850" s="1">
+        <v>848</v>
+      </c>
+      <c r="B850" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C850">
+        <v>1</v>
+      </c>
+      <c r="D850">
+        <v>10.6624</v>
       </c>
     </row>
   </sheetData>
@@ -47963,7 +48019,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D849"/>
+  <dimension ref="A1:D850"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59847,6 +59903,20 @@
       </c>
       <c r="D849">
         <v>97.1789</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4">
+      <c r="A850" s="1">
+        <v>848</v>
+      </c>
+      <c r="B850" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C850">
+        <v>1</v>
+      </c>
+      <c r="D850">
+        <v>96.9618</v>
       </c>
     </row>
   </sheetData>
@@ -59856,7 +59926,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D849"/>
+  <dimension ref="A1:D850"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -71740,6 +71810,20 @@
       </c>
       <c r="D849">
         <v>14.8062</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4">
+      <c r="A850" s="1">
+        <v>848</v>
+      </c>
+      <c r="B850" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C850">
+        <v>100</v>
+      </c>
+      <c r="D850">
+        <v>14.6812</v>
       </c>
     </row>
   </sheetData>
@@ -71749,7 +71833,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D849"/>
+  <dimension ref="A1:D850"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -83633,6 +83717,20 @@
       </c>
       <c r="D849">
         <v>45.2481</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4">
+      <c r="A850" s="1">
+        <v>848</v>
+      </c>
+      <c r="B850" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C850">
+        <v>100</v>
+      </c>
+      <c r="D850">
+        <v>45.0164</v>
       </c>
     </row>
   </sheetData>
@@ -83642,7 +83740,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D849"/>
+  <dimension ref="A1:D850"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -95528,6 +95626,20 @@
         <v>91.3175</v>
       </c>
     </row>
+    <row r="850" spans="1:4">
+      <c r="A850" s="1">
+        <v>848</v>
+      </c>
+      <c r="B850" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C850">
+        <v>1</v>
+      </c>
+      <c r="D850">
+        <v>90.7863</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D850"/>
+  <dimension ref="A1:D851"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12289,6 +12289,20 @@
       </c>
       <c r="D850">
         <v>72.1388</v>
+      </c>
+    </row>
+    <row r="851" spans="1:4">
+      <c r="A851" s="1">
+        <v>849</v>
+      </c>
+      <c r="B851" s="2">
+        <v>46191</v>
+      </c>
+      <c r="C851">
+        <v>1</v>
+      </c>
+      <c r="D851">
+        <v>72.7479</v>
       </c>
     </row>
   </sheetData>
@@ -12298,7 +12312,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D850"/>
+  <dimension ref="A1:D851"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24196,6 +24210,20 @@
       </c>
       <c r="D850">
         <v>83.7315</v>
+      </c>
+    </row>
+    <row r="851" spans="1:4">
+      <c r="A851" s="1">
+        <v>849</v>
+      </c>
+      <c r="B851" s="2">
+        <v>46191</v>
+      </c>
+      <c r="C851">
+        <v>1</v>
+      </c>
+      <c r="D851">
+        <v>84.3439</v>
       </c>
     </row>
   </sheetData>
@@ -24205,7 +24233,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D850"/>
+  <dimension ref="A1:D851"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36103,6 +36131,20 @@
       </c>
       <c r="D850">
         <v>50.8434</v>
+      </c>
+    </row>
+    <row r="851" spans="1:4">
+      <c r="A851" s="1">
+        <v>849</v>
+      </c>
+      <c r="B851" s="2">
+        <v>46191</v>
+      </c>
+      <c r="C851">
+        <v>1</v>
+      </c>
+      <c r="D851">
+        <v>51.3527</v>
       </c>
     </row>
   </sheetData>
@@ -36112,7 +36154,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D850"/>
+  <dimension ref="A1:D851"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48010,6 +48052,20 @@
       </c>
       <c r="D850">
         <v>10.6624</v>
+      </c>
+    </row>
+    <row r="851" spans="1:4">
+      <c r="A851" s="1">
+        <v>849</v>
+      </c>
+      <c r="B851" s="2">
+        <v>46191</v>
+      </c>
+      <c r="C851">
+        <v>1</v>
+      </c>
+      <c r="D851">
+        <v>10.7589</v>
       </c>
     </row>
   </sheetData>
@@ -48019,7 +48075,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D850"/>
+  <dimension ref="A1:D851"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59917,6 +59973,20 @@
       </c>
       <c r="D850">
         <v>96.9618</v>
+      </c>
+    </row>
+    <row r="851" spans="1:4">
+      <c r="A851" s="1">
+        <v>849</v>
+      </c>
+      <c r="B851" s="2">
+        <v>46191</v>
+      </c>
+      <c r="C851">
+        <v>1</v>
+      </c>
+      <c r="D851">
+        <v>97.6859</v>
       </c>
     </row>
   </sheetData>
@@ -59926,7 +59996,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D850"/>
+  <dimension ref="A1:D851"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -71824,6 +71894,20 @@
       </c>
       <c r="D850">
         <v>14.6812</v>
+      </c>
+    </row>
+    <row r="851" spans="1:4">
+      <c r="A851" s="1">
+        <v>849</v>
+      </c>
+      <c r="B851" s="2">
+        <v>46191</v>
+      </c>
+      <c r="C851">
+        <v>100</v>
+      </c>
+      <c r="D851">
+        <v>14.9328</v>
       </c>
     </row>
   </sheetData>
@@ -71833,7 +71917,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D850"/>
+  <dimension ref="A1:D851"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -83731,6 +83815,20 @@
       </c>
       <c r="D850">
         <v>45.0164</v>
+      </c>
+    </row>
+    <row r="851" spans="1:4">
+      <c r="A851" s="1">
+        <v>849</v>
+      </c>
+      <c r="B851" s="2">
+        <v>46191</v>
+      </c>
+      <c r="C851">
+        <v>100</v>
+      </c>
+      <c r="D851">
+        <v>45.3569</v>
       </c>
     </row>
   </sheetData>
@@ -83740,7 +83838,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D850"/>
+  <dimension ref="A1:D851"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -95640,6 +95738,20 @@
         <v>90.7863</v>
       </c>
     </row>
+    <row r="851" spans="1:4">
+      <c r="A851" s="1">
+        <v>849</v>
+      </c>
+      <c r="B851" s="2">
+        <v>46191</v>
+      </c>
+      <c r="C851">
+        <v>1</v>
+      </c>
+      <c r="D851">
+        <v>91.86499999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D851"/>
+  <dimension ref="A1:D852"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12303,6 +12303,20 @@
       </c>
       <c r="D851">
         <v>72.7479</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4">
+      <c r="A852" s="1">
+        <v>850</v>
+      </c>
+      <c r="B852" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C852">
+        <v>1</v>
+      </c>
+      <c r="D852">
+        <v>73.3591</v>
       </c>
     </row>
   </sheetData>
@@ -12312,7 +12326,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D851"/>
+  <dimension ref="A1:D852"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24224,6 +24238,20 @@
       </c>
       <c r="D851">
         <v>84.3439</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4">
+      <c r="A852" s="1">
+        <v>850</v>
+      </c>
+      <c r="B852" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C852">
+        <v>1</v>
+      </c>
+      <c r="D852">
+        <v>85.0305</v>
       </c>
     </row>
   </sheetData>
@@ -24233,7 +24261,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D851"/>
+  <dimension ref="A1:D852"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36145,6 +36173,20 @@
       </c>
       <c r="D851">
         <v>51.3527</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4">
+      <c r="A852" s="1">
+        <v>850</v>
+      </c>
+      <c r="B852" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C852">
+        <v>1</v>
+      </c>
+      <c r="D852">
+        <v>51.5788</v>
       </c>
     </row>
   </sheetData>
@@ -36154,7 +36196,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D851"/>
+  <dimension ref="A1:D852"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48066,6 +48108,20 @@
       </c>
       <c r="D851">
         <v>10.7589</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4">
+      <c r="A852" s="1">
+        <v>850</v>
+      </c>
+      <c r="B852" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C852">
+        <v>1</v>
+      </c>
+      <c r="D852">
+        <v>10.8284</v>
       </c>
     </row>
   </sheetData>
@@ -48075,7 +48131,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D851"/>
+  <dimension ref="A1:D852"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -59987,6 +60043,20 @@
       </c>
       <c r="D851">
         <v>97.6859</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4">
+      <c r="A852" s="1">
+        <v>850</v>
+      </c>
+      <c r="B852" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C852">
+        <v>1</v>
+      </c>
+      <c r="D852">
+        <v>98.2572</v>
       </c>
     </row>
   </sheetData>
@@ -59996,7 +60066,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D851"/>
+  <dimension ref="A1:D852"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -71908,6 +71978,20 @@
       </c>
       <c r="D851">
         <v>14.9328</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4">
+      <c r="A852" s="1">
+        <v>850</v>
+      </c>
+      <c r="B852" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C852">
+        <v>100</v>
+      </c>
+      <c r="D852">
+        <v>14.9899</v>
       </c>
     </row>
   </sheetData>
@@ -71917,7 +72001,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D851"/>
+  <dimension ref="A1:D852"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -83829,6 +83913,20 @@
       </c>
       <c r="D851">
         <v>45.3569</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4">
+      <c r="A852" s="1">
+        <v>850</v>
+      </c>
+      <c r="B852" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C852">
+        <v>100</v>
+      </c>
+      <c r="D852">
+        <v>45.6469</v>
       </c>
     </row>
   </sheetData>
@@ -83838,7 +83936,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D851"/>
+  <dimension ref="A1:D852"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -95752,6 +95850,20 @@
         <v>91.86499999999999</v>
       </c>
     </row>
+    <row r="852" spans="1:4">
+      <c r="A852" s="1">
+        <v>850</v>
+      </c>
+      <c r="B852" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C852">
+        <v>1</v>
+      </c>
+      <c r="D852">
+        <v>91.4132</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D852"/>
+  <dimension ref="A1:D853"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12317,6 +12317,20 @@
       </c>
       <c r="D852">
         <v>73.3591</v>
+      </c>
+    </row>
+    <row r="853" spans="1:4">
+      <c r="A853" s="1">
+        <v>851</v>
+      </c>
+      <c r="B853" s="2">
+        <v>46193</v>
+      </c>
+      <c r="C853">
+        <v>1</v>
+      </c>
+      <c r="D853">
+        <v>73.43899999999999</v>
       </c>
     </row>
   </sheetData>
@@ -12326,7 +12340,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D852"/>
+  <dimension ref="A1:D853"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24252,6 +24266,20 @@
       </c>
       <c r="D852">
         <v>85.0305</v>
+      </c>
+    </row>
+    <row r="853" spans="1:4">
+      <c r="A853" s="1">
+        <v>851</v>
+      </c>
+      <c r="B853" s="2">
+        <v>46193</v>
+      </c>
+      <c r="C853">
+        <v>1</v>
+      </c>
+      <c r="D853">
+        <v>84.16840000000001</v>
       </c>
     </row>
   </sheetData>
@@ -24261,7 +24289,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D852"/>
+  <dimension ref="A1:D853"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36187,6 +36215,20 @@
       </c>
       <c r="D852">
         <v>51.5788</v>
+      </c>
+    </row>
+    <row r="853" spans="1:4">
+      <c r="A853" s="1">
+        <v>851</v>
+      </c>
+      <c r="B853" s="2">
+        <v>46193</v>
+      </c>
+      <c r="C853">
+        <v>1</v>
+      </c>
+      <c r="D853">
+        <v>51.444</v>
       </c>
     </row>
   </sheetData>
@@ -36196,7 +36238,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D852"/>
+  <dimension ref="A1:D853"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48122,6 +48164,20 @@
       </c>
       <c r="D852">
         <v>10.8284</v>
+      </c>
+    </row>
+    <row r="853" spans="1:4">
+      <c r="A853" s="1">
+        <v>851</v>
+      </c>
+      <c r="B853" s="2">
+        <v>46193</v>
+      </c>
+      <c r="C853">
+        <v>1</v>
+      </c>
+      <c r="D853">
+        <v>10.806</v>
       </c>
     </row>
   </sheetData>
@@ -48131,7 +48187,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D852"/>
+  <dimension ref="A1:D853"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60057,6 +60113,20 @@
       </c>
       <c r="D852">
         <v>98.2572</v>
+      </c>
+    </row>
+    <row r="853" spans="1:4">
+      <c r="A853" s="1">
+        <v>851</v>
+      </c>
+      <c r="B853" s="2">
+        <v>46193</v>
+      </c>
+      <c r="C853">
+        <v>1</v>
+      </c>
+      <c r="D853">
+        <v>97.3287</v>
       </c>
     </row>
   </sheetData>
@@ -60066,7 +60136,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D852"/>
+  <dimension ref="A1:D853"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -71992,6 +72062,20 @@
       </c>
       <c r="D852">
         <v>14.9899</v>
+      </c>
+    </row>
+    <row r="853" spans="1:4">
+      <c r="A853" s="1">
+        <v>851</v>
+      </c>
+      <c r="B853" s="2">
+        <v>46193</v>
+      </c>
+      <c r="C853">
+        <v>100</v>
+      </c>
+      <c r="D853">
+        <v>15.0573</v>
       </c>
     </row>
   </sheetData>
@@ -72001,7 +72085,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D852"/>
+  <dimension ref="A1:D853"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -83927,6 +84011,20 @@
       </c>
       <c r="D852">
         <v>45.6469</v>
+      </c>
+    </row>
+    <row r="853" spans="1:4">
+      <c r="A853" s="1">
+        <v>851</v>
+      </c>
+      <c r="B853" s="2">
+        <v>46193</v>
+      </c>
+      <c r="C853">
+        <v>100</v>
+      </c>
+      <c r="D853">
+        <v>45.5775</v>
       </c>
     </row>
   </sheetData>
@@ -83936,7 +84034,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D852"/>
+  <dimension ref="A1:D853"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -95864,6 +95962,20 @@
         <v>91.4132</v>
       </c>
     </row>
+    <row r="853" spans="1:4">
+      <c r="A853" s="1">
+        <v>851</v>
+      </c>
+      <c r="B853" s="2">
+        <v>46193</v>
+      </c>
+      <c r="C853">
+        <v>1</v>
+      </c>
+      <c r="D853">
+        <v>91.1267</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D853"/>
+  <dimension ref="A1:D854"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12331,6 +12331,20 @@
       </c>
       <c r="D853">
         <v>73.43899999999999</v>
+      </c>
+    </row>
+    <row r="854" spans="1:4">
+      <c r="A854" s="1">
+        <v>852</v>
+      </c>
+      <c r="B854" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C854">
+        <v>1</v>
+      </c>
+      <c r="D854">
+        <v>73.765</v>
       </c>
     </row>
   </sheetData>
@@ -12340,7 +12354,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D853"/>
+  <dimension ref="A1:D854"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24280,6 +24294,20 @@
       </c>
       <c r="D853">
         <v>84.16840000000001</v>
+      </c>
+    </row>
+    <row r="854" spans="1:4">
+      <c r="A854" s="1">
+        <v>852</v>
+      </c>
+      <c r="B854" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C854">
+        <v>1</v>
+      </c>
+      <c r="D854">
+        <v>84.58629999999999</v>
       </c>
     </row>
   </sheetData>
@@ -24289,7 +24317,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D853"/>
+  <dimension ref="A1:D854"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36229,6 +36257,20 @@
       </c>
       <c r="D853">
         <v>51.444</v>
+      </c>
+    </row>
+    <row r="854" spans="1:4">
+      <c r="A854" s="1">
+        <v>852</v>
+      </c>
+      <c r="B854" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C854">
+        <v>1</v>
+      </c>
+      <c r="D854">
+        <v>51.665</v>
       </c>
     </row>
   </sheetData>
@@ -36238,7 +36280,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D853"/>
+  <dimension ref="A1:D854"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48178,6 +48220,20 @@
       </c>
       <c r="D853">
         <v>10.806</v>
+      </c>
+    </row>
+    <row r="854" spans="1:4">
+      <c r="A854" s="1">
+        <v>852</v>
+      </c>
+      <c r="B854" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C854">
+        <v>1</v>
+      </c>
+      <c r="D854">
+        <v>10.8847</v>
       </c>
     </row>
   </sheetData>
@@ -48187,7 +48243,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D853"/>
+  <dimension ref="A1:D854"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60127,6 +60183,20 @@
       </c>
       <c r="D853">
         <v>97.3287</v>
+      </c>
+    </row>
+    <row r="854" spans="1:4">
+      <c r="A854" s="1">
+        <v>852</v>
+      </c>
+      <c r="B854" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C854">
+        <v>1</v>
+      </c>
+      <c r="D854">
+        <v>97.5985</v>
       </c>
     </row>
   </sheetData>
@@ -60136,7 +60206,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D853"/>
+  <dimension ref="A1:D854"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -72076,6 +72146,20 @@
       </c>
       <c r="D853">
         <v>15.0573</v>
+      </c>
+    </row>
+    <row r="854" spans="1:4">
+      <c r="A854" s="1">
+        <v>852</v>
+      </c>
+      <c r="B854" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C854">
+        <v>100</v>
+      </c>
+      <c r="D854">
+        <v>15.1043</v>
       </c>
     </row>
   </sheetData>
@@ -72085,7 +72169,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D853"/>
+  <dimension ref="A1:D854"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -84025,6 +84109,20 @@
       </c>
       <c r="D853">
         <v>45.5775</v>
+      </c>
+    </row>
+    <row r="854" spans="1:4">
+      <c r="A854" s="1">
+        <v>852</v>
+      </c>
+      <c r="B854" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C854">
+        <v>100</v>
+      </c>
+      <c r="D854">
+        <v>45.6551</v>
       </c>
     </row>
   </sheetData>
@@ -84034,7 +84132,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D853"/>
+  <dimension ref="A1:D854"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -95976,6 +96074,20 @@
         <v>91.1267</v>
       </c>
     </row>
+    <row r="854" spans="1:4">
+      <c r="A854" s="1">
+        <v>852</v>
+      </c>
+      <c r="B854" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C854">
+        <v>1</v>
+      </c>
+      <c r="D854">
+        <v>91.282</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D854"/>
+  <dimension ref="A1:D855"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12345,6 +12345,20 @@
       </c>
       <c r="D854">
         <v>73.765</v>
+      </c>
+    </row>
+    <row r="855" spans="1:4">
+      <c r="A855" s="1">
+        <v>853</v>
+      </c>
+      <c r="B855" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C855">
+        <v>1</v>
+      </c>
+      <c r="D855">
+        <v>74.62</v>
       </c>
     </row>
   </sheetData>
@@ -12354,7 +12368,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D854"/>
+  <dimension ref="A1:D855"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24308,6 +24322,20 @@
       </c>
       <c r="D854">
         <v>84.58629999999999</v>
+      </c>
+    </row>
+    <row r="855" spans="1:4">
+      <c r="A855" s="1">
+        <v>853</v>
+      </c>
+      <c r="B855" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C855">
+        <v>1</v>
+      </c>
+      <c r="D855">
+        <v>85.4847</v>
       </c>
     </row>
   </sheetData>
@@ -24317,7 +24345,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D854"/>
+  <dimension ref="A1:D855"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36271,6 +36299,20 @@
       </c>
       <c r="D854">
         <v>51.665</v>
+      </c>
+    </row>
+    <row r="855" spans="1:4">
+      <c r="A855" s="1">
+        <v>853</v>
+      </c>
+      <c r="B855" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C855">
+        <v>1</v>
+      </c>
+      <c r="D855">
+        <v>51.9654</v>
       </c>
     </row>
   </sheetData>
@@ -36280,7 +36322,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D854"/>
+  <dimension ref="A1:D855"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48234,6 +48276,20 @@
       </c>
       <c r="D854">
         <v>10.8847</v>
+      </c>
+    </row>
+    <row r="855" spans="1:4">
+      <c r="A855" s="1">
+        <v>853</v>
+      </c>
+      <c r="B855" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C855">
+        <v>1</v>
+      </c>
+      <c r="D855">
+        <v>10.9947</v>
       </c>
     </row>
   </sheetData>
@@ -48243,7 +48299,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D854"/>
+  <dimension ref="A1:D855"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60197,6 +60253,20 @@
       </c>
       <c r="D854">
         <v>97.5985</v>
+      </c>
+    </row>
+    <row r="855" spans="1:4">
+      <c r="A855" s="1">
+        <v>853</v>
+      </c>
+      <c r="B855" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C855">
+        <v>1</v>
+      </c>
+      <c r="D855">
+        <v>98.961</v>
       </c>
     </row>
   </sheetData>
@@ -60206,7 +60276,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D854"/>
+  <dimension ref="A1:D855"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -72160,6 +72230,20 @@
       </c>
       <c r="D854">
         <v>15.1043</v>
+      </c>
+    </row>
+    <row r="855" spans="1:4">
+      <c r="A855" s="1">
+        <v>853</v>
+      </c>
+      <c r="B855" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C855">
+        <v>100</v>
+      </c>
+      <c r="D855">
+        <v>15.3221</v>
       </c>
     </row>
   </sheetData>
@@ -72169,7 +72253,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D854"/>
+  <dimension ref="A1:D855"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -84123,6 +84207,20 @@
       </c>
       <c r="D854">
         <v>45.6551</v>
+      </c>
+    </row>
+    <row r="855" spans="1:4">
+      <c r="A855" s="1">
+        <v>853</v>
+      </c>
+      <c r="B855" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C855">
+        <v>100</v>
+      </c>
+      <c r="D855">
+        <v>46.1757</v>
       </c>
     </row>
   </sheetData>
@@ -84132,7 +84230,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D854"/>
+  <dimension ref="A1:D855"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -96088,6 +96186,20 @@
         <v>91.282</v>
       </c>
     </row>
+    <row r="855" spans="1:4">
+      <c r="A855" s="1">
+        <v>853</v>
+      </c>
+      <c r="B855" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C855">
+        <v>1</v>
+      </c>
+      <c r="D855">
+        <v>92.14619999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D855"/>
+  <dimension ref="A1:D856"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12359,6 +12359,20 @@
       </c>
       <c r="D855">
         <v>74.62</v>
+      </c>
+    </row>
+    <row r="856" spans="1:4">
+      <c r="A856" s="1">
+        <v>854</v>
+      </c>
+      <c r="B856" s="2">
+        <v>46198</v>
+      </c>
+      <c r="C856">
+        <v>1</v>
+      </c>
+      <c r="D856">
+        <v>74.77379999999999</v>
       </c>
     </row>
   </sheetData>
@@ -12368,7 +12382,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D855"/>
+  <dimension ref="A1:D856"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24336,6 +24350,20 @@
       </c>
       <c r="D855">
         <v>85.4847</v>
+      </c>
+    </row>
+    <row r="856" spans="1:4">
+      <c r="A856" s="1">
+        <v>854</v>
+      </c>
+      <c r="B856" s="2">
+        <v>46198</v>
+      </c>
+      <c r="C856">
+        <v>1</v>
+      </c>
+      <c r="D856">
+        <v>85.1823</v>
       </c>
     </row>
   </sheetData>
@@ -24345,7 +24373,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D855"/>
+  <dimension ref="A1:D856"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36313,6 +36341,20 @@
       </c>
       <c r="D855">
         <v>51.9654</v>
+      </c>
+    </row>
+    <row r="856" spans="1:4">
+      <c r="A856" s="1">
+        <v>854</v>
+      </c>
+      <c r="B856" s="2">
+        <v>46198</v>
+      </c>
+      <c r="C856">
+        <v>1</v>
+      </c>
+      <c r="D856">
+        <v>51.6911</v>
       </c>
     </row>
   </sheetData>
@@ -36322,7 +36364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D855"/>
+  <dimension ref="A1:D856"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48290,6 +48332,20 @@
       </c>
       <c r="D855">
         <v>10.9947</v>
+      </c>
+    </row>
+    <row r="856" spans="1:4">
+      <c r="A856" s="1">
+        <v>854</v>
+      </c>
+      <c r="B856" s="2">
+        <v>46198</v>
+      </c>
+      <c r="C856">
+        <v>1</v>
+      </c>
+      <c r="D856">
+        <v>10.9713</v>
       </c>
     </row>
   </sheetData>
@@ -48299,7 +48355,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D855"/>
+  <dimension ref="A1:D856"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60267,6 +60323,20 @@
       </c>
       <c r="D855">
         <v>98.961</v>
+      </c>
+    </row>
+    <row r="856" spans="1:4">
+      <c r="A856" s="1">
+        <v>854</v>
+      </c>
+      <c r="B856" s="2">
+        <v>46198</v>
+      </c>
+      <c r="C856">
+        <v>1</v>
+      </c>
+      <c r="D856">
+        <v>98.7089</v>
       </c>
     </row>
   </sheetData>
@@ -60276,7 +60346,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D855"/>
+  <dimension ref="A1:D856"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -72244,6 +72314,20 @@
       </c>
       <c r="D855">
         <v>15.3221</v>
+      </c>
+    </row>
+    <row r="856" spans="1:4">
+      <c r="A856" s="1">
+        <v>854</v>
+      </c>
+      <c r="B856" s="2">
+        <v>46198</v>
+      </c>
+      <c r="C856">
+        <v>100</v>
+      </c>
+      <c r="D856">
+        <v>15.3795</v>
       </c>
     </row>
   </sheetData>
@@ -72253,7 +72337,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D855"/>
+  <dimension ref="A1:D856"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -84221,6 +84305,20 @@
       </c>
       <c r="D855">
         <v>46.1757</v>
+      </c>
+    </row>
+    <row r="856" spans="1:4">
+      <c r="A856" s="1">
+        <v>854</v>
+      </c>
+      <c r="B856" s="2">
+        <v>46198</v>
+      </c>
+      <c r="C856">
+        <v>100</v>
+      </c>
+      <c r="D856">
+        <v>46.2623</v>
       </c>
     </row>
   </sheetData>
@@ -84230,7 +84328,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D855"/>
+  <dimension ref="A1:D856"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -96200,6 +96298,20 @@
         <v>92.14619999999999</v>
       </c>
     </row>
+    <row r="856" spans="1:4">
+      <c r="A856" s="1">
+        <v>854</v>
+      </c>
+      <c r="B856" s="2">
+        <v>46198</v>
+      </c>
+      <c r="C856">
+        <v>1</v>
+      </c>
+      <c r="D856">
+        <v>92.1313</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D856"/>
+  <dimension ref="A1:D857"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12373,6 +12373,20 @@
       </c>
       <c r="D856">
         <v>74.77379999999999</v>
+      </c>
+    </row>
+    <row r="857" spans="1:4">
+      <c r="A857" s="1">
+        <v>855</v>
+      </c>
+      <c r="B857" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C857">
+        <v>1</v>
+      </c>
+      <c r="D857">
+        <v>75.6347</v>
       </c>
     </row>
   </sheetData>
@@ -12382,7 +12396,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D856"/>
+  <dimension ref="A1:D857"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24364,6 +24378,20 @@
       </c>
       <c r="D856">
         <v>85.1823</v>
+      </c>
+    </row>
+    <row r="857" spans="1:4">
+      <c r="A857" s="1">
+        <v>855</v>
+      </c>
+      <c r="B857" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C857">
+        <v>1</v>
+      </c>
+      <c r="D857">
+        <v>85.7697</v>
       </c>
     </row>
   </sheetData>
@@ -24373,7 +24401,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D856"/>
+  <dimension ref="A1:D857"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36355,6 +36383,20 @@
       </c>
       <c r="D856">
         <v>51.6911</v>
+      </c>
+    </row>
+    <row r="857" spans="1:4">
+      <c r="A857" s="1">
+        <v>855</v>
+      </c>
+      <c r="B857" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C857">
+        <v>1</v>
+      </c>
+      <c r="D857">
+        <v>52.1274</v>
       </c>
     </row>
   </sheetData>
@@ -36364,7 +36406,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D856"/>
+  <dimension ref="A1:D857"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48346,6 +48388,20 @@
       </c>
       <c r="D856">
         <v>10.9713</v>
+      </c>
+    </row>
+    <row r="857" spans="1:4">
+      <c r="A857" s="1">
+        <v>855</v>
+      </c>
+      <c r="B857" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C857">
+        <v>1</v>
+      </c>
+      <c r="D857">
+        <v>11.044</v>
       </c>
     </row>
   </sheetData>
@@ -48355,7 +48411,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D856"/>
+  <dimension ref="A1:D857"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60337,6 +60393,20 @@
       </c>
       <c r="D856">
         <v>98.7089</v>
+      </c>
+    </row>
+    <row r="857" spans="1:4">
+      <c r="A857" s="1">
+        <v>855</v>
+      </c>
+      <c r="B857" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C857">
+        <v>1</v>
+      </c>
+      <c r="D857">
+        <v>99.44450000000001</v>
       </c>
     </row>
   </sheetData>
@@ -60346,7 +60416,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D856"/>
+  <dimension ref="A1:D857"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -72328,6 +72398,20 @@
       </c>
       <c r="D856">
         <v>15.3795</v>
+      </c>
+    </row>
+    <row r="857" spans="1:4">
+      <c r="A857" s="1">
+        <v>855</v>
+      </c>
+      <c r="B857" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C857">
+        <v>100</v>
+      </c>
+      <c r="D857">
+        <v>15.5301</v>
       </c>
     </row>
   </sheetData>
@@ -72337,7 +72421,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D856"/>
+  <dimension ref="A1:D857"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -84319,6 +84403,20 @@
       </c>
       <c r="D856">
         <v>46.2623</v>
+      </c>
+    </row>
+    <row r="857" spans="1:4">
+      <c r="A857" s="1">
+        <v>855</v>
+      </c>
+      <c r="B857" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C857">
+        <v>100</v>
+      </c>
+      <c r="D857">
+        <v>46.7631</v>
       </c>
     </row>
   </sheetData>
@@ -84328,7 +84426,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D856"/>
+  <dimension ref="A1:D857"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -96312,6 +96410,20 @@
         <v>92.1313</v>
       </c>
     </row>
+    <row r="857" spans="1:4">
+      <c r="A857" s="1">
+        <v>855</v>
+      </c>
+      <c r="B857" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C857">
+        <v>1</v>
+      </c>
+      <c r="D857">
+        <v>93.27249999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D857"/>
+  <dimension ref="A1:D858"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12387,6 +12387,20 @@
       </c>
       <c r="D857">
         <v>75.6347</v>
+      </c>
+    </row>
+    <row r="858" spans="1:4">
+      <c r="A858" s="1">
+        <v>856</v>
+      </c>
+      <c r="B858" s="2">
+        <v>46200</v>
+      </c>
+      <c r="C858">
+        <v>1</v>
+      </c>
+      <c r="D858">
+        <v>77.0611</v>
       </c>
     </row>
   </sheetData>
@@ -12396,7 +12410,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D857"/>
+  <dimension ref="A1:D858"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24392,6 +24406,20 @@
       </c>
       <c r="D857">
         <v>85.7697</v>
+      </c>
+    </row>
+    <row r="858" spans="1:4">
+      <c r="A858" s="1">
+        <v>856</v>
+      </c>
+      <c r="B858" s="2">
+        <v>46200</v>
+      </c>
+      <c r="C858">
+        <v>1</v>
+      </c>
+      <c r="D858">
+        <v>87.4027</v>
       </c>
     </row>
   </sheetData>
@@ -24401,7 +24429,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D857"/>
+  <dimension ref="A1:D858"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36397,6 +36425,20 @@
       </c>
       <c r="D857">
         <v>52.1274</v>
+      </c>
+    </row>
+    <row r="858" spans="1:4">
+      <c r="A858" s="1">
+        <v>856</v>
+      </c>
+      <c r="B858" s="2">
+        <v>46200</v>
+      </c>
+      <c r="C858">
+        <v>1</v>
+      </c>
+      <c r="D858">
+        <v>53.1259</v>
       </c>
     </row>
   </sheetData>
@@ -36406,7 +36448,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D857"/>
+  <dimension ref="A1:D858"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48402,6 +48444,20 @@
       </c>
       <c r="D857">
         <v>11.044</v>
+      </c>
+    </row>
+    <row r="858" spans="1:4">
+      <c r="A858" s="1">
+        <v>856</v>
+      </c>
+      <c r="B858" s="2">
+        <v>46200</v>
+      </c>
+      <c r="C858">
+        <v>1</v>
+      </c>
+      <c r="D858">
+        <v>11.3359</v>
       </c>
     </row>
   </sheetData>
@@ -48411,7 +48467,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D857"/>
+  <dimension ref="A1:D858"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60407,6 +60463,20 @@
       </c>
       <c r="D857">
         <v>99.44450000000001</v>
+      </c>
+    </row>
+    <row r="858" spans="1:4">
+      <c r="A858" s="1">
+        <v>856</v>
+      </c>
+      <c r="B858" s="2">
+        <v>46200</v>
+      </c>
+      <c r="C858">
+        <v>1</v>
+      </c>
+      <c r="D858">
+        <v>101.7361</v>
       </c>
     </row>
   </sheetData>
@@ -60416,7 +60486,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D857"/>
+  <dimension ref="A1:D858"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -72412,6 +72482,20 @@
       </c>
       <c r="D857">
         <v>15.5301</v>
+      </c>
+    </row>
+    <row r="858" spans="1:4">
+      <c r="A858" s="1">
+        <v>856</v>
+      </c>
+      <c r="B858" s="2">
+        <v>46200</v>
+      </c>
+      <c r="C858">
+        <v>100</v>
+      </c>
+      <c r="D858">
+        <v>15.8758</v>
       </c>
     </row>
   </sheetData>
@@ -72421,7 +72505,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D857"/>
+  <dimension ref="A1:D858"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -84417,6 +84501,20 @@
       </c>
       <c r="D857">
         <v>46.7631</v>
+      </c>
+    </row>
+    <row r="858" spans="1:4">
+      <c r="A858" s="1">
+        <v>856</v>
+      </c>
+      <c r="B858" s="2">
+        <v>46200</v>
+      </c>
+      <c r="C858">
+        <v>100</v>
+      </c>
+      <c r="D858">
+        <v>47.6186</v>
       </c>
     </row>
   </sheetData>
@@ -84426,7 +84524,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D857"/>
+  <dimension ref="A1:D858"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -96424,6 +96522,20 @@
         <v>93.27249999999999</v>
       </c>
     </row>
+    <row r="858" spans="1:4">
+      <c r="A858" s="1">
+        <v>856</v>
+      </c>
+      <c r="B858" s="2">
+        <v>46200</v>
+      </c>
+      <c r="C858">
+        <v>1</v>
+      </c>
+      <c r="D858">
+        <v>95.32550000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D858"/>
+  <dimension ref="A1:D859"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12401,6 +12401,20 @@
       </c>
       <c r="D858">
         <v>77.0611</v>
+      </c>
+    </row>
+    <row r="859" spans="1:4">
+      <c r="A859" s="1">
+        <v>857</v>
+      </c>
+      <c r="B859" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C859">
+        <v>1</v>
+      </c>
+      <c r="D859">
+        <v>77.7539</v>
       </c>
     </row>
   </sheetData>
@@ -12410,7 +12424,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D858"/>
+  <dimension ref="A1:D859"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24420,6 +24434,20 @@
       </c>
       <c r="D858">
         <v>87.4027</v>
+      </c>
+    </row>
+    <row r="859" spans="1:4">
+      <c r="A859" s="1">
+        <v>857</v>
+      </c>
+      <c r="B859" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C859">
+        <v>1</v>
+      </c>
+      <c r="D859">
+        <v>88.6472</v>
       </c>
     </row>
   </sheetData>
@@ -24429,7 +24457,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D858"/>
+  <dimension ref="A1:D859"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36439,6 +36467,20 @@
       </c>
       <c r="D858">
         <v>53.1259</v>
+      </c>
+    </row>
+    <row r="859" spans="1:4">
+      <c r="A859" s="1">
+        <v>857</v>
+      </c>
+      <c r="B859" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C859">
+        <v>1</v>
+      </c>
+      <c r="D859">
+        <v>53.6191</v>
       </c>
     </row>
   </sheetData>
@@ -36448,7 +36490,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D858"/>
+  <dimension ref="A1:D859"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48458,6 +48500,20 @@
       </c>
       <c r="D858">
         <v>11.3359</v>
+      </c>
+    </row>
+    <row r="859" spans="1:4">
+      <c r="A859" s="1">
+        <v>857</v>
+      </c>
+      <c r="B859" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C859">
+        <v>1</v>
+      </c>
+      <c r="D859">
+        <v>11.4624</v>
       </c>
     </row>
   </sheetData>
@@ -48467,7 +48523,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D858"/>
+  <dimension ref="A1:D859"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60477,6 +60533,20 @@
       </c>
       <c r="D858">
         <v>101.7361</v>
+      </c>
+    </row>
+    <row r="859" spans="1:4">
+      <c r="A859" s="1">
+        <v>857</v>
+      </c>
+      <c r="B859" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C859">
+        <v>1</v>
+      </c>
+      <c r="D859">
+        <v>102.6118</v>
       </c>
     </row>
   </sheetData>
@@ -60486,7 +60556,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D858"/>
+  <dimension ref="A1:D859"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -72496,6 +72566,20 @@
       </c>
       <c r="D858">
         <v>15.8758</v>
+      </c>
+    </row>
+    <row r="859" spans="1:4">
+      <c r="A859" s="1">
+        <v>857</v>
+      </c>
+      <c r="B859" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C859">
+        <v>100</v>
+      </c>
+      <c r="D859">
+        <v>15.9833</v>
       </c>
     </row>
   </sheetData>
@@ -72505,7 +72589,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D858"/>
+  <dimension ref="A1:D859"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -84515,6 +84599,20 @@
       </c>
       <c r="D858">
         <v>47.6186</v>
+      </c>
+    </row>
+    <row r="859" spans="1:4">
+      <c r="A859" s="1">
+        <v>857</v>
+      </c>
+      <c r="B859" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C859">
+        <v>100</v>
+      </c>
+      <c r="D859">
+        <v>48.0556</v>
       </c>
     </row>
   </sheetData>
@@ -84524,7 +84622,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D858"/>
+  <dimension ref="A1:D859"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -96536,6 +96634,20 @@
         <v>95.32550000000001</v>
       </c>
     </row>
+    <row r="859" spans="1:4">
+      <c r="A859" s="1">
+        <v>857</v>
+      </c>
+      <c r="B859" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C859">
+        <v>1</v>
+      </c>
+      <c r="D859">
+        <v>96.0992</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D859"/>
+  <dimension ref="A1:D860"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12415,6 +12415,20 @@
       </c>
       <c r="D859">
         <v>77.7539</v>
+      </c>
+    </row>
+    <row r="860" spans="1:4">
+      <c r="A860" s="1">
+        <v>858</v>
+      </c>
+      <c r="B860" s="2">
+        <v>46204</v>
+      </c>
+      <c r="C860">
+        <v>1</v>
+      </c>
+      <c r="D860">
+        <v>78.2696</v>
       </c>
     </row>
   </sheetData>
@@ -12424,7 +12438,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D859"/>
+  <dimension ref="A1:D860"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24448,6 +24462,20 @@
       </c>
       <c r="D859">
         <v>88.6472</v>
+      </c>
+    </row>
+    <row r="860" spans="1:4">
+      <c r="A860" s="1">
+        <v>858</v>
+      </c>
+      <c r="B860" s="2">
+        <v>46204</v>
+      </c>
+      <c r="C860">
+        <v>1</v>
+      </c>
+      <c r="D860">
+        <v>89.2743</v>
       </c>
     </row>
   </sheetData>
@@ -24457,7 +24485,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D859"/>
+  <dimension ref="A1:D860"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36481,6 +36509,20 @@
       </c>
       <c r="D859">
         <v>53.6191</v>
+      </c>
+    </row>
+    <row r="860" spans="1:4">
+      <c r="A860" s="1">
+        <v>858</v>
+      </c>
+      <c r="B860" s="2">
+        <v>46204</v>
+      </c>
+      <c r="C860">
+        <v>1</v>
+      </c>
+      <c r="D860">
+        <v>53.7634</v>
       </c>
     </row>
   </sheetData>
@@ -36490,7 +36532,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D859"/>
+  <dimension ref="A1:D860"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48514,6 +48556,20 @@
       </c>
       <c r="D859">
         <v>11.4624</v>
+      </c>
+    </row>
+    <row r="860" spans="1:4">
+      <c r="A860" s="1">
+        <v>858</v>
+      </c>
+      <c r="B860" s="2">
+        <v>46204</v>
+      </c>
+      <c r="C860">
+        <v>1</v>
+      </c>
+      <c r="D860">
+        <v>11.4932</v>
       </c>
     </row>
   </sheetData>
@@ -48523,7 +48579,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D859"/>
+  <dimension ref="A1:D860"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60547,6 +60603,20 @@
       </c>
       <c r="D859">
         <v>102.6118</v>
+      </c>
+    </row>
+    <row r="860" spans="1:4">
+      <c r="A860" s="1">
+        <v>858</v>
+      </c>
+      <c r="B860" s="2">
+        <v>46204</v>
+      </c>
+      <c r="C860">
+        <v>1</v>
+      </c>
+      <c r="D860">
+        <v>103.6681</v>
       </c>
     </row>
   </sheetData>
@@ -60556,7 +60626,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D859"/>
+  <dimension ref="A1:D860"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -72580,6 +72650,20 @@
       </c>
       <c r="D859">
         <v>15.9833</v>
+      </c>
+    </row>
+    <row r="860" spans="1:4">
+      <c r="A860" s="1">
+        <v>858</v>
+      </c>
+      <c r="B860" s="2">
+        <v>46204</v>
+      </c>
+      <c r="C860">
+        <v>100</v>
+      </c>
+      <c r="D860">
+        <v>16.1108</v>
       </c>
     </row>
   </sheetData>
@@ -72589,7 +72673,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D859"/>
+  <dimension ref="A1:D860"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -84613,6 +84697,20 @@
       </c>
       <c r="D859">
         <v>48.0556</v>
+      </c>
+    </row>
+    <row r="860" spans="1:4">
+      <c r="A860" s="1">
+        <v>858</v>
+      </c>
+      <c r="B860" s="2">
+        <v>46204</v>
+      </c>
+      <c r="C860">
+        <v>100</v>
+      </c>
+      <c r="D860">
+        <v>48.255</v>
       </c>
     </row>
   </sheetData>
@@ -84622,7 +84720,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D859"/>
+  <dimension ref="A1:D860"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -96648,6 +96746,20 @@
         <v>96.0992</v>
       </c>
     </row>
+    <row r="860" spans="1:4">
+      <c r="A860" s="1">
+        <v>858</v>
+      </c>
+      <c r="B860" s="2">
+        <v>46204</v>
+      </c>
+      <c r="C860">
+        <v>1</v>
+      </c>
+      <c r="D860">
+        <v>96.6888</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D860"/>
+  <dimension ref="A1:D861"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12429,6 +12429,20 @@
       </c>
       <c r="D860">
         <v>78.2696</v>
+      </c>
+    </row>
+    <row r="861" spans="1:4">
+      <c r="A861" s="1">
+        <v>859</v>
+      </c>
+      <c r="B861" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C861">
+        <v>1</v>
+      </c>
+      <c r="D861">
+        <v>78.26519999999999</v>
       </c>
     </row>
   </sheetData>
@@ -12438,7 +12452,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D860"/>
+  <dimension ref="A1:D861"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24476,6 +24490,20 @@
       </c>
       <c r="D860">
         <v>89.2743</v>
+      </c>
+    </row>
+    <row r="861" spans="1:4">
+      <c r="A861" s="1">
+        <v>859</v>
+      </c>
+      <c r="B861" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C861">
+        <v>1</v>
+      </c>
+      <c r="D861">
+        <v>89.1754</v>
       </c>
     </row>
   </sheetData>
@@ -24485,7 +24513,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D860"/>
+  <dimension ref="A1:D861"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36523,6 +36551,20 @@
       </c>
       <c r="D860">
         <v>53.7634</v>
+      </c>
+    </row>
+    <row r="861" spans="1:4">
+      <c r="A861" s="1">
+        <v>859</v>
+      </c>
+      <c r="B861" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C861">
+        <v>1</v>
+      </c>
+      <c r="D861">
+        <v>53.9639</v>
       </c>
     </row>
   </sheetData>
@@ -36532,7 +36574,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D860"/>
+  <dimension ref="A1:D861"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48570,6 +48612,20 @@
       </c>
       <c r="D860">
         <v>11.4932</v>
+      </c>
+    </row>
+    <row r="861" spans="1:4">
+      <c r="A861" s="1">
+        <v>859</v>
+      </c>
+      <c r="B861" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C861">
+        <v>1</v>
+      </c>
+      <c r="D861">
+        <v>11.4842</v>
       </c>
     </row>
   </sheetData>
@@ -48579,7 +48635,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D860"/>
+  <dimension ref="A1:D861"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60617,6 +60673,20 @@
       </c>
       <c r="D860">
         <v>103.6681</v>
+      </c>
+    </row>
+    <row r="861" spans="1:4">
+      <c r="A861" s="1">
+        <v>859</v>
+      </c>
+      <c r="B861" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C861">
+        <v>1</v>
+      </c>
+      <c r="D861">
+        <v>103.8814</v>
       </c>
     </row>
   </sheetData>
@@ -60626,7 +60696,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D860"/>
+  <dimension ref="A1:D861"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -72664,6 +72734,20 @@
       </c>
       <c r="D860">
         <v>16.1108</v>
+      </c>
+    </row>
+    <row r="861" spans="1:4">
+      <c r="A861" s="1">
+        <v>859</v>
+      </c>
+      <c r="B861" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C861">
+        <v>100</v>
+      </c>
+      <c r="D861">
+        <v>16.2808</v>
       </c>
     </row>
   </sheetData>
@@ -72673,7 +72757,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D860"/>
+  <dimension ref="A1:D861"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -84711,6 +84795,20 @@
       </c>
       <c r="D860">
         <v>48.255</v>
+      </c>
+    </row>
+    <row r="861" spans="1:4">
+      <c r="A861" s="1">
+        <v>859</v>
+      </c>
+      <c r="B861" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C861">
+        <v>100</v>
+      </c>
+      <c r="D861">
+        <v>48.104</v>
       </c>
     </row>
   </sheetData>
@@ -84720,7 +84818,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D860"/>
+  <dimension ref="A1:D861"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -96760,6 +96858,20 @@
         <v>96.6888</v>
       </c>
     </row>
+    <row r="861" spans="1:4">
+      <c r="A861" s="1">
+        <v>859</v>
+      </c>
+      <c r="B861" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C861">
+        <v>1</v>
+      </c>
+      <c r="D861">
+        <v>96.67140000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D861"/>
+  <dimension ref="A1:D862"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12443,6 +12443,20 @@
       </c>
       <c r="D861">
         <v>78.26519999999999</v>
+      </c>
+    </row>
+    <row r="862" spans="1:4">
+      <c r="A862" s="1">
+        <v>860</v>
+      </c>
+      <c r="B862" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C862">
+        <v>1</v>
+      </c>
+      <c r="D862">
+        <v>77.9293</v>
       </c>
     </row>
   </sheetData>
@@ -12452,7 +12466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D861"/>
+  <dimension ref="A1:D862"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24504,6 +24518,20 @@
       </c>
       <c r="D861">
         <v>89.1754</v>
+      </c>
+    </row>
+    <row r="862" spans="1:4">
+      <c r="A862" s="1">
+        <v>860</v>
+      </c>
+      <c r="B862" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C862">
+        <v>1</v>
+      </c>
+      <c r="D862">
+        <v>88.7069</v>
       </c>
     </row>
   </sheetData>
@@ -24513,7 +24541,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D861"/>
+  <dimension ref="A1:D862"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36565,6 +36593,20 @@
       </c>
       <c r="D861">
         <v>53.9639</v>
+      </c>
+    </row>
+    <row r="862" spans="1:4">
+      <c r="A862" s="1">
+        <v>860</v>
+      </c>
+      <c r="B862" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C862">
+        <v>1</v>
+      </c>
+      <c r="D862">
+        <v>53.7245</v>
       </c>
     </row>
   </sheetData>
@@ -36574,7 +36616,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D861"/>
+  <dimension ref="A1:D862"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48626,6 +48668,20 @@
       </c>
       <c r="D861">
         <v>11.4842</v>
+      </c>
+    </row>
+    <row r="862" spans="1:4">
+      <c r="A862" s="1">
+        <v>860</v>
+      </c>
+      <c r="B862" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C862">
+        <v>1</v>
+      </c>
+      <c r="D862">
+        <v>11.4693</v>
       </c>
     </row>
   </sheetData>
@@ -48635,7 +48691,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D861"/>
+  <dimension ref="A1:D862"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60687,6 +60743,20 @@
       </c>
       <c r="D861">
         <v>103.8814</v>
+      </c>
+    </row>
+    <row r="862" spans="1:4">
+      <c r="A862" s="1">
+        <v>860</v>
+      </c>
+      <c r="B862" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C862">
+        <v>1</v>
+      </c>
+      <c r="D862">
+        <v>103.4745</v>
       </c>
     </row>
   </sheetData>
@@ -60696,7 +60766,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D861"/>
+  <dimension ref="A1:D862"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -72748,6 +72818,20 @@
       </c>
       <c r="D861">
         <v>16.2808</v>
+      </c>
+    </row>
+    <row r="862" spans="1:4">
+      <c r="A862" s="1">
+        <v>860</v>
+      </c>
+      <c r="B862" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C862">
+        <v>100</v>
+      </c>
+      <c r="D862">
+        <v>16.2603</v>
       </c>
     </row>
   </sheetData>
@@ -72757,7 +72841,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D861"/>
+  <dimension ref="A1:D862"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -84809,6 +84893,20 @@
       </c>
       <c r="D861">
         <v>48.104</v>
+      </c>
+    </row>
+    <row r="862" spans="1:4">
+      <c r="A862" s="1">
+        <v>860</v>
+      </c>
+      <c r="B862" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C862">
+        <v>100</v>
+      </c>
+      <c r="D862">
+        <v>47.9329</v>
       </c>
     </row>
   </sheetData>
@@ -84818,7 +84916,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D861"/>
+  <dimension ref="A1:D862"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -96872,6 +96970,20 @@
         <v>96.67140000000001</v>
       </c>
     </row>
+    <row r="862" spans="1:4">
+      <c r="A862" s="1">
+        <v>860</v>
+      </c>
+      <c r="B862" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C862">
+        <v>1</v>
+      </c>
+      <c r="D862">
+        <v>96.85469999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D862"/>
+  <dimension ref="A1:D863"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12457,6 +12457,20 @@
       </c>
       <c r="D862">
         <v>77.9293</v>
+      </c>
+    </row>
+    <row r="863" spans="1:4">
+      <c r="A863" s="1">
+        <v>861</v>
+      </c>
+      <c r="B863" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C863">
+        <v>1</v>
+      </c>
+      <c r="D863">
+        <v>77.2264</v>
       </c>
     </row>
   </sheetData>
@@ -12466,7 +12480,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D862"/>
+  <dimension ref="A1:D863"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24532,6 +24546,20 @@
       </c>
       <c r="D862">
         <v>88.7069</v>
+      </c>
+    </row>
+    <row r="863" spans="1:4">
+      <c r="A863" s="1">
+        <v>861</v>
+      </c>
+      <c r="B863" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C863">
+        <v>1</v>
+      </c>
+      <c r="D863">
+        <v>88.0304</v>
       </c>
     </row>
   </sheetData>
@@ -24541,7 +24569,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D862"/>
+  <dimension ref="A1:D863"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36607,6 +36635,20 @@
       </c>
       <c r="D862">
         <v>53.7245</v>
+      </c>
+    </row>
+    <row r="863" spans="1:4">
+      <c r="A863" s="1">
+        <v>861</v>
+      </c>
+      <c r="B863" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C863">
+        <v>1</v>
+      </c>
+      <c r="D863">
+        <v>53.6028</v>
       </c>
     </row>
   </sheetData>
@@ -36616,7 +36658,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D862"/>
+  <dimension ref="A1:D863"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48682,6 +48724,20 @@
       </c>
       <c r="D862">
         <v>11.4693</v>
+      </c>
+    </row>
+    <row r="863" spans="1:4">
+      <c r="A863" s="1">
+        <v>861</v>
+      </c>
+      <c r="B863" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C863">
+        <v>1</v>
+      </c>
+      <c r="D863">
+        <v>11.3803</v>
       </c>
     </row>
   </sheetData>
@@ -48691,7 +48747,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D862"/>
+  <dimension ref="A1:D863"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60757,6 +60813,20 @@
       </c>
       <c r="D862">
         <v>103.4745</v>
+      </c>
+    </row>
+    <row r="863" spans="1:4">
+      <c r="A863" s="1">
+        <v>861</v>
+      </c>
+      <c r="B863" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C863">
+        <v>1</v>
+      </c>
+      <c r="D863">
+        <v>103.298</v>
       </c>
     </row>
   </sheetData>
@@ -60766,7 +60836,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D862"/>
+  <dimension ref="A1:D863"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -72832,6 +72902,20 @@
       </c>
       <c r="D862">
         <v>16.2603</v>
+      </c>
+    </row>
+    <row r="863" spans="1:4">
+      <c r="A863" s="1">
+        <v>861</v>
+      </c>
+      <c r="B863" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C863">
+        <v>100</v>
+      </c>
+      <c r="D863">
+        <v>16.2764</v>
       </c>
     </row>
   </sheetData>
@@ -72841,7 +72925,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D862"/>
+  <dimension ref="A1:D863"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -84907,6 +84991,20 @@
       </c>
       <c r="D862">
         <v>47.9329</v>
+      </c>
+    </row>
+    <row r="863" spans="1:4">
+      <c r="A863" s="1">
+        <v>861</v>
+      </c>
+      <c r="B863" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C863">
+        <v>100</v>
+      </c>
+      <c r="D863">
+        <v>47.8923</v>
       </c>
     </row>
   </sheetData>
@@ -84916,7 +85014,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D862"/>
+  <dimension ref="A1:D863"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -96984,6 +97082,20 @@
         <v>96.85469999999999</v>
       </c>
     </row>
+    <row r="863" spans="1:4">
+      <c r="A863" s="1">
+        <v>861</v>
+      </c>
+      <c r="B863" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C863">
+        <v>1</v>
+      </c>
+      <c r="D863">
+        <v>96.2443</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D863"/>
+  <dimension ref="A1:D864"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12471,6 +12471,20 @@
       </c>
       <c r="D863">
         <v>77.2264</v>
+      </c>
+    </row>
+    <row r="864" spans="1:4">
+      <c r="A864" s="1">
+        <v>862</v>
+      </c>
+      <c r="B864" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C864">
+        <v>1</v>
+      </c>
+      <c r="D864">
+        <v>77.9695</v>
       </c>
     </row>
   </sheetData>
@@ -12480,7 +12494,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D863"/>
+  <dimension ref="A1:D864"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24560,6 +24574,20 @@
       </c>
       <c r="D863">
         <v>88.0304</v>
+      </c>
+    </row>
+    <row r="864" spans="1:4">
+      <c r="A864" s="1">
+        <v>862</v>
+      </c>
+      <c r="B864" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C864">
+        <v>1</v>
+      </c>
+      <c r="D864">
+        <v>89.2595</v>
       </c>
     </row>
   </sheetData>
@@ -24569,7 +24597,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D863"/>
+  <dimension ref="A1:D864"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36649,6 +36677,20 @@
       </c>
       <c r="D863">
         <v>53.6028</v>
+      </c>
+    </row>
+    <row r="864" spans="1:4">
+      <c r="A864" s="1">
+        <v>862</v>
+      </c>
+      <c r="B864" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C864">
+        <v>1</v>
+      </c>
+      <c r="D864">
+        <v>54.0407</v>
       </c>
     </row>
   </sheetData>
@@ -36658,7 +36700,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D863"/>
+  <dimension ref="A1:D864"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48738,6 +48780,20 @@
       </c>
       <c r="D863">
         <v>11.3803</v>
+      </c>
+    </row>
+    <row r="864" spans="1:4">
+      <c r="A864" s="1">
+        <v>862</v>
+      </c>
+      <c r="B864" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C864">
+        <v>1</v>
+      </c>
+      <c r="D864">
+        <v>11.4555</v>
       </c>
     </row>
   </sheetData>
@@ -48747,7 +48803,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D863"/>
+  <dimension ref="A1:D864"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60827,6 +60883,20 @@
       </c>
       <c r="D863">
         <v>103.298</v>
+      </c>
+    </row>
+    <row r="864" spans="1:4">
+      <c r="A864" s="1">
+        <v>862</v>
+      </c>
+      <c r="B864" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C864">
+        <v>1</v>
+      </c>
+      <c r="D864">
+        <v>104.1361</v>
       </c>
     </row>
   </sheetData>
@@ -60836,7 +60906,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D863"/>
+  <dimension ref="A1:D864"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -72916,6 +72986,20 @@
       </c>
       <c r="D863">
         <v>16.2764</v>
+      </c>
+    </row>
+    <row r="864" spans="1:4">
+      <c r="A864" s="1">
+        <v>862</v>
+      </c>
+      <c r="B864" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C864">
+        <v>100</v>
+      </c>
+      <c r="D864">
+        <v>16.5179</v>
       </c>
     </row>
   </sheetData>
@@ -72925,7 +73009,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D863"/>
+  <dimension ref="A1:D864"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -85005,6 +85089,20 @@
       </c>
       <c r="D863">
         <v>47.8923</v>
+      </c>
+    </row>
+    <row r="864" spans="1:4">
+      <c r="A864" s="1">
+        <v>862</v>
+      </c>
+      <c r="B864" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C864">
+        <v>100</v>
+      </c>
+      <c r="D864">
+        <v>48.2574</v>
       </c>
     </row>
   </sheetData>
@@ -85014,7 +85112,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D863"/>
+  <dimension ref="A1:D864"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -97096,6 +97194,20 @@
         <v>96.2443</v>
       </c>
     </row>
+    <row r="864" spans="1:4">
+      <c r="A864" s="1">
+        <v>862</v>
+      </c>
+      <c r="B864" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C864">
+        <v>1</v>
+      </c>
+      <c r="D864">
+        <v>96.79640000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D864"/>
+  <dimension ref="A1:D865"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12485,6 +12485,20 @@
       </c>
       <c r="D864">
         <v>77.9695</v>
+      </c>
+    </row>
+    <row r="865" spans="1:4">
+      <c r="A865" s="1">
+        <v>863</v>
+      </c>
+      <c r="B865" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C865">
+        <v>1</v>
+      </c>
+      <c r="D865">
+        <v>76.1258</v>
       </c>
     </row>
   </sheetData>
@@ -12494,7 +12508,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D864"/>
+  <dimension ref="A1:D865"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24588,6 +24602,20 @@
       </c>
       <c r="D864">
         <v>89.2595</v>
+      </c>
+    </row>
+    <row r="865" spans="1:4">
+      <c r="A865" s="1">
+        <v>863</v>
+      </c>
+      <c r="B865" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C865">
+        <v>1</v>
+      </c>
+      <c r="D865">
+        <v>86.8976</v>
       </c>
     </row>
   </sheetData>
@@ -24597,7 +24625,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D864"/>
+  <dimension ref="A1:D865"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36691,6 +36719,20 @@
       </c>
       <c r="D864">
         <v>54.0407</v>
+      </c>
+    </row>
+    <row r="865" spans="1:4">
+      <c r="A865" s="1">
+        <v>863</v>
+      </c>
+      <c r="B865" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C865">
+        <v>1</v>
+      </c>
+      <c r="D865">
+        <v>52.8465</v>
       </c>
     </row>
   </sheetData>
@@ -36700,7 +36742,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D864"/>
+  <dimension ref="A1:D865"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48794,6 +48836,20 @@
       </c>
       <c r="D864">
         <v>11.4555</v>
+      </c>
+    </row>
+    <row r="865" spans="1:4">
+      <c r="A865" s="1">
+        <v>863</v>
+      </c>
+      <c r="B865" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C865">
+        <v>1</v>
+      </c>
+      <c r="D865">
+        <v>11.2068</v>
       </c>
     </row>
   </sheetData>
@@ -48803,7 +48859,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D864"/>
+  <dimension ref="A1:D865"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60897,6 +60953,20 @@
       </c>
       <c r="D864">
         <v>104.1361</v>
+      </c>
+    </row>
+    <row r="865" spans="1:4">
+      <c r="A865" s="1">
+        <v>863</v>
+      </c>
+      <c r="B865" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C865">
+        <v>1</v>
+      </c>
+      <c r="D865">
+        <v>101.6736</v>
       </c>
     </row>
   </sheetData>
@@ -60906,7 +60976,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D864"/>
+  <dimension ref="A1:D865"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -73000,6 +73070,20 @@
       </c>
       <c r="D864">
         <v>16.5179</v>
+      </c>
+    </row>
+    <row r="865" spans="1:4">
+      <c r="A865" s="1">
+        <v>863</v>
+      </c>
+      <c r="B865" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C865">
+        <v>100</v>
+      </c>
+      <c r="D865">
+        <v>16.1273</v>
       </c>
     </row>
   </sheetData>
@@ -73009,7 +73093,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D864"/>
+  <dimension ref="A1:D865"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -85103,6 +85187,20 @@
       </c>
       <c r="D864">
         <v>48.2574</v>
+      </c>
+    </row>
+    <row r="865" spans="1:4">
+      <c r="A865" s="1">
+        <v>863</v>
+      </c>
+      <c r="B865" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C865">
+        <v>100</v>
+      </c>
+      <c r="D865">
+        <v>46.9507</v>
       </c>
     </row>
   </sheetData>
@@ -85112,7 +85210,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D864"/>
+  <dimension ref="A1:D865"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -97208,6 +97306,20 @@
         <v>96.79640000000001</v>
       </c>
     </row>
+    <row r="865" spans="1:4">
+      <c r="A865" s="1">
+        <v>863</v>
+      </c>
+      <c r="B865" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C865">
+        <v>1</v>
+      </c>
+      <c r="D865">
+        <v>94.402</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D865"/>
+  <dimension ref="A1:D866"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12499,6 +12499,20 @@
       </c>
       <c r="D865">
         <v>76.1258</v>
+      </c>
+    </row>
+    <row r="866" spans="1:4">
+      <c r="A866" s="1">
+        <v>864</v>
+      </c>
+      <c r="B866" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C866">
+        <v>1</v>
+      </c>
+      <c r="D866">
+        <v>76.40260000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12508,7 +12522,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D865"/>
+  <dimension ref="A1:D866"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24616,6 +24630,20 @@
       </c>
       <c r="D865">
         <v>86.8976</v>
+      </c>
+    </row>
+    <row r="866" spans="1:4">
+      <c r="A866" s="1">
+        <v>864</v>
+      </c>
+      <c r="B866" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C866">
+        <v>1</v>
+      </c>
+      <c r="D866">
+        <v>87.3511</v>
       </c>
     </row>
   </sheetData>
@@ -24625,7 +24653,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D865"/>
+  <dimension ref="A1:D866"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36733,6 +36761,20 @@
       </c>
       <c r="D865">
         <v>52.8465</v>
+      </c>
+    </row>
+    <row r="866" spans="1:4">
+      <c r="A866" s="1">
+        <v>864</v>
+      </c>
+      <c r="B866" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C866">
+        <v>1</v>
+      </c>
+      <c r="D866">
+        <v>53.0463</v>
       </c>
     </row>
   </sheetData>
@@ -36742,7 +36784,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D865"/>
+  <dimension ref="A1:D866"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48850,6 +48892,20 @@
       </c>
       <c r="D865">
         <v>11.2068</v>
+      </c>
+    </row>
+    <row r="866" spans="1:4">
+      <c r="A866" s="1">
+        <v>864</v>
+      </c>
+      <c r="B866" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C866">
+        <v>1</v>
+      </c>
+      <c r="D866">
+        <v>11.2219</v>
       </c>
     </row>
   </sheetData>
@@ -48859,7 +48915,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D865"/>
+  <dimension ref="A1:D866"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -60967,6 +61023,20 @@
       </c>
       <c r="D865">
         <v>101.6736</v>
+      </c>
+    </row>
+    <row r="866" spans="1:4">
+      <c r="A866" s="1">
+        <v>864</v>
+      </c>
+      <c r="B866" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C866">
+        <v>1</v>
+      </c>
+      <c r="D866">
+        <v>102.219</v>
       </c>
     </row>
   </sheetData>
@@ -60976,7 +61046,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D865"/>
+  <dimension ref="A1:D866"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -73084,6 +73154,20 @@
       </c>
       <c r="D865">
         <v>16.1273</v>
+      </c>
+    </row>
+    <row r="866" spans="1:4">
+      <c r="A866" s="1">
+        <v>864</v>
+      </c>
+      <c r="B866" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C866">
+        <v>100</v>
+      </c>
+      <c r="D866">
+        <v>16.22</v>
       </c>
     </row>
   </sheetData>
@@ -73093,7 +73177,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D865"/>
+  <dimension ref="A1:D866"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -85201,6 +85285,20 @@
       </c>
       <c r="D865">
         <v>46.9507</v>
+      </c>
+    </row>
+    <row r="866" spans="1:4">
+      <c r="A866" s="1">
+        <v>864</v>
+      </c>
+      <c r="B866" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C866">
+        <v>100</v>
+      </c>
+      <c r="D866">
+        <v>47.0633</v>
       </c>
     </row>
   </sheetData>
@@ -85210,7 +85308,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D865"/>
+  <dimension ref="A1:D866"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -97320,6 +97418,20 @@
         <v>94.402</v>
       </c>
     </row>
+    <row r="866" spans="1:4">
+      <c r="A866" s="1">
+        <v>864</v>
+      </c>
+      <c r="B866" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C866">
+        <v>1</v>
+      </c>
+      <c r="D866">
+        <v>94.58110000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D866"/>
+  <dimension ref="A1:D867"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12513,6 +12513,20 @@
       </c>
       <c r="D866">
         <v>76.40260000000001</v>
+      </c>
+    </row>
+    <row r="867" spans="1:4">
+      <c r="A867" s="1">
+        <v>865</v>
+      </c>
+      <c r="B867" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C867">
+        <v>1</v>
+      </c>
+      <c r="D867">
+        <v>75.93000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12522,7 +12536,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D866"/>
+  <dimension ref="A1:D867"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24644,6 +24658,20 @@
       </c>
       <c r="D866">
         <v>87.3511</v>
+      </c>
+    </row>
+    <row r="867" spans="1:4">
+      <c r="A867" s="1">
+        <v>865</v>
+      </c>
+      <c r="B867" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C867">
+        <v>1</v>
+      </c>
+      <c r="D867">
+        <v>86.59059999999999</v>
       </c>
     </row>
   </sheetData>
@@ -24653,7 +24681,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D866"/>
+  <dimension ref="A1:D867"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36775,6 +36803,20 @@
       </c>
       <c r="D866">
         <v>53.0463</v>
+      </c>
+    </row>
+    <row r="867" spans="1:4">
+      <c r="A867" s="1">
+        <v>865</v>
+      </c>
+      <c r="B867" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C867">
+        <v>1</v>
+      </c>
+      <c r="D867">
+        <v>52.703</v>
       </c>
     </row>
   </sheetData>
@@ -36784,7 +36826,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D866"/>
+  <dimension ref="A1:D867"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48906,6 +48948,20 @@
       </c>
       <c r="D866">
         <v>11.2219</v>
+      </c>
+    </row>
+    <row r="867" spans="1:4">
+      <c r="A867" s="1">
+        <v>865</v>
+      </c>
+      <c r="B867" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C867">
+        <v>1</v>
+      </c>
+      <c r="D867">
+        <v>11.1616</v>
       </c>
     </row>
   </sheetData>
@@ -48915,7 +48971,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D866"/>
+  <dimension ref="A1:D867"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61037,6 +61093,20 @@
       </c>
       <c r="D866">
         <v>102.219</v>
+      </c>
+    </row>
+    <row r="867" spans="1:4">
+      <c r="A867" s="1">
+        <v>865</v>
+      </c>
+      <c r="B867" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C867">
+        <v>1</v>
+      </c>
+      <c r="D867">
+        <v>101.5412</v>
       </c>
     </row>
   </sheetData>
@@ -61046,7 +61116,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D866"/>
+  <dimension ref="A1:D867"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -73168,6 +73238,20 @@
       </c>
       <c r="D866">
         <v>16.22</v>
+      </c>
+    </row>
+    <row r="867" spans="1:4">
+      <c r="A867" s="1">
+        <v>865</v>
+      </c>
+      <c r="B867" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C867">
+        <v>100</v>
+      </c>
+      <c r="D867">
+        <v>16.2251</v>
       </c>
     </row>
   </sheetData>
@@ -73177,7 +73261,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D866"/>
+  <dimension ref="A1:D867"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -85299,6 +85383,20 @@
       </c>
       <c r="D866">
         <v>47.0633</v>
+      </c>
+    </row>
+    <row r="867" spans="1:4">
+      <c r="A867" s="1">
+        <v>865</v>
+      </c>
+      <c r="B867" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C867">
+        <v>100</v>
+      </c>
+      <c r="D867">
+        <v>46.7377</v>
       </c>
     </row>
   </sheetData>
@@ -85308,7 +85406,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D866"/>
+  <dimension ref="A1:D867"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -97432,6 +97530,20 @@
         <v>94.58110000000001</v>
       </c>
     </row>
+    <row r="867" spans="1:4">
+      <c r="A867" s="1">
+        <v>865</v>
+      </c>
+      <c r="B867" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C867">
+        <v>1</v>
+      </c>
+      <c r="D867">
+        <v>94.1009</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D867"/>
+  <dimension ref="A1:D868"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12527,6 +12527,20 @@
       </c>
       <c r="D867">
         <v>75.93000000000001</v>
+      </c>
+    </row>
+    <row r="868" spans="1:4">
+      <c r="A868" s="1">
+        <v>866</v>
+      </c>
+      <c r="B868" s="2">
+        <v>46214</v>
+      </c>
+      <c r="C868">
+        <v>1</v>
+      </c>
+      <c r="D868">
+        <v>76.6647</v>
       </c>
     </row>
   </sheetData>
@@ -12536,7 +12550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D867"/>
+  <dimension ref="A1:D868"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24672,6 +24686,20 @@
       </c>
       <c r="D867">
         <v>86.59059999999999</v>
+      </c>
+    </row>
+    <row r="868" spans="1:4">
+      <c r="A868" s="1">
+        <v>866</v>
+      </c>
+      <c r="B868" s="2">
+        <v>46214</v>
+      </c>
+      <c r="C868">
+        <v>1</v>
+      </c>
+      <c r="D868">
+        <v>87.6661</v>
       </c>
     </row>
   </sheetData>
@@ -24681,7 +24709,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D867"/>
+  <dimension ref="A1:D868"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36817,6 +36845,20 @@
       </c>
       <c r="D867">
         <v>52.703</v>
+      </c>
+    </row>
+    <row r="868" spans="1:4">
+      <c r="A868" s="1">
+        <v>866</v>
+      </c>
+      <c r="B868" s="2">
+        <v>46214</v>
+      </c>
+      <c r="C868">
+        <v>1</v>
+      </c>
+      <c r="D868">
+        <v>53.2743</v>
       </c>
     </row>
   </sheetData>
@@ -36826,7 +36868,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D867"/>
+  <dimension ref="A1:D868"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -48962,6 +49004,20 @@
       </c>
       <c r="D867">
         <v>11.1616</v>
+      </c>
+    </row>
+    <row r="868" spans="1:4">
+      <c r="A868" s="1">
+        <v>866</v>
+      </c>
+      <c r="B868" s="2">
+        <v>46214</v>
+      </c>
+      <c r="C868">
+        <v>1</v>
+      </c>
+      <c r="D868">
+        <v>11.3037</v>
       </c>
     </row>
   </sheetData>
@@ -48971,7 +49027,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D867"/>
+  <dimension ref="A1:D868"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61107,6 +61163,20 @@
       </c>
       <c r="D867">
         <v>101.5412</v>
+      </c>
+    </row>
+    <row r="868" spans="1:4">
+      <c r="A868" s="1">
+        <v>866</v>
+      </c>
+      <c r="B868" s="2">
+        <v>46214</v>
+      </c>
+      <c r="C868">
+        <v>1</v>
+      </c>
+      <c r="D868">
+        <v>102.6617</v>
       </c>
     </row>
   </sheetData>
@@ -61116,7 +61186,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D867"/>
+  <dimension ref="A1:D868"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -73252,6 +73322,20 @@
       </c>
       <c r="D867">
         <v>16.2251</v>
+      </c>
+    </row>
+    <row r="868" spans="1:4">
+      <c r="A868" s="1">
+        <v>866</v>
+      </c>
+      <c r="B868" s="2">
+        <v>46214</v>
+      </c>
+      <c r="C868">
+        <v>100</v>
+      </c>
+      <c r="D868">
+        <v>16.402</v>
       </c>
     </row>
   </sheetData>
@@ -73261,7 +73345,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D867"/>
+  <dimension ref="A1:D868"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -85397,6 +85481,20 @@
       </c>
       <c r="D867">
         <v>46.7377</v>
+      </c>
+    </row>
+    <row r="868" spans="1:4">
+      <c r="A868" s="1">
+        <v>866</v>
+      </c>
+      <c r="B868" s="2">
+        <v>46214</v>
+      </c>
+      <c r="C868">
+        <v>100</v>
+      </c>
+      <c r="D868">
+        <v>47.2976</v>
       </c>
     </row>
   </sheetData>
@@ -85406,7 +85504,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D867"/>
+  <dimension ref="A1:D868"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -97544,6 +97642,20 @@
         <v>94.1009</v>
       </c>
     </row>
+    <row r="868" spans="1:4">
+      <c r="A868" s="1">
+        <v>866</v>
+      </c>
+      <c r="B868" s="2">
+        <v>46214</v>
+      </c>
+      <c r="C868">
+        <v>1</v>
+      </c>
+      <c r="D868">
+        <v>95.0821</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D868"/>
+  <dimension ref="A1:D869"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12541,6 +12541,20 @@
       </c>
       <c r="D868">
         <v>76.6647</v>
+      </c>
+    </row>
+    <row r="869" spans="1:4">
+      <c r="A869" s="1">
+        <v>867</v>
+      </c>
+      <c r="B869" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C869">
+        <v>1</v>
+      </c>
+      <c r="D869">
+        <v>76.62130000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12550,7 +12564,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D868"/>
+  <dimension ref="A1:D869"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24700,6 +24714,20 @@
       </c>
       <c r="D868">
         <v>87.6661</v>
+      </c>
+    </row>
+    <row r="869" spans="1:4">
+      <c r="A869" s="1">
+        <v>867</v>
+      </c>
+      <c r="B869" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C869">
+        <v>1</v>
+      </c>
+      <c r="D869">
+        <v>87.57810000000001</v>
       </c>
     </row>
   </sheetData>
@@ -24709,7 +24737,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D868"/>
+  <dimension ref="A1:D869"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36859,6 +36887,20 @@
       </c>
       <c r="D868">
         <v>53.2743</v>
+      </c>
+    </row>
+    <row r="869" spans="1:4">
+      <c r="A869" s="1">
+        <v>867</v>
+      </c>
+      <c r="B869" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C869">
+        <v>1</v>
+      </c>
+      <c r="D869">
+        <v>53.0986</v>
       </c>
     </row>
   </sheetData>
@@ -36868,7 +36910,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D868"/>
+  <dimension ref="A1:D869"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49018,6 +49060,20 @@
       </c>
       <c r="D868">
         <v>11.3037</v>
+      </c>
+    </row>
+    <row r="869" spans="1:4">
+      <c r="A869" s="1">
+        <v>867</v>
+      </c>
+      <c r="B869" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C869">
+        <v>1</v>
+      </c>
+      <c r="D869">
+        <v>11.2925</v>
       </c>
     </row>
   </sheetData>
@@ -49027,7 +49083,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D868"/>
+  <dimension ref="A1:D869"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61177,6 +61233,20 @@
       </c>
       <c r="D868">
         <v>102.6617</v>
+      </c>
+    </row>
+    <row r="869" spans="1:4">
+      <c r="A869" s="1">
+        <v>867</v>
+      </c>
+      <c r="B869" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C869">
+        <v>1</v>
+      </c>
+      <c r="D869">
+        <v>102.7492</v>
       </c>
     </row>
   </sheetData>
@@ -61186,7 +61256,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D868"/>
+  <dimension ref="A1:D869"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -73336,6 +73406,20 @@
       </c>
       <c r="D868">
         <v>16.402</v>
+      </c>
+    </row>
+    <row r="869" spans="1:4">
+      <c r="A869" s="1">
+        <v>867</v>
+      </c>
+      <c r="B869" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C869">
+        <v>100</v>
+      </c>
+      <c r="D869">
+        <v>16.488</v>
       </c>
     </row>
   </sheetData>
@@ -73345,7 +73429,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D868"/>
+  <dimension ref="A1:D869"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -85495,6 +85579,20 @@
       </c>
       <c r="D868">
         <v>47.2976</v>
+      </c>
+    </row>
+    <row r="869" spans="1:4">
+      <c r="A869" s="1">
+        <v>867</v>
+      </c>
+      <c r="B869" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C869">
+        <v>100</v>
+      </c>
+      <c r="D869">
+        <v>47.2679</v>
       </c>
     </row>
   </sheetData>
@@ -85504,7 +85602,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D868"/>
+  <dimension ref="A1:D869"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -97656,6 +97754,20 @@
         <v>95.0821</v>
       </c>
     </row>
+    <row r="869" spans="1:4">
+      <c r="A869" s="1">
+        <v>867</v>
+      </c>
+      <c r="B869" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C869">
+        <v>1</v>
+      </c>
+      <c r="D869">
+        <v>94.8049</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D869"/>
+  <dimension ref="A1:D870"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12555,6 +12555,20 @@
       </c>
       <c r="D869">
         <v>76.62130000000001</v>
+      </c>
+    </row>
+    <row r="870" spans="1:4">
+      <c r="A870" s="1">
+        <v>868</v>
+      </c>
+      <c r="B870" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C870">
+        <v>1</v>
+      </c>
+      <c r="D870">
+        <v>77.49120000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12564,7 +12578,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D869"/>
+  <dimension ref="A1:D870"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24728,6 +24742,20 @@
       </c>
       <c r="D869">
         <v>87.57810000000001</v>
+      </c>
+    </row>
+    <row r="870" spans="1:4">
+      <c r="A870" s="1">
+        <v>868</v>
+      </c>
+      <c r="B870" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C870">
+        <v>1</v>
+      </c>
+      <c r="D870">
+        <v>88.52589999999999</v>
       </c>
     </row>
   </sheetData>
@@ -24737,7 +24765,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D869"/>
+  <dimension ref="A1:D870"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36901,6 +36929,20 @@
       </c>
       <c r="D869">
         <v>53.0986</v>
+      </c>
+    </row>
+    <row r="870" spans="1:4">
+      <c r="A870" s="1">
+        <v>868</v>
+      </c>
+      <c r="B870" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C870">
+        <v>1</v>
+      </c>
+      <c r="D870">
+        <v>53.7401</v>
       </c>
     </row>
   </sheetData>
@@ -36910,7 +36952,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D869"/>
+  <dimension ref="A1:D870"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49074,6 +49116,20 @@
       </c>
       <c r="D869">
         <v>11.2925</v>
+      </c>
+    </row>
+    <row r="870" spans="1:4">
+      <c r="A870" s="1">
+        <v>868</v>
+      </c>
+      <c r="B870" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C870">
+        <v>1</v>
+      </c>
+      <c r="D870">
+        <v>11.3775</v>
       </c>
     </row>
   </sheetData>
@@ -49083,7 +49139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D869"/>
+  <dimension ref="A1:D870"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61247,6 +61303,20 @@
       </c>
       <c r="D869">
         <v>102.7492</v>
+      </c>
+    </row>
+    <row r="870" spans="1:4">
+      <c r="A870" s="1">
+        <v>868</v>
+      </c>
+      <c r="B870" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C870">
+        <v>1</v>
+      </c>
+      <c r="D870">
+        <v>103.6755</v>
       </c>
     </row>
   </sheetData>
@@ -61256,7 +61326,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D869"/>
+  <dimension ref="A1:D870"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -73420,6 +73490,20 @@
       </c>
       <c r="D869">
         <v>16.488</v>
+      </c>
+    </row>
+    <row r="870" spans="1:4">
+      <c r="A870" s="1">
+        <v>868</v>
+      </c>
+      <c r="B870" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C870">
+        <v>100</v>
+      </c>
+      <c r="D870">
+        <v>16.2418</v>
       </c>
     </row>
   </sheetData>
@@ -73429,7 +73513,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D869"/>
+  <dimension ref="A1:D870"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -85593,6 +85677,20 @@
       </c>
       <c r="D869">
         <v>47.2679</v>
+      </c>
+    </row>
+    <row r="870" spans="1:4">
+      <c r="A870" s="1">
+        <v>868</v>
+      </c>
+      <c r="B870" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C870">
+        <v>100</v>
+      </c>
+      <c r="D870">
+        <v>47.7339</v>
       </c>
     </row>
   </sheetData>
@@ -85602,7 +85700,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D869"/>
+  <dimension ref="A1:D870"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -97768,6 +97866,20 @@
         <v>94.8049</v>
       </c>
     </row>
+    <row r="870" spans="1:4">
+      <c r="A870" s="1">
+        <v>868</v>
+      </c>
+      <c r="B870" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C870">
+        <v>1</v>
+      </c>
+      <c r="D870">
+        <v>95.36199999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D870"/>
+  <dimension ref="A1:D871"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12569,6 +12569,20 @@
       </c>
       <c r="D870">
         <v>77.49120000000001</v>
+      </c>
+    </row>
+    <row r="871" spans="1:4">
+      <c r="A871" s="1">
+        <v>869</v>
+      </c>
+      <c r="B871" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C871">
+        <v>1</v>
+      </c>
+      <c r="D871">
+        <v>77.9568</v>
       </c>
     </row>
   </sheetData>
@@ -12578,7 +12592,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D870"/>
+  <dimension ref="A1:D871"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24756,6 +24770,20 @@
       </c>
       <c r="D870">
         <v>88.52589999999999</v>
+      </c>
+    </row>
+    <row r="871" spans="1:4">
+      <c r="A871" s="1">
+        <v>869</v>
+      </c>
+      <c r="B871" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C871">
+        <v>1</v>
+      </c>
+      <c r="D871">
+        <v>88.9097</v>
       </c>
     </row>
   </sheetData>
@@ -24765,7 +24793,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D870"/>
+  <dimension ref="A1:D871"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36943,6 +36971,20 @@
       </c>
       <c r="D870">
         <v>53.7401</v>
+      </c>
+    </row>
+    <row r="871" spans="1:4">
+      <c r="A871" s="1">
+        <v>869</v>
+      </c>
+      <c r="B871" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C871">
+        <v>1</v>
+      </c>
+      <c r="D871">
+        <v>54.4762</v>
       </c>
     </row>
   </sheetData>
@@ -36952,7 +36994,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D870"/>
+  <dimension ref="A1:D871"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49130,6 +49172,20 @@
       </c>
       <c r="D870">
         <v>11.3775</v>
+      </c>
+    </row>
+    <row r="871" spans="1:4">
+      <c r="A871" s="1">
+        <v>869</v>
+      </c>
+      <c r="B871" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C871">
+        <v>1</v>
+      </c>
+      <c r="D871">
+        <v>11.5136</v>
       </c>
     </row>
   </sheetData>
@@ -49139,7 +49195,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D870"/>
+  <dimension ref="A1:D871"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61317,6 +61373,20 @@
       </c>
       <c r="D870">
         <v>103.6755</v>
+      </c>
+    </row>
+    <row r="871" spans="1:4">
+      <c r="A871" s="1">
+        <v>869</v>
+      </c>
+      <c r="B871" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C871">
+        <v>1</v>
+      </c>
+      <c r="D871">
+        <v>104.5011</v>
       </c>
     </row>
   </sheetData>
@@ -61326,7 +61396,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D870"/>
+  <dimension ref="A1:D871"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -73504,6 +73574,20 @@
       </c>
       <c r="D870">
         <v>16.2418</v>
+      </c>
+    </row>
+    <row r="871" spans="1:4">
+      <c r="A871" s="1">
+        <v>869</v>
+      </c>
+      <c r="B871" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C871">
+        <v>100</v>
+      </c>
+      <c r="D871">
+        <v>16.6262</v>
       </c>
     </row>
   </sheetData>
@@ -73513,7 +73597,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D870"/>
+  <dimension ref="A1:D871"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -85691,6 +85775,20 @@
       </c>
       <c r="D870">
         <v>47.7339</v>
+      </c>
+    </row>
+    <row r="871" spans="1:4">
+      <c r="A871" s="1">
+        <v>869</v>
+      </c>
+      <c r="B871" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C871">
+        <v>100</v>
+      </c>
+      <c r="D871">
+        <v>48.0799</v>
       </c>
     </row>
   </sheetData>
@@ -85700,7 +85798,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D870"/>
+  <dimension ref="A1:D871"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -97880,6 +97978,20 @@
         <v>95.36199999999999</v>
       </c>
     </row>
+    <row r="871" spans="1:4">
+      <c r="A871" s="1">
+        <v>869</v>
+      </c>
+      <c r="B871" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C871">
+        <v>1</v>
+      </c>
+      <c r="D871">
+        <v>96.2192</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D871"/>
+  <dimension ref="A1:D872"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12583,6 +12583,20 @@
       </c>
       <c r="D871">
         <v>77.9568</v>
+      </c>
+    </row>
+    <row r="872" spans="1:4">
+      <c r="A872" s="1">
+        <v>870</v>
+      </c>
+      <c r="B872" s="2">
+        <v>46220</v>
+      </c>
+      <c r="C872">
+        <v>1</v>
+      </c>
+      <c r="D872">
+        <v>78.3181</v>
       </c>
     </row>
   </sheetData>
@@ -12592,7 +12606,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D871"/>
+  <dimension ref="A1:D872"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24784,6 +24798,20 @@
       </c>
       <c r="D871">
         <v>88.9097</v>
+      </c>
+    </row>
+    <row r="872" spans="1:4">
+      <c r="A872" s="1">
+        <v>870</v>
+      </c>
+      <c r="B872" s="2">
+        <v>46220</v>
+      </c>
+      <c r="C872">
+        <v>1</v>
+      </c>
+      <c r="D872">
+        <v>89.3296</v>
       </c>
     </row>
   </sheetData>
@@ -24793,7 +24821,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D871"/>
+  <dimension ref="A1:D872"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36985,6 +37013,20 @@
       </c>
       <c r="D871">
         <v>54.4762</v>
+      </c>
+    </row>
+    <row r="872" spans="1:4">
+      <c r="A872" s="1">
+        <v>870</v>
+      </c>
+      <c r="B872" s="2">
+        <v>46220</v>
+      </c>
+      <c r="C872">
+        <v>1</v>
+      </c>
+      <c r="D872">
+        <v>54.7992</v>
       </c>
     </row>
   </sheetData>
@@ -36994,7 +37036,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D871"/>
+  <dimension ref="A1:D872"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49186,6 +49228,20 @@
       </c>
       <c r="D871">
         <v>11.5136</v>
+      </c>
+    </row>
+    <row r="872" spans="1:4">
+      <c r="A872" s="1">
+        <v>870</v>
+      </c>
+      <c r="B872" s="2">
+        <v>46220</v>
+      </c>
+      <c r="C872">
+        <v>1</v>
+      </c>
+      <c r="D872">
+        <v>11.5139</v>
       </c>
     </row>
   </sheetData>
@@ -49195,7 +49251,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D871"/>
+  <dimension ref="A1:D872"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61387,6 +61443,20 @@
       </c>
       <c r="D871">
         <v>104.5011</v>
+      </c>
+    </row>
+    <row r="872" spans="1:4">
+      <c r="A872" s="1">
+        <v>870</v>
+      </c>
+      <c r="B872" s="2">
+        <v>46220</v>
+      </c>
+      <c r="C872">
+        <v>1</v>
+      </c>
+      <c r="D872">
+        <v>105.565</v>
       </c>
     </row>
   </sheetData>
@@ -61396,7 +61466,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D871"/>
+  <dimension ref="A1:D872"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -73588,6 +73658,20 @@
       </c>
       <c r="D871">
         <v>16.6262</v>
+      </c>
+    </row>
+    <row r="872" spans="1:4">
+      <c r="A872" s="1">
+        <v>870</v>
+      </c>
+      <c r="B872" s="2">
+        <v>46220</v>
+      </c>
+      <c r="C872">
+        <v>100</v>
+      </c>
+      <c r="D872">
+        <v>16.6737</v>
       </c>
     </row>
   </sheetData>
@@ -73597,7 +73681,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D871"/>
+  <dimension ref="A1:D872"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -85789,6 +85873,20 @@
       </c>
       <c r="D871">
         <v>48.0799</v>
+      </c>
+    </row>
+    <row r="872" spans="1:4">
+      <c r="A872" s="1">
+        <v>870</v>
+      </c>
+      <c r="B872" s="2">
+        <v>46220</v>
+      </c>
+      <c r="C872">
+        <v>100</v>
+      </c>
+      <c r="D872">
+        <v>48.2998</v>
       </c>
     </row>
   </sheetData>
@@ -85798,7 +85896,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D871"/>
+  <dimension ref="A1:D872"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -97992,6 +98090,20 @@
         <v>96.2192</v>
       </c>
     </row>
+    <row r="872" spans="1:4">
+      <c r="A872" s="1">
+        <v>870</v>
+      </c>
+      <c r="B872" s="2">
+        <v>46220</v>
+      </c>
+      <c r="C872">
+        <v>1</v>
+      </c>
+      <c r="D872">
+        <v>97.0485</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D872"/>
+  <dimension ref="A1:D873"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12597,6 +12597,20 @@
       </c>
       <c r="D872">
         <v>78.3181</v>
+      </c>
+    </row>
+    <row r="873" spans="1:4">
+      <c r="A873" s="1">
+        <v>871</v>
+      </c>
+      <c r="B873" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C873">
+        <v>1</v>
+      </c>
+      <c r="D873">
+        <v>78.39870000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12606,7 +12620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D872"/>
+  <dimension ref="A1:D873"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24812,6 +24826,20 @@
       </c>
       <c r="D872">
         <v>89.3296</v>
+      </c>
+    </row>
+    <row r="873" spans="1:4">
+      <c r="A873" s="1">
+        <v>871</v>
+      </c>
+      <c r="B873" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C873">
+        <v>1</v>
+      </c>
+      <c r="D873">
+        <v>89.8998</v>
       </c>
     </row>
   </sheetData>
@@ -24821,7 +24849,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D872"/>
+  <dimension ref="A1:D873"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37027,6 +37055,20 @@
       </c>
       <c r="D872">
         <v>54.7992</v>
+      </c>
+    </row>
+    <row r="873" spans="1:4">
+      <c r="A873" s="1">
+        <v>871</v>
+      </c>
+      <c r="B873" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C873">
+        <v>1</v>
+      </c>
+      <c r="D873">
+        <v>54.7223</v>
       </c>
     </row>
   </sheetData>
@@ -37036,7 +37078,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D872"/>
+  <dimension ref="A1:D873"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49242,6 +49284,20 @@
       </c>
       <c r="D872">
         <v>11.5139</v>
+      </c>
+    </row>
+    <row r="873" spans="1:4">
+      <c r="A873" s="1">
+        <v>871</v>
+      </c>
+      <c r="B873" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C873">
+        <v>1</v>
+      </c>
+      <c r="D873">
+        <v>11.5602</v>
       </c>
     </row>
   </sheetData>
@@ -49251,7 +49307,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D872"/>
+  <dimension ref="A1:D873"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61457,6 +61513,20 @@
       </c>
       <c r="D872">
         <v>105.565</v>
+      </c>
+    </row>
+    <row r="873" spans="1:4">
+      <c r="A873" s="1">
+        <v>871</v>
+      </c>
+      <c r="B873" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C873">
+        <v>1</v>
+      </c>
+      <c r="D873">
+        <v>105.752</v>
       </c>
     </row>
   </sheetData>
@@ -61466,7 +61536,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D872"/>
+  <dimension ref="A1:D873"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -73672,6 +73742,20 @@
       </c>
       <c r="D872">
         <v>16.6737</v>
+      </c>
+    </row>
+    <row r="873" spans="1:4">
+      <c r="A873" s="1">
+        <v>871</v>
+      </c>
+      <c r="B873" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C873">
+        <v>100</v>
+      </c>
+      <c r="D873">
+        <v>16.5979</v>
       </c>
     </row>
   </sheetData>
@@ -73681,7 +73765,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D872"/>
+  <dimension ref="A1:D873"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -85887,6 +85971,20 @@
       </c>
       <c r="D872">
         <v>48.2998</v>
+      </c>
+    </row>
+    <row r="873" spans="1:4">
+      <c r="A873" s="1">
+        <v>871</v>
+      </c>
+      <c r="B873" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C873">
+        <v>100</v>
+      </c>
+      <c r="D873">
+        <v>48.2721</v>
       </c>
     </row>
   </sheetData>
@@ -85896,7 +85994,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D872"/>
+  <dimension ref="A1:D873"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -98104,6 +98202,20 @@
         <v>97.0485</v>
       </c>
     </row>
+    <row r="873" spans="1:4">
+      <c r="A873" s="1">
+        <v>871</v>
+      </c>
+      <c r="B873" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C873">
+        <v>1</v>
+      </c>
+      <c r="D873">
+        <v>97.2086</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D873"/>
+  <dimension ref="A1:D874"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12611,6 +12611,20 @@
       </c>
       <c r="D873">
         <v>78.39870000000001</v>
+      </c>
+    </row>
+    <row r="874" spans="1:4">
+      <c r="A874" s="1">
+        <v>872</v>
+      </c>
+      <c r="B874" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C874">
+        <v>1</v>
+      </c>
+      <c r="D874">
+        <v>78.3159</v>
       </c>
     </row>
   </sheetData>
@@ -12620,7 +12634,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D873"/>
+  <dimension ref="A1:D874"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24840,6 +24854,20 @@
       </c>
       <c r="D873">
         <v>89.8998</v>
+      </c>
+    </row>
+    <row r="874" spans="1:4">
+      <c r="A874" s="1">
+        <v>872</v>
+      </c>
+      <c r="B874" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C874">
+        <v>1</v>
+      </c>
+      <c r="D874">
+        <v>89.55419999999999</v>
       </c>
     </row>
   </sheetData>
@@ -24849,7 +24877,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D873"/>
+  <dimension ref="A1:D874"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37069,6 +37097,20 @@
       </c>
       <c r="D873">
         <v>54.7223</v>
+      </c>
+    </row>
+    <row r="874" spans="1:4">
+      <c r="A874" s="1">
+        <v>872</v>
+      </c>
+      <c r="B874" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C874">
+        <v>1</v>
+      </c>
+      <c r="D874">
+        <v>54.7506</v>
       </c>
     </row>
   </sheetData>
@@ -37078,7 +37120,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D873"/>
+  <dimension ref="A1:D874"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49298,6 +49340,20 @@
       </c>
       <c r="D873">
         <v>11.5602</v>
+      </c>
+    </row>
+    <row r="874" spans="1:4">
+      <c r="A874" s="1">
+        <v>872</v>
+      </c>
+      <c r="B874" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C874">
+        <v>1</v>
+      </c>
+      <c r="D874">
+        <v>11.5698</v>
       </c>
     </row>
   </sheetData>
@@ -49307,7 +49363,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D873"/>
+  <dimension ref="A1:D874"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61527,6 +61583,20 @@
       </c>
       <c r="D873">
         <v>105.752</v>
+      </c>
+    </row>
+    <row r="874" spans="1:4">
+      <c r="A874" s="1">
+        <v>872</v>
+      </c>
+      <c r="B874" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C874">
+        <v>1</v>
+      </c>
+      <c r="D874">
+        <v>105.3036</v>
       </c>
     </row>
   </sheetData>
@@ -61536,7 +61606,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D873"/>
+  <dimension ref="A1:D874"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -73756,6 +73826,20 @@
       </c>
       <c r="D873">
         <v>16.5979</v>
+      </c>
+    </row>
+    <row r="874" spans="1:4">
+      <c r="A874" s="1">
+        <v>872</v>
+      </c>
+      <c r="B874" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C874">
+        <v>100</v>
+      </c>
+      <c r="D874">
+        <v>16.669</v>
       </c>
     </row>
   </sheetData>
@@ -73765,7 +73849,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D873"/>
+  <dimension ref="A1:D874"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -85985,6 +86069,20 @@
       </c>
       <c r="D873">
         <v>48.2721</v>
+      </c>
+    </row>
+    <row r="874" spans="1:4">
+      <c r="A874" s="1">
+        <v>872</v>
+      </c>
+      <c r="B874" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C874">
+        <v>100</v>
+      </c>
+      <c r="D874">
+        <v>48.2211</v>
       </c>
     </row>
   </sheetData>
@@ -85994,7 +86092,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D873"/>
+  <dimension ref="A1:D874"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -98216,6 +98314,20 @@
         <v>97.2086</v>
       </c>
     </row>
+    <row r="874" spans="1:4">
+      <c r="A874" s="1">
+        <v>872</v>
+      </c>
+      <c r="B874" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C874">
+        <v>1</v>
+      </c>
+      <c r="D874">
+        <v>97.0578</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D874"/>
+  <dimension ref="A1:D875"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12625,6 +12625,20 @@
       </c>
       <c r="D874">
         <v>78.3159</v>
+      </c>
+    </row>
+    <row r="875" spans="1:4">
+      <c r="A875" s="1">
+        <v>873</v>
+      </c>
+      <c r="B875" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C875">
+        <v>1</v>
+      </c>
+      <c r="D875">
+        <v>78.554</v>
       </c>
     </row>
   </sheetData>
@@ -12634,7 +12648,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D874"/>
+  <dimension ref="A1:D875"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24868,6 +24882,20 @@
       </c>
       <c r="D874">
         <v>89.55419999999999</v>
+      </c>
+    </row>
+    <row r="875" spans="1:4">
+      <c r="A875" s="1">
+        <v>873</v>
+      </c>
+      <c r="B875" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C875">
+        <v>1</v>
+      </c>
+      <c r="D875">
+        <v>89.75579999999999</v>
       </c>
     </row>
   </sheetData>
@@ -24877,7 +24905,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D874"/>
+  <dimension ref="A1:D875"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37111,6 +37139,20 @@
       </c>
       <c r="D874">
         <v>54.7506</v>
+      </c>
+    </row>
+    <row r="875" spans="1:4">
+      <c r="A875" s="1">
+        <v>873</v>
+      </c>
+      <c r="B875" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C875">
+        <v>1</v>
+      </c>
+      <c r="D875">
+        <v>55.0585</v>
       </c>
     </row>
   </sheetData>
@@ -37120,7 +37162,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D874"/>
+  <dimension ref="A1:D875"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49354,6 +49396,20 @@
       </c>
       <c r="D874">
         <v>11.5698</v>
+      </c>
+    </row>
+    <row r="875" spans="1:4">
+      <c r="A875" s="1">
+        <v>873</v>
+      </c>
+      <c r="B875" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C875">
+        <v>1</v>
+      </c>
+      <c r="D875">
+        <v>11.6091</v>
       </c>
     </row>
   </sheetData>
@@ -49363,7 +49419,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D874"/>
+  <dimension ref="A1:D875"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61597,6 +61653,20 @@
       </c>
       <c r="D874">
         <v>105.3036</v>
+      </c>
+    </row>
+    <row r="875" spans="1:4">
+      <c r="A875" s="1">
+        <v>873</v>
+      </c>
+      <c r="B875" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C875">
+        <v>1</v>
+      </c>
+      <c r="D875">
+        <v>105.5766</v>
       </c>
     </row>
   </sheetData>
@@ -61606,7 +61676,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D874"/>
+  <dimension ref="A1:D875"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -73840,6 +73910,20 @@
       </c>
       <c r="D874">
         <v>16.669</v>
+      </c>
+    </row>
+    <row r="875" spans="1:4">
+      <c r="A875" s="1">
+        <v>873</v>
+      </c>
+      <c r="B875" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C875">
+        <v>100</v>
+      </c>
+      <c r="D875">
+        <v>16.7037</v>
       </c>
     </row>
   </sheetData>
@@ -73849,7 +73933,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D874"/>
+  <dimension ref="A1:D875"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -86083,6 +86167,20 @@
       </c>
       <c r="D874">
         <v>48.2211</v>
+      </c>
+    </row>
+    <row r="875" spans="1:4">
+      <c r="A875" s="1">
+        <v>873</v>
+      </c>
+      <c r="B875" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C875">
+        <v>100</v>
+      </c>
+      <c r="D875">
+        <v>48.3379</v>
       </c>
     </row>
   </sheetData>
@@ -86092,7 +86190,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D874"/>
+  <dimension ref="A1:D875"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -98328,6 +98426,20 @@
         <v>97.0578</v>
       </c>
     </row>
+    <row r="875" spans="1:4">
+      <c r="A875" s="1">
+        <v>873</v>
+      </c>
+      <c r="B875" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C875">
+        <v>1</v>
+      </c>
+      <c r="D875">
+        <v>96.9443</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D875"/>
+  <dimension ref="A1:D876"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12639,6 +12639,20 @@
       </c>
       <c r="D875">
         <v>78.554</v>
+      </c>
+    </row>
+    <row r="876" spans="1:4">
+      <c r="A876" s="1">
+        <v>874</v>
+      </c>
+      <c r="B876" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C876">
+        <v>1</v>
+      </c>
+      <c r="D876">
+        <v>78.4756</v>
       </c>
     </row>
   </sheetData>
@@ -12648,7 +12662,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D875"/>
+  <dimension ref="A1:D876"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24896,6 +24910,20 @@
       </c>
       <c r="D875">
         <v>89.75579999999999</v>
+      </c>
+    </row>
+    <row r="876" spans="1:4">
+      <c r="A876" s="1">
+        <v>874</v>
+      </c>
+      <c r="B876" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C876">
+        <v>1</v>
+      </c>
+      <c r="D876">
+        <v>89.60339999999999</v>
       </c>
     </row>
   </sheetData>
@@ -24905,7 +24933,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D875"/>
+  <dimension ref="A1:D876"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37153,6 +37181,20 @@
       </c>
       <c r="D875">
         <v>55.0585</v>
+      </c>
+    </row>
+    <row r="876" spans="1:4">
+      <c r="A876" s="1">
+        <v>874</v>
+      </c>
+      <c r="B876" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C876">
+        <v>1</v>
+      </c>
+      <c r="D876">
+        <v>54.9094</v>
       </c>
     </row>
   </sheetData>
@@ -37162,7 +37204,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D875"/>
+  <dimension ref="A1:D876"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49410,6 +49452,20 @@
       </c>
       <c r="D875">
         <v>11.6091</v>
+      </c>
+    </row>
+    <row r="876" spans="1:4">
+      <c r="A876" s="1">
+        <v>874</v>
+      </c>
+      <c r="B876" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C876">
+        <v>1</v>
+      </c>
+      <c r="D876">
+        <v>11.5782</v>
       </c>
     </row>
   </sheetData>
@@ -49419,7 +49475,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D875"/>
+  <dimension ref="A1:D876"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61667,6 +61723,20 @@
       </c>
       <c r="D875">
         <v>105.5766</v>
+      </c>
+    </row>
+    <row r="876" spans="1:4">
+      <c r="A876" s="1">
+        <v>874</v>
+      </c>
+      <c r="B876" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C876">
+        <v>1</v>
+      </c>
+      <c r="D876">
+        <v>104.9376</v>
       </c>
     </row>
   </sheetData>
@@ -61676,7 +61746,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D875"/>
+  <dimension ref="A1:D876"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -73924,6 +73994,20 @@
       </c>
       <c r="D875">
         <v>16.7037</v>
+      </c>
+    </row>
+    <row r="876" spans="1:4">
+      <c r="A876" s="1">
+        <v>874</v>
+      </c>
+      <c r="B876" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C876">
+        <v>100</v>
+      </c>
+      <c r="D876">
+        <v>16.7115</v>
       </c>
     </row>
   </sheetData>
@@ -73933,7 +74017,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D875"/>
+  <dimension ref="A1:D876"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -86181,6 +86265,20 @@
       </c>
       <c r="D875">
         <v>48.3379</v>
+      </c>
+    </row>
+    <row r="876" spans="1:4">
+      <c r="A876" s="1">
+        <v>874</v>
+      </c>
+      <c r="B876" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C876">
+        <v>100</v>
+      </c>
+      <c r="D876">
+        <v>48.1003</v>
       </c>
     </row>
   </sheetData>
@@ -86190,7 +86288,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D875"/>
+  <dimension ref="A1:D876"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -98440,6 +98538,20 @@
         <v>96.9443</v>
       </c>
     </row>
+    <row r="876" spans="1:4">
+      <c r="A876" s="1">
+        <v>874</v>
+      </c>
+      <c r="B876" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C876">
+        <v>1</v>
+      </c>
+      <c r="D876">
+        <v>96.6567</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D876"/>
+  <dimension ref="A1:D877"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12653,6 +12653,20 @@
       </c>
       <c r="D876">
         <v>78.4756</v>
+      </c>
+    </row>
+    <row r="877" spans="1:4">
+      <c r="A877" s="1">
+        <v>875</v>
+      </c>
+      <c r="B877" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C877">
+        <v>1</v>
+      </c>
+      <c r="D877">
+        <v>78.4049</v>
       </c>
     </row>
   </sheetData>
@@ -12662,7 +12676,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D876"/>
+  <dimension ref="A1:D877"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24924,6 +24938,20 @@
       </c>
       <c r="D876">
         <v>89.60339999999999</v>
+      </c>
+    </row>
+    <row r="877" spans="1:4">
+      <c r="A877" s="1">
+        <v>875</v>
+      </c>
+      <c r="B877" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C877">
+        <v>1</v>
+      </c>
+      <c r="D877">
+        <v>89.4443</v>
       </c>
     </row>
   </sheetData>
@@ -24933,7 +24961,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D876"/>
+  <dimension ref="A1:D877"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37195,6 +37223,20 @@
       </c>
       <c r="D876">
         <v>54.9094</v>
+      </c>
+    </row>
+    <row r="877" spans="1:4">
+      <c r="A877" s="1">
+        <v>875</v>
+      </c>
+      <c r="B877" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C877">
+        <v>1</v>
+      </c>
+      <c r="D877">
+        <v>54.9854</v>
       </c>
     </row>
   </sheetData>
@@ -37204,7 +37246,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D876"/>
+  <dimension ref="A1:D877"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49466,6 +49508,20 @@
       </c>
       <c r="D876">
         <v>11.5782</v>
+      </c>
+    </row>
+    <row r="877" spans="1:4">
+      <c r="A877" s="1">
+        <v>875</v>
+      </c>
+      <c r="B877" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C877">
+        <v>1</v>
+      </c>
+      <c r="D877">
+        <v>11.5826</v>
       </c>
     </row>
   </sheetData>
@@ -49475,7 +49531,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D876"/>
+  <dimension ref="A1:D877"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61737,6 +61793,20 @@
       </c>
       <c r="D876">
         <v>104.9376</v>
+      </c>
+    </row>
+    <row r="877" spans="1:4">
+      <c r="A877" s="1">
+        <v>875</v>
+      </c>
+      <c r="B877" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C877">
+        <v>1</v>
+      </c>
+      <c r="D877">
+        <v>104.8666</v>
       </c>
     </row>
   </sheetData>
@@ -61746,7 +61816,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D876"/>
+  <dimension ref="A1:D877"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -74008,6 +74078,20 @@
       </c>
       <c r="D876">
         <v>16.7115</v>
+      </c>
+    </row>
+    <row r="877" spans="1:4">
+      <c r="A877" s="1">
+        <v>875</v>
+      </c>
+      <c r="B877" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C877">
+        <v>100</v>
+      </c>
+      <c r="D877">
+        <v>16.7657</v>
       </c>
     </row>
   </sheetData>
@@ -74017,7 +74101,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D876"/>
+  <dimension ref="A1:D877"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -86279,6 +86363,20 @@
       </c>
       <c r="D876">
         <v>48.1003</v>
+      </c>
+    </row>
+    <row r="877" spans="1:4">
+      <c r="A877" s="1">
+        <v>875</v>
+      </c>
+      <c r="B877" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C877">
+        <v>100</v>
+      </c>
+      <c r="D877">
+        <v>48.0835</v>
       </c>
     </row>
   </sheetData>
@@ -86288,7 +86386,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D876"/>
+  <dimension ref="A1:D877"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -98552,6 +98650,20 @@
         <v>96.6567</v>
       </c>
     </row>
+    <row r="877" spans="1:4">
+      <c r="A877" s="1">
+        <v>875</v>
+      </c>
+      <c r="B877" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C877">
+        <v>1</v>
+      </c>
+      <c r="D877">
+        <v>96.2259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D877"/>
+  <dimension ref="A1:D878"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12667,6 +12667,20 @@
       </c>
       <c r="D877">
         <v>78.4049</v>
+      </c>
+    </row>
+    <row r="878" spans="1:4">
+      <c r="A878" s="1">
+        <v>876</v>
+      </c>
+      <c r="B878" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C878">
+        <v>1</v>
+      </c>
+      <c r="D878">
+        <v>78.0308</v>
       </c>
     </row>
   </sheetData>
@@ -12676,7 +12690,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D877"/>
+  <dimension ref="A1:D878"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24952,6 +24966,20 @@
       </c>
       <c r="D877">
         <v>89.4443</v>
+      </c>
+    </row>
+    <row r="878" spans="1:4">
+      <c r="A878" s="1">
+        <v>876</v>
+      </c>
+      <c r="B878" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C878">
+        <v>1</v>
+      </c>
+      <c r="D878">
+        <v>88.8927</v>
       </c>
     </row>
   </sheetData>
@@ -24961,7 +24989,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D877"/>
+  <dimension ref="A1:D878"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37237,6 +37265,20 @@
       </c>
       <c r="D877">
         <v>54.9854</v>
+      </c>
+    </row>
+    <row r="878" spans="1:4">
+      <c r="A878" s="1">
+        <v>876</v>
+      </c>
+      <c r="B878" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C878">
+        <v>1</v>
+      </c>
+      <c r="D878">
+        <v>54.4265</v>
       </c>
     </row>
   </sheetData>
@@ -37246,7 +37288,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D877"/>
+  <dimension ref="A1:D878"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49522,6 +49564,20 @@
       </c>
       <c r="D877">
         <v>11.5826</v>
+      </c>
+    </row>
+    <row r="878" spans="1:4">
+      <c r="A878" s="1">
+        <v>876</v>
+      </c>
+      <c r="B878" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C878">
+        <v>1</v>
+      </c>
+      <c r="D878">
+        <v>11.5025</v>
       </c>
     </row>
   </sheetData>
@@ -49531,7 +49587,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D877"/>
+  <dimension ref="A1:D878"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61807,6 +61863,20 @@
       </c>
       <c r="D877">
         <v>104.8666</v>
+      </c>
+    </row>
+    <row r="878" spans="1:4">
+      <c r="A878" s="1">
+        <v>876</v>
+      </c>
+      <c r="B878" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C878">
+        <v>1</v>
+      </c>
+      <c r="D878">
+        <v>103.937</v>
       </c>
     </row>
   </sheetData>
@@ -61816,7 +61886,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D877"/>
+  <dimension ref="A1:D878"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -74092,6 +74162,20 @@
       </c>
       <c r="D877">
         <v>16.7657</v>
+      </c>
+    </row>
+    <row r="878" spans="1:4">
+      <c r="A878" s="1">
+        <v>876</v>
+      </c>
+      <c r="B878" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C878">
+        <v>100</v>
+      </c>
+      <c r="D878">
+        <v>16.7542</v>
       </c>
     </row>
   </sheetData>
@@ -74101,7 +74185,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D877"/>
+  <dimension ref="A1:D878"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -86377,6 +86461,20 @@
       </c>
       <c r="D877">
         <v>48.0835</v>
+      </c>
+    </row>
+    <row r="878" spans="1:4">
+      <c r="A878" s="1">
+        <v>876</v>
+      </c>
+      <c r="B878" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C878">
+        <v>100</v>
+      </c>
+      <c r="D878">
+        <v>47.6001</v>
       </c>
     </row>
   </sheetData>
@@ -86386,7 +86484,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D877"/>
+  <dimension ref="A1:D878"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -98664,6 +98762,20 @@
         <v>96.2259</v>
       </c>
     </row>
+    <row r="878" spans="1:4">
+      <c r="A878" s="1">
+        <v>876</v>
+      </c>
+      <c r="B878" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C878">
+        <v>1</v>
+      </c>
+      <c r="D878">
+        <v>95.56740000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D878"/>
+  <dimension ref="A1:D879"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12681,6 +12681,20 @@
       </c>
       <c r="D878">
         <v>78.0308</v>
+      </c>
+    </row>
+    <row r="879" spans="1:4">
+      <c r="A879" s="1">
+        <v>877</v>
+      </c>
+      <c r="B879" s="2">
+        <v>46231</v>
+      </c>
+      <c r="C879">
+        <v>1</v>
+      </c>
+      <c r="D879">
+        <v>78.0172</v>
       </c>
     </row>
   </sheetData>
@@ -12690,7 +12704,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D878"/>
+  <dimension ref="A1:D879"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24980,6 +24994,20 @@
       </c>
       <c r="D878">
         <v>88.8927</v>
+      </c>
+    </row>
+    <row r="879" spans="1:4">
+      <c r="A879" s="1">
+        <v>877</v>
+      </c>
+      <c r="B879" s="2">
+        <v>46231</v>
+      </c>
+      <c r="C879">
+        <v>1</v>
+      </c>
+      <c r="D879">
+        <v>88.7602</v>
       </c>
     </row>
   </sheetData>
@@ -24989,7 +25017,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D878"/>
+  <dimension ref="A1:D879"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37279,6 +37307,20 @@
       </c>
       <c r="D878">
         <v>54.4265</v>
+      </c>
+    </row>
+    <row r="879" spans="1:4">
+      <c r="A879" s="1">
+        <v>877</v>
+      </c>
+      <c r="B879" s="2">
+        <v>46231</v>
+      </c>
+      <c r="C879">
+        <v>1</v>
+      </c>
+      <c r="D879">
+        <v>54.6354</v>
       </c>
     </row>
   </sheetData>
@@ -37288,7 +37330,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D878"/>
+  <dimension ref="A1:D879"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49578,6 +49620,20 @@
       </c>
       <c r="D878">
         <v>11.5025</v>
+      </c>
+    </row>
+    <row r="879" spans="1:4">
+      <c r="A879" s="1">
+        <v>877</v>
+      </c>
+      <c r="B879" s="2">
+        <v>46231</v>
+      </c>
+      <c r="C879">
+        <v>1</v>
+      </c>
+      <c r="D879">
+        <v>11.5218</v>
       </c>
     </row>
   </sheetData>
@@ -49587,7 +49643,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D878"/>
+  <dimension ref="A1:D879"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61877,6 +61933,20 @@
       </c>
       <c r="D878">
         <v>103.937</v>
+      </c>
+    </row>
+    <row r="879" spans="1:4">
+      <c r="A879" s="1">
+        <v>877</v>
+      </c>
+      <c r="B879" s="2">
+        <v>46231</v>
+      </c>
+      <c r="C879">
+        <v>1</v>
+      </c>
+      <c r="D879">
+        <v>103.9735</v>
       </c>
     </row>
   </sheetData>
@@ -61886,7 +61956,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D878"/>
+  <dimension ref="A1:D879"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -74176,6 +74246,20 @@
       </c>
       <c r="D878">
         <v>16.7542</v>
+      </c>
+    </row>
+    <row r="879" spans="1:4">
+      <c r="A879" s="1">
+        <v>877</v>
+      </c>
+      <c r="B879" s="2">
+        <v>46231</v>
+      </c>
+      <c r="C879">
+        <v>100</v>
+      </c>
+      <c r="D879">
+        <v>16.3878</v>
       </c>
     </row>
   </sheetData>
@@ -74185,7 +74269,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D878"/>
+  <dimension ref="A1:D879"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -86475,6 +86559,20 @@
       </c>
       <c r="D878">
         <v>47.6001</v>
+      </c>
+    </row>
+    <row r="879" spans="1:4">
+      <c r="A879" s="1">
+        <v>877</v>
+      </c>
+      <c r="B879" s="2">
+        <v>46231</v>
+      </c>
+      <c r="C879">
+        <v>100</v>
+      </c>
+      <c r="D879">
+        <v>47.6732</v>
       </c>
     </row>
   </sheetData>
@@ -86484,7 +86582,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D878"/>
+  <dimension ref="A1:D879"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -98776,6 +98874,20 @@
         <v>95.56740000000001</v>
       </c>
     </row>
+    <row r="879" spans="1:4">
+      <c r="A879" s="1">
+        <v>877</v>
+      </c>
+      <c r="B879" s="2">
+        <v>46231</v>
+      </c>
+      <c r="C879">
+        <v>1</v>
+      </c>
+      <c r="D879">
+        <v>95.7384</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D879"/>
+  <dimension ref="A1:D880"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12695,6 +12695,20 @@
       </c>
       <c r="D879">
         <v>78.0172</v>
+      </c>
+    </row>
+    <row r="880" spans="1:4">
+      <c r="A880" s="1">
+        <v>878</v>
+      </c>
+      <c r="B880" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C880">
+        <v>1</v>
+      </c>
+      <c r="D880">
+        <v>78.69799999999999</v>
       </c>
     </row>
   </sheetData>
@@ -12704,7 +12718,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D879"/>
+  <dimension ref="A1:D880"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25008,6 +25022,20 @@
       </c>
       <c r="D879">
         <v>88.7602</v>
+      </c>
+    </row>
+    <row r="880" spans="1:4">
+      <c r="A880" s="1">
+        <v>878</v>
+      </c>
+      <c r="B880" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C880">
+        <v>1</v>
+      </c>
+      <c r="D880">
+        <v>89.6292</v>
       </c>
     </row>
   </sheetData>
@@ -25017,7 +25045,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D879"/>
+  <dimension ref="A1:D880"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37321,6 +37349,20 @@
       </c>
       <c r="D879">
         <v>54.6354</v>
+      </c>
+    </row>
+    <row r="880" spans="1:4">
+      <c r="A880" s="1">
+        <v>878</v>
+      </c>
+      <c r="B880" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C880">
+        <v>1</v>
+      </c>
+      <c r="D880">
+        <v>54.8289</v>
       </c>
     </row>
   </sheetData>
@@ -37330,7 +37372,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D879"/>
+  <dimension ref="A1:D880"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49634,6 +49676,20 @@
       </c>
       <c r="D879">
         <v>11.5218</v>
+      </c>
+    </row>
+    <row r="880" spans="1:4">
+      <c r="A880" s="1">
+        <v>878</v>
+      </c>
+      <c r="B880" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C880">
+        <v>1</v>
+      </c>
+      <c r="D880">
+        <v>11.5911</v>
       </c>
     </row>
   </sheetData>
@@ -49643,7 +49699,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D879"/>
+  <dimension ref="A1:D880"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -61947,6 +62003,20 @@
       </c>
       <c r="D879">
         <v>103.9735</v>
+      </c>
+    </row>
+    <row r="880" spans="1:4">
+      <c r="A880" s="1">
+        <v>878</v>
+      </c>
+      <c r="B880" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C880">
+        <v>1</v>
+      </c>
+      <c r="D880">
+        <v>104.6998</v>
       </c>
     </row>
   </sheetData>
@@ -61956,7 +62026,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D879"/>
+  <dimension ref="A1:D880"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -74260,6 +74330,20 @@
       </c>
       <c r="D879">
         <v>16.3878</v>
+      </c>
+    </row>
+    <row r="880" spans="1:4">
+      <c r="A880" s="1">
+        <v>878</v>
+      </c>
+      <c r="B880" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C880">
+        <v>100</v>
+      </c>
+      <c r="D880">
+        <v>16.624</v>
       </c>
     </row>
   </sheetData>
@@ -74269,7 +74353,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D879"/>
+  <dimension ref="A1:D880"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -86573,6 +86657,20 @@
       </c>
       <c r="D879">
         <v>47.6732</v>
+      </c>
+    </row>
+    <row r="880" spans="1:4">
+      <c r="A880" s="1">
+        <v>878</v>
+      </c>
+      <c r="B880" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C880">
+        <v>100</v>
+      </c>
+      <c r="D880">
+        <v>48.0452</v>
       </c>
     </row>
   </sheetData>
@@ -86582,7 +86680,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D879"/>
+  <dimension ref="A1:D880"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -98888,6 +98986,20 @@
         <v>95.7384</v>
       </c>
     </row>
+    <row r="880" spans="1:4">
+      <c r="A880" s="1">
+        <v>878</v>
+      </c>
+      <c r="B880" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C880">
+        <v>1</v>
+      </c>
+      <c r="D880">
+        <v>96.04340000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D880"/>
+  <dimension ref="A1:D881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12709,6 +12709,20 @@
       </c>
       <c r="D880">
         <v>78.69799999999999</v>
+      </c>
+    </row>
+    <row r="881" spans="1:4">
+      <c r="A881" s="1">
+        <v>879</v>
+      </c>
+      <c r="B881" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C881">
+        <v>1</v>
+      </c>
+      <c r="D881">
+        <v>79.357</v>
       </c>
     </row>
   </sheetData>
@@ -12718,7 +12732,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D880"/>
+  <dimension ref="A1:D881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25036,6 +25050,20 @@
       </c>
       <c r="D880">
         <v>89.6292</v>
+      </c>
+    </row>
+    <row r="881" spans="1:4">
+      <c r="A881" s="1">
+        <v>879</v>
+      </c>
+      <c r="B881" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C881">
+        <v>1</v>
+      </c>
+      <c r="D881">
+        <v>90.2051</v>
       </c>
     </row>
   </sheetData>
@@ -25045,7 +25073,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D880"/>
+  <dimension ref="A1:D881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37363,6 +37391,20 @@
       </c>
       <c r="D880">
         <v>54.8289</v>
+      </c>
+    </row>
+    <row r="881" spans="1:4">
+      <c r="A881" s="1">
+        <v>879</v>
+      </c>
+      <c r="B881" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C881">
+        <v>1</v>
+      </c>
+      <c r="D881">
+        <v>55.2007</v>
       </c>
     </row>
   </sheetData>
@@ -37372,7 +37414,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D880"/>
+  <dimension ref="A1:D881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49690,6 +49732,20 @@
       </c>
       <c r="D880">
         <v>11.5911</v>
+      </c>
+    </row>
+    <row r="881" spans="1:4">
+      <c r="A881" s="1">
+        <v>879</v>
+      </c>
+      <c r="B881" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C881">
+        <v>1</v>
+      </c>
+      <c r="D881">
+        <v>11.7215</v>
       </c>
     </row>
   </sheetData>
@@ -49699,7 +49755,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D880"/>
+  <dimension ref="A1:D881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -62017,6 +62073,20 @@
       </c>
       <c r="D880">
         <v>104.6998</v>
+      </c>
+    </row>
+    <row r="881" spans="1:4">
+      <c r="A881" s="1">
+        <v>879</v>
+      </c>
+      <c r="B881" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C881">
+        <v>1</v>
+      </c>
+      <c r="D881">
+        <v>105.4813</v>
       </c>
     </row>
   </sheetData>
@@ -62026,7 +62096,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D880"/>
+  <dimension ref="A1:D881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -74344,6 +74414,20 @@
       </c>
       <c r="D880">
         <v>16.624</v>
+      </c>
+    </row>
+    <row r="881" spans="1:4">
+      <c r="A881" s="1">
+        <v>879</v>
+      </c>
+      <c r="B881" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C881">
+        <v>100</v>
+      </c>
+      <c r="D881">
+        <v>16.6454</v>
       </c>
     </row>
   </sheetData>
@@ -74353,7 +74437,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D880"/>
+  <dimension ref="A1:D881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -86671,6 +86755,20 @@
       </c>
       <c r="D880">
         <v>48.0452</v>
+      </c>
+    </row>
+    <row r="881" spans="1:4">
+      <c r="A881" s="1">
+        <v>879</v>
+      </c>
+      <c r="B881" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C881">
+        <v>100</v>
+      </c>
+      <c r="D881">
+        <v>48.483</v>
       </c>
     </row>
   </sheetData>
@@ -86680,7 +86778,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D880"/>
+  <dimension ref="A1:D881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -99000,6 +99098,20 @@
         <v>96.04340000000001</v>
       </c>
     </row>
+    <row r="881" spans="1:4">
+      <c r="A881" s="1">
+        <v>879</v>
+      </c>
+      <c r="B881" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C881">
+        <v>1</v>
+      </c>
+      <c r="D881">
+        <v>96.895</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D881"/>
+  <dimension ref="A1:D882"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12723,6 +12723,20 @@
       </c>
       <c r="D881">
         <v>79.357</v>
+      </c>
+    </row>
+    <row r="882" spans="1:4">
+      <c r="A882" s="1">
+        <v>880</v>
+      </c>
+      <c r="B882" s="2">
+        <v>46234</v>
+      </c>
+      <c r="C882">
+        <v>1</v>
+      </c>
+      <c r="D882">
+        <v>79.8573</v>
       </c>
     </row>
   </sheetData>
@@ -12732,7 +12746,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D881"/>
+  <dimension ref="A1:D882"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25064,6 +25078,20 @@
       </c>
       <c r="D881">
         <v>90.2051</v>
+      </c>
+    </row>
+    <row r="882" spans="1:4">
+      <c r="A882" s="1">
+        <v>880</v>
+      </c>
+      <c r="B882" s="2">
+        <v>46234</v>
+      </c>
+      <c r="C882">
+        <v>1</v>
+      </c>
+      <c r="D882">
+        <v>90.8776</v>
       </c>
     </row>
   </sheetData>
@@ -25073,7 +25101,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D881"/>
+  <dimension ref="A1:D882"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37405,6 +37433,20 @@
       </c>
       <c r="D881">
         <v>55.2007</v>
+      </c>
+    </row>
+    <row r="882" spans="1:4">
+      <c r="A882" s="1">
+        <v>880</v>
+      </c>
+      <c r="B882" s="2">
+        <v>46234</v>
+      </c>
+      <c r="C882">
+        <v>1</v>
+      </c>
+      <c r="D882">
+        <v>55.5088</v>
       </c>
     </row>
   </sheetData>
@@ -37414,7 +37456,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D881"/>
+  <dimension ref="A1:D882"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49746,6 +49788,20 @@
       </c>
       <c r="D881">
         <v>11.7215</v>
+      </c>
+    </row>
+    <row r="882" spans="1:4">
+      <c r="A882" s="1">
+        <v>880</v>
+      </c>
+      <c r="B882" s="2">
+        <v>46234</v>
+      </c>
+      <c r="C882">
+        <v>1</v>
+      </c>
+      <c r="D882">
+        <v>11.8194</v>
       </c>
     </row>
   </sheetData>
@@ -49755,7 +49811,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D881"/>
+  <dimension ref="A1:D882"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -62087,6 +62143,20 @@
       </c>
       <c r="D881">
         <v>105.4813</v>
+      </c>
+    </row>
+    <row r="882" spans="1:4">
+      <c r="A882" s="1">
+        <v>880</v>
+      </c>
+      <c r="B882" s="2">
+        <v>46234</v>
+      </c>
+      <c r="C882">
+        <v>1</v>
+      </c>
+      <c r="D882">
+        <v>106.1064</v>
       </c>
     </row>
   </sheetData>
@@ -62096,7 +62166,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D881"/>
+  <dimension ref="A1:D882"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -74428,6 +74498,20 @@
       </c>
       <c r="D881">
         <v>16.6454</v>
+      </c>
+    </row>
+    <row r="882" spans="1:4">
+      <c r="A882" s="1">
+        <v>880</v>
+      </c>
+      <c r="B882" s="2">
+        <v>46234</v>
+      </c>
+      <c r="C882">
+        <v>100</v>
+      </c>
+      <c r="D882">
+        <v>16.7356</v>
       </c>
     </row>
   </sheetData>
@@ -74437,7 +74521,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D881"/>
+  <dimension ref="A1:D882"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -86769,6 +86853,20 @@
       </c>
       <c r="D881">
         <v>48.483</v>
+      </c>
+    </row>
+    <row r="882" spans="1:4">
+      <c r="A882" s="1">
+        <v>880</v>
+      </c>
+      <c r="B882" s="2">
+        <v>46234</v>
+      </c>
+      <c r="C882">
+        <v>100</v>
+      </c>
+      <c r="D882">
+        <v>48.8633</v>
       </c>
     </row>
   </sheetData>
@@ -86778,7 +86876,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D881"/>
+  <dimension ref="A1:D882"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -99112,6 +99210,20 @@
         <v>96.895</v>
       </c>
     </row>
+    <row r="882" spans="1:4">
+      <c r="A882" s="1">
+        <v>880</v>
+      </c>
+      <c r="B882" s="2">
+        <v>46234</v>
+      </c>
+      <c r="C882">
+        <v>1</v>
+      </c>
+      <c r="D882">
+        <v>97.8523</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D882"/>
+  <dimension ref="A1:D883"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12737,6 +12737,20 @@
       </c>
       <c r="D882">
         <v>79.8573</v>
+      </c>
+    </row>
+    <row r="883" spans="1:4">
+      <c r="A883" s="1">
+        <v>881</v>
+      </c>
+      <c r="B883" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C883">
+        <v>1</v>
+      </c>
+      <c r="D883">
+        <v>79.4637</v>
       </c>
     </row>
   </sheetData>
@@ -12746,7 +12760,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D882"/>
+  <dimension ref="A1:D883"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25092,6 +25106,20 @@
       </c>
       <c r="D882">
         <v>90.8776</v>
+      </c>
+    </row>
+    <row r="883" spans="1:4">
+      <c r="A883" s="1">
+        <v>881</v>
+      </c>
+      <c r="B883" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C883">
+        <v>1</v>
+      </c>
+      <c r="D883">
+        <v>91.1925</v>
       </c>
     </row>
   </sheetData>
@@ -25101,7 +25129,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D882"/>
+  <dimension ref="A1:D883"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37447,6 +37475,20 @@
       </c>
       <c r="D882">
         <v>55.5088</v>
+      </c>
+    </row>
+    <row r="883" spans="1:4">
+      <c r="A883" s="1">
+        <v>881</v>
+      </c>
+      <c r="B883" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C883">
+        <v>1</v>
+      </c>
+      <c r="D883">
+        <v>55.863</v>
       </c>
     </row>
   </sheetData>
@@ -37456,7 +37498,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D882"/>
+  <dimension ref="A1:D883"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49802,6 +49844,20 @@
       </c>
       <c r="D882">
         <v>11.8194</v>
+      </c>
+    </row>
+    <row r="883" spans="1:4">
+      <c r="A883" s="1">
+        <v>881</v>
+      </c>
+      <c r="B883" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C883">
+        <v>1</v>
+      </c>
+      <c r="D883">
+        <v>11.7694</v>
       </c>
     </row>
   </sheetData>
@@ -49811,7 +49867,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D882"/>
+  <dimension ref="A1:D883"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -62157,6 +62213,20 @@
       </c>
       <c r="D882">
         <v>106.1064</v>
+      </c>
+    </row>
+    <row r="883" spans="1:4">
+      <c r="A883" s="1">
+        <v>881</v>
+      </c>
+      <c r="B883" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C883">
+        <v>1</v>
+      </c>
+      <c r="D883">
+        <v>106.68</v>
       </c>
     </row>
   </sheetData>
@@ -62166,7 +62236,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D882"/>
+  <dimension ref="A1:D883"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -74512,6 +74582,20 @@
       </c>
       <c r="D882">
         <v>16.7356</v>
+      </c>
+    </row>
+    <row r="883" spans="1:4">
+      <c r="A883" s="1">
+        <v>881</v>
+      </c>
+      <c r="B883" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C883">
+        <v>100</v>
+      </c>
+      <c r="D883">
+        <v>16.7422</v>
       </c>
     </row>
   </sheetData>
@@ -74521,7 +74605,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D882"/>
+  <dimension ref="A1:D883"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -86867,6 +86951,20 @@
       </c>
       <c r="D882">
         <v>48.8633</v>
+      </c>
+    </row>
+    <row r="883" spans="1:4">
+      <c r="A883" s="1">
+        <v>881</v>
+      </c>
+      <c r="B883" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C883">
+        <v>100</v>
+      </c>
+      <c r="D883">
+        <v>49.4669</v>
       </c>
     </row>
   </sheetData>
@@ -86876,7 +86974,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D882"/>
+  <dimension ref="A1:D883"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -99224,6 +99322,20 @@
         <v>97.8523</v>
       </c>
     </row>
+    <row r="883" spans="1:4">
+      <c r="A883" s="1">
+        <v>881</v>
+      </c>
+      <c r="B883" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C883">
+        <v>1</v>
+      </c>
+      <c r="D883">
+        <v>98.54130000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D883"/>
+  <dimension ref="A1:D885"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12751,6 +12751,34 @@
       </c>
       <c r="D883">
         <v>79.4637</v>
+      </c>
+    </row>
+    <row r="884" spans="1:4">
+      <c r="A884" s="1">
+        <v>882</v>
+      </c>
+      <c r="B884" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C884">
+        <v>1</v>
+      </c>
+      <c r="D884">
+        <v>80.06870000000001</v>
+      </c>
+    </row>
+    <row r="885" spans="1:4">
+      <c r="A885" s="1">
+        <v>883</v>
+      </c>
+      <c r="B885" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C885">
+        <v>1</v>
+      </c>
+      <c r="D885">
+        <v>81.12909999999999</v>
       </c>
     </row>
   </sheetData>
@@ -12760,7 +12788,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D883"/>
+  <dimension ref="A1:D885"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25120,6 +25148,34 @@
       </c>
       <c r="D883">
         <v>91.1925</v>
+      </c>
+    </row>
+    <row r="884" spans="1:4">
+      <c r="A884" s="1">
+        <v>882</v>
+      </c>
+      <c r="B884" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C884">
+        <v>1</v>
+      </c>
+      <c r="D884">
+        <v>91.9589</v>
+      </c>
+    </row>
+    <row r="885" spans="1:4">
+      <c r="A885" s="1">
+        <v>883</v>
+      </c>
+      <c r="B885" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C885">
+        <v>1</v>
+      </c>
+      <c r="D885">
+        <v>93.58240000000001</v>
       </c>
     </row>
   </sheetData>
@@ -25129,7 +25185,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D883"/>
+  <dimension ref="A1:D885"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37489,6 +37545,34 @@
       </c>
       <c r="D883">
         <v>55.863</v>
+      </c>
+    </row>
+    <row r="884" spans="1:4">
+      <c r="A884" s="1">
+        <v>882</v>
+      </c>
+      <c r="B884" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C884">
+        <v>1</v>
+      </c>
+      <c r="D884">
+        <v>56.2883</v>
+      </c>
+    </row>
+    <row r="885" spans="1:4">
+      <c r="A885" s="1">
+        <v>883</v>
+      </c>
+      <c r="B885" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C885">
+        <v>1</v>
+      </c>
+      <c r="D885">
+        <v>56.9445</v>
       </c>
     </row>
   </sheetData>
@@ -37498,7 +37582,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D883"/>
+  <dimension ref="A1:D885"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49858,6 +49942,34 @@
       </c>
       <c r="D883">
         <v>11.7694</v>
+      </c>
+    </row>
+    <row r="884" spans="1:4">
+      <c r="A884" s="1">
+        <v>882</v>
+      </c>
+      <c r="B884" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C884">
+        <v>1</v>
+      </c>
+      <c r="D884">
+        <v>11.8342</v>
+      </c>
+    </row>
+    <row r="885" spans="1:4">
+      <c r="A885" s="1">
+        <v>883</v>
+      </c>
+      <c r="B885" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C885">
+        <v>1</v>
+      </c>
+      <c r="D885">
+        <v>11.9677</v>
       </c>
     </row>
   </sheetData>
@@ -49867,7 +49979,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D883"/>
+  <dimension ref="A1:D885"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -62227,6 +62339,34 @@
       </c>
       <c r="D883">
         <v>106.68</v>
+      </c>
+    </row>
+    <row r="884" spans="1:4">
+      <c r="A884" s="1">
+        <v>882</v>
+      </c>
+      <c r="B884" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C884">
+        <v>1</v>
+      </c>
+      <c r="D884">
+        <v>107.7484</v>
+      </c>
+    </row>
+    <row r="885" spans="1:4">
+      <c r="A885" s="1">
+        <v>883</v>
+      </c>
+      <c r="B885" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C885">
+        <v>1</v>
+      </c>
+      <c r="D885">
+        <v>109.0132</v>
       </c>
     </row>
   </sheetData>
@@ -62236,7 +62376,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D883"/>
+  <dimension ref="A1:D885"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -74596,6 +74736,34 @@
       </c>
       <c r="D883">
         <v>16.7422</v>
+      </c>
+    </row>
+    <row r="884" spans="1:4">
+      <c r="A884" s="1">
+        <v>882</v>
+      </c>
+      <c r="B884" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C884">
+        <v>100</v>
+      </c>
+      <c r="D884">
+        <v>16.9068</v>
+      </c>
+    </row>
+    <row r="885" spans="1:4">
+      <c r="A885" s="1">
+        <v>883</v>
+      </c>
+      <c r="B885" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C885">
+        <v>100</v>
+      </c>
+      <c r="D885">
+        <v>17.0662</v>
       </c>
     </row>
   </sheetData>
@@ -74605,7 +74773,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D883"/>
+  <dimension ref="A1:D885"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -86965,6 +87133,34 @@
       </c>
       <c r="D883">
         <v>49.4669</v>
+      </c>
+    </row>
+    <row r="884" spans="1:4">
+      <c r="A884" s="1">
+        <v>882</v>
+      </c>
+      <c r="B884" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C884">
+        <v>100</v>
+      </c>
+      <c r="D884">
+        <v>51.1621</v>
+      </c>
+    </row>
+    <row r="885" spans="1:4">
+      <c r="A885" s="1">
+        <v>883</v>
+      </c>
+      <c r="B885" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C885">
+        <v>100</v>
+      </c>
+      <c r="D885">
+        <v>51.5171</v>
       </c>
     </row>
   </sheetData>
@@ -86974,7 +87170,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D883"/>
+  <dimension ref="A1:D885"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -99336,6 +99532,34 @@
         <v>98.54130000000001</v>
       </c>
     </row>
+    <row r="884" spans="1:4">
+      <c r="A884" s="1">
+        <v>882</v>
+      </c>
+      <c r="B884" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C884">
+        <v>1</v>
+      </c>
+      <c r="D884">
+        <v>98.97239999999999</v>
+      </c>
+    </row>
+    <row r="885" spans="1:4">
+      <c r="A885" s="1">
+        <v>883</v>
+      </c>
+      <c r="B885" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C885">
+        <v>1</v>
+      </c>
+      <c r="D885">
+        <v>100.1347</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D885"/>
+  <dimension ref="A1:D886"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12779,6 +12779,20 @@
       </c>
       <c r="D885">
         <v>81.12909999999999</v>
+      </c>
+    </row>
+    <row r="886" spans="1:4">
+      <c r="A886" s="1">
+        <v>884</v>
+      </c>
+      <c r="B886" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C886">
+        <v>1</v>
+      </c>
+      <c r="D886">
+        <v>80.9293</v>
       </c>
     </row>
   </sheetData>
@@ -12788,7 +12802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D885"/>
+  <dimension ref="A1:D886"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25176,6 +25190,20 @@
       </c>
       <c r="D885">
         <v>93.58240000000001</v>
+      </c>
+    </row>
+    <row r="886" spans="1:4">
+      <c r="A886" s="1">
+        <v>884</v>
+      </c>
+      <c r="B886" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C886">
+        <v>1</v>
+      </c>
+      <c r="D886">
+        <v>93.1901</v>
       </c>
     </row>
   </sheetData>
@@ -25185,7 +25213,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D885"/>
+  <dimension ref="A1:D886"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37573,6 +37601,20 @@
       </c>
       <c r="D885">
         <v>56.9445</v>
+      </c>
+    </row>
+    <row r="886" spans="1:4">
+      <c r="A886" s="1">
+        <v>884</v>
+      </c>
+      <c r="B886" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C886">
+        <v>1</v>
+      </c>
+      <c r="D886">
+        <v>57.0471</v>
       </c>
     </row>
   </sheetData>
@@ -37582,7 +37624,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D885"/>
+  <dimension ref="A1:D886"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -49970,6 +50012,20 @@
       </c>
       <c r="D885">
         <v>11.9677</v>
+      </c>
+    </row>
+    <row r="886" spans="1:4">
+      <c r="A886" s="1">
+        <v>884</v>
+      </c>
+      <c r="B886" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C886">
+        <v>1</v>
+      </c>
+      <c r="D886">
+        <v>11.9684</v>
       </c>
     </row>
   </sheetData>
@@ -49979,7 +50035,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D885"/>
+  <dimension ref="A1:D886"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -62367,6 +62423,20 @@
       </c>
       <c r="D885">
         <v>109.0132</v>
+      </c>
+    </row>
+    <row r="886" spans="1:4">
+      <c r="A886" s="1">
+        <v>884</v>
+      </c>
+      <c r="B886" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C886">
+        <v>1</v>
+      </c>
+      <c r="D886">
+        <v>108.8256</v>
       </c>
     </row>
   </sheetData>
@@ -62376,7 +62446,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D885"/>
+  <dimension ref="A1:D886"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -74764,6 +74834,20 @@
       </c>
       <c r="D885">
         <v>17.0662</v>
+      </c>
+    </row>
+    <row r="886" spans="1:4">
+      <c r="A886" s="1">
+        <v>884</v>
+      </c>
+      <c r="B886" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C886">
+        <v>100</v>
+      </c>
+      <c r="D886">
+        <v>17.1468</v>
       </c>
     </row>
   </sheetData>
@@ -74773,7 +74857,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D885"/>
+  <dimension ref="A1:D886"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -87161,6 +87245,20 @@
       </c>
       <c r="D885">
         <v>51.5171</v>
+      </c>
+    </row>
+    <row r="886" spans="1:4">
+      <c r="A886" s="1">
+        <v>884</v>
+      </c>
+      <c r="B886" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C886">
+        <v>100</v>
+      </c>
+      <c r="D886">
+        <v>51.3706</v>
       </c>
     </row>
   </sheetData>
@@ -87170,7 +87268,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D885"/>
+  <dimension ref="A1:D886"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -99560,6 +99658,20 @@
         <v>100.1347</v>
       </c>
     </row>
+    <row r="886" spans="1:4">
+      <c r="A886" s="1">
+        <v>884</v>
+      </c>
+      <c r="B886" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C886">
+        <v>1</v>
+      </c>
+      <c r="D886">
+        <v>99.9374</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D886"/>
+  <dimension ref="A1:D887"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12793,6 +12793,20 @@
       </c>
       <c r="D886">
         <v>80.9293</v>
+      </c>
+    </row>
+    <row r="887" spans="1:4">
+      <c r="A887" s="1">
+        <v>885</v>
+      </c>
+      <c r="B887" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C887">
+        <v>1</v>
+      </c>
+      <c r="D887">
+        <v>81.40770000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12802,7 +12816,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D886"/>
+  <dimension ref="A1:D887"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25204,6 +25218,20 @@
       </c>
       <c r="D886">
         <v>93.1901</v>
+      </c>
+    </row>
+    <row r="887" spans="1:4">
+      <c r="A887" s="1">
+        <v>885</v>
+      </c>
+      <c r="B887" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C887">
+        <v>1</v>
+      </c>
+      <c r="D887">
+        <v>94.0585</v>
       </c>
     </row>
   </sheetData>
@@ -25213,7 +25241,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D886"/>
+  <dimension ref="A1:D887"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37615,6 +37643,20 @@
       </c>
       <c r="D886">
         <v>57.0471</v>
+      </c>
+    </row>
+    <row r="887" spans="1:4">
+      <c r="A887" s="1">
+        <v>885</v>
+      </c>
+      <c r="B887" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C887">
+        <v>1</v>
+      </c>
+      <c r="D887">
+        <v>57.3843</v>
       </c>
     </row>
   </sheetData>
@@ -37624,7 +37666,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D886"/>
+  <dimension ref="A1:D887"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50026,6 +50068,20 @@
       </c>
       <c r="D886">
         <v>11.9684</v>
+      </c>
+    </row>
+    <row r="887" spans="1:4">
+      <c r="A887" s="1">
+        <v>885</v>
+      </c>
+      <c r="B887" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C887">
+        <v>1</v>
+      </c>
+      <c r="D887">
+        <v>12.0637</v>
       </c>
     </row>
   </sheetData>
@@ -50035,7 +50091,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D886"/>
+  <dimension ref="A1:D887"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -62437,6 +62493,20 @@
       </c>
       <c r="D886">
         <v>108.8256</v>
+      </c>
+    </row>
+    <row r="887" spans="1:4">
+      <c r="A887" s="1">
+        <v>885</v>
+      </c>
+      <c r="B887" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C887">
+        <v>1</v>
+      </c>
+      <c r="D887">
+        <v>109.7294</v>
       </c>
     </row>
   </sheetData>
@@ -62446,7 +62516,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D886"/>
+  <dimension ref="A1:D887"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -74848,6 +74918,20 @@
       </c>
       <c r="D886">
         <v>17.1468</v>
+      </c>
+    </row>
+    <row r="887" spans="1:4">
+      <c r="A887" s="1">
+        <v>885</v>
+      </c>
+      <c r="B887" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C887">
+        <v>100</v>
+      </c>
+      <c r="D887">
+        <v>17.3263</v>
       </c>
     </row>
   </sheetData>
@@ -74857,7 +74941,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D886"/>
+  <dimension ref="A1:D887"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -87259,6 +87343,20 @@
       </c>
       <c r="D886">
         <v>51.3706</v>
+      </c>
+    </row>
+    <row r="887" spans="1:4">
+      <c r="A887" s="1">
+        <v>885</v>
+      </c>
+      <c r="B887" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C887">
+        <v>100</v>
+      </c>
+      <c r="D887">
+        <v>51.6121</v>
       </c>
     </row>
   </sheetData>
@@ -87268,7 +87366,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D886"/>
+  <dimension ref="A1:D887"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -99672,6 +99770,20 @@
         <v>99.9374</v>
       </c>
     </row>
+    <row r="887" spans="1:4">
+      <c r="A887" s="1">
+        <v>885</v>
+      </c>
+      <c r="B887" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C887">
+        <v>1</v>
+      </c>
+      <c r="D887">
+        <v>100.6649</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D887"/>
+  <dimension ref="A1:D888"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12807,6 +12807,20 @@
       </c>
       <c r="D887">
         <v>81.40770000000001</v>
+      </c>
+    </row>
+    <row r="888" spans="1:4">
+      <c r="A888" s="1">
+        <v>886</v>
+      </c>
+      <c r="B888" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C888">
+        <v>1</v>
+      </c>
+      <c r="D888">
+        <v>82.1665</v>
       </c>
     </row>
   </sheetData>
@@ -12816,7 +12830,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D887"/>
+  <dimension ref="A1:D888"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25232,6 +25246,20 @@
       </c>
       <c r="D887">
         <v>94.0585</v>
+      </c>
+    </row>
+    <row r="888" spans="1:4">
+      <c r="A888" s="1">
+        <v>886</v>
+      </c>
+      <c r="B888" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C888">
+        <v>1</v>
+      </c>
+      <c r="D888">
+        <v>94.8366</v>
       </c>
     </row>
   </sheetData>
@@ -25241,7 +25269,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D887"/>
+  <dimension ref="A1:D888"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37657,6 +37685,20 @@
       </c>
       <c r="D887">
         <v>57.3843</v>
+      </c>
+    </row>
+    <row r="888" spans="1:4">
+      <c r="A888" s="1">
+        <v>886</v>
+      </c>
+      <c r="B888" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C888">
+        <v>1</v>
+      </c>
+      <c r="D888">
+        <v>57.7548</v>
       </c>
     </row>
   </sheetData>
@@ -37666,7 +37708,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D887"/>
+  <dimension ref="A1:D888"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50082,6 +50124,20 @@
       </c>
       <c r="D887">
         <v>12.0637</v>
+      </c>
+    </row>
+    <row r="888" spans="1:4">
+      <c r="A888" s="1">
+        <v>886</v>
+      </c>
+      <c r="B888" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C888">
+        <v>1</v>
+      </c>
+      <c r="D888">
+        <v>12.1655</v>
       </c>
     </row>
   </sheetData>
@@ -50091,7 +50147,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D887"/>
+  <dimension ref="A1:D888"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -62507,6 +62563,20 @@
       </c>
       <c r="D887">
         <v>109.7294</v>
+      </c>
+    </row>
+    <row r="888" spans="1:4">
+      <c r="A888" s="1">
+        <v>886</v>
+      </c>
+      <c r="B888" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C888">
+        <v>1</v>
+      </c>
+      <c r="D888">
+        <v>110.6454</v>
       </c>
     </row>
   </sheetData>
@@ -62516,7 +62586,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D887"/>
+  <dimension ref="A1:D888"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -74932,6 +75002,20 @@
       </c>
       <c r="D887">
         <v>17.3263</v>
+      </c>
+    </row>
+    <row r="888" spans="1:4">
+      <c r="A888" s="1">
+        <v>886</v>
+      </c>
+      <c r="B888" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C888">
+        <v>100</v>
+      </c>
+      <c r="D888">
+        <v>17.5765</v>
       </c>
     </row>
   </sheetData>
@@ -74941,7 +75025,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D887"/>
+  <dimension ref="A1:D888"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -87357,6 +87441,20 @@
       </c>
       <c r="D887">
         <v>51.6121</v>
+      </c>
+    </row>
+    <row r="888" spans="1:4">
+      <c r="A888" s="1">
+        <v>886</v>
+      </c>
+      <c r="B888" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C888">
+        <v>100</v>
+      </c>
+      <c r="D888">
+        <v>51.8204</v>
       </c>
     </row>
   </sheetData>
@@ -87366,7 +87464,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D887"/>
+  <dimension ref="A1:D888"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -99784,6 +99882,20 @@
         <v>100.6649</v>
       </c>
     </row>
+    <row r="888" spans="1:4">
+      <c r="A888" s="1">
+        <v>886</v>
+      </c>
+      <c r="B888" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C888">
+        <v>1</v>
+      </c>
+      <c r="D888">
+        <v>101.3026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D888"/>
+  <dimension ref="A1:D889"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12821,6 +12821,20 @@
       </c>
       <c r="D888">
         <v>82.1665</v>
+      </c>
+    </row>
+    <row r="889" spans="1:4">
+      <c r="A889" s="1">
+        <v>887</v>
+      </c>
+      <c r="B889" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C889">
+        <v>1</v>
+      </c>
+      <c r="D889">
+        <v>82.60599999999999</v>
       </c>
     </row>
   </sheetData>
@@ -12830,7 +12844,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D888"/>
+  <dimension ref="A1:D889"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25260,6 +25274,20 @@
       </c>
       <c r="D888">
         <v>94.8366</v>
+      </c>
+    </row>
+    <row r="889" spans="1:4">
+      <c r="A889" s="1">
+        <v>887</v>
+      </c>
+      <c r="B889" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C889">
+        <v>1</v>
+      </c>
+      <c r="D889">
+        <v>95.286</v>
       </c>
     </row>
   </sheetData>
@@ -25269,7 +25297,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D888"/>
+  <dimension ref="A1:D889"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37699,6 +37727,20 @@
       </c>
       <c r="D888">
         <v>57.7548</v>
+      </c>
+    </row>
+    <row r="889" spans="1:4">
+      <c r="A889" s="1">
+        <v>887</v>
+      </c>
+      <c r="B889" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C889">
+        <v>1</v>
+      </c>
+      <c r="D889">
+        <v>58.3942</v>
       </c>
     </row>
   </sheetData>
@@ -37708,7 +37750,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D888"/>
+  <dimension ref="A1:D889"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50138,6 +50180,20 @@
       </c>
       <c r="D888">
         <v>12.1655</v>
+      </c>
+    </row>
+    <row r="889" spans="1:4">
+      <c r="A889" s="1">
+        <v>887</v>
+      </c>
+      <c r="B889" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C889">
+        <v>1</v>
+      </c>
+      <c r="D889">
+        <v>12.2546</v>
       </c>
     </row>
   </sheetData>
@@ -50147,7 +50203,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D888"/>
+  <dimension ref="A1:D889"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -62577,6 +62633,20 @@
       </c>
       <c r="D888">
         <v>110.6454</v>
+      </c>
+    </row>
+    <row r="889" spans="1:4">
+      <c r="A889" s="1">
+        <v>887</v>
+      </c>
+      <c r="B889" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C889">
+        <v>1</v>
+      </c>
+      <c r="D889">
+        <v>111.4272</v>
       </c>
     </row>
   </sheetData>
@@ -62586,7 +62656,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D888"/>
+  <dimension ref="A1:D889"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -75016,6 +75086,20 @@
       </c>
       <c r="D888">
         <v>17.5765</v>
+      </c>
+    </row>
+    <row r="889" spans="1:4">
+      <c r="A889" s="1">
+        <v>887</v>
+      </c>
+      <c r="B889" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C889">
+        <v>100</v>
+      </c>
+      <c r="D889">
+        <v>17.5784</v>
       </c>
     </row>
   </sheetData>
@@ -75025,7 +75109,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D888"/>
+  <dimension ref="A1:D889"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -87455,6 +87539,20 @@
       </c>
       <c r="D888">
         <v>51.8204</v>
+      </c>
+    </row>
+    <row r="889" spans="1:4">
+      <c r="A889" s="1">
+        <v>887</v>
+      </c>
+      <c r="B889" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C889">
+        <v>100</v>
+      </c>
+      <c r="D889">
+        <v>52.3021</v>
       </c>
     </row>
   </sheetData>
@@ -87464,7 +87562,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D888"/>
+  <dimension ref="A1:D889"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -99896,6 +99994,20 @@
         <v>101.3026</v>
       </c>
     </row>
+    <row r="889" spans="1:4">
+      <c r="A889" s="1">
+        <v>887</v>
+      </c>
+      <c r="B889" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C889">
+        <v>1</v>
+      </c>
+      <c r="D889">
+        <v>102.2098</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D889"/>
+  <dimension ref="A1:D890"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12835,6 +12835,20 @@
       </c>
       <c r="D889">
         <v>82.60599999999999</v>
+      </c>
+    </row>
+    <row r="890" spans="1:4">
+      <c r="A890" s="1">
+        <v>888</v>
+      </c>
+      <c r="B890" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C890">
+        <v>1</v>
+      </c>
+      <c r="D890">
+        <v>82.3742</v>
       </c>
     </row>
   </sheetData>
@@ -12844,7 +12858,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D889"/>
+  <dimension ref="A1:D890"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25288,6 +25302,20 @@
       </c>
       <c r="D889">
         <v>95.286</v>
+      </c>
+    </row>
+    <row r="890" spans="1:4">
+      <c r="A890" s="1">
+        <v>888</v>
+      </c>
+      <c r="B890" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C890">
+        <v>1</v>
+      </c>
+      <c r="D890">
+        <v>95.18340000000001</v>
       </c>
     </row>
   </sheetData>
@@ -25297,7 +25325,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D889"/>
+  <dimension ref="A1:D890"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37741,6 +37769,20 @@
       </c>
       <c r="D889">
         <v>58.3942</v>
+      </c>
+    </row>
+    <row r="890" spans="1:4">
+      <c r="A890" s="1">
+        <v>888</v>
+      </c>
+      <c r="B890" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C890">
+        <v>1</v>
+      </c>
+      <c r="D890">
+        <v>58.1232</v>
       </c>
     </row>
   </sheetData>
@@ -37750,7 +37792,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D889"/>
+  <dimension ref="A1:D890"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50194,6 +50236,20 @@
       </c>
       <c r="D889">
         <v>12.2546</v>
+      </c>
+    </row>
+    <row r="890" spans="1:4">
+      <c r="A890" s="1">
+        <v>888</v>
+      </c>
+      <c r="B890" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C890">
+        <v>1</v>
+      </c>
+      <c r="D890">
+        <v>12.1819</v>
       </c>
     </row>
   </sheetData>
@@ -50203,7 +50259,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D889"/>
+  <dimension ref="A1:D890"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -62647,6 +62703,20 @@
       </c>
       <c r="D889">
         <v>111.4272</v>
+      </c>
+    </row>
+    <row r="890" spans="1:4">
+      <c r="A890" s="1">
+        <v>888</v>
+      </c>
+      <c r="B890" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C890">
+        <v>1</v>
+      </c>
+      <c r="D890">
+        <v>111.3782</v>
       </c>
     </row>
   </sheetData>
@@ -62656,7 +62726,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D889"/>
+  <dimension ref="A1:D890"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -75100,6 +75170,20 @@
       </c>
       <c r="D889">
         <v>17.5784</v>
+      </c>
+    </row>
+    <row r="890" spans="1:4">
+      <c r="A890" s="1">
+        <v>888</v>
+      </c>
+      <c r="B890" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C890">
+        <v>100</v>
+      </c>
+      <c r="D890">
+        <v>17.6738</v>
       </c>
     </row>
   </sheetData>
@@ -75109,7 +75193,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D889"/>
+  <dimension ref="A1:D890"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -87553,6 +87637,20 @@
       </c>
       <c r="D889">
         <v>52.3021</v>
+      </c>
+    </row>
+    <row r="890" spans="1:4">
+      <c r="A890" s="1">
+        <v>888</v>
+      </c>
+      <c r="B890" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C890">
+        <v>100</v>
+      </c>
+      <c r="D890">
+        <v>52.1554</v>
       </c>
     </row>
   </sheetData>
@@ -87562,7 +87660,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D889"/>
+  <dimension ref="A1:D890"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -100008,6 +100106,20 @@
         <v>102.2098</v>
       </c>
     </row>
+    <row r="890" spans="1:4">
+      <c r="A890" s="1">
+        <v>888</v>
+      </c>
+      <c r="B890" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C890">
+        <v>1</v>
+      </c>
+      <c r="D890">
+        <v>101.5586</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D890"/>
+  <dimension ref="A1:D894"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12849,6 +12849,62 @@
       </c>
       <c r="D890">
         <v>82.3742</v>
+      </c>
+    </row>
+    <row r="891" spans="1:4">
+      <c r="A891" s="1">
+        <v>889</v>
+      </c>
+      <c r="B891" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C891">
+        <v>1</v>
+      </c>
+      <c r="D891">
+        <v>82.99769999999999</v>
+      </c>
+    </row>
+    <row r="892" spans="1:4">
+      <c r="A892" s="1">
+        <v>890</v>
+      </c>
+      <c r="B892" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C892">
+        <v>1</v>
+      </c>
+      <c r="D892">
+        <v>83.8058</v>
+      </c>
+    </row>
+    <row r="893" spans="1:4">
+      <c r="A893" s="1">
+        <v>891</v>
+      </c>
+      <c r="B893" s="2">
+        <v>46249</v>
+      </c>
+      <c r="C893">
+        <v>1</v>
+      </c>
+      <c r="D893">
+        <v>84.5449</v>
+      </c>
+    </row>
+    <row r="894" spans="1:4">
+      <c r="A894" s="1">
+        <v>892</v>
+      </c>
+      <c r="B894" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C894">
+        <v>1</v>
+      </c>
+      <c r="D894">
+        <v>85.0136</v>
       </c>
     </row>
   </sheetData>
@@ -12858,7 +12914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D890"/>
+  <dimension ref="A1:D894"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25316,6 +25372,62 @@
       </c>
       <c r="D890">
         <v>95.18340000000001</v>
+      </c>
+    </row>
+    <row r="891" spans="1:4">
+      <c r="A891" s="1">
+        <v>889</v>
+      </c>
+      <c r="B891" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C891">
+        <v>1</v>
+      </c>
+      <c r="D891">
+        <v>95.77930000000001</v>
+      </c>
+    </row>
+    <row r="892" spans="1:4">
+      <c r="A892" s="1">
+        <v>890</v>
+      </c>
+      <c r="B892" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C892">
+        <v>1</v>
+      </c>
+      <c r="D892">
+        <v>96.7538</v>
+      </c>
+    </row>
+    <row r="893" spans="1:4">
+      <c r="A893" s="1">
+        <v>891</v>
+      </c>
+      <c r="B893" s="2">
+        <v>46249</v>
+      </c>
+      <c r="C893">
+        <v>1</v>
+      </c>
+      <c r="D893">
+        <v>97.5141</v>
+      </c>
+    </row>
+    <row r="894" spans="1:4">
+      <c r="A894" s="1">
+        <v>892</v>
+      </c>
+      <c r="B894" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C894">
+        <v>1</v>
+      </c>
+      <c r="D894">
+        <v>98.3352</v>
       </c>
     </row>
   </sheetData>
@@ -25325,7 +25437,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D890"/>
+  <dimension ref="A1:D894"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37783,6 +37895,62 @@
       </c>
       <c r="D890">
         <v>58.1232</v>
+      </c>
+    </row>
+    <row r="891" spans="1:4">
+      <c r="A891" s="1">
+        <v>889</v>
+      </c>
+      <c r="B891" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C891">
+        <v>1</v>
+      </c>
+      <c r="D891">
+        <v>58.6047</v>
+      </c>
+    </row>
+    <row r="892" spans="1:4">
+      <c r="A892" s="1">
+        <v>890</v>
+      </c>
+      <c r="B892" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C892">
+        <v>1</v>
+      </c>
+      <c r="D892">
+        <v>59.0831</v>
+      </c>
+    </row>
+    <row r="893" spans="1:4">
+      <c r="A893" s="1">
+        <v>891</v>
+      </c>
+      <c r="B893" s="2">
+        <v>46249</v>
+      </c>
+      <c r="C893">
+        <v>1</v>
+      </c>
+      <c r="D893">
+        <v>59.7563</v>
+      </c>
+    </row>
+    <row r="894" spans="1:4">
+      <c r="A894" s="1">
+        <v>892</v>
+      </c>
+      <c r="B894" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C894">
+        <v>1</v>
+      </c>
+      <c r="D894">
+        <v>60.4787</v>
       </c>
     </row>
   </sheetData>
@@ -37792,7 +37960,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D890"/>
+  <dimension ref="A1:D894"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50250,6 +50418,62 @@
       </c>
       <c r="D890">
         <v>12.1819</v>
+      </c>
+    </row>
+    <row r="891" spans="1:4">
+      <c r="A891" s="1">
+        <v>889</v>
+      </c>
+      <c r="B891" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C891">
+        <v>1</v>
+      </c>
+      <c r="D891">
+        <v>12.278</v>
+      </c>
+    </row>
+    <row r="892" spans="1:4">
+      <c r="A892" s="1">
+        <v>890</v>
+      </c>
+      <c r="B892" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C892">
+        <v>1</v>
+      </c>
+      <c r="D892">
+        <v>12.4175</v>
+      </c>
+    </row>
+    <row r="893" spans="1:4">
+      <c r="A893" s="1">
+        <v>891</v>
+      </c>
+      <c r="B893" s="2">
+        <v>46249</v>
+      </c>
+      <c r="C893">
+        <v>1</v>
+      </c>
+      <c r="D893">
+        <v>12.4789</v>
+      </c>
+    </row>
+    <row r="894" spans="1:4">
+      <c r="A894" s="1">
+        <v>892</v>
+      </c>
+      <c r="B894" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C894">
+        <v>1</v>
+      </c>
+      <c r="D894">
+        <v>12.6275</v>
       </c>
     </row>
   </sheetData>
@@ -50259,7 +50483,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D890"/>
+  <dimension ref="A1:D894"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -62717,6 +62941,62 @@
       </c>
       <c r="D890">
         <v>111.3782</v>
+      </c>
+    </row>
+    <row r="891" spans="1:4">
+      <c r="A891" s="1">
+        <v>889</v>
+      </c>
+      <c r="B891" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C891">
+        <v>1</v>
+      </c>
+      <c r="D891">
+        <v>112.1216</v>
+      </c>
+    </row>
+    <row r="892" spans="1:4">
+      <c r="A892" s="1">
+        <v>890</v>
+      </c>
+      <c r="B892" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C892">
+        <v>1</v>
+      </c>
+      <c r="D892">
+        <v>113.2133</v>
+      </c>
+    </row>
+    <row r="893" spans="1:4">
+      <c r="A893" s="1">
+        <v>891</v>
+      </c>
+      <c r="B893" s="2">
+        <v>46249</v>
+      </c>
+      <c r="C893">
+        <v>1</v>
+      </c>
+      <c r="D893">
+        <v>114.1948</v>
+      </c>
+    </row>
+    <row r="894" spans="1:4">
+      <c r="A894" s="1">
+        <v>892</v>
+      </c>
+      <c r="B894" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C894">
+        <v>1</v>
+      </c>
+      <c r="D894">
+        <v>115.1849</v>
       </c>
     </row>
   </sheetData>
@@ -62726,7 +63006,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D890"/>
+  <dimension ref="A1:D894"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -75184,6 +75464,62 @@
       </c>
       <c r="D890">
         <v>17.6738</v>
+      </c>
+    </row>
+    <row r="891" spans="1:4">
+      <c r="A891" s="1">
+        <v>889</v>
+      </c>
+      <c r="B891" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C891">
+        <v>100</v>
+      </c>
+      <c r="D891">
+        <v>17.8206</v>
+      </c>
+    </row>
+    <row r="892" spans="1:4">
+      <c r="A892" s="1">
+        <v>890</v>
+      </c>
+      <c r="B892" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C892">
+        <v>100</v>
+      </c>
+      <c r="D892">
+        <v>18.0154</v>
+      </c>
+    </row>
+    <row r="893" spans="1:4">
+      <c r="A893" s="1">
+        <v>891</v>
+      </c>
+      <c r="B893" s="2">
+        <v>46249</v>
+      </c>
+      <c r="C893">
+        <v>100</v>
+      </c>
+      <c r="D893">
+        <v>18.1743</v>
+      </c>
+    </row>
+    <row r="894" spans="1:4">
+      <c r="A894" s="1">
+        <v>892</v>
+      </c>
+      <c r="B894" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C894">
+        <v>100</v>
+      </c>
+      <c r="D894">
+        <v>18.3211</v>
       </c>
     </row>
   </sheetData>
@@ -75193,7 +75529,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D890"/>
+  <dimension ref="A1:D894"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -87651,6 +87987,62 @@
       </c>
       <c r="D890">
         <v>52.1554</v>
+      </c>
+    </row>
+    <row r="891" spans="1:4">
+      <c r="A891" s="1">
+        <v>889</v>
+      </c>
+      <c r="B891" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C891">
+        <v>100</v>
+      </c>
+      <c r="D891">
+        <v>52.0852</v>
+      </c>
+    </row>
+    <row r="892" spans="1:4">
+      <c r="A892" s="1">
+        <v>890</v>
+      </c>
+      <c r="B892" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C892">
+        <v>100</v>
+      </c>
+      <c r="D892">
+        <v>52.5956</v>
+      </c>
+    </row>
+    <row r="893" spans="1:4">
+      <c r="A893" s="1">
+        <v>891</v>
+      </c>
+      <c r="B893" s="2">
+        <v>46249</v>
+      </c>
+      <c r="C893">
+        <v>100</v>
+      </c>
+      <c r="D893">
+        <v>53.0461</v>
+      </c>
+    </row>
+    <row r="894" spans="1:4">
+      <c r="A894" s="1">
+        <v>892</v>
+      </c>
+      <c r="B894" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C894">
+        <v>100</v>
+      </c>
+      <c r="D894">
+        <v>53.4542</v>
       </c>
     </row>
   </sheetData>
@@ -87660,7 +88052,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D890"/>
+  <dimension ref="A1:D894"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -100120,6 +100512,62 @@
         <v>101.5586</v>
       </c>
     </row>
+    <row r="891" spans="1:4">
+      <c r="A891" s="1">
+        <v>889</v>
+      </c>
+      <c r="B891" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C891">
+        <v>1</v>
+      </c>
+      <c r="D891">
+        <v>102.1259</v>
+      </c>
+    </row>
+    <row r="892" spans="1:4">
+      <c r="A892" s="1">
+        <v>890</v>
+      </c>
+      <c r="B892" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C892">
+        <v>1</v>
+      </c>
+      <c r="D892">
+        <v>103.1075</v>
+      </c>
+    </row>
+    <row r="893" spans="1:4">
+      <c r="A893" s="1">
+        <v>891</v>
+      </c>
+      <c r="B893" s="2">
+        <v>46249</v>
+      </c>
+      <c r="C893">
+        <v>1</v>
+      </c>
+      <c r="D893">
+        <v>103.9146</v>
+      </c>
+    </row>
+    <row r="894" spans="1:4">
+      <c r="A894" s="1">
+        <v>892</v>
+      </c>
+      <c r="B894" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C894">
+        <v>1</v>
+      </c>
+      <c r="D894">
+        <v>105.0588</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D894"/>
+  <dimension ref="A1:D895"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12905,6 +12905,20 @@
       </c>
       <c r="D894">
         <v>85.0136</v>
+      </c>
+    </row>
+    <row r="895" spans="1:4">
+      <c r="A895" s="1">
+        <v>893</v>
+      </c>
+      <c r="B895" s="2">
+        <v>46253</v>
+      </c>
+      <c r="C895">
+        <v>1</v>
+      </c>
+      <c r="D895">
+        <v>85.1645</v>
       </c>
     </row>
   </sheetData>
@@ -12914,7 +12928,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D894"/>
+  <dimension ref="A1:D895"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25428,6 +25442,20 @@
       </c>
       <c r="D894">
         <v>98.3352</v>
+      </c>
+    </row>
+    <row r="895" spans="1:4">
+      <c r="A895" s="1">
+        <v>893</v>
+      </c>
+      <c r="B895" s="2">
+        <v>46253</v>
+      </c>
+      <c r="C895">
+        <v>1</v>
+      </c>
+      <c r="D895">
+        <v>98.7312</v>
       </c>
     </row>
   </sheetData>
@@ -25437,7 +25465,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D894"/>
+  <dimension ref="A1:D895"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37951,6 +37979,20 @@
       </c>
       <c r="D894">
         <v>60.4787</v>
+      </c>
+    </row>
+    <row r="895" spans="1:4">
+      <c r="A895" s="1">
+        <v>893</v>
+      </c>
+      <c r="B895" s="2">
+        <v>46253</v>
+      </c>
+      <c r="C895">
+        <v>1</v>
+      </c>
+      <c r="D895">
+        <v>60.4753</v>
       </c>
     </row>
   </sheetData>
@@ -37960,7 +38002,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D894"/>
+  <dimension ref="A1:D895"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50474,6 +50516,20 @@
       </c>
       <c r="D894">
         <v>12.6275</v>
+      </c>
+    </row>
+    <row r="895" spans="1:4">
+      <c r="A895" s="1">
+        <v>893</v>
+      </c>
+      <c r="B895" s="2">
+        <v>46253</v>
+      </c>
+      <c r="C895">
+        <v>1</v>
+      </c>
+      <c r="D895">
+        <v>12.624</v>
       </c>
     </row>
   </sheetData>
@@ -50483,7 +50539,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D894"/>
+  <dimension ref="A1:D895"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -62997,6 +63053,20 @@
       </c>
       <c r="D894">
         <v>115.1849</v>
+      </c>
+    </row>
+    <row r="895" spans="1:4">
+      <c r="A895" s="1">
+        <v>893</v>
+      </c>
+      <c r="B895" s="2">
+        <v>46253</v>
+      </c>
+      <c r="C895">
+        <v>1</v>
+      </c>
+      <c r="D895">
+        <v>115.4234</v>
       </c>
     </row>
   </sheetData>
@@ -63006,7 +63076,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D894"/>
+  <dimension ref="A1:D895"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -75520,6 +75590,20 @@
       </c>
       <c r="D894">
         <v>18.3211</v>
+      </c>
+    </row>
+    <row r="895" spans="1:4">
+      <c r="A895" s="1">
+        <v>893</v>
+      </c>
+      <c r="B895" s="2">
+        <v>46253</v>
+      </c>
+      <c r="C895">
+        <v>100</v>
+      </c>
+      <c r="D895">
+        <v>18.4582</v>
       </c>
     </row>
   </sheetData>
@@ -75529,7 +75613,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D894"/>
+  <dimension ref="A1:D895"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88043,6 +88127,20 @@
       </c>
       <c r="D894">
         <v>53.4542</v>
+      </c>
+    </row>
+    <row r="895" spans="1:4">
+      <c r="A895" s="1">
+        <v>893</v>
+      </c>
+      <c r="B895" s="2">
+        <v>46253</v>
+      </c>
+      <c r="C895">
+        <v>100</v>
+      </c>
+      <c r="D895">
+        <v>53.4014</v>
       </c>
     </row>
   </sheetData>
@@ -88052,7 +88150,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D894"/>
+  <dimension ref="A1:D895"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -100568,6 +100666,20 @@
         <v>105.0588</v>
       </c>
     </row>
+    <row r="895" spans="1:4">
+      <c r="A895" s="1">
+        <v>893</v>
+      </c>
+      <c r="B895" s="2">
+        <v>46253</v>
+      </c>
+      <c r="C895">
+        <v>1</v>
+      </c>
+      <c r="D895">
+        <v>104.947</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D895"/>
+  <dimension ref="A1:D896"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12919,6 +12919,20 @@
       </c>
       <c r="D895">
         <v>85.1645</v>
+      </c>
+    </row>
+    <row r="896" spans="1:4">
+      <c r="A896" s="1">
+        <v>894</v>
+      </c>
+      <c r="B896" s="2">
+        <v>46254</v>
+      </c>
+      <c r="C896">
+        <v>1</v>
+      </c>
+      <c r="D896">
+        <v>85.1293</v>
       </c>
     </row>
   </sheetData>
@@ -12928,7 +12942,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D895"/>
+  <dimension ref="A1:D896"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25456,6 +25470,20 @@
       </c>
       <c r="D895">
         <v>98.7312</v>
+      </c>
+    </row>
+    <row r="896" spans="1:4">
+      <c r="A896" s="1">
+        <v>894</v>
+      </c>
+      <c r="B896" s="2">
+        <v>46254</v>
+      </c>
+      <c r="C896">
+        <v>1</v>
+      </c>
+      <c r="D896">
+        <v>98.5457</v>
       </c>
     </row>
   </sheetData>
@@ -25465,7 +25493,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D895"/>
+  <dimension ref="A1:D896"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37993,6 +38021,20 @@
       </c>
       <c r="D895">
         <v>60.4753</v>
+      </c>
+    </row>
+    <row r="896" spans="1:4">
+      <c r="A896" s="1">
+        <v>894</v>
+      </c>
+      <c r="B896" s="2">
+        <v>46254</v>
+      </c>
+      <c r="C896">
+        <v>1</v>
+      </c>
+      <c r="D896">
+        <v>60.1864</v>
       </c>
     </row>
   </sheetData>
@@ -38002,7 +38044,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D895"/>
+  <dimension ref="A1:D896"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50530,6 +50572,20 @@
       </c>
       <c r="D895">
         <v>12.624</v>
+      </c>
+    </row>
+    <row r="896" spans="1:4">
+      <c r="A896" s="1">
+        <v>894</v>
+      </c>
+      <c r="B896" s="2">
+        <v>46254</v>
+      </c>
+      <c r="C896">
+        <v>1</v>
+      </c>
+      <c r="D896">
+        <v>12.6301</v>
       </c>
     </row>
   </sheetData>
@@ -50539,7 +50595,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D895"/>
+  <dimension ref="A1:D896"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -63067,6 +63123,20 @@
       </c>
       <c r="D895">
         <v>115.4234</v>
+      </c>
+    </row>
+    <row r="896" spans="1:4">
+      <c r="A896" s="1">
+        <v>894</v>
+      </c>
+      <c r="B896" s="2">
+        <v>46254</v>
+      </c>
+      <c r="C896">
+        <v>1</v>
+      </c>
+      <c r="D896">
+        <v>115.2906</v>
       </c>
     </row>
   </sheetData>
@@ -63076,7 +63146,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D895"/>
+  <dimension ref="A1:D896"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -75604,6 +75674,20 @@
       </c>
       <c r="D895">
         <v>18.4582</v>
+      </c>
+    </row>
+    <row r="896" spans="1:4">
+      <c r="A896" s="1">
+        <v>894</v>
+      </c>
+      <c r="B896" s="2">
+        <v>46254</v>
+      </c>
+      <c r="C896">
+        <v>100</v>
+      </c>
+      <c r="D896">
+        <v>18.5011</v>
       </c>
     </row>
   </sheetData>
@@ -75613,7 +75697,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D895"/>
+  <dimension ref="A1:D896"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88141,6 +88225,20 @@
       </c>
       <c r="D895">
         <v>53.4014</v>
+      </c>
+    </row>
+    <row r="896" spans="1:4">
+      <c r="A896" s="1">
+        <v>894</v>
+      </c>
+      <c r="B896" s="2">
+        <v>46254</v>
+      </c>
+      <c r="C896">
+        <v>100</v>
+      </c>
+      <c r="D896">
+        <v>53.4027</v>
       </c>
     </row>
   </sheetData>
@@ -88150,7 +88248,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D895"/>
+  <dimension ref="A1:D896"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -100680,6 +100778,20 @@
         <v>104.947</v>
       </c>
     </row>
+    <row r="896" spans="1:4">
+      <c r="A896" s="1">
+        <v>894</v>
+      </c>
+      <c r="B896" s="2">
+        <v>46254</v>
+      </c>
+      <c r="C896">
+        <v>1</v>
+      </c>
+      <c r="D896">
+        <v>104.9813</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D896"/>
+  <dimension ref="A1:D897"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12933,6 +12933,20 @@
       </c>
       <c r="D896">
         <v>85.1293</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4">
+      <c r="A897" s="1">
+        <v>895</v>
+      </c>
+      <c r="B897" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C897">
+        <v>1</v>
+      </c>
+      <c r="D897">
+        <v>83.355</v>
       </c>
     </row>
   </sheetData>
@@ -12942,7 +12956,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D896"/>
+  <dimension ref="A1:D897"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25484,6 +25498,20 @@
       </c>
       <c r="D896">
         <v>98.5457</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4">
+      <c r="A897" s="1">
+        <v>895</v>
+      </c>
+      <c r="B897" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C897">
+        <v>1</v>
+      </c>
+      <c r="D897">
+        <v>96.73350000000001</v>
       </c>
     </row>
   </sheetData>
@@ -25493,7 +25521,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D896"/>
+  <dimension ref="A1:D897"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -38035,6 +38063,20 @@
       </c>
       <c r="D896">
         <v>60.1864</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4">
+      <c r="A897" s="1">
+        <v>895</v>
+      </c>
+      <c r="B897" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C897">
+        <v>1</v>
+      </c>
+      <c r="D897">
+        <v>59.3154</v>
       </c>
     </row>
   </sheetData>
@@ -38044,7 +38086,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D896"/>
+  <dimension ref="A1:D897"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50586,6 +50628,20 @@
       </c>
       <c r="D896">
         <v>12.6301</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4">
+      <c r="A897" s="1">
+        <v>895</v>
+      </c>
+      <c r="B897" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C897">
+        <v>1</v>
+      </c>
+      <c r="D897">
+        <v>12.4057</v>
       </c>
     </row>
   </sheetData>
@@ -50595,7 +50651,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D896"/>
+  <dimension ref="A1:D897"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -63137,6 +63193,20 @@
       </c>
       <c r="D896">
         <v>115.2906</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4">
+      <c r="A897" s="1">
+        <v>895</v>
+      </c>
+      <c r="B897" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C897">
+        <v>1</v>
+      </c>
+      <c r="D897">
+        <v>113.4295</v>
       </c>
     </row>
   </sheetData>
@@ -63146,7 +63216,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D896"/>
+  <dimension ref="A1:D897"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -75688,6 +75758,20 @@
       </c>
       <c r="D896">
         <v>18.5011</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4">
+      <c r="A897" s="1">
+        <v>895</v>
+      </c>
+      <c r="B897" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C897">
+        <v>100</v>
+      </c>
+      <c r="D897">
+        <v>18.0336</v>
       </c>
     </row>
   </sheetData>
@@ -75697,7 +75781,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D896"/>
+  <dimension ref="A1:D897"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88239,6 +88323,20 @@
       </c>
       <c r="D896">
         <v>53.4027</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4">
+      <c r="A897" s="1">
+        <v>895</v>
+      </c>
+      <c r="B897" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C897">
+        <v>100</v>
+      </c>
+      <c r="D897">
+        <v>52.6165</v>
       </c>
     </row>
   </sheetData>
@@ -88248,7 +88346,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D896"/>
+  <dimension ref="A1:D897"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -100792,6 +100890,20 @@
         <v>104.9813</v>
       </c>
     </row>
+    <row r="897" spans="1:4">
+      <c r="A897" s="1">
+        <v>895</v>
+      </c>
+      <c r="B897" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C897">
+        <v>1</v>
+      </c>
+      <c r="D897">
+        <v>104.468</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D897"/>
+  <dimension ref="A1:D898"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12947,6 +12947,20 @@
       </c>
       <c r="D897">
         <v>83.355</v>
+      </c>
+    </row>
+    <row r="898" spans="1:4">
+      <c r="A898" s="1">
+        <v>896</v>
+      </c>
+      <c r="B898" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C898">
+        <v>1</v>
+      </c>
+      <c r="D898">
+        <v>82.9211</v>
       </c>
     </row>
   </sheetData>
@@ -12956,7 +12970,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D897"/>
+  <dimension ref="A1:D898"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25512,6 +25526,20 @@
       </c>
       <c r="D897">
         <v>96.73350000000001</v>
+      </c>
+    </row>
+    <row r="898" spans="1:4">
+      <c r="A898" s="1">
+        <v>896</v>
+      </c>
+      <c r="B898" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C898">
+        <v>1</v>
+      </c>
+      <c r="D898">
+        <v>96.8601</v>
       </c>
     </row>
   </sheetData>
@@ -25521,7 +25549,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D897"/>
+  <dimension ref="A1:D898"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -38077,6 +38105,20 @@
       </c>
       <c r="D897">
         <v>59.3154</v>
+      </c>
+    </row>
+    <row r="898" spans="1:4">
+      <c r="A898" s="1">
+        <v>896</v>
+      </c>
+      <c r="B898" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C898">
+        <v>1</v>
+      </c>
+      <c r="D898">
+        <v>59.2471</v>
       </c>
     </row>
   </sheetData>
@@ -38086,7 +38128,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D897"/>
+  <dimension ref="A1:D898"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50642,6 +50684,20 @@
       </c>
       <c r="D897">
         <v>12.4057</v>
+      </c>
+    </row>
+    <row r="898" spans="1:4">
+      <c r="A898" s="1">
+        <v>896</v>
+      </c>
+      <c r="B898" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C898">
+        <v>1</v>
+      </c>
+      <c r="D898">
+        <v>12.3343</v>
       </c>
     </row>
   </sheetData>
@@ -50651,7 +50707,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D897"/>
+  <dimension ref="A1:D898"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -63207,6 +63263,20 @@
       </c>
       <c r="D897">
         <v>113.4295</v>
+      </c>
+    </row>
+    <row r="898" spans="1:4">
+      <c r="A898" s="1">
+        <v>896</v>
+      </c>
+      <c r="B898" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C898">
+        <v>1</v>
+      </c>
+      <c r="D898">
+        <v>113.038</v>
       </c>
     </row>
   </sheetData>
@@ -63216,7 +63286,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D897"/>
+  <dimension ref="A1:D898"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -75772,6 +75842,20 @@
       </c>
       <c r="D897">
         <v>18.0336</v>
+      </c>
+    </row>
+    <row r="898" spans="1:4">
+      <c r="A898" s="1">
+        <v>896</v>
+      </c>
+      <c r="B898" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C898">
+        <v>100</v>
+      </c>
+      <c r="D898">
+        <v>18.096</v>
       </c>
     </row>
   </sheetData>
@@ -75781,7 +75865,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D897"/>
+  <dimension ref="A1:D898"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88337,6 +88421,20 @@
       </c>
       <c r="D897">
         <v>52.6165</v>
+      </c>
+    </row>
+    <row r="898" spans="1:4">
+      <c r="A898" s="1">
+        <v>896</v>
+      </c>
+      <c r="B898" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C898">
+        <v>100</v>
+      </c>
+      <c r="D898">
+        <v>52.1221</v>
       </c>
     </row>
   </sheetData>
@@ -88346,7 +88444,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D897"/>
+  <dimension ref="A1:D898"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -100904,6 +101002,20 @@
         <v>104.468</v>
       </c>
     </row>
+    <row r="898" spans="1:4">
+      <c r="A898" s="1">
+        <v>896</v>
+      </c>
+      <c r="B898" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C898">
+        <v>1</v>
+      </c>
+      <c r="D898">
+        <v>103.7032</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D898"/>
+  <dimension ref="A1:D899"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12961,6 +12961,20 @@
       </c>
       <c r="D898">
         <v>82.9211</v>
+      </c>
+    </row>
+    <row r="899" spans="1:4">
+      <c r="A899" s="1">
+        <v>897</v>
+      </c>
+      <c r="B899" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C899">
+        <v>1</v>
+      </c>
+      <c r="D899">
+        <v>83.2878</v>
       </c>
     </row>
   </sheetData>
@@ -12970,7 +12984,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D898"/>
+  <dimension ref="A1:D899"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25540,6 +25554,20 @@
       </c>
       <c r="D898">
         <v>96.8601</v>
+      </c>
+    </row>
+    <row r="899" spans="1:4">
+      <c r="A899" s="1">
+        <v>897</v>
+      </c>
+      <c r="B899" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C899">
+        <v>1</v>
+      </c>
+      <c r="D899">
+        <v>97.4384</v>
       </c>
     </row>
   </sheetData>
@@ -25549,7 +25577,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D898"/>
+  <dimension ref="A1:D899"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -38119,6 +38147,20 @@
       </c>
       <c r="D898">
         <v>59.2471</v>
+      </c>
+    </row>
+    <row r="899" spans="1:4">
+      <c r="A899" s="1">
+        <v>897</v>
+      </c>
+      <c r="B899" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C899">
+        <v>1</v>
+      </c>
+      <c r="D899">
+        <v>59.709</v>
       </c>
     </row>
   </sheetData>
@@ -38128,7 +38170,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D898"/>
+  <dimension ref="A1:D899"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50698,6 +50740,20 @@
       </c>
       <c r="D898">
         <v>12.3343</v>
+      </c>
+    </row>
+    <row r="899" spans="1:4">
+      <c r="A899" s="1">
+        <v>897</v>
+      </c>
+      <c r="B899" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C899">
+        <v>1</v>
+      </c>
+      <c r="D899">
+        <v>12.3853</v>
       </c>
     </row>
   </sheetData>
@@ -50707,7 +50763,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D898"/>
+  <dimension ref="A1:D899"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -63277,6 +63333,20 @@
       </c>
       <c r="D898">
         <v>113.038</v>
+      </c>
+    </row>
+    <row r="899" spans="1:4">
+      <c r="A899" s="1">
+        <v>897</v>
+      </c>
+      <c r="B899" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C899">
+        <v>1</v>
+      </c>
+      <c r="D899">
+        <v>113.4796</v>
       </c>
     </row>
   </sheetData>
@@ -63286,7 +63356,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D898"/>
+  <dimension ref="A1:D899"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -75856,6 +75926,20 @@
       </c>
       <c r="D898">
         <v>18.096</v>
+      </c>
+    </row>
+    <row r="899" spans="1:4">
+      <c r="A899" s="1">
+        <v>897</v>
+      </c>
+      <c r="B899" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C899">
+        <v>100</v>
+      </c>
+      <c r="D899">
+        <v>18.2297</v>
       </c>
     </row>
   </sheetData>
@@ -75865,7 +75949,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D898"/>
+  <dimension ref="A1:D899"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88435,6 +88519,20 @@
       </c>
       <c r="D898">
         <v>52.1221</v>
+      </c>
+    </row>
+    <row r="899" spans="1:4">
+      <c r="A899" s="1">
+        <v>897</v>
+      </c>
+      <c r="B899" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C899">
+        <v>100</v>
+      </c>
+      <c r="D899">
+        <v>52.4548</v>
       </c>
     </row>
   </sheetData>
@@ -88444,7 +88542,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D898"/>
+  <dimension ref="A1:D899"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -101016,6 +101114,20 @@
         <v>103.7032</v>
       </c>
     </row>
+    <row r="899" spans="1:4">
+      <c r="A899" s="1">
+        <v>897</v>
+      </c>
+      <c r="B899" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C899">
+        <v>1</v>
+      </c>
+      <c r="D899">
+        <v>103.8242</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D899"/>
+  <dimension ref="A1:D900"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12975,6 +12975,20 @@
       </c>
       <c r="D899">
         <v>83.2878</v>
+      </c>
+    </row>
+    <row r="900" spans="1:4">
+      <c r="A900" s="1">
+        <v>898</v>
+      </c>
+      <c r="B900" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C900">
+        <v>1</v>
+      </c>
+      <c r="D900">
+        <v>84.4635</v>
       </c>
     </row>
   </sheetData>
@@ -12984,7 +12998,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D899"/>
+  <dimension ref="A1:D900"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25568,6 +25582,20 @@
       </c>
       <c r="D899">
         <v>97.4384</v>
+      </c>
+    </row>
+    <row r="900" spans="1:4">
+      <c r="A900" s="1">
+        <v>898</v>
+      </c>
+      <c r="B900" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C900">
+        <v>1</v>
+      </c>
+      <c r="D900">
+        <v>98.51819999999999</v>
       </c>
     </row>
   </sheetData>
@@ -25577,7 +25605,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D899"/>
+  <dimension ref="A1:D900"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -38161,6 +38189,20 @@
       </c>
       <c r="D899">
         <v>59.709</v>
+      </c>
+    </row>
+    <row r="900" spans="1:4">
+      <c r="A900" s="1">
+        <v>898</v>
+      </c>
+      <c r="B900" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C900">
+        <v>1</v>
+      </c>
+      <c r="D900">
+        <v>60.3914</v>
       </c>
     </row>
   </sheetData>
@@ -38170,7 +38212,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D899"/>
+  <dimension ref="A1:D900"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50754,6 +50796,20 @@
       </c>
       <c r="D899">
         <v>12.3853</v>
+      </c>
+    </row>
+    <row r="900" spans="1:4">
+      <c r="A900" s="1">
+        <v>898</v>
+      </c>
+      <c r="B900" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C900">
+        <v>1</v>
+      </c>
+      <c r="D900">
+        <v>12.5659</v>
       </c>
     </row>
   </sheetData>
@@ -50763,7 +50819,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D899"/>
+  <dimension ref="A1:D900"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -63347,6 +63403,20 @@
       </c>
       <c r="D899">
         <v>113.4796</v>
+      </c>
+    </row>
+    <row r="900" spans="1:4">
+      <c r="A900" s="1">
+        <v>898</v>
+      </c>
+      <c r="B900" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C900">
+        <v>1</v>
+      </c>
+      <c r="D900">
+        <v>115.166</v>
       </c>
     </row>
   </sheetData>
@@ -63356,7 +63426,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D899"/>
+  <dimension ref="A1:D900"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -75940,6 +76010,20 @@
       </c>
       <c r="D899">
         <v>18.2297</v>
+      </c>
+    </row>
+    <row r="900" spans="1:4">
+      <c r="A900" s="1">
+        <v>898</v>
+      </c>
+      <c r="B900" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C900">
+        <v>100</v>
+      </c>
+      <c r="D900">
+        <v>18.4422</v>
       </c>
     </row>
   </sheetData>
@@ -75949,7 +76033,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D899"/>
+  <dimension ref="A1:D900"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88533,6 +88617,20 @@
       </c>
       <c r="D899">
         <v>52.4548</v>
+      </c>
+    </row>
+    <row r="900" spans="1:4">
+      <c r="A900" s="1">
+        <v>898</v>
+      </c>
+      <c r="B900" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C900">
+        <v>100</v>
+      </c>
+      <c r="D900">
+        <v>53.0616</v>
       </c>
     </row>
   </sheetData>
@@ -88542,7 +88640,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D899"/>
+  <dimension ref="A1:D900"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -101128,6 +101226,20 @@
         <v>103.8242</v>
       </c>
     </row>
+    <row r="900" spans="1:4">
+      <c r="A900" s="1">
+        <v>898</v>
+      </c>
+      <c r="B900" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C900">
+        <v>1</v>
+      </c>
+      <c r="D900">
+        <v>105.198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D900"/>
+  <dimension ref="A1:D901"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12989,6 +12989,20 @@
       </c>
       <c r="D900">
         <v>84.4635</v>
+      </c>
+    </row>
+    <row r="901" spans="1:4">
+      <c r="A901" s="1">
+        <v>899</v>
+      </c>
+      <c r="B901" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C901">
+        <v>1</v>
+      </c>
+      <c r="D901">
+        <v>84.282</v>
       </c>
     </row>
   </sheetData>
@@ -12998,7 +13012,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D900"/>
+  <dimension ref="A1:D901"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25596,6 +25610,20 @@
       </c>
       <c r="D900">
         <v>98.51819999999999</v>
+      </c>
+    </row>
+    <row r="901" spans="1:4">
+      <c r="A901" s="1">
+        <v>899</v>
+      </c>
+      <c r="B901" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C901">
+        <v>1</v>
+      </c>
+      <c r="D901">
+        <v>98.2897</v>
       </c>
     </row>
   </sheetData>
@@ -25605,7 +25633,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D900"/>
+  <dimension ref="A1:D901"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -38203,6 +38231,20 @@
       </c>
       <c r="D900">
         <v>60.3914</v>
+      </c>
+    </row>
+    <row r="901" spans="1:4">
+      <c r="A901" s="1">
+        <v>899</v>
+      </c>
+      <c r="B901" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C901">
+        <v>1</v>
+      </c>
+      <c r="D901">
+        <v>60.5313</v>
       </c>
     </row>
   </sheetData>
@@ -38212,7 +38254,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D900"/>
+  <dimension ref="A1:D901"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50810,6 +50852,20 @@
       </c>
       <c r="D900">
         <v>12.5659</v>
+      </c>
+    </row>
+    <row r="901" spans="1:4">
+      <c r="A901" s="1">
+        <v>899</v>
+      </c>
+      <c r="B901" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C901">
+        <v>1</v>
+      </c>
+      <c r="D901">
+        <v>12.5294</v>
       </c>
     </row>
   </sheetData>
@@ -50819,7 +50875,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D900"/>
+  <dimension ref="A1:D901"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -63417,6 +63473,20 @@
       </c>
       <c r="D900">
         <v>115.166</v>
+      </c>
+    </row>
+    <row r="901" spans="1:4">
+      <c r="A901" s="1">
+        <v>899</v>
+      </c>
+      <c r="B901" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C901">
+        <v>1</v>
+      </c>
+      <c r="D901">
+        <v>114.9017</v>
       </c>
     </row>
   </sheetData>
@@ -63426,7 +63496,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D900"/>
+  <dimension ref="A1:D901"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -76024,6 +76094,20 @@
       </c>
       <c r="D900">
         <v>18.4422</v>
+      </c>
+    </row>
+    <row r="901" spans="1:4">
+      <c r="A901" s="1">
+        <v>899</v>
+      </c>
+      <c r="B901" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C901">
+        <v>100</v>
+      </c>
+      <c r="D901">
+        <v>18.3829</v>
       </c>
     </row>
   </sheetData>
@@ -76033,7 +76117,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D900"/>
+  <dimension ref="A1:D901"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88631,6 +88715,20 @@
       </c>
       <c r="D900">
         <v>53.0616</v>
+      </c>
+    </row>
+    <row r="901" spans="1:4">
+      <c r="A901" s="1">
+        <v>899</v>
+      </c>
+      <c r="B901" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C901">
+        <v>100</v>
+      </c>
+      <c r="D901">
+        <v>52.9709</v>
       </c>
     </row>
   </sheetData>
@@ -88640,7 +88738,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D900"/>
+  <dimension ref="A1:D901"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -101240,6 +101338,20 @@
         <v>105.198</v>
       </c>
     </row>
+    <row r="901" spans="1:4">
+      <c r="A901" s="1">
+        <v>899</v>
+      </c>
+      <c r="B901" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C901">
+        <v>1</v>
+      </c>
+      <c r="D901">
+        <v>104.8805</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D901"/>
+  <dimension ref="A1:D902"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -13003,6 +13003,20 @@
       </c>
       <c r="D901">
         <v>84.282</v>
+      </c>
+    </row>
+    <row r="902" spans="1:4">
+      <c r="A902" s="1">
+        <v>900</v>
+      </c>
+      <c r="B902" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C902">
+        <v>1</v>
+      </c>
+      <c r="D902">
+        <v>85.9541</v>
       </c>
     </row>
   </sheetData>
@@ -13012,7 +13026,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D901"/>
+  <dimension ref="A1:D902"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25624,6 +25638,20 @@
       </c>
       <c r="D901">
         <v>98.2897</v>
+      </c>
+    </row>
+    <row r="902" spans="1:4">
+      <c r="A902" s="1">
+        <v>900</v>
+      </c>
+      <c r="B902" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C902">
+        <v>1</v>
+      </c>
+      <c r="D902">
+        <v>100.2998</v>
       </c>
     </row>
   </sheetData>
@@ -25633,7 +25661,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D901"/>
+  <dimension ref="A1:D902"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -38245,6 +38273,20 @@
       </c>
       <c r="D901">
         <v>60.5313</v>
+      </c>
+    </row>
+    <row r="902" spans="1:4">
+      <c r="A902" s="1">
+        <v>900</v>
+      </c>
+      <c r="B902" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C902">
+        <v>1</v>
+      </c>
+      <c r="D902">
+        <v>61.7408</v>
       </c>
     </row>
   </sheetData>
@@ -38254,7 +38296,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D901"/>
+  <dimension ref="A1:D902"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50866,6 +50908,20 @@
       </c>
       <c r="D901">
         <v>12.5294</v>
+      </c>
+    </row>
+    <row r="902" spans="1:4">
+      <c r="A902" s="1">
+        <v>900</v>
+      </c>
+      <c r="B902" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C902">
+        <v>1</v>
+      </c>
+      <c r="D902">
+        <v>12.7691</v>
       </c>
     </row>
   </sheetData>
@@ -50875,7 +50931,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D901"/>
+  <dimension ref="A1:D902"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -63487,6 +63543,20 @@
       </c>
       <c r="D901">
         <v>114.9017</v>
+      </c>
+    </row>
+    <row r="902" spans="1:4">
+      <c r="A902" s="1">
+        <v>900</v>
+      </c>
+      <c r="B902" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C902">
+        <v>1</v>
+      </c>
+      <c r="D902">
+        <v>116.7944</v>
       </c>
     </row>
   </sheetData>
@@ -63496,7 +63566,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D901"/>
+  <dimension ref="A1:D902"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -76108,6 +76178,20 @@
       </c>
       <c r="D901">
         <v>18.3829</v>
+      </c>
+    </row>
+    <row r="902" spans="1:4">
+      <c r="A902" s="1">
+        <v>900</v>
+      </c>
+      <c r="B902" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C902">
+        <v>100</v>
+      </c>
+      <c r="D902">
+        <v>18.7317</v>
       </c>
     </row>
   </sheetData>
@@ -76117,7 +76201,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D901"/>
+  <dimension ref="A1:D902"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88729,6 +88813,20 @@
       </c>
       <c r="D901">
         <v>52.9709</v>
+      </c>
+    </row>
+    <row r="902" spans="1:4">
+      <c r="A902" s="1">
+        <v>900</v>
+      </c>
+      <c r="B902" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C902">
+        <v>100</v>
+      </c>
+      <c r="D902">
+        <v>54.0014</v>
       </c>
     </row>
   </sheetData>
@@ -88738,7 +88836,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D901"/>
+  <dimension ref="A1:D902"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -101352,6 +101450,20 @@
         <v>104.8805</v>
       </c>
     </row>
+    <row r="902" spans="1:4">
+      <c r="A902" s="1">
+        <v>900</v>
+      </c>
+      <c r="B902" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C902">
+        <v>1</v>
+      </c>
+      <c r="D902">
+        <v>106.6958</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D902"/>
+  <dimension ref="A1:D903"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -13017,6 +13017,20 @@
       </c>
       <c r="D902">
         <v>85.9541</v>
+      </c>
+    </row>
+    <row r="903" spans="1:4">
+      <c r="A903" s="1">
+        <v>901</v>
+      </c>
+      <c r="B903" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C903">
+        <v>1</v>
+      </c>
+      <c r="D903">
+        <v>85.6007</v>
       </c>
     </row>
   </sheetData>
@@ -13026,7 +13040,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D902"/>
+  <dimension ref="A1:D903"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25652,6 +25666,20 @@
       </c>
       <c r="D902">
         <v>100.2998</v>
+      </c>
+    </row>
+    <row r="903" spans="1:4">
+      <c r="A903" s="1">
+        <v>901</v>
+      </c>
+      <c r="B903" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C903">
+        <v>1</v>
+      </c>
+      <c r="D903">
+        <v>99.682</v>
       </c>
     </row>
   </sheetData>
@@ -25661,7 +25689,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D902"/>
+  <dimension ref="A1:D903"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -38287,6 +38315,20 @@
       </c>
       <c r="D902">
         <v>61.7408</v>
+      </c>
+    </row>
+    <row r="903" spans="1:4">
+      <c r="A903" s="1">
+        <v>901</v>
+      </c>
+      <c r="B903" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C903">
+        <v>1</v>
+      </c>
+      <c r="D903">
+        <v>61.5983</v>
       </c>
     </row>
   </sheetData>
@@ -38296,7 +38338,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D902"/>
+  <dimension ref="A1:D903"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50922,6 +50964,20 @@
       </c>
       <c r="D902">
         <v>12.7691</v>
+      </c>
+    </row>
+    <row r="903" spans="1:4">
+      <c r="A903" s="1">
+        <v>901</v>
+      </c>
+      <c r="B903" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C903">
+        <v>1</v>
+      </c>
+      <c r="D903">
+        <v>12.7335</v>
       </c>
     </row>
   </sheetData>
@@ -50931,7 +50987,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D902"/>
+  <dimension ref="A1:D903"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -63557,6 +63613,20 @@
       </c>
       <c r="D902">
         <v>116.7944</v>
+      </c>
+    </row>
+    <row r="903" spans="1:4">
+      <c r="A903" s="1">
+        <v>901</v>
+      </c>
+      <c r="B903" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C903">
+        <v>1</v>
+      </c>
+      <c r="D903">
+        <v>116.2629</v>
       </c>
     </row>
   </sheetData>
@@ -63566,7 +63636,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D902"/>
+  <dimension ref="A1:D903"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -76192,6 +76262,20 @@
       </c>
       <c r="D902">
         <v>18.7317</v>
+      </c>
+    </row>
+    <row r="903" spans="1:4">
+      <c r="A903" s="1">
+        <v>901</v>
+      </c>
+      <c r="B903" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C903">
+        <v>100</v>
+      </c>
+      <c r="D903">
+        <v>18.5163</v>
       </c>
     </row>
   </sheetData>
@@ -76201,7 +76285,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D902"/>
+  <dimension ref="A1:D903"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88827,6 +88911,20 @@
       </c>
       <c r="D902">
         <v>54.0014</v>
+      </c>
+    </row>
+    <row r="903" spans="1:4">
+      <c r="A903" s="1">
+        <v>901</v>
+      </c>
+      <c r="B903" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C903">
+        <v>100</v>
+      </c>
+      <c r="D903">
+        <v>53.7153</v>
       </c>
     </row>
   </sheetData>
@@ -88836,7 +88934,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D902"/>
+  <dimension ref="A1:D903"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -101464,6 +101562,20 @@
         <v>106.6958</v>
       </c>
     </row>
+    <row r="903" spans="1:4">
+      <c r="A903" s="1">
+        <v>901</v>
+      </c>
+      <c r="B903" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C903">
+        <v>1</v>
+      </c>
+      <c r="D903">
+        <v>106.4421</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D903"/>
+  <dimension ref="A1:D904"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -13031,6 +13031,20 @@
       </c>
       <c r="D903">
         <v>85.6007</v>
+      </c>
+    </row>
+    <row r="904" spans="1:4">
+      <c r="A904" s="1">
+        <v>902</v>
+      </c>
+      <c r="B904" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C904">
+        <v>1</v>
+      </c>
+      <c r="D904">
+        <v>86.3793</v>
       </c>
     </row>
   </sheetData>
@@ -13040,7 +13054,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D903"/>
+  <dimension ref="A1:D904"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25680,6 +25694,20 @@
       </c>
       <c r="D903">
         <v>99.682</v>
+      </c>
+    </row>
+    <row r="904" spans="1:4">
+      <c r="A904" s="1">
+        <v>902</v>
+      </c>
+      <c r="B904" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C904">
+        <v>1</v>
+      </c>
+      <c r="D904">
+        <v>100.5714</v>
       </c>
     </row>
   </sheetData>
@@ -25689,7 +25717,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D903"/>
+  <dimension ref="A1:D904"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -38329,6 +38357,20 @@
       </c>
       <c r="D903">
         <v>61.5983</v>
+      </c>
+    </row>
+    <row r="904" spans="1:4">
+      <c r="A904" s="1">
+        <v>902</v>
+      </c>
+      <c r="B904" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C904">
+        <v>1</v>
+      </c>
+      <c r="D904">
+        <v>61.8994</v>
       </c>
     </row>
   </sheetData>
@@ -38338,7 +38380,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D903"/>
+  <dimension ref="A1:D904"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -50978,6 +51020,20 @@
       </c>
       <c r="D903">
         <v>12.7335</v>
+      </c>
+    </row>
+    <row r="904" spans="1:4">
+      <c r="A904" s="1">
+        <v>902</v>
+      </c>
+      <c r="B904" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C904">
+        <v>1</v>
+      </c>
+      <c r="D904">
+        <v>12.858</v>
       </c>
     </row>
   </sheetData>
@@ -50987,7 +51043,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D903"/>
+  <dimension ref="A1:D904"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -63627,6 +63683,20 @@
       </c>
       <c r="D903">
         <v>116.2629</v>
+      </c>
+    </row>
+    <row r="904" spans="1:4">
+      <c r="A904" s="1">
+        <v>902</v>
+      </c>
+      <c r="B904" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C904">
+        <v>1</v>
+      </c>
+      <c r="D904">
+        <v>117.3204</v>
       </c>
     </row>
   </sheetData>
@@ -63636,7 +63706,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D903"/>
+  <dimension ref="A1:D904"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -76276,6 +76346,20 @@
       </c>
       <c r="D903">
         <v>18.5163</v>
+      </c>
+    </row>
+    <row r="904" spans="1:4">
+      <c r="A904" s="1">
+        <v>902</v>
+      </c>
+      <c r="B904" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C904">
+        <v>100</v>
+      </c>
+      <c r="D904">
+        <v>18.5854</v>
       </c>
     </row>
   </sheetData>
@@ -76285,7 +76369,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D903"/>
+  <dimension ref="A1:D904"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -88925,6 +89009,20 @@
       </c>
       <c r="D903">
         <v>53.7153</v>
+      </c>
+    </row>
+    <row r="904" spans="1:4">
+      <c r="A904" s="1">
+        <v>902</v>
+      </c>
+      <c r="B904" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C904">
+        <v>100</v>
+      </c>
+      <c r="D904">
+        <v>53.9837</v>
       </c>
     </row>
   </sheetData>
@@ -88934,7 +89032,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D903"/>
+  <dimension ref="A1:D904"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -101576,6 +101674,20 @@
         <v>106.4421</v>
       </c>
     </row>
+    <row r="904" spans="1:4">
+      <c r="A904" s="1">
+        <v>902</v>
+      </c>
+      <c r="B904" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C904">
+        <v>1</v>
+      </c>
+      <c r="D904">
+        <v>106.7993</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_currency.xlsx
+++ b/LME/parser_beta_2.0/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D904"/>
+  <dimension ref="A1:D905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -13045,6 +13045,20 @@
       </c>
       <c r="D904">
         <v>86.3793</v>
+      </c>
+    </row>
+    <row r="905" spans="1:4">
+      <c r="A905" s="1">
+        <v>903</v>
+      </c>
+      <c r="B905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C905">
+        <v>1</v>
+      </c>
+      <c r="D905">
+        <v>86.753</v>
       </c>
     </row>
   </sheetData>
@@ -13054,7 +13068,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D904"/>
+  <dimension ref="A1:D905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25708,6 +25722,20 @@
       </c>
       <c r="D904">
         <v>100.5714</v>
+      </c>
+    </row>
+    <row r="905" spans="1:4">
+      <c r="A905" s="1">
+        <v>903</v>
+      </c>
+      <c r="B905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C905">
+        <v>1</v>
+      </c>
+      <c r="D905">
+        <v>100.5988</v>
       </c>
     </row>
   </sheetData>
@@ -25717,7 +25745,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D904"/>
+  <dimension ref="A1:D905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -38371,6 +38399,20 @@
       </c>
       <c r="D904">
         <v>61.8994</v>
+      </c>
+    </row>
+    <row r="905" spans="1:4">
+      <c r="A905" s="1">
+        <v>903</v>
+      </c>
+      <c r="B905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C905">
+        <v>1</v>
+      </c>
+      <c r="D905">
+        <v>62.2019</v>
       </c>
     </row>
   </sheetData>
@@ -38380,7 +38422,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D904"/>
+  <dimension ref="A1:D905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -51034,6 +51076,20 @@
       </c>
       <c r="D904">
         <v>12.858</v>
+      </c>
+    </row>
+    <row r="905" spans="1:4">
+      <c r="A905" s="1">
+        <v>903</v>
+      </c>
+      <c r="B905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C905">
+        <v>1</v>
+      </c>
+      <c r="D905">
+        <v>12.897</v>
       </c>
     </row>
   </sheetData>
@@ -51043,7 +51099,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D904"/>
+  <dimension ref="A1:D905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -63697,6 +63753,20 @@
       </c>
       <c r="D904">
         <v>117.3204</v>
+      </c>
+    </row>
+    <row r="905" spans="1:4">
+      <c r="A905" s="1">
+        <v>903</v>
+      </c>
+      <c r="B905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C905">
+        <v>1</v>
+      </c>
+      <c r="D905">
+        <v>117.7325</v>
       </c>
     </row>
   </sheetData>
@@ -63706,7 +63776,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D904"/>
+  <dimension ref="A1:D905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -76360,6 +76430,20 @@
       </c>
       <c r="D904">
         <v>18.5854</v>
+      </c>
+    </row>
+    <row r="905" spans="1:4">
+      <c r="A905" s="1">
+        <v>903</v>
+      </c>
+      <c r="B905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C905">
+        <v>100</v>
+      </c>
+      <c r="D905">
+        <v>18.7651</v>
       </c>
     </row>
   </sheetData>
@@ -76369,7 +76453,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D904"/>
+  <dimension ref="A1:D905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -89023,6 +89107,20 @@
       </c>
       <c r="D904">
         <v>53.9837</v>
+      </c>
+    </row>
+    <row r="905" spans="1:4">
+      <c r="A905" s="1">
+        <v>903</v>
+      </c>
+      <c r="B905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C905">
+        <v>100</v>
+      </c>
+      <c r="D905">
+        <v>54.2987</v>
       </c>
     </row>
   </sheetData>
@@ -89032,7 +89130,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D904"/>
+  <dimension ref="A1:D905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -101688,6 +101786,20 @@
         <v>106.7993</v>
       </c>
     </row>
+    <row r="905" spans="1:4">
+      <c r="A905" s="1">
+        <v>903</v>
+      </c>
+      <c r="B905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C905">
+        <v>1</v>
+      </c>
+      <c r="D905">
+        <v>107.0892</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
